--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R20013cea40554f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R1e906291cad74cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="Rcd676307fc7e43ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="R8e2c1419cc4449ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R0aca771b9b7e4936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="Rb2ce782d014c4cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="Rb5aac374f1d04105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rb9a564940b9b4b2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2593,10 +2593,8 @@
     </x:row>
     <x:row r="107"/>
     <x:row r="108" s="1" customFormat="1" ht="39" customHeight="1">
-      <x:c r="A108" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">11일차  |  온톨로지·에이전트·프로세스를 내 주제에 적용하고 마무리하기</x:t>
-        </x:is>
+      <x:c r="A108" s="43" t="str">
+        <x:v>11일차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</x:v>
       </x:c>
       <x:c r="D108" s="44" t="inlineStr">
         <x:is>
@@ -2672,13 +2670,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B112" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">내 주제의 자료·업무 목표·완료 조건 정의하기</x:t>
-        </x:is>
+      <x:c r="B112" s="55" t="str">
+        <x:v>교대 인수인계의 입력과 완료 조건 정의하기</x:v>
       </x:c>
       <x:c r="C112" s="53" t="str">
-        <x:v>배운 로컬 랩에서 직접 만들 목적·입력·근거·완료 조건을 정한다. 제공 제조 자료를 활용하거나 준비된 자료로 완주 가능한 개인 주제를 선택한다.</x:v>
+        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
       </x:c>
       <x:c r="D112" s="54" t="n">
         <x:v>30</x:v>
@@ -2690,15 +2686,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B113" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">내 문서에서 주요 정보를 뽑아 작은 지식 구조 만들기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C113" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">제공 문서 또는 본인의 공개 가능 자료에서 핵심 개념·속성·관계를 구분해 스키마와 샘플 인스턴스를 작성한다. 출처와 식별자를 남기며 수업용 별도 이름 공간 또는 샘플 데이터로 검증한다.</x:t>
-        </x:is>
+      <x:c r="B113" s="62" t="str">
+        <x:v>보충 매뉴얼을 추출·검토하여 기존 지식에 추가하기</x:v>
+      </x:c>
+      <x:c r="C113" s="60" t="str">
+        <x:v>강사가 제공한 설비 점검·이상 확인 보충 매뉴얼에서 절차·조건·근거를 추출하고 원문 대조 후 적재한다. 기존 제조 스키마와 지식은 유지하며 새 문서로 추가한다. 동일 조건의 추출 결과를 재사용할 때는 이를 표시한다. 임의 문서는 허용하지 않는다.</x:v>
       </x:c>
       <x:c r="D113" s="61" t="n">
         <x:v>30</x:v>
@@ -2710,15 +2702,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B114" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">내 지식과 연결 도구를 사용해 업무를 제안하는 에이전트 만들기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C114" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">앞서 만든 스키마·자료를 활용하는 작은 에이전트를 VS Code에서 구성한다. 사용할 수 있는 읽기 MCP를 연결하여 정보가 확인될 때만 제안하고, 미확인 값과 권한 없는 작업은 보류하는 결과를 만든다.</x:t>
-        </x:is>
+      <x:c r="B114" s="55" t="str">
+        <x:v>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</x:v>
+      </x:c>
+      <x:c r="C114" s="53" t="str">
+        <x:v>기존 지식과 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 완료 메모와 열린 작업지시, 부품 도착 예정과 실제 재고의 불일치를 확인 사항으로 남긴다. 최신 값은 원천에서 조회하고 미확인 업무를 완료로 추정하지 않는다.</x:v>
       </x:c>
       <x:c r="D114" s="54" t="n">
         <x:v>30</x:v>
@@ -2731,10 +2719,10 @@
         </x:is>
       </x:c>
       <x:c r="B115" s="62" t="str">
-        <x:v>공통 업무 흐름을 확인하고 개인 결과 완성하기</x:v>
+        <x:v>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</x:v>
       </x:c>
       <x:c r="C115" s="60" t="str">
-        <x:v>기존 검증된 포털 예제로 업무 흐름을 실행하고 역할·승인·완료 상태를 확인한다. 개인 로컬 결과는 별도로 실행·수정하고 사용 방법을 저장한다. 학생 코드를 포털 기본 에이전트에 자동 등록하거나 새로 연결하지 않는다.</x:v>
+        <x:v>bpmn.io에서 자료 조회→인계안 작성→인계자 검토→인수자 확인 또는 보완 요청→완료 기록을 설계한다. 포털에서 별도 정의·시작 폼·에이전트·역할을 연결해 등록한다. 설비·교대를 입력해 시작하고 정상·불일치·보완 경로와 인계 기록을 확인한다.</x:v>
       </x:c>
       <x:c r="D115" s="61" t="n">
         <x:v>30</x:v>
@@ -4251,10 +4239,8 @@
       <x:c r="D86" s="50" t="n"/>
     </x:row>
     <x:row r="87" s="1" customFormat="1" ht="39" customHeight="1">
-      <x:c r="A87" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">08일차  |  배운 전 과정을 내 주제에 활용하고 지식 자산으로 마무리하기</x:t>
-        </x:is>
+      <x:c r="A87" s="43" t="str">
+        <x:v>08일차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</x:v>
       </x:c>
       <x:c r="D87" s="44" t="inlineStr">
         <x:is>
@@ -4330,13 +4316,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B91" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">내 주제의 자료와 업무 완료 조건 정의하기</x:t>
-        </x:is>
+      <x:c r="B91" s="55" t="str">
+        <x:v>교대 인수인계의 입력과 완료 조건 정의하기</x:v>
       </x:c>
       <x:c r="C91" s="53" t="str">
-        <x:v>앞 활용 랩에서 기능 하나를 골라 직접 사용할 목적·입력·근거·완료 기준을 정한다. 기존 자료와 로컬 코드·스킬로 완주 가능한 범위를 선택한다.</x:v>
+        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
       </x:c>
       <x:c r="D91" s="54" t="n">
         <x:v>30</x:v>
@@ -4348,13 +4332,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B92" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">개인 자료에서 작은 지식 구조 만들기</x:t>
-        </x:is>
+      <x:c r="B92" s="62" t="str">
+        <x:v>보충 매뉴얼을 추출·검토하여 기존 지식에 추가하기</x:v>
       </x:c>
       <x:c r="C92" s="60" t="str">
-        <x:v>선택한 목적에 필요한 문서·기존 랩 자료로 작은 지식 구조를 구성한다. 고유 ID와 출처를 보존하고 목적에 필요한 질문의 답을 확인한다.</x:v>
+        <x:v>강사가 제공한 설비 점검·이상 확인 보충 매뉴얼에서 절차·조건·근거를 추출하고 원문 대조 후 적재한다. 기존 제조 스키마와 지식은 유지하며 새 문서로 추가한다. 동일 조건의 추출 결과를 재사용할 때는 이를 표시한다. 임의 문서는 허용하지 않는다.</x:v>
       </x:c>
       <x:c r="D92" s="61" t="n">
         <x:v>30</x:v>
@@ -4366,13 +4348,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B93" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">내 지식과 연결 도구로 업무 제안 에이전트 만들기</x:t>
-        </x:is>
+      <x:c r="B93" s="55" t="str">
+        <x:v>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</x:v>
       </x:c>
       <x:c r="C93" s="53" t="str">
-        <x:v>앞 지식과 제공 도구를 활용해 목적에 맞는 제안·카드·보고서 등 로컬 결과를 만든다. 미확인·근거 부족을 표시하고 실제 출력과 완료 기준을 대조한다.</x:v>
+        <x:v>기존 지식과 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 완료 메모와 열린 작업지시, 부품 도착 예정과 실제 재고의 불일치를 확인 사항으로 남긴다. 최신 값은 원천에서 조회하고 미확인 업무를 완료로 추정하지 않는다.</x:v>
       </x:c>
       <x:c r="D93" s="54" t="n">
         <x:v>30</x:v>
@@ -4385,10 +4365,10 @@
         </x:is>
       </x:c>
       <x:c r="B94" s="62" t="str">
-        <x:v>공통 업무 흐름을 확인하고 개인 결과 완성하기</x:v>
+        <x:v>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</x:v>
       </x:c>
       <x:c r="C94" s="60" t="str">
-        <x:v>기존 검증된 포털 예제로 업무 흐름을 실행하고 역할·승인·완료 상태를 확인한다. 개인 로컬 결과는 별도로 실행·수정하고 사용 방법을 저장한다. 학생 코드를 포털 기본 에이전트에 자동 등록하거나 새로 연결하지 않는다.</x:v>
+        <x:v>bpmn.io에서 자료 조회→인계안 작성→인계자 검토→인수자 확인 또는 보완 요청→완료 기록을 설계한다. 포털에서 별도 정의·시작 폼·에이전트·역할을 연결해 등록한다. 설비·교대를 입력해 시작하고 정상·불일치·보완 경로와 인계 기록을 확인한다.</x:v>
       </x:c>
       <x:c r="D94" s="61" t="n">
         <x:v>30</x:v>
@@ -6049,7 +6029,7 @@
     </x:row>
     <x:row r="94" s="1" customFormat="1" ht="36" customHeight="1">
       <x:c r="A94" s="43" t="str">
-        <x:v>09회차 | 프로세스를 실행·검증하고 개인 제작 시작하기</x:v>
+        <x:v>09회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</x:v>
       </x:c>
       <x:c r="B94"/>
       <x:c r="C94"/>
@@ -6079,7 +6059,7 @@
         <x:v>정의·실행 상태·오류 위치와 복구</x:v>
       </x:c>
       <x:c r="C96" s="127" t="str">
-        <x:v>정의·실행 상태·오류 위치와 복구을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9 + 11 개인 적용 / 실전 온라인6 + 8 개인 적용. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
+        <x:v>정의·실행 상태·오류 위치와 복구를 오늘 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9·11 / 실전 온라인6·8. 교대 인수인계의 시작 폼·역할·완료 조건을 구분한다.</x:v>
       </x:c>
       <x:c r="D96" s="128" t="n">
         <x:v>15</x:v>
@@ -6132,10 +6112,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B100" s="130" t="str">
-        <x:v>개인 제작: 앞선 로컬 랩 하나를 선택하고 용도·입력·완료 기준 정하기</x:v>
+        <x:v>교대 인수인계의 입력·근거·완료 조건 정하기</x:v>
       </x:c>
       <x:c r="C100" s="131" t="str">
-        <x:v>앞 로컬 랩 하나를 골라 사용할 목적·입력·완료 기준을 정한다.</x:v>
+        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
       </x:c>
       <x:c r="D100" s="132" t="n">
         <x:v>25</x:v>
@@ -6146,10 +6126,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B101" s="130" t="str">
-        <x:v>개인 제작: 기존 자료·기능으로 첫 결과 구현</x:v>
+        <x:v>보충 매뉴얼 적재와 인수인계 에이전트 구성</x:v>
       </x:c>
       <x:c r="C101" s="131" t="str">
-        <x:v>기존 자료·코드·스킬로 개인 결과를 구현한다. 새 포털 연동은 요구하지 않는다.</x:v>
+        <x:v>제공 보충 매뉴얼의 추출 결과를 원문 대조하여 기존 제조 지식에 추가한다. 허용된 설비·정비·ERP 조회를 사용해 인계안을 만들고, 기록 불일치와 미확인 사항을 남긴다. 같은 조건의 추출 재사용은 표시한다.</x:v>
       </x:c>
       <x:c r="D101" s="132" t="n">
         <x:v>60</x:v>
@@ -6160,10 +6140,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B102" s="130" t="str">
-        <x:v>개별 오류 해결·중간 결과 저장</x:v>
+        <x:v>교대 인수인계 BPMN 설계·매핑과 중간 결과 저장</x:v>
       </x:c>
       <x:c r="C102" s="131" t="str">
-        <x:v>오류를 해결하고 중간 결과를 저장해 마지막 회차에서 이어 쓴다.</x:v>
+        <x:v>bpmn.io에서 조회·인계안·인계자 검토·인수자 확인·보완·완료 흐름을 작성한다. 포털의 별도 정의에 시작 폼·에이전트·역할을 연결하고 판본을 저장한다. 실제 실행은 다음 회차로 이어간다.</x:v>
       </x:c>
       <x:c r="D102" s="132" t="n">
         <x:v>20</x:v>
@@ -6182,7 +6162,7 @@
     </x:row>
     <x:row r="104" ht="58" customHeight="1">
       <x:c r="A104" s="66" t="str">
-        <x:v>완료 결과: 공통 포털 실행 결과와 별개의 개인 로컬 프로젝트. 포털에 개인 코드를 자동 등록하거나 연결하지 않는다.</x:v>
+        <x:v>완료 결과: 추가 지식의 검토·적재 기록, 인수인계 에이전트·스킬, 별도 BPMN·매핑·시작 폼. 기존 ABC 정의는 보존한다. 임의 코드 자동 연결이나 임의 외부 도구는 요구하지 않는다.</x:v>
       </x:c>
       <x:c r="B104"/>
       <x:c r="C104"/>
@@ -6193,7 +6173,7 @@
     </x:row>
     <x:row r="106" ht="36" customHeight="1">
       <x:c r="A106" s="43" t="str">
-        <x:v>10회차 | 정비·구매에 적용하고 개인 결과물 완성하기</x:v>
+        <x:v>10회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</x:v>
       </x:c>
       <x:c r="B106"/>
       <x:c r="C106"/>
@@ -6290,10 +6270,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B113" s="130" t="str">
-        <x:v>앞 회차 개인 결과물 완성·실행·사용 방법 저장</x:v>
+        <x:v>교대 인수인계 흐름 실행·보완·완료 기록 확인</x:v>
       </x:c>
       <x:c r="C113" s="131" t="str">
-        <x:v>앞 회차 개인 프로젝트를 실행·수정하고 결과와 사용 방법을 저장한다.</x:v>
+        <x:v>앞 회차의 인수인계 흐름을 설비·교대 입력으로 시작한다. 정상·기록 불일치·정보 누락 사례에서 인계자 검토와 인수자 확인 또는 보완 요청을 수행하고, 근거·판본·완료 기록을 저장한다.</x:v>
       </x:c>
       <x:c r="D113" s="132" t="n">
         <x:v>30</x:v>
@@ -6326,7 +6306,7 @@
     </x:row>
     <x:row r="116" ht="58" customHeight="1">
       <x:c r="A116" s="66" t="str">
-        <x:v>완료 결과: 정비·구매는 공통 시나리오 그대로 수행. 개인 결과는 로컬 코드·스킬·보고서로 완료하며 새 포털 기능이나 외부 서비스 쓰기를 요구하지 않는다. ProcessGPT는 준비된 제품 화면을 강사가 20분 시연한다. 학생 계정 설정이나 별도 제품 실습은 포함하지 않는다.</x:v>
+        <x:v>완료 결과: 정비·구매는 기존 공통 시나리오로 수행하고 교대 인수인계는 별도 정의로 실행한다. 실제 설비 제어·발주를 인계 확인과 혼동하지 않는다. ProcessGPT는 강사가 20분 시연한다. 준비·실행 시간과 완주는 별도 실측한다.</x:v>
       </x:c>
       <x:c r="B116"/>
       <x:c r="C116"/>
@@ -7724,7 +7704,7 @@
     </x:row>
     <x:row r="81" s="1" customFormat="1" ht="36" customHeight="1">
       <x:c r="A81" s="43" t="str">
-        <x:v>08회차 | 프로세스를 실행·검증하고 개인 제작 시작하기</x:v>
+        <x:v>08회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</x:v>
       </x:c>
       <x:c r="B81"/>
       <x:c r="C81"/>
@@ -7754,7 +7734,7 @@
         <x:v>정의·실행 상태·오류 위치와 복구</x:v>
       </x:c>
       <x:c r="C83" s="127" t="str">
-        <x:v>정의·실행 상태·오류 위치와 복구을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9 + 11 개인 적용 / 실전 온라인6 + 8 개인 적용. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
+        <x:v>정의·실행 상태·오류 위치와 복구를 오늘 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9·11 / 실전 온라인6·8. 교대 인수인계의 시작 폼·역할·완료 조건을 구분한다.</x:v>
       </x:c>
       <x:c r="D83" s="128" t="n">
         <x:v>15</x:v>
@@ -7807,10 +7787,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B87" s="130" t="str">
-        <x:v>개인 제작: 앞선 로컬 랩 하나를 선택하고 용도·입력·완료 기준 정하기</x:v>
+        <x:v>교대 인수인계의 입력·근거·완료 조건 정하기</x:v>
       </x:c>
       <x:c r="C87" s="131" t="str">
-        <x:v>앞 로컬 랩 하나를 골라 사용할 목적·입력·완료 기준을 정한다.</x:v>
+        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
       </x:c>
       <x:c r="D87" s="132" t="n">
         <x:v>25</x:v>
@@ -7821,10 +7801,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B88" s="130" t="str">
-        <x:v>개인 제작: 기존 자료·기능으로 첫 결과 구현</x:v>
+        <x:v>보충 매뉴얼 적재와 인수인계 에이전트 구성</x:v>
       </x:c>
       <x:c r="C88" s="131" t="str">
-        <x:v>기존 자료·코드·스킬로 개인 결과를 구현한다. 새 포털 연동은 요구하지 않는다.</x:v>
+        <x:v>제공 보충 매뉴얼의 추출 결과를 원문 대조하여 기존 제조 지식에 추가한다. 허용된 설비·정비·ERP 조회를 사용해 인계안을 만들고, 기록 불일치와 미확인 사항을 남긴다. 같은 조건의 추출 재사용은 표시한다.</x:v>
       </x:c>
       <x:c r="D88" s="132" t="n">
         <x:v>60</x:v>
@@ -7835,10 +7815,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B89" s="130" t="str">
-        <x:v>개별 오류 해결·중간 결과 저장</x:v>
+        <x:v>교대 인수인계 BPMN 설계·매핑과 중간 결과 저장</x:v>
       </x:c>
       <x:c r="C89" s="131" t="str">
-        <x:v>오류를 해결하고 중간 결과를 저장해 마지막 회차에서 이어 쓴다.</x:v>
+        <x:v>bpmn.io에서 조회·인계안·인계자 검토·인수자 확인·보완·완료 흐름을 작성한다. 포털의 별도 정의에 시작 폼·에이전트·역할을 연결하고 판본을 저장한다. 실제 실행은 다음 회차로 이어간다.</x:v>
       </x:c>
       <x:c r="D89" s="132" t="n">
         <x:v>20</x:v>
@@ -7857,7 +7837,7 @@
     </x:row>
     <x:row r="91" ht="58" customHeight="1">
       <x:c r="A91" s="66" t="str">
-        <x:v>완료 결과: 공통 포털 실행 결과와 별개의 개인 로컬 프로젝트. 포털에 개인 코드를 자동 등록하거나 연결하지 않는다.</x:v>
+        <x:v>완료 결과: 추가 지식의 검토·적재 기록, 인수인계 에이전트·스킬, 별도 BPMN·매핑·시작 폼. 기존 ABC 정의는 보존한다. 임의 코드 자동 연결이나 임의 외부 도구는 요구하지 않는다.</x:v>
       </x:c>
       <x:c r="B91"/>
       <x:c r="C91"/>
@@ -7868,7 +7848,7 @@
     </x:row>
     <x:row r="93" ht="36" customHeight="1">
       <x:c r="A93" s="43" t="str">
-        <x:v>09회차 | 정비·구매에 적용하고 개인 결과물 완성하기</x:v>
+        <x:v>09회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</x:v>
       </x:c>
       <x:c r="B93"/>
       <x:c r="C93"/>
@@ -7965,10 +7945,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B100" s="130" t="str">
-        <x:v>앞 회차 개인 결과물 완성·실행·사용 방법 저장</x:v>
+        <x:v>교대 인수인계 흐름 실행·보완·완료 기록 확인</x:v>
       </x:c>
       <x:c r="C100" s="131" t="str">
-        <x:v>앞 회차 개인 프로젝트를 실행·수정하고 결과와 사용 방법을 저장한다.</x:v>
+        <x:v>앞 회차의 인수인계 흐름을 설비·교대 입력으로 시작한다. 정상·기록 불일치·정보 누락 사례에서 인계자 검토와 인수자 확인 또는 보완 요청을 수행하고, 근거·판본·완료 기록을 저장한다.</x:v>
       </x:c>
       <x:c r="D100" s="132" t="n">
         <x:v>30</x:v>
@@ -8001,7 +7981,7 @@
     </x:row>
     <x:row r="103" ht="58" customHeight="1">
       <x:c r="A103" s="66" t="str">
-        <x:v>완료 결과: 정비·구매는 공통 시나리오 그대로 수행. 개인 결과는 로컬 코드·스킬·보고서로 완료하며 새 포털 기능이나 외부 서비스 쓰기를 요구하지 않는다. ProcessGPT는 준비된 제품 화면을 강사가 20분 시연한다. 학생 계정 설정이나 별도 제품 실습은 포함하지 않는다.</x:v>
+        <x:v>완료 결과: 정비·구매는 기존 공통 시나리오로 수행하고 교대 인수인계는 별도 정의로 실행한다. 실제 설비 제어·발주를 인계 확인과 혼동하지 않는다. ProcessGPT는 강사가 20분 시연한다. 준비·실행 시간과 완주는 별도 실측한다.</x:v>
       </x:c>
       <x:c r="B103"/>
       <x:c r="C103"/>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R0aca771b9b7e4936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="Rb2ce782d014c4cc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="Rb5aac374f1d04105"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rb9a564940b9b4b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Rb671491d80264b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R7f4a1a1f640b4bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R86cff5214ecc4afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Raaeb30ffe83747c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="18">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -117,8 +117,25 @@
       <x:color rgb="FF536679"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24364B"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -190,6 +207,26 @@
         <x:fgColor rgb="FFF3F7FB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173C57"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6EFF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F7FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -197,7 +234,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="133">
+  <x:cellXfs count="145">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
@@ -569,6 +606,40 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -914,10 +985,8 @@
           <x:t xml:space="preserve">학습 내용을 지식 자산으로 전환하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 설명한다.</x:t>
-        </x:is>
+      <x:c r="C6" s="19" t="str">
+        <x:v>단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 살펴본다.</x:v>
       </x:c>
       <x:c r="D6" s="25" t="n">
         <x:v>10</x:v>
@@ -935,7 +1004,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="27" t="str">
-        <x:v>Notion에서 학습노트 홈과 주제별 카드·페이지를 구성한다. 샘플 개념·출처·실습 결과를 연결하고 검색·보완·재사용할 수 있도록 저장·재열기를 확인한다. 정해진 별도 자료 DB나 실수노트 분류를 강제하지 않는다.</x:v>
+        <x:v>Notion에서 학습노트 홈과 주제별 카드·페이지를 구성한다. 샘플 개념·출처·실습 결과를 연결하고 검색·보완·재사용할 수 있도록 저장·재열기를 확인한다.</x:v>
       </x:c>
       <x:c r="D7" s="33" t="n">
         <x:v>50</x:v>
@@ -952,10 +1021,8 @@
           <x:t xml:space="preserve">설비 데이터가 판단으로 이어지는 시스템 구조와 데이터 흐름 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">선행 SCADA 교육에서 다룬 설비·센서·PLC·관제 화면의 역할을 간단히 복습한다. HYD 시스템의 전체 아키텍처와 L1~L9 레이어, OT·DMZ·IT 영역의 구분과 역할을 학습한다. 센서 데이터가 MQTT·메시지 처리·시계열 DB·분석 서비스를 거쳐 화면과 판단 기능에 활용되는 경로를 설명한다. 데이터 리니지의 개념을 배우고, 원천 데이터·가공 데이터·이상 이벤트·판단 결과가 어떤 구성요소를 거쳐 생성되는지 살펴본다. 분석 결과가 실제 조치로 이어질 때 명령 게이트웨이와 설비 제어 영역이 필요한 이유도 이해한다.</x:t>
-        </x:is>
+      <x:c r="C8" s="19" t="str">
+        <x:v>선행 SCADA 교육에서 다룬 설비·센서·PLC·관제 화면의 역할을 간단히 복습한다. HYD 시스템의 전체 아키텍처와 L1~L9 레이어, OT·DMZ·IT 영역의 구분과 역할을 학습한다. 센서 데이터가 MQTT·메시지 처리·시계열 DB·분석 서비스를 거쳐 화면과 판단 기능에 활용되는 경로를 살펴본다. 데이터 리니지의 개념을 배우고, 원천 데이터·가공 데이터·이상 이벤트·판단 결과가 어떤 구성요소를 거쳐 생성되는지 살펴본다. 분석 결과가 실제 조치로 이어질 때 명령 게이트웨이와 설비 제어 영역이 필요한 이유도 이해한다.</x:v>
       </x:c>
       <x:c r="D8" s="25" t="n">
         <x:v>50</x:v>
@@ -973,7 +1040,7 @@
         </x:is>
       </x:c>
       <x:c r="C9" s="27" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex·Python·Docker Desktop·Docker Compose 등 교육에서 사용할 주요 도구의 역할과 필요한 버전·설정·접속 조건을 안내한다. 각 도구가 개발·AI 코딩·서비스 실행에서 어떤 역할을 하는지 설명한다. 별도 설치를 진행하지 않고 준비된 환경에서 Docker Compose로 HYD 서비스를 실행한다. 컨테이너 상태와 주요 서비스 접속 여부를 확인한 뒤 HYD 포털에 접속해 시스템이 정상적으로 실행되는 상태를 확인한다.</x:v>
+        <x:v>VS Code·GitHub Copilot·Codex·Python·Docker Desktop·Docker Compose가 개발·AI 코딩·서비스 실행에서 맡는 역할을 구분한다. 준비된 학교 PC에서 필요한 도구와 접속 조건을 확인한다. 제공된 실행 절차로 HYD 서비스를 시작하고 컨테이너 상태·주요 서비스·포털 접속 결과를 확인한다.</x:v>
       </x:c>
       <x:c r="D9" s="33" t="n">
         <x:v>30</x:v>
@@ -990,10 +1057,8 @@
           <x:t xml:space="preserve">설비 이상 발생부터 판단·승인·조치까지 전체 과정 경험하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털에서 쿨러 열화 시나리오를 강사가 처음부터 끝까지 시연한다. 설비 이상 발생, 센서 변화와 경보 감지, 원인 분석, 근거에 기반한 조치 추천, 담당자 승인, 시스템 조치, 재관측 및 최종 결과를 순서대로 보여준다. 각 단계에서 어떤 정보가 사용되고 어떤 결과가 다음 단계로 전달되는지 설명한다. 세부 기술과 내부 실행 구조는 이후 학습에서 다루며, 이 시간에는 전체 과정이 실제로 어떤 문제를 해결하는지 이해하는 데 집중한다.</x:t>
-        </x:is>
+      <x:c r="C10" s="19" t="str">
+        <x:v>HYD 포털의 쿨러 열화 시연을 보며 설비 이상→센서 변화·경보→원인 분석→조치 추천→담당자 승인→시스템 조치→효과 재확인의 흐름을 따라간다. 각 단계에 사용된 정보와 다음 단계로 전달된 결과를 비교하고, AI의 추천과 사람의 승인·실제 조치가 서로 다른 단계임을 확인한다.</x:v>
       </x:c>
       <x:c r="D10" s="25" t="n">
         <x:v>20</x:v>
@@ -1010,10 +1075,8 @@
           <x:t xml:space="preserve">설비 데이터에 의미와 관계를 부여하는 온톨로지 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">센서에서 온도가 상승했다는 사실만으로는 어느 부품에 문제가 있는지, 가능한 원인이 무엇인지, 어떤 조치를 취해야 하는지 알기 어려운 이유를 설명한다. 개별 수치와 데이터, 데이터에 의미를 부여한 정보, 판단에 활용할 수 있는 지식의 차이를 이해한다. 온톨로지가 대상의 종류·속성·관계·제약을 명시적으로 정의해 공통된 의미로 이해하도록 하는 지식 모델임을 배운다. 설비·센서·부품·증상·원인·조치·근거 문서가 어떻게 연결되는지 설명하고, 단순한 관계 그림이나 그래프 DB 자체가 온톨로지와 동일한 것은 아니라는 점을 구분한다. 이를 통해 이후 원인 탐색과 근거 기반 판단에 온톨로지가 필요한 이유를 이해한다.</x:t>
-        </x:is>
+      <x:c r="C11" s="27" t="str">
+        <x:v>센서에서 온도가 상승했다는 사실만으로는 어느 부품에 문제가 있는지, 가능한 원인이 무엇인지, 어떤 조치를 취해야 하는지 알기 어려운 이유를 살펴본다. 개별 수치와 데이터, 데이터에 의미를 부여한 정보, 판단에 활용할 수 있는 지식의 차이를 이해한다. 온톨로지가 대상의 종류·속성·관계·제약을 명시적으로 정의해 공통된 의미로 이해하도록 하는 지식 모델임을 배운다. 설비·센서·부품·증상·원인·조치·근거 문서가 어떻게 연결되는지 살펴보고, 단순한 관계 그림이나 그래프 DB 자체가 온톨로지와 동일한 것은 아니라는 점을 구분한다. 이를 통해 이후 원인 탐색과 근거 기반 판단에 온톨로지가 필요한 이유를 이해한다.</x:v>
       </x:c>
       <x:c r="D11" s="33" t="n">
         <x:v>50</x:v>
@@ -1030,10 +1093,8 @@
           <x:t xml:space="preserve">설비 이상과 원인·조치의 관계를 시각화하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">arrows.app의 노드·관계·레이블 작성 방법을 익힌다. 간단한 설비 이상 사례를 바탕으로 설비·센서·증상·원인·조치를 배치하고 각각의 연결 관계를 직접 그린다. 어떤 대상이 다른 대상과 연결되는지, 관계의 방향을 어떻게 표현하는지 살펴본다. 완성한 관계도를 통해 단순히 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 복잡한 온톨로지 스키마와 제약은 다음 학습에서 다룬다.</x:t>
-        </x:is>
+      <x:c r="C12" s="19" t="str">
+        <x:v>arrows.app의 노드·관계·레이블 작성 방법을 익힌다. 간단한 설비 이상 사례를 바탕으로 설비·센서·증상·원인·조치를 배치하고 각각의 연결 관계를 직접 그린다. 어떤 대상이 다른 대상과 연결되는지, 관계의 방향을 어떻게 표현하는지 살펴본다. 완성한 관계도를 통해 단순히 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 복잡한 온톨로지 스키마와 제약은 다음 학습에서 다룬다.</x:v>
       </x:c>
       <x:c r="D12" s="25" t="n">
         <x:v>30</x:v>
@@ -1101,10 +1162,8 @@
           <x:t xml:space="preserve">클래스와 인스턴스를 통해 현장 정보의 구조 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C17" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">온톨로지에서 클래스·인스턴스·속성·관계의 정확한 정의와 역할을 학습한다. 클래스가 공통 특성을 가진 대상의 유형을 표현하고, 인스턴스는 그 유형에 속하는 실제 개별 대상을 나타낸다는 점을 설명한다. 설비·센서·부품과 HYD-01·TS1·쿨러를 비교하며 구분한다. 클래스 계층과 상속의 기초, 데이터 속성과 객체 간 관계의 차이, 속성값과 인스턴스의 구별, 관계 유형·방향·카디널리티(1:1, 1:N, N:M)를 배운다. 언제 새로운 클래스를 정의하고 언제 속성이나 관계로 표현해야 하는지 구체적인 설비 사례로 비교한다.</x:t>
-        </x:is>
+      <x:c r="C17" s="27" t="str">
+        <x:v>온톨로지에서 클래스·인스턴스·속성·관계의 정확한 정의와 역할을 학습한다. 클래스가 공통 특성을 가진 대상의 유형을 표현하고, 인스턴스는 그 유형에 속하는 실제 개별 대상을 나타낸다는 점을 살펴본다. 설비·센서·부품과 HYD-01·TS1·쿨러를 비교하며 구분한다. 클래스 계층과 상속의 기초, 데이터 속성과 객체 간 관계의 차이, 속성값과 인스턴스의 구별, 관계 유형·방향·카디널리티(1:1, 1:N, N:M)를 배운다. 언제 새로운 클래스를 정의하고 언제 속성이나 관계로 표현해야 하는지 구체적인 설비 사례로 비교한다.</x:v>
       </x:c>
       <x:c r="D17" s="33" t="n">
         <x:v>50</x:v>
@@ -1121,10 +1180,8 @@
           <x:t xml:space="preserve">일관된 지식 구조를 만들기 위한 온톨로지 스키마 설계 원리 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">온톨로지 스키마가 클래스·속성·관계·제약을 일관되게 정의하는 구조임을 배운다. 클래스 이름과 의미, 속성명·자료형·필수 여부, 식별자, 관계의 시작·종료 클래스, 카디널리티와 유효한 연결 조건을 설명한다. 공통 식별자를 활용해 동일한 대상을 구분하는 방법, 스키마와 인스턴스 데이터의 차이, 스키마가 없는 데이터 연결에서 발생할 수 있는 의미 불일치를 살펴본다. 간단한 설비 모델을 스키마 정의로 발전시키는 과정을 단계별로 설명하고, HYD의 온톨로지 v2에 설비·진단·판단·성과 등의 클래스가 이미 정의되어 있다는 점도 소개한다.</x:t>
-        </x:is>
+      <x:c r="C18" s="19" t="str">
+        <x:v>온톨로지 스키마가 클래스·속성·관계·제약을 일관되게 정의하는 구조임을 배운다. 클래스 이름과 의미, 속성명·자료형·필수 여부, 식별자, 관계의 시작·종료 클래스, 카디널리티와 유효한 연결 조건을 살펴본다. 공통 식별자를 활용해 동일한 대상을 구분하는 방법, 스키마와 인스턴스 데이터의 차이, 스키마가 없는 데이터 연결에서 발생할 수 있는 의미 불일치를 살펴본다. 간단한 설비 모델을 스키마 정의로 발전시키는 과정을 단계별로 살펴보고, HYD의 온톨로지 v2에 설비·진단·판단·성과 등의 클래스가 이미 정의되어 있다는 점도 확인한다.</x:v>
       </x:c>
       <x:c r="D18" s="25" t="n">
         <x:v>40</x:v>
@@ -1141,28 +1198,24 @@
           <x:t xml:space="preserve">그래프 DB를 활용해 연결된 지식을 저장하고 조회하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그래프 DB의 기본 개념과 노드·관계·속성 구조를 학습하고 관계형 DB의 테이블·행·조인과 비교한다. 온톨로지 스키마와 Neo4j의 레이블·관계 유형·DB 제약 조건을 구분한다. Neo4j Browser의 역할을 소개하고 Cypher에서 노드와 관계를 표현하는 문법을 설명한다. MATCH·WHERE·RETURN을 통한 조회, CREATE를 통한 생성, MERGE를 통한 기존 대상 조회 또는 생성을 예제로 학습한다.</x:t>
-        </x:is>
+      <x:c r="C19" s="27" t="str">
+        <x:v>그래프 DB의 기본 개념과 노드·관계·속성 구조를 학습하고 관계형 DB의 테이블·행·조인과 비교한다. 온톨로지 스키마와 Neo4j의 레이블·관계 유형·DB 제약 조건을 구분한다. Neo4j Browser의 역할을 살펴보고 Cypher에서 노드와 관계를 표현하는 문법을 살펴본다. MATCH·WHERE·RETURN을 통한 조회, CREATE를 통한 생성, MERGE를 통한 기존 대상 조회 또는 생성을 예제로 학습한다.</x:v>
       </x:c>
       <x:c r="D19" s="33" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" s="1" customFormat="1" ht="65" customHeight="1">
+    <x:row r="20" s="1" customFormat="1" ht="114" customHeight="1">
       <x:c r="A20" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B20" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그래프 DB에서 관계를 따라 필요한 정보 조회하기</x:t>
-        </x:is>
+      <x:c r="B20" s="23" t="str">
+        <x:v>Cypher로 그래프를 생성·조회·수정·삭제하고 설비 관계 탐색하기</x:v>
       </x:c>
       <x:c r="C20" s="19" t="str">
-        <x:v>Neo4j Browser의 제공 예제에서 레이블·속성·관계 방향을 확인한다. 설비의 구성 요소·센서·물리량·교체 부품을 MATCH·WHERE·RETURN으로 조회하고 한 단계·여러 단계 결과 및 집계의 원래 행을 대조한다. 예제 DB와 포털 기준 DB를 구별한다.</x:v>
+        <x:v>Neo4j Browser의 연결·쿼리 실행·그래프와 표 보기 방법을 익힌다. 작은 예제에서 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 노드와 관계를 생성·조회·수정하고 그래프를 클릭해 속성을 확인한다. RETURN의 대상에 따른 그래프·표 결과를 비교한다. DELETE·DETACH DELETE 후 재조회해 연습 데이터를 정리한다. 이어 제공 설비 예제에서 구성 요소·센서·부품의 연결을 한 단계·여러 단계 경로로 조회하고 조건·집계 결과를 원래 행과 대조한다. 실습용 예제 DB와 포털 기준 DB를 구분한다.</x:v>
       </x:c>
       <x:c r="D20" s="25" t="n">
         <x:v>25</x:v>
@@ -1179,10 +1232,8 @@
           <x:t xml:space="preserve">설비 지식의 구조와 연결 관계 탐색하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C21" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털의 지식 지도에서 설비를 선택해 구성요소·센서 등의 연결 관계를 탐색한다. 노드의 종류와 속성, 관계 방향을 확인하고 앞서 배운 클래스·인스턴스·스키마가 실제 시스템에서 어떻게 활용되는지 살펴본다. 랩 전용 그래프와 HYD의 기준 지식 지도가 서로 다른 환경이라는 점도 이해한다.</x:t>
-        </x:is>
+      <x:c r="C21" s="27" t="str">
+        <x:v>포털 지식 지도에서 설비를 선택하고 연결된 센서·부품을 펼친다. 노드를 눌러 식별자와 속성을 확인하고 관계의 방향을 읽는다. 같은 센서 이름과 서로 다른 식별자를 구분하며, 별도 랩 DB에서 만든 모델과 포털의 기준 지도를 비교한다.</x:v>
       </x:c>
       <x:c r="D21" s="33" t="n">
         <x:v>20</x:v>
@@ -1284,10 +1335,8 @@
           <x:t xml:space="preserve">설비 상태에 맞는 안전한 조치 절차와 수행 기준 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C28" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">설비 고장 원인을 진단하는 것과 실제 조치 방법을 결정하는 것이 서로 다른 단계임을 이해한다. SOP(Standard Operating Procedure)의 목적과 역할을 배우고, 적용 대상·작업 전제 조건·안전 조건·준비사항·수행 단계·금지 사항·담당 역할·완료 확인 기준 등 SOP의 구성요소를 설명한다. 작업 절차의 순서와 조건을 구분하고, 동일한 조치도 설비 운전 상태에 따라 수행 가능 여부가 달라지는 이유를 학습한다. HYD 온톨로지에서 고장 유형·원인·조치 방법(Skill)·작업 단계(Step)·근거 매뉴얼이 연결되는 구조와, 즉시 완화·근본 조치·예방 조치의 차이를 살펴본다.</x:t>
-        </x:is>
+      <x:c r="C28" s="19" t="str">
+        <x:v>설비 고장 원인을 진단하는 것과 실제 조치 방법을 결정하는 것이 서로 다른 단계임을 이해한다. SOP(Standard Operating Procedure)의 목적과 역할을 배우고, 적용 대상·작업 전제 조건·안전 조건·준비사항·수행 단계·금지 사항·담당 역할·완료 확인 기준 등 SOP의 구성요소를 살펴본다. 작업 절차의 순서와 조건을 구분하고, 동일한 조치도 설비 운전 상태에 따라 수행 가능 여부가 달라지는 이유를 학습한다. HYD 온톨로지에서 고장 유형·원인·조치 방법(Skill)·작업 단계(Step)·근거 매뉴얼이 연결되는 구조와, 즉시 완화·근본 조치·예방 조치의 차이를 살펴본다.</x:v>
       </x:c>
       <x:c r="D28" s="25" t="n">
         <x:v>35</x:v>
@@ -1304,10 +1353,8 @@
           <x:t xml:space="preserve">업무 조건에 따라 적절한 조치를 선택하는 판단 규칙 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C29" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DMN(Decision Model and Notation)이 업무 의사결정을 명확하게 정의하기 위한 표준이라는 점을 배우고, SOP와 DMN의 차이를 설명한다. 판단에 필요한 입력 데이터(InputData), 결정(Decision), 결정표(DecisionTable), 규칙(Rule), 조건과 출력의 관계를 학습한다. 비교 연산자·임계값·범위·복수 조건을 이용해 결정표를 구성하는 원리를 설명한다. 규칙의 중복·누락·상충이 어떤 문제를 일으키는지 알아보고, 여러 규칙이 일치했을 때 결과를 선택하는 Hit Policy의 기본 개념과 HYD에서 사용하는 판단 방식을 이해한다. 설비 상태에 따른 조치 허용·제외·감점과 해당 판단의 근거를 표현하는 방법까지 학습한다.</x:t>
-        </x:is>
+      <x:c r="C29" s="27" t="str">
+        <x:v>DMN(Decision Model and Notation)이 업무 의사결정을 명확하게 정의하기 위한 표준이라는 점을 배우고, SOP와 DMN의 차이를 살펴본다. 판단에 필요한 입력 데이터(InputData), 결정(Decision), 결정표(DecisionTable), 규칙(Rule), 조건과 출력의 관계를 학습한다. 비교 연산자·임계값·범위·복수 조건을 이용해 결정표를 구성하는 원리를 살펴본다. 규칙의 중복·누락·상충이 어떤 문제를 일으키는지 알아보고, 여러 규칙이 일치했을 때 결과를 선택하는 Hit Policy의 기본 개념과 HYD에서 사용하는 판단 방식을 이해한다. 설비 상태에 따른 조치 허용·제외·감점과 해당 판단의 근거를 표현하는 방법까지 학습한다.</x:v>
       </x:c>
       <x:c r="D29" s="33" t="n">
         <x:v>40</x:v>
@@ -1324,10 +1371,8 @@
           <x:t xml:space="preserve">조치의 효과를 여러 성과 관점에서 평가하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C30" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BSC(Balanced Scorecard)의 목적과 재무·고객·내부 프로세스·학습과 성장이라는 네 관점을 배운다. 전략 목표와 KPI(Key Performance Indicator)의 차이, 지표의 정의·단위·목표값·측정 주기·실제값·목표 대비 차이를 설명한다. 전략맵에서 목표 사이의 인과관계를 표현하는 방식과 선행 지표·후행 지표의 차이를 이해한다. 설비 복구 시간·생산 차질·전력비·품질·안전처럼 서로 상충할 수 있는 성과를 비교한다. 조치 가능 여부를 판단하는 규칙과, 허용된 조치의 효과·비용을 평가하는 기준을 구분하고, 가정값을 변경해 결과를 비교하는 What-if 분석의 목적과 한계를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C30" s="19" t="str">
+        <x:v>BSC(Balanced Scorecard)의 목적과 재무·고객·내부 프로세스·학습과 성장이라는 네 관점을 배운다. 전략 목표와 KPI(Key Performance Indicator)의 차이, 지표의 정의·단위·목표값·측정 주기·실제값·목표 대비 차이를 살펴본다. 전략맵에서 목표 사이의 인과관계를 표현하는 방식과 선행 지표·후행 지표의 차이를 이해한다. 설비 복구 시간·생산 차질·전력비·품질·안전처럼 서로 상충할 수 있는 성과를 비교한다. 조치 가능 여부를 판단하는 규칙과, 허용된 조치의 효과·비용을 평가하는 기준을 구분하고, 가정값을 변경해 결과를 비교하는 What-if 분석의 목적과 한계를 살펴본다.</x:v>
       </x:c>
       <x:c r="D30" s="25" t="n">
         <x:v>35</x:v>
@@ -1344,10 +1389,8 @@
           <x:t xml:space="preserve">운전 조건과 성과 기준에 따른 조치 결과 비교하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C31" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털의 조치 판단 규칙·손익/What-if·성과 지표 기능을 활용한다. 특정 설비와 이상 상황을 선택하고 판단에 사용되는 입력값·규칙·조치 후보를 확인한다. 운전 조건과 시험값을 변경해 어떤 규칙이 적용되며 어떤 조치가 허용·제외되는지 비교한다. 허용된 조치의 예상 손익과 판단 순위를 살펴보고, 성과 관점의 중요도나 KPI 목표를 변경했을 때 결과가 어떻게 달라지는지 확인한다. 해당 판단의 근거와 계산에 사용된 출처를 확인하며 시험값 변경이 원본 업무 데이터나 지식을 수정하는 것이 아니라는 점을 이해한다.</x:t>
-        </x:is>
+      <x:c r="C31" s="27" t="str">
+        <x:v>포털 What-if에서 같은 설비의 시험 입력을 바꾸고 적용 규칙·허용 또는 제외된 조치·예상 성과를 비교한다. 결과의 근거와 입력 단위를 확인하고 시험값 변경과 실제 설비 조치를 구분한다.</x:v>
       </x:c>
       <x:c r="D31" s="33" t="n">
         <x:v>35</x:v>
@@ -1451,10 +1494,8 @@
           <x:t xml:space="preserve">현장 자료를 온톨로지 지식으로 전환하는 과정 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C38" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">인제스천(Ingestion)의 의미와 필요성을 학습하고, 매뉴얼·SOP 문서·업무 DB 등 서로 다른 형태의 원천 자료를 지식으로 전환하는 전체 과정을 이해한다. 원천 확보와 보관 → 문서 내용 분석 → 증상·원인·부품·조치·판단 조건 등 지식 후보 추출 → 기존 온톨로지 스키마와 식별자에 매핑 → 원문 근거 대조와 사람 검토 → 승인된 지식 적재 → 그래프 관계·출처 조회의 단계별 역할을 설명한다. LLM의 문서 이해 및 구조화 출력 원리를 소개하고, 추출 과정에서 발생할 수 있는 부정 조건 누락·수치/단위 오류·잘못된 관계 추론·근거 없는 내용 생성의 위험을 배운다. 원문 페이지·문단·인용 구간, 문서 식별자와 개정 이력, 지식 소유 관계 및 변경 추적이 필요한 이유를 설명한다. 검색해 문서를 참고하는 방식과 구조화된 지식으로 등록하는 방식의 차이도 이해한다. 마지막으로 설비의 원인·절차·규칙처럼 상대적으로 안정적인 지식과 센서·재고·운전시간처럼 지속적으로 변하는 값을 구분하고, 실제 값은 업무 DB·시계열 DB 등 원천에서 조회하도록 연결하는 원리를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C38" s="19" t="str">
+        <x:v>인제스천(Ingestion)의 의미와 필요성을 학습하고, 매뉴얼·SOP 문서·업무 DB 등 서로 다른 형태의 원천 자료를 지식으로 전환하는 전체 과정을 이해한다. 원천 확보와 보관 → 문서 내용 분석 → 증상·원인·부품·조치·판단 조건 등 지식 후보 추출 → 기존 온톨로지 스키마와 식별자에 매핑 → 원문 근거 대조와 사람 검토 → 승인된 지식 적재 → 그래프 관계·출처 조회의 단계별 역할을 살펴본다. LLM의 문서 이해 및 구조화 출력 원리를 살펴보고, 추출 과정에서 발생할 수 있는 부정 조건 누락·수치/단위 오류·잘못된 관계 추론·근거 없는 내용 생성의 위험을 배운다. 원문 페이지·문단·인용 구간, 문서 식별자와 개정 이력, 지식 소유 관계 및 변경 추적이 필요한 이유를 살펴본다. 검색해 문서를 참고하는 방식과 구조화된 지식으로 등록하는 방식의 차이도 이해한다. 마지막으로 설비의 원인·절차·규칙처럼 상대적으로 안정적인 지식과 센서·재고·운전시간처럼 지속적으로 변하는 값을 구분하고, 실제 값은 업무 DB·시계열 DB 등 원천에서 조회하도록 연결하는 원리를 살펴본다.</x:v>
       </x:c>
       <x:c r="D38" s="25" t="n">
         <x:v>40</x:v>
@@ -1471,10 +1512,8 @@
           <x:t xml:space="preserve">현장 매뉴얼에서 판단 근거를 추출하고 검증된 지식으로 등록하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C39" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털의 지식 관리에서 제공된 설비 정비 매뉴얼을 등록하고, 원문 보관과 추출 작업 요청부터 진행한다. 추출된 작업 절차·고장 유형·원인·조치 방법·수행 조건·규칙과 원문 구간을 검토한다. 특히 부정 조건·단위·작업 단계 순서·대상 설비를 원문과 비교하여 누락되거나 잘못 해석된 항목을 수정·제외한다. 검토를 통과한 후보가 기존 온톨로지의 어떤 클래스·인스턴스·관계에 연결되는지 확인한 뒤 승인하여 그래프 DB에 등록한다. 지식 지도에서 등록된 조치·원인·근거 문서의 관계를 확인하고, 데이터 연결 화면에서는 정적인 판단 기준과 실제 업무 DB·시계열 DB에서 조회되는 현재값의 차이를 살펴본다.</x:t>
-        </x:is>
+      <x:c r="C39" s="27" t="str">
+        <x:v>제공 매뉴얼의 원문과 포털에 등록된 추출·검토 결과를 나란히 확인한다. 작업 순서·단위·금지 조건·대상 설비를 비교하고 수정하거나 제외할 후보를 표시한다. 지식 지도에서 채택된 항목의 설비·조치·출처 연결을 찾는다. 직접 추가 적재는 마지막 교대 실습에서 제공 보충 매뉴얼로 수행한다.</x:v>
       </x:c>
       <x:c r="D39" s="33" t="n">
         <x:v>70</x:v>
@@ -1527,10 +1566,8 @@
           <x:t xml:space="preserve">온톨로지 설계부터 지식 활용까지의 전체 과정 정리하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1일차 온톨로지의 필요성에서 시작해 2일차 클래스·인스턴스·속성·관계·스키마와 그래프 DB, 3일차 SOP·DMN·BSC/KPI의 조치·판단·성과 체계, 4일차 원천 자료 추출·검토·인제스천·출처 관리를 하나의 흐름으로 복습한다. 각 단계의 입력과 결과물, 지식 구조와 실제 데이터의 차이, 판단 규칙과 근거 문서의 관계를 되짚는다. 이렇게 구축된 지식과 규칙이 이후 에이전트의 업무 판단과 도구 활용에 어떤 역할을 하는지 연결해 설명한다. 새로운 실습은 진행하지 않는다.</x:t>
-        </x:is>
+      <x:c r="C42" s="19" t="str">
+        <x:v>1일차 온톨로지의 필요성에서 시작해 2일차 클래스·인스턴스·속성·관계·스키마와 그래프 DB, 3일차 SOP·DMN·BSC/KPI의 조치·판단·성과 체계, 4일차 원천 자료 추출·검토·인제스천·출처 관리를 하나의 흐름으로 복습한다. 각 단계의 입력과 결과물, 지식 구조와 실제 데이터의 차이, 판단 규칙과 근거 문서의 관계를 되짚는다. 이렇게 구축된 지식과 규칙이 이후 에이전트의 업무 판단과 도구 활용에 어떤 역할을 하는지 연결해 살펴본다. 새로운 실습은 진행하지 않는다.</x:v>
       </x:c>
       <x:c r="D42" s="25" t="n">
         <x:v>30</x:v>
@@ -1593,10 +1630,8 @@
           <x:t xml:space="preserve">질문하는 AI와 일하는 AI의 차이 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LLM의 응답 생성, RAG의 근거 검색, Agent의 목표 지향 작업 수행을 구분한다. 요청 해석→계획→도구 선택·호출→결과 관찰→필요 시 재시도→종료의 실행 고리를 설명하고, 단순 답변과 점검·요청 등 업무 산출물 생성의 차이를 쿨러 사례로 연결한다.</x:t>
-        </x:is>
+      <x:c r="C47" s="53" t="str">
+        <x:v>LLM의 응답 생성, RAG의 근거 검색, Agent의 목표 지향 작업 수행을 구분한다. 요청 해석→계획→도구 선택·호출→결과 관찰→필요 시 재시도→종료의 실행 고리를 살펴보고, 단순 답변과 점검·요청 등 업무 산출물 생성의 차이를 쿨러 사례로 연결한다.</x:v>
       </x:c>
       <x:c r="D47" s="54" t="n">
         <x:v>40</x:v>
@@ -1613,10 +1648,8 @@
           <x:t xml:space="preserve">에이전트가 다양한 정보와 도구를 사용하는 원리 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C48" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">온톨로지(설비·증상·원인 관계), 시계열 DB(실제 시각의 측정값), 업무 DB(정비·재고), SOP(작업 방법)의 역할을 구분한다. 지식과 현재값을 혼동하지 않는 방법, 근거 부족과 도구 호출 실패·권한 제한 시 멈춤 조건, 구조화 출력과 실행 기록을 설명한다.</x:t>
-        </x:is>
+      <x:c r="C48" s="60" t="str">
+        <x:v>온톨로지(설비·증상·원인 관계), 시계열 DB(실제 시각의 측정값), 업무 DB(정비·재고), SOP(작업 방법)의 역할을 구분한다. 지식과 현재값을 혼동하지 않는 방법, 근거 부족과 도구 호출 실패·권한 제한 시 멈춤 조건, 구조화 출력과 실행 기록을 살펴본다.</x:v>
       </x:c>
       <x:c r="D48" s="61" t="n">
         <x:v>40</x:v>
@@ -1628,15 +1661,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B49" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">나의 첫 업무 에이전트 직접 구성하기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C49" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털의 에이전트 화면에서 학생용 에이전트 이름·목표·역할·사용 도구를 설정하고 직접 질문한다. 답변의 근거와 호출 기록을 확인하고, 기준 에이전트와 자신이 설정한 역할이 다른 부분을 확인한다. 준비된 학생 계정과 사용 가능한 읽기 도구를 전제로 한다.</x:t>
-        </x:is>
+      <x:c r="B49" s="55" t="str">
+        <x:v>업무 에이전트에 질문하고 도구와 근거 확인하기</x:v>
+      </x:c>
+      <x:c r="C49" s="53" t="str">
+        <x:v>포털에서 준비된 에이전트의 역할과 사용 도구를 확인하고 수업용 설비 질문을 입력한다. 답변의 근거와 도구 호출 결과를 대조하여 확인된 사실과 추가 확인이 필요한 내용을 구분한다. 에이전트 구현은 이어지는 VS Code 랩에서 수행한다.</x:v>
       </x:c>
       <x:c r="D49" s="54" t="n">
         <x:v>30</x:v>
@@ -1671,10 +1700,8 @@
           <x:t xml:space="preserve">품질 불량 접수를 후속 업무로 연결하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C51" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">별도 제공된 불량 접수 메시지와 분류 기준을 사용해 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 작은 에이전트를 구현한다. 불량 원인 미확정 시 단정하지 않고 조사 요청으로 넘기는 분기를 두고, 결과를 구조화된 품질 대응 카드로 저장한다.</x:t>
-        </x:is>
+      <x:c r="C51" s="53" t="str">
+        <x:v>별도 제공된 불량 접수 메시지와 분류 기준을 사용해 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 작은 에이전트를 구현한다. 불량 원인 미확정 시 단정하지 않고 조사 요청으로 넘기는 분기를 두고, 결과를 구조화된 품질 대응 카드로 저장한다.</x:v>
       </x:c>
       <x:c r="D51" s="54" t="n">
         <x:v>45</x:v>
@@ -1691,10 +1718,8 @@
           <x:t xml:space="preserve">여러 센서에서 이상 징후를 찾아 시각화하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C52" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기존 HYD 센서 시계열 또는 사전 배포 CSV에서 온도·압력·시간 변화와 상승 구간을 비교하고 도표를 생성한다. 이상 구간·관련 태그·조회 기간을 근거와 함께 요약하되 상관관계로 고장 원인을 단정하지 않는 출력을 점검한다.</x:t>
-        </x:is>
+      <x:c r="C52" s="60" t="str">
+        <x:v>기존 HYD 센서 시계열 또는 사전 배포 CSV에서 온도·압력·시간 변화와 상승 구간을 비교하고 도표를 생성한다. 이상 구간·관련 태그·조회 기간을 근거와 함께 요약하되 상관관계로 고장 원인을 단정하지 않는 출력을 점검한다.</x:v>
       </x:c>
       <x:c r="D52" s="61" t="n">
         <x:v>40</x:v>
@@ -1757,10 +1782,8 @@
           <x:t xml:space="preserve">업무 수행 방법을 재사용 가능한 능력으로 만들기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C57" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Agent Skill의 목적, SKILL.md의 작업 목적·호출 조건·입력·출력·순서·예외 지침, SOP의 현장 작업 절차와 에이전트 실행 지침의 차이를 설명한다. 재사용 지침과 한번의 프롬프트를 구분한다.</x:t>
-        </x:is>
+      <x:c r="C57" s="53" t="str">
+        <x:v>Agent Skill의 목적, SKILL.md의 작업 목적·호출 조건·입력·출력·순서·예외 지침, SOP의 현장 작업 절차와 에이전트 실행 지침의 차이를 살펴본다. 재사용 지침과 한번의 프롬프트를 구분한다.</x:v>
       </x:c>
       <x:c r="D57" s="54" t="n">
         <x:v>35</x:v>
@@ -1777,16 +1800,14 @@
           <x:t xml:space="preserve">AI가 여러 시스템의 기능을 사용하는 원리 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MCP의 Host·Client·Server·Tool 구성, 도구 목록 발견, 입력 스키마와 응답, stdio·HTTP 연결 방식을 설명한다. Skill은 수행 방법, MCP는 연결된 실행 도구라는 역할을 명확히 구분한다.</x:t>
-        </x:is>
+      <x:c r="C58" s="60" t="str">
+        <x:v>MCP의 Host·Client·Server·Tool 구성, 도구 목록 발견, 입력 스키마와 응답, stdio·HTTP 연결 방식을 살펴본다. Skill은 수행 방법, MCP는 연결된 실행 도구라는 역할을 명확히 구분한다.</x:v>
       </x:c>
       <x:c r="D58" s="61" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="59" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A59" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1797,30 +1818,24 @@
           <x:t xml:space="preserve">여러 도구를 연결할 때 지켜야 할 안전 기준 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C59" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">도구별 읽기/쓰기 권한, 파일 접근 범위, 인증 비밀값, 외부 응답의 불완전성, 실패·타임아웃과 근거 표시를 설명한다. HYD 포털의 학생 등록 도구는 연결 검사 후 읽기 전용 선택 제한이 있음을 실제 제약으로 안내한다.</x:t>
-        </x:is>
+      <x:c r="C59" s="53" t="str">
+        <x:v>도구별 읽기/쓰기 권한, 파일 접근 범위, 인증 비밀값, 외부 응답의 불완전성, 실패·타임아웃과 근거 표시를 살펴본다. HYD 포털에서 학생이 등록한 서버는 연결 검사 후 읽기 전용 도구를 선택해 사용하는 범위를 확인한다.</x:v>
       </x:c>
       <x:c r="D59" s="54" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="60" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A60" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B60" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 업무 도구를 직접 연결하고 호출하기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C60" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">포털의 도구(MCP) 메뉴에서 사전 준비된 업무 DB/판단 도구 서버의 등록 상태를 확인하고, 수강생 등록 서버는 연결 검사 후 읽기 도구를 시험한다. 도구 이름·입력 값·반환된 행·호출 기록을 확인하고 기존 에이전트에 연결한다.</x:t>
-        </x:is>
+      <x:c r="B60" s="62" t="str">
+        <x:v>에이전트의 업무 도구 입력과 반환값 확인하기</x:v>
+      </x:c>
+      <x:c r="C60" s="60" t="str">
+        <x:v>포털에 준비된 에이전트의 도구 호출 기록에서 도구 이름·입력·반환값을 확인한다. 같은 질문에 사용된 설비 지식과 현재 업무 조회 결과를 구분하고, 각 반환값이 답변의 어느 근거에 사용됐는지 대조한다. 외부 MCP 연결은 제공된 로컬 VS Code 실습에서 수행한다.</x:v>
       </x:c>
       <x:c r="D60" s="61" t="n">
         <x:v>20</x:v>
@@ -1838,7 +1853,7 @@
         </x:is>
       </x:c>
       <x:c r="C61" s="53" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex에서 사전 준비된 파일시스템·Git·시간 MCP 서버 3종 이상의 실행·접근 권한을 각각 설정하고 도구 목록과 호출 결과를 비교한다. 파일 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청에 조합한다. HYD 포털과 로컬 개발 도구의 연결 방식 차이를 설명한다.</x:v>
+        <x:v>VS Code·GitHub Copilot·Codex에서 사전 준비된 파일시스템·Git·시간 MCP 서버 3종 이상의 실행·접근 권한을 각각 설정하고 도구 목록과 호출 결과를 비교한다. 파일 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청에 조합한다. HYD 포털과 로컬 개발 도구의 연결 방식 차이를 살펴본다.</x:v>
       </x:c>
       <x:c r="D61" s="54" t="n">
         <x:v>45</x:v>
@@ -1855,10 +1870,8 @@
           <x:t xml:space="preserve">회의 내용을 실제 후속 업무로 전환하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C62" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">예제 회의록 텍스트를 입력받아 결정사항·담당자·완료 시점을 추출하는 SKILL.md를 작성한다. 담당자와 기한이 없는 항목은 미정으로 표시하고 Markdown/JSON 작업 목록을 생성·검토한다. 회의록 요약만으로 끝내지 않고 다음 행동을 명확히 만든다.</x:t>
-        </x:is>
+      <x:c r="C62" s="60" t="str">
+        <x:v>예제 회의록 텍스트를 입력받아 결정사항·담당자·완료 시점을 추출하는 SKILL.md를 작성한다. 담당자와 기한이 없는 항목은 미정으로 표시하고 Markdown/JSON 작업 목록을 생성·검토한다. 회의록 요약만으로 끝내지 않고 다음 행동을 명확히 만든다.</x:v>
       </x:c>
       <x:c r="D62" s="61" t="n">
         <x:v>45</x:v>
@@ -1875,10 +1888,8 @@
           <x:t xml:space="preserve">나만의 대화형 AI 학습 코치 만들기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C63" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notion에서 내보낸 Markdown 학습노트나 제공 매뉴얼로 문항 생성→학생 답변 입력→정답·출처 기반 피드백→다음 문항 제공의 대화를 구성한다. 텍스트 파일 기반으로 우선 완주하며 실서비스 Notion API 연동은 필수로 가정하지 않는다.</x:t>
-        </x:is>
+      <x:c r="C63" s="53" t="str">
+        <x:v>Notion에서 내보낸 Markdown 학습노트나 제공 매뉴얼로 문항 생성→학생 답변 입력→정답·출처 기반 피드백→다음 문항 제공의 대화를 구성한다. 텍스트 파일 기반으로 우선 완주하며 실서비스 Notion API 연동은 필수로 가정하지 않는다.</x:v>
       </x:c>
       <x:c r="D63" s="54" t="n">
         <x:v>45</x:v>
@@ -1941,16 +1952,14 @@
           <x:t xml:space="preserve">AI가 멈추고 사람에게 물어야 하는 상황 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C68" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HITL의 정의, 자동 처리와 승인·보류·거절의 구분, 승인권자와 권한의 경계, 사람의 책임과 결정 기록을 설명한다. AI의 자기 검토와 실제 사람 승인 절차는 다른 것임을 구분한다.</x:t>
-        </x:is>
+      <x:c r="C68" s="53" t="str">
+        <x:v>HITL의 정의, 자동 처리와 승인·보류·거절의 구분, 승인권자와 권한의 경계, 사람의 책임과 결정 기록을 살펴본다. AI의 자기 검토와 실제 사람 승인 절차는 다른 것임을 구분한다.</x:v>
       </x:c>
       <x:c r="D68" s="54" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="69" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A69" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1961,10 +1970,8 @@
           <x:t xml:space="preserve">사람의 확인이 실제 업무 결과를 바꾸는 과정 확인하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C69" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털의 처리 건·내 작업함에서 기존 승인 대기 건과 역할을 확인한다. 권한이 있는 담당자의 승인·거절이 흐름 상태에 미치는 영향을 확인하고, 쓰기 권한이 없는 계정의 제한을 설명한다. 실제 수업용 시나리오와 역할을 사전 준비한다.</x:t>
-        </x:is>
+      <x:c r="C69" s="60" t="str">
+        <x:v>포털의 처리 건과 내 작업함에서 승인 대기 작업·담당 역할·추천 근거를 확인한다. 수업용 승인·거절 사례의 처리 결과를 비교하고, 대기 상태와 완료 상태를 구분한다. 승인하지 않은 추천이 실제 명령이나 업무 처리로 이어지지 않는지 실행 이력을 확인한다.</x:v>
       </x:c>
       <x:c r="D69" s="61" t="n">
         <x:v>20</x:v>
@@ -1982,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c r="C70" s="53" t="str">
-        <x:v>5회차에서 만든 후속 업무 요청 결과와 처리 프로젝트를 재사용한다. 해당 업무의 필수 정보가 빠지면 확정하지 않고 확인 질문을 생성하며, 추가 입력 후 다시 판단해 상태 변화를 기록한다. 다른 도메인으로 전환한다면 제공 시작본과 필드 대응을 명시한다.</x:v>
+        <x:v>5회차에서 만든 후속 업무 요청 결과와 처리 프로젝트를 재사용한다. 해당 업무의 필수 정보가 빠지면 확정하지 않고 확인 질문을 생성하며, 추가 입력 후 다시 판단해 상태 변화를 기록한다.</x:v>
       </x:c>
       <x:c r="D70" s="54" t="n">
         <x:v>45</x:v>
@@ -1999,10 +2006,8 @@
           <x:t xml:space="preserve">서로 다른 에이전트가 제안과 검토를 나눠 수행하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작성 역할은 업무 요청 초안을 만들고 검토 역할은 근거·수량·승인 정보 누락을 독립적으로 검토한다. 검토 의견에 따라 작성 결과를 수정하고, AI 간 상호 검토와 사람의 최종 승인 여부를 서로 다른 필드로 남긴다.</x:t>
-        </x:is>
+      <x:c r="C71" s="60" t="str">
+        <x:v>작성 역할은 업무 요청 초안을 만들고 검토 역할은 근거·수량·승인 정보 누락을 독립적으로 검토한다. 검토 의견에 따라 작성 결과를 수정하고, AI 간 상호 검토와 사람의 최종 승인 여부를 서로 다른 필드로 남긴다.</x:v>
       </x:c>
       <x:c r="D71" s="61" t="n">
         <x:v>45</x:v>
@@ -2019,10 +2024,8 @@
           <x:t xml:space="preserve">요구사항이 바뀌어도 기존 기능을 지키는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C72" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SDD를 요구사항·입력/출력 계약·금지 조건·수용 기준을 구현 전에 명확하게 하는 방식으로 설명한다. 바이브 코딩의 모호한 기능 추가가 기존 출력이나 승인 규칙을 흔들 수 있음을 예로 들되, 실패가 항상 발생한다고 단정하지 않는다.</x:t>
-        </x:is>
+      <x:c r="C72" s="53" t="str">
+        <x:v>SDD를 요구사항·입력/출력 계약·금지 조건·수용 기준을 구현 전에 명확하게 하는 방식으로 살펴본다. 바이브 코딩의 모호한 기능 추가가 기존 출력이나 승인 규칙을 흔들 수 있음을 예로 들되, 실패가 항상 발생한다고 단정하지 않는다.</x:v>
       </x:c>
       <x:c r="D72" s="54" t="n">
         <x:v>35</x:v>
@@ -2038,7 +2041,7 @@
         <x:v>모호한 기능 변경이 기존 계약에 미치는 영향 확인하기</x:v>
       </x:c>
       <x:c r="C73" s="60" t="str">
-        <x:v>앞 실습과 같은 업무 요청 프로젝트에 긴급 조건을 추가한다. 모호한 요청으로 변경한 결과와 기존 일반 요청의 출력·승인 계약을 비교한다. 사전 검증된 실패 사례를 사용하되 재현되지 않으면 실제 차이만 기록하며 실패를 연출하지 않는다.</x:v>
+        <x:v>앞 실습과 같은 업무 요청 프로젝트에 긴급 조건을 추가한다. 모호한 요청으로 변경한 결과와 기존 일반 요청의 출력·승인 계약을 비교한다. 제공된 사례를 실행하고 실제로 달라진 입력·출력·승인 조건을 기록한다.</x:v>
       </x:c>
       <x:c r="D73" s="61" t="n">
         <x:v>50</x:v>
@@ -2056,7 +2059,7 @@
         </x:is>
       </x:c>
       <x:c r="C74" s="53" t="str">
-        <x:v>같은 프로젝트의 spec.md에 일반·긴급 요청, 필수 정보 누락 시 보류, 승인 없이 확정 금지, 결과 형식·수용 기준을 명시한다. 구현 후 두 요청을 재실행하고 다음 회차 BDD의 입력·기대 결과를 저장한다.</x:v>
+        <x:v>같은 프로젝트의 spec.md에 일반·긴급 요청, 필수 정보 누락 시 보류, 승인 없이 확정 금지, 결과 형식·수용 기준을 명시한다. 구현 후 두 요청을 재실행하고 실제 출력과 명세의 기대 결과를 비교한다.</x:v>
       </x:c>
       <x:c r="D74" s="54" t="n">
         <x:v>25</x:v>
@@ -2119,10 +2122,8 @@
           <x:t xml:space="preserve">기대한 행동을 실제로 검증하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C79" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BDD의 Given/When/Then 구조, 요구 명세(SDD)와 행동 검증(BDD)의 차이, 정상·경계·예외·회귀 테스트를 설명한다. 자연어 시나리오가 실행 가능한 검증 입력·기대 결과와 연결돼야 하는 이유를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C79" s="53" t="str">
+        <x:v>BDD의 Given/When/Then 구조, 요구 명세(SDD)와 행동 검증(BDD)의 차이, 정상·경계·예외·회귀 테스트를 살펴본다. 자연어 시나리오가 실행 가능한 검증 입력·기대 결과와 연결돼야 하는 이유를 살펴본다.</x:v>
       </x:c>
       <x:c r="D79" s="54" t="n">
         <x:v>40</x:v>
@@ -2139,10 +2140,8 @@
           <x:t xml:space="preserve">새로운 기능과 기존 기능의 행동 기준 정하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C80" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7일차 spec.md와 동일 에이전트를 활용한다. 일반 정비, 긴급 정비, 필수 정보 누락, 승인 거절, 도구 오류에 대해 Given·When·Then과 입력값·기대 상태·출력 계약을 작성한다.</x:t>
-        </x:is>
+      <x:c r="C80" s="60" t="str">
+        <x:v>7일차 spec.md와 동일 에이전트를 활용한다. 일반 정비, 긴급 정비, 필수 정보 누락, 승인 거절, 도구 오류에 대해 Given·When·Then과 입력값·기대 상태·출력 계약을 작성한다.</x:v>
       </x:c>
       <x:c r="D80" s="61" t="n">
         <x:v>40</x:v>
@@ -2159,10 +2158,8 @@
           <x:t xml:space="preserve">에이전트의 동작을 반복 검증하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C81" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">준비한 자동 테스트 또는 반복 실행 스크립트에 BDD 시나리오를 연결한다. 실제 출력과 기대값을 비교하고 어떤 조건에서 규칙을 어겼는지 로그·결과 파일로 확인한다. 모델 출력의 표현 차이와 필수 계약 위반을 구별한다.</x:t>
-        </x:is>
+      <x:c r="C81" s="53" t="str">
+        <x:v>준비한 자동 테스트 또는 반복 실행 스크립트에 BDD 시나리오를 연결한다. 실제 출력과 기대값을 비교하고 어떤 조건에서 규칙을 어겼는지 로그·결과 파일로 확인한다. 모델 출력의 표현 차이와 필수 계약 위반을 구별한다.</x:v>
       </x:c>
       <x:c r="D81" s="54" t="n">
         <x:v>50</x:v>
@@ -2179,10 +2176,8 @@
           <x:t xml:space="preserve">오류를 수정하고 기존 기능이 유지되는지 확인하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C82" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">실제로 실패한 시나리오만 원인을 추적해 프롬프트·명세·코드 중 수정 대상 구분 후 재실행한다. 긴급 조건이 동작하는 동시에 기존 일반 요청·보류·거절 조건이 유지되는지 전체 회귀 검증으로 확인한다.</x:t>
-        </x:is>
+      <x:c r="C82" s="60" t="str">
+        <x:v>실제로 실패한 시나리오만 원인을 추적해 프롬프트·명세·코드 중 수정 대상 구분 후 재실행한다. 긴급 조건이 동작하는 동시에 기존 일반 요청·보류·거절 조건이 유지되는지 전체 회귀 검증으로 확인한다.</x:v>
       </x:c>
       <x:c r="D82" s="61" t="n">
         <x:v>35</x:v>
@@ -2199,10 +2194,8 @@
           <x:t xml:space="preserve">서로 다른 업무 데이터를 연결해 교대 업무 인수인계 완성하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C83" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">기존 설비 이벤트·정비 이력·부품 DB의 실제 연결 가능한 조회 결과 또는 동일 스키마의 수업 준비 자료를 조합한다. 완료 작업·미완료 요청·주의 사항·근거 시각을 포함한 인수인계서를 생성한다. 데이터 패브릭 관점의 다중 출처 통합이지 새 데이터 플랫폼 구축이 아니다.</x:t>
-        </x:is>
+      <x:c r="C83" s="53" t="str">
+        <x:v>기존 설비 이벤트·정비 이력·부품 DB의 실제 연결 가능한 조회 결과 또는 동일 스키마의 수업 준비 자료를 조합한다. 완료 작업·미완료 요청·주의 사항·근거 시각을 포함한 인수인계서를 생성한다. 데이터 패브릭 관점의 다중 출처 통합이지 새 데이터 플랫폼 구축이 아니다.</x:v>
       </x:c>
       <x:c r="D83" s="54" t="n">
         <x:v>45</x:v>
@@ -2219,10 +2212,8 @@
           <x:t xml:space="preserve">에이전트 제작부터 검증까지 전체 과정 정리하기 — Wrap-up</x:t>
         </x:is>
       </x:c>
-      <x:c r="C84" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">에이전트의 목표와 도구, Skill·MCP의 구분, HITL, SDD·BDD와 회귀 검증, 응용별 산출물의 차이를 복습한다. 신규 실습·과제 없이 배운 내용을 정리한다.</x:t>
-        </x:is>
+      <x:c r="C84" s="60" t="str">
+        <x:v>에이전트의 목표와 도구, Skill·MCP의 구분, HITL, SDD·BDD와 회귀 검증, 응용별 산출물의 차이를 복습한다. 신규 실습·과제 없이 배운 내용을 정리한다.</x:v>
       </x:c>
       <x:c r="D84" s="61" t="n">
         <x:v>30</x:v>
@@ -2285,10 +2276,8 @@
           <x:t xml:space="preserve">개별 작업을 하나의 비즈니스 프로세스로 관리하는 이유 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C89" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">비즈니스 프로세스의 정의, Task와 End-to-End의 차이, 시작 조건·입력·출력·책임자·완료 조건을 설명한다. BPM의 분석→설계→실행→모니터링→개선과 AS-IS/TO-BE를 다루고 에이전트만으로 전체 업무 순서와 책임이 보장되지 않는 이유를 연결한다.</x:t>
-        </x:is>
+      <x:c r="C89" s="53" t="str">
+        <x:v>비즈니스 프로세스의 정의, Task와 End-to-End의 차이, 시작 조건·입력·출력·책임자·완료 조건을 살펴본다. BPM의 분석→설계→실행→모니터링→개선과 AS-IS/TO-BE를 다루고 에이전트만으로 전체 업무 순서와 책임이 보장되지 않는 이유를 연결한다.</x:v>
       </x:c>
       <x:c r="D89" s="54" t="n">
         <x:v>35</x:v>
@@ -2305,16 +2294,14 @@
           <x:t xml:space="preserve">복잡한 업무를 공통된 그림으로 표현하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C90" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BPMN 2.0의 Start/End Event, Activity/Task, Gateway, Sequence Flow, Pool·Lane, Message Flow, Timer·Boundary Event를 구분한다. 승인·거절과 분기, 사람·에이전트·시스템의 책임 배치를 설비 조치 예제로 설명한다. 병렬·하위 프로세스는 개념만 소개하고 실습 구현을 주장하지 않는다.</x:t>
-        </x:is>
+      <x:c r="C90" s="60" t="str">
+        <x:v>BPMN 2.0의 Start/End Event, Activity/Task, Gateway, Sequence Flow, Pool·Lane, Message Flow, Timer·Boundary Event를 구분한다. 승인·거절과 분기, 사람·에이전트·시스템의 책임 배치를 설비 조치 예제로 살펴본다. 병렬·하위 프로세스는 개념만 살펴보고 실습 구현을 주장하지 않는다.</x:v>
       </x:c>
       <x:c r="D90" s="61" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="91" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A91" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2325,10 +2312,8 @@
           <x:t xml:space="preserve">설계한 업무가 실제로 실행되는 프로세스 오케스트레이션 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C91" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">프로세스 정의와 인스턴스, Token의 진행 개념, 변수와 결과 전달, User Task·Service Task와 HYD 에이전트 단계, 실행 상태·승인 대기·배포 버전·감사 기록을 설명한다. 온톨로지·DB·SOP를 쓰는 에이전트의 결과를 BPMN이 어떤 순서로 연결하는지 보여준다.</x:t>
-        </x:is>
+      <x:c r="C91" s="53" t="str">
+        <x:v>프로세스 정의와 인스턴스, Token의 진행 개념, 변수와 결과 전달, User Task·Service Task와 HYD 에이전트 단계, 실행 상태·승인 대기·배포 버전·감사 기록을 살펴본다. 온톨로지·DB·SOP를 쓰는 에이전트의 결과가 BPMN에서 어떤 순서로 전달되는지 확인한다.</x:v>
       </x:c>
       <x:c r="D91" s="54" t="n">
         <x:v>25</x:v>
@@ -2345,10 +2330,8 @@
           <x:t xml:space="preserve">업무 흐름을 그리는 도구로 간단한 승인 절차 작성하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C92" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io의 팔레트·요소 배치·연결·속성·저장·열기 조작을 익힌 뒤 '정비 요청→담당자 확인→승인 여부→승인/반려 종료'를 직접 작도한다. Gateway의 각 분기와 End Event 연결을 확인해 .bpmn 파일을 만든다.</x:t>
-        </x:is>
+      <x:c r="C92" s="60" t="str">
+        <x:v>bpmn.io의 팔레트·요소 배치·연결·속성·저장·열기 조작을 익힌 뒤 '정비 요청→담당자 확인→승인 여부→승인/반려 종료'를 직접 작도한다. Gateway의 각 분기와 End Event 연결을 확인해 .bpmn 파일을 만든다.</x:v>
       </x:c>
       <x:c r="D92" s="61" t="n">
         <x:v>35</x:v>
@@ -2365,10 +2348,8 @@
           <x:t xml:space="preserve">설비 이상 대응의 역할과 승인 조건을 갖춘 업무 흐름 만들기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C93" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io에서 쿨러 열화 시작→에이전트 진단·조치 제안→운전원 승인→PLC 명령→효과 재확인→결과 보고를 작업별 Lane으로 작도한다. 승인/거절 분기, 정상/반려 종료와 승인을 중단하지 않는 지연 알림 Timer를 포함해 파일로 저장한다.</x:t>
-        </x:is>
+      <x:c r="C93" s="53" t="str">
+        <x:v>bpmn.io에서 쿨러 열화 시작→에이전트 진단·조치 제안→운전원 승인→PLC 명령→효과 재확인→결과 보고를 작업별 Lane으로 작도한다. 승인/거절 분기, 정상/반려 종료와 승인을 중단하지 않는 지연 알림 Timer를 포함해 파일로 저장한다.</x:v>
       </x:c>
       <x:c r="D93" s="54" t="n">
         <x:v>45</x:v>
@@ -2380,15 +2361,11 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B94" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작성한 흐름을 기존 에이전트와 실제 시스템에 연결하기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C94" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD 포털 흐름 가져오기→쿨러 경보 시작 조건→기존 에이전트·운전원 역할·시스템 단계 매핑→사전 검사→등록·배포 순서로 진행한다. 포털에 입력란이 없는 시스템 세부 연결은 제공된 students/flows/cooling-emergency.mapping.json과 검증된 API 절차로 보완한다.</x:t>
-        </x:is>
+      <x:c r="B94" s="62" t="str">
+        <x:v>작성한 BPMN과 등록된 실행 흐름의 연결 비교하기</x:v>
+      </x:c>
+      <x:c r="C94" s="60" t="str">
+        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</x:v>
       </x:c>
       <x:c r="D94" s="61" t="n">
         <x:v>40</x:v>
@@ -2405,10 +2382,8 @@
           <x:t xml:space="preserve">실제 설비 이벤트로 프로세스를 실행하고 처리 이력 확인하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C95" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">쿨러 열화 버튼으로 처리 건 생성, 에이전트 판단·승인→PLC 명령→유온 재확인→완료를 확인한다. 포털 처리 건에서 단계별 담당·대기·결과를 추적하고 배포된 학생 흐름과 기준 흐름의 차이를 살펴본다. 승인 대기·정상 종료를 혼동하지 않는다.</x:t>
-        </x:is>
+      <x:c r="C95" s="53" t="str">
+        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D95" s="54" t="n">
         <x:v>35</x:v>
@@ -2471,10 +2446,8 @@
           <x:t xml:space="preserve">다양한 업무를 하나의 프로세스 설계 원리로 관리하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C100" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">설비 경보, 정기 점검 도래, 재고 부족이라는 시작 조건과 에이전트·승인자·실행 시스템의 차이를 비교한다. 프로세스 정의·인스턴스·배포, 대기와 완료 상태, 실행 기록·모니터링·병목·지표를 설명하고 같은 BPMN 패턴의 재사용 원리를 정리한다.</x:t>
-        </x:is>
+      <x:c r="C100" s="53" t="str">
+        <x:v>설비 경보, 정기 점검 도래, 재고 부족이라는 시작 조건과 에이전트·승인자·실행 시스템의 차이를 비교한다. 프로세스 정의·인스턴스·배포, 대기와 완료 상태, 실행 기록·모니터링·병목·지표를 설명하고 같은 BPMN 패턴의 재사용 원리를 정리한다.</x:v>
       </x:c>
       <x:c r="D100" s="54" t="n">
         <x:v>35</x:v>
@@ -2491,10 +2464,8 @@
           <x:t xml:space="preserve">정기 점검부터 작업지시까지 이어지는 업무 흐름 설계하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C101" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인/거절→CMMS 정비 오더→생산팀 공지→결과 보고를 작도한다. 9일차의 Task·Lane·Gateway·Timer 패턴을 재사용하고 승인·반려 경로를 구분한다.</x:t>
-        </x:is>
+      <x:c r="C101" s="60" t="str">
+        <x:v>bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인/거절→CMMS 정비 오더→생산팀 공지→결과 보고를 작도한다. 9일차의 Task·Lane·Gateway·Timer 패턴을 재사용하고 승인·반려 경로를 구분한다.</x:v>
       </x:c>
       <x:c r="D101" s="61" t="n">
         <x:v>45</x:v>
@@ -2511,16 +2482,14 @@
           <x:t xml:space="preserve">정기 점검 프로세스를 실제 업무로 실행하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C102" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD에 작성한 BPMN을 가져와 정기 점검(PM_DUE) 이벤트·기존 정비 계획 에이전트·담당 역할·CMMS·공지 작업을 연결하고 사전 검사→등록→배포한다. 포털의 정기 점검 버튼으로 실행해 승인 후 오더·생산 공지·종료를 확인한다. 화면 밖 연결 값은 수업 제공 매핑 파일/절차를 사용한다.</x:t>
-        </x:is>
+      <x:c r="C102" s="53" t="str">
+        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
       </x:c>
       <x:c r="D102" s="54" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="103" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A103" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2531,10 +2500,8 @@
           <x:t xml:space="preserve">재고 부족부터 구매·입고까지 이어지는 업무 흐름 설계하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C103" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인/거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 작도한다. 공급사 실거래가 아닌 HYD 기업 시스템 시뮬레이션이라는 범위를 명시한다.</x:t>
-        </x:is>
+      <x:c r="C103" s="60" t="str">
+        <x:v>bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인/거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 작도한다. HYD의 기업 시스템 시뮬레이션에서 발주·통지·입고가 연결되는 구조를 확인한다.</x:v>
       </x:c>
       <x:c r="D103" s="61" t="n">
         <x:v>45</x:v>
@@ -2551,10 +2518,8 @@
           <x:t xml:space="preserve">구매 프로세스를 실제 업무로 실행하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C104" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">재고 부족(SPARE_BELOW_MIN) 이벤트와 기존 구매 에이전트·승인 역할·ERP·통지·입고 반영 부품을 매핑해 검사·등록·배포한다. 포털 재고 보충 버튼으로 실행하여 발주·통지·시뮬레이션상 즉시 입고·재고 반영 및 종료 기록을 확인한다.</x:t>
-        </x:is>
+      <x:c r="C104" s="53" t="str">
+        <x:v>포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
       </x:c>
       <x:c r="D104" s="54" t="n">
         <x:v>40</x:v>
@@ -2571,10 +2536,8 @@
           <x:t xml:space="preserve">AI와 사람이 함께 수행하는 전체 업무 흐름 정리하기 — Wrap-up</x:t>
         </x:is>
       </x:c>
-      <x:c r="C105" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">설비 조치·정기 점검·재고 보충의 시작 이벤트, 에이전트 판단, 사람 승인·반려, 시스템 처리와 종료 기록을 되짚는다. 온톨로지→에이전트→프로세스의 연결을 복습하며 새로운 실습은 하지 않는다.</x:t>
-        </x:is>
+      <x:c r="C105" s="60" t="str">
+        <x:v>설비 조치·정기 점검·재고 보충의 시작 이벤트, 에이전트 판단, 사람 승인·반려, 시스템 처리와 종료 기록을 되짚는다. 온톨로지→에이전트→프로세스의 연결을 복습하며 새로운 실습은 하지 않는다.</x:v>
       </x:c>
       <x:c r="D105" s="61" t="n">
         <x:v>30</x:v>
@@ -2635,10 +2598,8 @@
           <x:t xml:space="preserve">현장 지식이 AI의 판단 근거가 되는 과정 복습하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C110" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">설비·센서·고장 관계를 정의하는 클래스·인스턴스·스키마, 그래프 질의, SOP·DMN·BSC/KPI, 문서 인제스천과 출처, 정적 지식과 현재 DB 값의 구분을 되짚는다. 앞선 영역 Wrap-up의 단순 반복보다 에이전트 입력으로 연결되는 구조를 중심으로 정리한다.</x:t>
-        </x:is>
+      <x:c r="C110" s="53" t="str">
+        <x:v>설비·센서·고장 관계를 정의하는 클래스·인스턴스·스키마, 그래프 질의, SOP·DMN·BSC/KPI, 문서 인제스천과 출처, 정적 지식과 현재 DB 값의 구분을 되짚는다. 앞선 영역 Wrap-up의 단순 반복보다 에이전트 입력으로 연결되는 구조를 중심으로 정리한다.</x:v>
       </x:c>
       <x:c r="D110" s="54" t="n">
         <x:v>30</x:v>
@@ -2655,10 +2616,8 @@
           <x:t xml:space="preserve">에이전트의 결과가 업무 완료로 이어지는 전체 구조 복습하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C111" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">에이전트 실행·Skill·MCP·HITL·SDD·BDD와 BPMN 정의·인스턴스·승인·시스템 실행의 역할 차이를 정리한다. 개별 제안이 실제 처리 건에서 누구의 승인과 어떤 업무 시스템 실행을 거쳐 종료되는지 설명한다.</x:t>
-        </x:is>
+      <x:c r="C111" s="60" t="str">
+        <x:v>에이전트 실행·Skill·MCP·HITL·SDD·BDD와 BPMN 정의·인스턴스·승인·시스템 실행의 역할 차이를 정리한다. 개별 제안이 실제 처리 건에서 누구의 승인과 어떤 업무 시스템 실행을 거쳐 종료되는지 살펴본다.</x:v>
       </x:c>
       <x:c r="D111" s="61" t="n">
         <x:v>30</x:v>
@@ -2690,7 +2649,7 @@
         <x:v>보충 매뉴얼을 추출·검토하여 기존 지식에 추가하기</x:v>
       </x:c>
       <x:c r="C113" s="60" t="str">
-        <x:v>강사가 제공한 설비 점검·이상 확인 보충 매뉴얼에서 절차·조건·근거를 추출하고 원문 대조 후 적재한다. 기존 제조 스키마와 지식은 유지하며 새 문서로 추가한다. 동일 조건의 추출 결과를 재사용할 때는 이를 표시한다. 임의 문서는 허용하지 않는다.</x:v>
+        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다.</x:v>
       </x:c>
       <x:c r="D113" s="61" t="n">
         <x:v>30</x:v>
@@ -2706,13 +2665,13 @@
         <x:v>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</x:v>
       </x:c>
       <x:c r="C114" s="53" t="str">
-        <x:v>기존 지식과 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 완료 메모와 열린 작업지시, 부품 도착 예정과 실제 재고의 불일치를 확인 사항으로 남긴다. 최신 값은 원천에서 조회하고 미확인 업무를 완료로 추정하지 않는다.</x:v>
+        <x:v>교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
       </x:c>
       <x:c r="D114" s="54" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="115" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A115" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2722,7 +2681,7 @@
         <x:v>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</x:v>
       </x:c>
       <x:c r="C115" s="60" t="str">
-        <x:v>bpmn.io에서 자료 조회→인계안 작성→인계자 검토→인수자 확인 또는 보완 요청→완료 기록을 설계한다. 포털에서 별도 정의·시작 폼·에이전트·역할을 연결해 등록한다. 설비·교대를 입력해 시작하고 정상·불일치·보완 경로와 인계 기록을 확인한다.</x:v>
+        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
       </x:c>
       <x:c r="D115" s="61" t="n">
         <x:v>30</x:v>
@@ -2739,10 +2698,8 @@
           <x:t xml:space="preserve">ProcessGPT 시연으로 지식·에이전트·프로세스의 연결 확인하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C116" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[강사 시연] 지금까지 만든 지식·에이전트·프로세스와 HYD 포털보다 고도화된 제품인 ProcessGPT를 강사가 직접 보여 준다. ProcessGPT의 제품 개념과 HYD가 따라 구현한 프로세스 정의·인스턴스·작업함·에이전트 단계의 관계를 설명한다. 프로토타입과 제품 구현을 구분하고 기업 업무 적용 시 필요한 통제 요소를 소개한다.</x:t>
-        </x:is>
+      <x:c r="C116" s="60" t="str">
+        <x:v>ProcessGPT 시연을 보며 지금까지 만든 지식·에이전트·프로세스가 실제 제품의 업무 흐름에 어떻게 연결되는지 살펴본다. 프로세스 정의·실행 인스턴스·작업함·에이전트 활동을 HYD 수업용 구현과 비교하고, 기업 업무에 적용할 때 필요한 권한·승인·실행 기록을 확인한다.</x:v>
       </x:c>
       <x:c r="D116" s="61" t="n">
         <x:v>40</x:v>
@@ -2759,10 +2716,8 @@
           <x:t xml:space="preserve">학습 내용과 제작 결과를 개인 지식 자산으로 정리하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C117" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">첫날 준비한 Notion 학습노트에 개념·참고 자료·실습 산출물·검증 결과를 연결해 기록한다. 수업 계정에서 Notion 연결과 쓰기 권한이 검증된 경우 MCP 연동을 시연하고, 미연결 환경에서는 준비한 Markdown을 Notion에 직접 정리한다.</x:t>
-        </x:is>
+      <x:c r="C117" s="60" t="str">
+        <x:v>첫날 준비한 Notion 학습노트에 개념·참고 자료·실습 산출물·검증 결과를 연결해 기록한다. 수업 계정에서 Notion 연결과 쓰기 권한이 검증된 경우 MCP 연동을 시연하고, 미연결 환경에서는 준비한 Markdown을 Notion에 직접 정리한다.</x:v>
       </x:c>
       <x:c r="D117" s="61" t="n">
         <x:v>20</x:v>
@@ -2925,7 +2880,7 @@
         <x:v>학습 내용을 지식 자산으로 전환하는 방법 이해하기</x:v>
       </x:c>
       <x:c r="C6" s="53" t="str">
-        <x:v>단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 설명한다.</x:v>
+        <x:v>단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 살펴본다.</x:v>
       </x:c>
       <x:c r="D6" s="54" t="n">
         <x:v>10</x:v>
@@ -2939,7 +2894,7 @@
         <x:v>Notion으로 지식 자산화를 위한 학습노트 만들기</x:v>
       </x:c>
       <x:c r="C7" s="60" t="str">
-        <x:v>Notion에서 학습노트 홈과 주제별 카드·페이지를 구성한다. 샘플 개념·출처·실습 결과를 연결하고 검색·보완·재사용할 수 있도록 저장·재열기를 확인한다. 정해진 별도 자료 DB나 실수노트 분류를 강제하지 않는다.</x:v>
+        <x:v>Notion에서 학습노트 홈과 주제별 카드·페이지를 구성한다. 샘플 개념·출처·실습 결과를 연결하고 검색·보완·재사용할 수 있도록 저장·재열기를 확인한다.</x:v>
       </x:c>
       <x:c r="D7" s="61" t="n">
         <x:v>50</x:v>
@@ -2953,7 +2908,7 @@
         <x:v>설비 데이터가 판단으로 이어지는 시스템 구조와 데이터 흐름 이해하기</x:v>
       </x:c>
       <x:c r="C8" s="53" t="str">
-        <x:v>선행 SCADA 교육에서 다룬 설비·센서·PLC·관제 화면의 역할을 간단히 복습한다. HYD 시스템의 전체 아키텍처와 L1~L9 레이어, OT·DMZ·IT 영역의 구분과 역할을 학습한다. 센서 데이터가 MQTT·메시지 처리·시계열 DB·분석 서비스를 거쳐 화면과 판단 기능에 활용되는 경로를 설명한다. 데이터 리니지의 개념을 배우고, 원천 데이터·가공 데이터·이상 이벤트·판단 결과가 어떤 구성요소를 거쳐 생성되는지 살펴본다. 분석 결과가 실제 조치로 이어질 때 명령 게이트웨이와 설비 제어 영역이 필요한 이유도 이해한다.</x:v>
+        <x:v>선행 SCADA 교육에서 다룬 설비·센서·PLC·관제 화면의 역할을 간단히 복습한다. HYD 시스템의 전체 아키텍처와 L1~L9 레이어, OT·DMZ·IT 영역의 구분과 역할을 학습한다. 센서 데이터가 MQTT·메시지 처리·시계열 DB·분석 서비스를 거쳐 화면과 판단 기능에 활용되는 경로를 살펴본다. 데이터 리니지의 개념을 배우고, 원천 데이터·가공 데이터·이상 이벤트·판단 결과가 어떤 구성요소를 거쳐 생성되는지 살펴본다. 분석 결과가 실제 조치로 이어질 때 명령 게이트웨이와 설비 제어 영역이 필요한 이유도 이해한다.</x:v>
       </x:c>
       <x:c r="D8" s="54" t="n">
         <x:v>50</x:v>
@@ -2967,7 +2922,7 @@
         <x:v>시스템 실행 환경을 구성하고 주요 서비스 동작 확인하기</x:v>
       </x:c>
       <x:c r="C9" s="60" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex·Python·Docker Desktop·Docker Compose 등 교육에서 사용할 주요 도구의 역할과 필요한 버전·설정·접속 조건을 안내한다. 각 도구가 개발·AI 코딩·서비스 실행에서 어떤 역할을 하는지 설명한다. 별도 설치를 진행하지 않고 준비된 환경에서 Docker Compose로 HYD 서비스를 실행한다. 컨테이너 상태와 주요 서비스 접속 여부를 확인한 뒤 HYD 포털에 접속해 시스템이 정상적으로 실행되는 상태를 확인한다.</x:v>
+        <x:v>VS Code·GitHub Copilot·Codex·Python·Docker Desktop·Docker Compose가 개발·AI 코딩·서비스 실행에서 맡는 역할을 구분한다. 준비된 학교 PC에서 필요한 도구와 접속 조건을 확인한다. 제공된 실행 절차로 HYD 서비스를 시작하고 컨테이너 상태·주요 서비스·포털 접속 결과를 확인한다.</x:v>
       </x:c>
       <x:c r="D9" s="61" t="n">
         <x:v>30</x:v>
@@ -2981,7 +2936,7 @@
         <x:v>설비 이상 발생부터 판단·승인·조치까지 전체 과정 경험하기</x:v>
       </x:c>
       <x:c r="C10" s="53" t="str">
-        <x:v>HYD 포털에서 쿨러 열화 시나리오를 강사가 처음부터 끝까지 시연한다. 설비 이상 발생, 센서 변화와 경보 감지, 원인 분석, 근거에 기반한 조치 추천, 담당자 승인, 시스템 조치, 재관측 및 최종 결과를 순서대로 보여준다. 각 단계에서 어떤 정보가 사용되고 어떤 결과가 다음 단계로 전달되는지 설명한다. 세부 기술과 내부 실행 구조는 이후 학습에서 다루며, 이 시간에는 전체 과정이 실제로 어떤 문제를 해결하는지 이해하는 데 집중한다.</x:v>
+        <x:v>HYD 포털의 쿨러 열화 시연을 보며 설비 이상→센서 변화·경보→원인 분석→조치 추천→담당자 승인→시스템 조치→효과 재확인의 흐름을 따라간다. 각 단계에 사용된 정보와 다음 단계로 전달된 결과를 비교하고, AI의 추천과 사람의 승인·실제 조치가 서로 다른 단계임을 확인한다.</x:v>
       </x:c>
       <x:c r="D10" s="54" t="n">
         <x:v>20</x:v>
@@ -2995,7 +2950,7 @@
         <x:v>설비 데이터에 의미와 관계를 부여하는 온톨로지 이해하기</x:v>
       </x:c>
       <x:c r="C11" s="60" t="str">
-        <x:v>센서에서 온도가 상승했다는 사실만으로는 어느 부품에 문제가 있는지, 가능한 원인이 무엇인지, 어떤 조치를 취해야 하는지 알기 어려운 이유를 설명한다. 개별 수치와 데이터, 데이터에 의미를 부여한 정보, 판단에 활용할 수 있는 지식의 차이를 이해한다. 온톨로지가 대상의 종류·속성·관계·제약을 명시적으로 정의해 공통된 의미로 이해하도록 하는 지식 모델임을 배운다. 설비·센서·부품·증상·원인·조치·근거 문서가 어떻게 연결되는지 설명하고, 단순한 관계 그림이나 그래프 DB 자체가 온톨로지와 동일한 것은 아니라는 점을 구분한다. 이를 통해 이후 원인 탐색과 근거 기반 판단에 온톨로지가 필요한 이유를 이해한다.</x:v>
+        <x:v>센서에서 온도가 상승했다는 사실만으로는 어느 부품에 문제가 있는지, 가능한 원인이 무엇인지, 어떤 조치를 취해야 하는지 알기 어려운 이유를 살펴본다. 개별 수치와 데이터, 데이터에 의미를 부여한 정보, 판단에 활용할 수 있는 지식의 차이를 이해한다. 온톨로지가 대상의 종류·속성·관계·제약을 명시적으로 정의해 공통된 의미로 이해하도록 하는 지식 모델임을 배운다. 설비·센서·부품·증상·원인·조치·근거 문서가 어떻게 연결되는지 살펴보고, 단순한 관계 그림이나 그래프 DB 자체가 온톨로지와 동일한 것은 아니라는 점을 구분한다. 이를 통해 이후 원인 탐색과 근거 기반 판단에 온톨로지가 필요한 이유를 이해한다.</x:v>
       </x:c>
       <x:c r="D11" s="61" t="n">
         <x:v>50</x:v>
@@ -3077,10 +3032,8 @@
           <x:t xml:space="preserve">클래스와 인스턴스를 구분해 현장 정보의 구조 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C17" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">클래스·인스턴스·속성·관계, 관계 방향, 카디널리티를 HYD 설비와 센서 실례로 설명한다. 같은 종류의 설비와 실제 설비 1대를 구별한다.</x:t>
-        </x:is>
+      <x:c r="C17" s="53" t="str">
+        <x:v>클래스·인스턴스·속성·관계, 관계 방향, 카디널리티를 HYD 설비와 센서 실례로 살펴본다. 같은 종류의 설비와 실제 설비 1대를 구별한다.</x:v>
       </x:c>
       <x:c r="D17" s="54" t="n">
         <x:v>25</x:v>
@@ -3097,10 +3050,8 @@
           <x:t xml:space="preserve">일관된 지식 구조를 만들기 위한 스키마 설계 원리 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">고유 식별자, 자료형, 필수값, 레이블, 노드 간 관계·제약, 스키마와 인스턴스의 역할 차이를 설명한다. 중복 부품 명칭과 동일 설비 구분 문제를 예로 든다.</x:t>
-        </x:is>
+      <x:c r="C18" s="60" t="str">
+        <x:v>고유 식별자, 자료형, 필수값, 레이블, 노드 간 관계·제약, 스키마와 인스턴스의 역할 차이를 살펴본다. 중복 부품 명칭과 동일 설비 구분 문제를 예로 든다.</x:v>
       </x:c>
       <x:c r="D18" s="61" t="n">
         <x:v>20</x:v>
@@ -3117,34 +3068,30 @@
           <x:t xml:space="preserve">그래프 DB에서 연결 관계를 조회하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Neo4j의 노드·관계·속성과 Cypher의 MATCH·WHERE·RETURN·CREATE·MERGE의 목적을 설명한다. 구조 조회와 실제 데이터 적재를 구분한다.</x:t>
-        </x:is>
+      <x:c r="C19" s="53" t="str">
+        <x:v>Neo4j의 노드·관계·속성과 Cypher의 MATCH·WHERE·RETURN·CREATE·MERGE의 목적을 살펴본다. 구조 조회와 실제 데이터 적재를 구분한다.</x:v>
       </x:c>
       <x:c r="D19" s="54" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="20" s="1" customFormat="1" ht="114" customHeight="1">
       <x:c r="A20" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B20" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그래프 DB에서 설비의 연결 관계 조회하기</x:t>
-        </x:is>
+      <x:c r="B20" s="62" t="str">
+        <x:v>Cypher로 그래프를 다루고 설비 조회 결과 해석하기</x:v>
       </x:c>
       <x:c r="C20" s="60" t="str">
-        <x:v>Neo4j Browser의 제공 예제에서 레이블·속성·관계 방향을 확인한다. 설비의 구성 요소·센서·물리량·교체 부품을 MATCH·WHERE·RETURN으로 조회하고 한 단계·여러 단계 결과 및 집계의 원래 행을 대조한다. 예제 DB와 포털 기준 DB를 구별한다.</x:v>
+        <x:v>Neo4j Browser의 연결·쿼리 실행·그래프와 표 보기 방법을 익힌다. 작은 예제에서 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 노드와 관계를 생성·조회·수정하고 그래프를 클릭해 속성을 확인한다. RETURN의 대상에 따른 그래프·표 결과를 비교한다. DELETE·DETACH DELETE 후 재조회해 연습 데이터를 정리한다. 이어 제공 설비 예제에서 구성 요소·센서·부품의 연결을 한 단계·여러 단계 경로로 조회하고 조건·집계 결과를 원래 행과 대조한다. 실습용 예제 DB와 포털 기준 DB를 구분한다.</x:v>
       </x:c>
       <x:c r="D20" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="21" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A21" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3156,7 +3103,7 @@
         </x:is>
       </x:c>
       <x:c r="C21" s="53" t="str">
-        <x:v>HYD 포털의 지식 지도에서 설비를 선택해 구성요소·센서 등의 연결 관계를 탐색한다. 노드의 종류와 속성, 관계 방향을 확인하고 앞서 배운 클래스·인스턴스·스키마가 실제 시스템에서 어떻게 활용되는지 살펴본다. 랩 전용 그래프와 HYD의 기준 지식 지도가 서로 다른 환경이라는 점도 이해한다.</x:v>
+        <x:v>포털 지식 지도에서 설비를 선택하고 연결된 센서·부품을 펼친다. 노드를 눌러 식별자와 속성을 확인하고 관계의 방향을 읽는다. 같은 센서 이름과 서로 다른 식별자를 구분하며, 별도 랩 DB에서 만든 모델과 포털의 기준 지도를 비교한다. 선택한 부품이 어느 설비와 연결되는지 찾아 조회 결과의 사용 범위를 확인한다.</x:v>
       </x:c>
       <x:c r="D21" s="54" t="n">
         <x:v>10</x:v>
@@ -3205,10 +3152,8 @@
           <x:t xml:space="preserve">작업 절차와 판단 조건이 다른 이유 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C24" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SOP의 단계·안전 전제·금지 조건과 DMN의 입력 조건·결정표·출력 판단을 비교한다. 절차를 모두 규칙으로 대체할 수 없다는 점을 설명한다.</x:t>
-        </x:is>
+      <x:c r="C24" s="60" t="str">
+        <x:v>SOP의 단계·안전 전제·금지 조건과 DMN의 입력 조건·결정표·출력 판단을 비교한다. 절차를 모두 규칙으로 대체할 수 없다는 점을 살펴본다.</x:v>
       </x:c>
       <x:c r="D24" s="61" t="n">
         <x:v>35</x:v>
@@ -3292,10 +3237,8 @@
           <x:t xml:space="preserve">조치의 효과를 비용과 성과 관점에서 평가하는 기준 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C30" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BSC 4관점과 전략 목표·KPI의 역할, 안전을 만족한 후보 사이에서 예상 비용·생산 영향·품질·에너지 측면을 비교하는 이유, What-if 분석의 개념을 설명한다.</x:t>
-        </x:is>
+      <x:c r="C30" s="53" t="str">
+        <x:v>BSC 4관점과 전략 목표·KPI의 역할, 안전을 만족한 후보 사이에서 예상 비용·생산 영향·품질·에너지 측면을 비교하는 이유, What-if 분석의 개념을 살펴본다.</x:v>
       </x:c>
       <x:c r="D30" s="54" t="n">
         <x:v>20</x:v>
@@ -3313,7 +3256,7 @@
         </x:is>
       </x:c>
       <x:c r="C31" s="60" t="str">
-        <x:v>HYD 포털의 조치 판단 규칙·손익/What-if·성과 지표 기능을 활용한다. 특정 설비와 이상 상황을 선택하고 판단에 사용되는 입력값·규칙·조치 후보를 확인한다. 운전 조건과 시험값을 변경해 어떤 규칙이 적용되며 어떤 조치가 허용·제외되는지 비교한다. 허용된 조치의 예상 손익과 판단 순위를 살펴보고, 성과 관점의 중요도나 KPI 목표를 변경했을 때 결과가 어떻게 달라지는지 확인한다. 해당 판단의 근거와 계산에 사용된 출처를 확인하며 시험값 변경이 원본 업무 데이터나 지식을 수정하는 것이 아니라는 점을 이해한다.</x:v>
+        <x:v>포털 What-if에서 같은 설비의 시험 입력을 바꾸고 적용 규칙·허용 또는 제외된 조치·예상 성과를 비교한다. 결과의 근거와 입력 단위를 확인하고 시험값 변경과 실제 설비 조치를 구분한다. 순위가 높은 후보라도 금지 조건에 해당하면 선택할 수 없는 이유를 결과에서 찾는다.</x:v>
       </x:c>
       <x:c r="D31" s="61" t="n">
         <x:v>15</x:v>
@@ -3346,10 +3289,8 @@
           <x:t xml:space="preserve">현장 문서를 검토 가능한 지식으로 전환하는 전체 과정 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C33" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회, 출처·개정 기록의 원리를 설명한다. 2일차 샘플 인스턴스 적재와 본격 문서 인제스천의 차이를 구분한다.</x:t>
-        </x:is>
+      <x:c r="C33" s="60" t="str">
+        <x:v>원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회, 출처·개정 기록의 원리를 살펴본다. 2일차 샘플 인스턴스 적재와 본격 문서 인제스천의 차이를 구분한다.</x:v>
       </x:c>
       <x:c r="D33" s="61" t="n">
         <x:v>30</x:v>
@@ -3367,7 +3308,7 @@
         </x:is>
       </x:c>
       <x:c r="C34" s="53" t="str">
-        <x:v>HYD 포털의 지식 관리에서 제공된 설비 정비 매뉴얼을 등록하고, 원문 보관과 추출 작업 요청부터 진행한다. 추출된 작업 절차·고장 유형·원인·조치 방법·수행 조건·규칙과 원문 구간을 검토한다. 특히 부정 조건·단위·작업 단계 순서·대상 설비를 원문과 비교하여 누락되거나 잘못 해석된 항목을 수정·제외한다. 검토를 통과한 후보가 기존 온톨로지의 어떤 클래스·인스턴스·관계에 연결되는지 확인한 뒤 승인하여 그래프 DB에 등록한다. 지식 지도에서 등록된 조치·원인·근거 문서의 관계를 확인하고, 데이터 연결 화면에서는 정적인 판단 기준과 실제 업무 DB·시계열 DB에서 조회되는 현재값의 차이를 살펴본다.</x:v>
+        <x:v>제공 매뉴얼의 원문과 포털에 등록된 추출·검토 결과를 나란히 확인한다. 작업 순서·단위·금지 조건·대상 설비를 비교하고 수정하거나 제외할 후보를 표시한다. 지식 지도에서 채택된 항목의 설비·조치·출처 연결을 찾는다. 직접 추가 적재는 마지막 교대 실습에서 제공 보충 매뉴얼로 수행한다. 선택한 작업에 필요한 준비·금지·완료 조건을 원문 근거와 함께 정리한다.</x:v>
       </x:c>
       <x:c r="D34" s="54" t="n">
         <x:v>35</x:v>
@@ -3383,7 +3324,7 @@
         <x:v>작업 조건과 출처를 보존해 문서 지식 추출하기</x:v>
       </x:c>
       <x:c r="C35" s="60" t="str">
-        <x:v>제공 매뉴얼의 표·작업 순서·단위·금지 조건을 구조화해 추출한다. 문서 ID·페이지 또는 구간·원문 인용을 보존하고 후보를 원문과 대조해 수정·채택한다. 다음 실습의 작업 확인 카드에 사용할 근거를 준비한다.</x:v>
+        <x:v>제공 매뉴얼의 표·작업 순서·단위·금지 조건을 구조화해 추출한다. 문서 ID·페이지 또는 구간·원문 인용을 보존하고 후보를 원문과 대조해 수정·채택한다. 작업별 조건과 해당 조건의 원문 근거를 연결한다.</x:v>
       </x:c>
       <x:c r="D35" s="61" t="n">
         <x:v>40</x:v>
@@ -3416,10 +3357,8 @@
           <x:t xml:space="preserve">온톨로지 설계부터 지식 활용까지 전체 과정 정리하기 — Wrap-up</x:t>
         </x:is>
       </x:c>
-      <x:c r="C37" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">온톨로지 WHY→클래스·스키마→그래프 DB→SOP·DMN→BSC·KPI→매뉴얼 인제스천의 역할과 다음 에이전트 학습으로 이어지는 지식 자산을 복습한다. 신규 실습 없음.</x:t>
-        </x:is>
+      <x:c r="C37" s="60" t="str">
+        <x:v>온톨로지 WHY→클래스·스키마→그래프 DB→SOP·DMN→BSC·KPI→매뉴얼 인제스천의 역할과 다음 에이전트 학습으로 이어지는 지식 자산을 복습한다. 신규 실습 없음.</x:v>
       </x:c>
       <x:c r="D37" s="61" t="n">
         <x:v>30</x:v>
@@ -3487,34 +3426,30 @@
           <x:t xml:space="preserve">실제 업무를 수행하는 AI의 구조 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LLM·RAG·Agent의 목표·도구·반복 실행 차이, 온톨로지·업무 DB·SOP를 근거로 선택하는 과정과 실패 시 확인해야 할 실행 기록을 압축해 설명한다.</x:t>
-        </x:is>
+      <x:c r="C42" s="53" t="str">
+        <x:v>LLM·RAG·Agent의 목표·도구·반복 실행 차이, 온톨로지·업무 DB·SOP를 근거로 선택하는 과정과 실패 시 확인해야 할 실행 기록을 사례로 살펴본다.</x:v>
       </x:c>
       <x:c r="D42" s="54" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="43" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A43" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B43" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">나의 업무 에이전트 직접 구성하기</x:t>
-        </x:is>
+      <x:c r="B43" s="62" t="str">
+        <x:v>에이전트 답변에서 점검에 필요한 근거 확인하기</x:v>
       </x:c>
       <x:c r="C43" s="60" t="str">
-        <x:v>HYD 포털의 에이전트 화면에서 학생용 에이전트 이름·목표·역할·사용 도구를 설정하고 직접 질문한다. 답변의 근거와 호출 기록을 확인하고, 기준 에이전트와 자신이 설정한 역할이 다른 부분을 확인한다. 준비된 학생 계정과 사용 가능한 읽기 도구를 전제로 한다.</x:v>
+        <x:v>포털에서 준비된 에이전트의 역할과 사용 도구를 확인하고 수업용 설비 질문을 입력한다. 답변의 근거와 도구 호출 결과를 대조하여 확인된 사실과 추가 확인이 필요한 내용을 구분한다. 에이전트 구현은 이어지는 VS Code 랩에서 수행한다. 답변에서 점검 대상·근거·확인할 항목을 찾아 점검 요청에 사용할 정보를 구분한다.</x:v>
       </x:c>
       <x:c r="D43" s="61" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="44" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A44" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3524,7 +3459,7 @@
         <x:v>원인 분석을 점검 요청 초안으로 연결하기</x:v>
       </x:c>
       <x:c r="C44" s="53" t="str">
-        <x:v>설비·문서·부품·센서 자료로 원인 후보와 점검 순서를 제안하는 로컬 에이전트를 만든다. 점검 대상·근거·확인 항목을 담은 요청 초안까지 한 과제로 완성한다. 확인되지 않은 원인은 가설로 표시하고 결과를 5회차 입력으로 저장한다. 포털 작업지시 연동은 하지 않는다.</x:v>
+        <x:v>설비·문서·부품·센서 자료로 원인 후보와 점검 순서를 제안하는 로컬 에이전트를 만든다. 점검 대상·근거·확인 항목을 담은 요청 초안까지 한 과제로 완성한다. 확인되지 않은 원인은 가설로 표시하고 점검 요청 초안에 근거와 미확인 항목을 함께 남긴다. 포털 작업지시 연동은 하지 않는다.</x:v>
       </x:c>
       <x:c r="D44" s="54" t="n">
         <x:v>45</x:v>
@@ -3541,10 +3476,8 @@
           <x:t xml:space="preserve">반복 업무를 재사용 가능한 능력으로 만들기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C45" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SKILL.md의 목표·호출 조건·입출력·절차, 현장 SOP와 Agent Skill의 차이를 학습한다. 여러 업무에 같은 지침을 재사용하는 이유를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C45" s="60" t="str">
+        <x:v>SKILL.md의 목표·호출 조건·입출력·절차, 현장 SOP와 Agent Skill의 차이를 학습한다. 여러 업무에 같은 지침을 재사용하는 이유를 살펴본다.</x:v>
       </x:c>
       <x:c r="D45" s="61" t="n">
         <x:v>25</x:v>
@@ -3577,10 +3510,8 @@
           <x:t xml:space="preserve">외부 시스템과 안전하게 연결하는 방법 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MCP Host·Client·Server·Tool, stdio·HTTP, 입력 스키마·출력, 읽기/쓰기 권한·호출 실패, HYD 포털과 로컬 MCP 설정의 차이를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C47" s="60" t="str">
+        <x:v>MCP Host·Client·Server·Tool, stdio·HTTP, 입력 스키마·출력, 읽기/쓰기 권한·호출 실패, HYD 포털과 로컬 MCP 설정의 차이를 살펴본다.</x:v>
       </x:c>
       <x:c r="D47" s="61" t="n">
         <x:v>25</x:v>
@@ -3664,16 +3595,14 @@
           <x:t xml:space="preserve">사람이 최종 판단해야 하는 상황 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C53" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HITL의 승인·보류·거절, 역할별 책임·감사 기록, AI의 자체 검토와 사람 결정의 차이를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C53" s="53" t="str">
+        <x:v>HITL의 승인·보류·거절, 역할별 책임·감사 기록, AI의 자체 검토와 사람 결정의 차이를 살펴본다.</x:v>
       </x:c>
       <x:c r="D53" s="54" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="54" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A54" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3685,7 +3614,7 @@
         </x:is>
       </x:c>
       <x:c r="C54" s="60" t="str">
-        <x:v>HYD 포털의 처리 건·내 작업함에서 기존 승인 대기 건과 역할을 확인한다. 권한이 있는 담당자의 승인·거절이 흐름 상태에 미치는 영향을 확인하고, 쓰기 권한이 없는 계정의 제한을 설명한다. 실제 수업용 시나리오와 역할을 사전 준비한다.</x:v>
+        <x:v>포털의 처리 건과 내 작업함에서 승인 대기 작업·담당 역할·추천 근거를 확인한다. 수업용 승인·거절 사례의 처리 결과를 비교하고, 대기 상태와 완료 상태를 구분한다. 승인하지 않은 추천이 실제 명령이나 업무 처리로 이어지지 않는지 실행 이력을 확인한다.</x:v>
       </x:c>
       <x:c r="D54" s="61" t="n">
         <x:v>15</x:v>
@@ -3718,10 +3647,8 @@
           <x:t xml:space="preserve">기존 기능을 보존하면서 요구사항 확장하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C56" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SDD의 입력/출력 계약·제약·수용 기준과 모호한 바이브 코딩 변경의 위험을 설명한다. spec.md에 지켜야 할 일반 업무 기능과 긴급 요청의 차이를 명시하는 이유를 연결한다.</x:t>
-        </x:is>
+      <x:c r="C56" s="60" t="str">
+        <x:v>SDD의 입력/출력 계약·제약·수용 기준과 모호한 바이브 코딩 변경의 위험을 살펴본다. spec.md에 지켜야 할 일반 업무 기능과 긴급 요청의 차이를 명시하는 이유를 연결한다.</x:v>
       </x:c>
       <x:c r="D56" s="61" t="n">
         <x:v>30</x:v>
@@ -3737,7 +3664,7 @@
         <x:v>내 활용 기능의 요구 변경을 명세하고 구현하기</x:v>
       </x:c>
       <x:c r="C57" s="53" t="str">
-        <x:v>같은 점검 요청 프로젝트에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기존 기능을 보존하며 변경한다. 새 분야로 전환하거나 정해진 수의 예외를 억지로 추가하지 않는다.</x:v>
+        <x:v>같은 점검 요청 프로젝트에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기존 기능을 보존하며 변경한다.</x:v>
       </x:c>
       <x:c r="D57" s="54" t="n">
         <x:v>50</x:v>
@@ -3754,10 +3681,8 @@
           <x:t xml:space="preserve">에이전트의 행동을 시나리오로 검증하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BDD의 Given/When/Then, SDD와의 차이, 정상·누락·거절·경계 조건 및 회귀 검증을 설명한다.</x:t>
-        </x:is>
+      <x:c r="C58" s="60" t="str">
+        <x:v>BDD의 Given/When/Then, SDD와의 차이, 정상·누락·거절·경계 조건 및 회귀 검증을 살펴본다.</x:v>
       </x:c>
       <x:c r="D58" s="61" t="n">
         <x:v>20</x:v>
@@ -3773,7 +3698,7 @@
         <x:v>직접 정한 기대 결과로 활용 기능 검증하기</x:v>
       </x:c>
       <x:c r="C59" s="53" t="str">
-        <x:v>같은 프로젝트와 spec.md를 기준으로 정상·정보 누락·변경 요구·기존 기능의 기대 결과를 Given/When/Then으로 작성한다. 실제 결과와 비교하고 발견된 오류를 수정해 회귀 확인한다. 실패를 연출하거나 검증하지 않은 성공을 기록하지 않는다.</x:v>
+        <x:v>같은 프로젝트와 spec.md를 기준으로 정상·정보 누락·변경 요구·기존 기능의 기대 결과를 Given/When/Then으로 작성한다. 실제 결과와 비교하고 발견된 오류를 수정해 회귀 확인한다.</x:v>
       </x:c>
       <x:c r="D59" s="54" t="n">
         <x:v>40</x:v>
@@ -3790,10 +3715,8 @@
           <x:t xml:space="preserve">업무 에이전트의 제작과 검증 과정 정리하기 — Wrap-up</x:t>
         </x:is>
       </x:c>
-      <x:c r="C60" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Agent·Skill·MCP·HITL·SDD·BDD가 각각 해결하는 문제와 구현 산출물을 복습하고 BPMN 업무 연결을 예고한다. 새로운 실습 없음.</x:t>
-        </x:is>
+      <x:c r="C60" s="60" t="str">
+        <x:v>Agent·Skill·MCP·HITL·SDD·BDD가 각각 해결하는 문제와 구현 산출물을 복습하고 BPMN 업무 연결을 예고한다. 새로운 실습 없음.</x:v>
       </x:c>
       <x:c r="D60" s="61" t="n">
         <x:v>30</x:v>
@@ -3861,10 +3784,8 @@
           <x:t xml:space="preserve">AI 작업과 비즈니스 프로세스의 차이 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C65" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">End-to-End 업무, 시작·입력·담당·완료와 BPM의 분석·설계·실행·모니터링·개선, 에이전트의 단일 작업과 오케스트레이션의 전체 흐름 책임을 설명한다.</x:t>
-        </x:is>
+      <x:c r="C65" s="53" t="str">
+        <x:v>End-to-End 업무, 시작·입력·담당·완료와 BPM의 분석·설계·실행·모니터링·개선, 에이전트의 단일 작업과 오케스트레이션의 전체 흐름 책임을 살펴본다.</x:v>
       </x:c>
       <x:c r="D65" s="54" t="n">
         <x:v>20</x:v>
@@ -3881,10 +3802,8 @@
           <x:t xml:space="preserve">업무 흐름을 표현하는 공통 규칙 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C66" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BPMN의 Event·Task·Gateway·Lane·Sequence Flow·Message Flow, 승인·거절·Timer·Boundary Event를 설비 이상 대응을 통해 설명한다.</x:t>
-        </x:is>
+      <x:c r="C66" s="60" t="str">
+        <x:v>BPMN의 Event·Task·Gateway·Lane·Sequence Flow·Message Flow, 승인·거절·Timer·Boundary Event를 설비 이상 대응을 통해 살펴본다.</x:v>
       </x:c>
       <x:c r="D66" s="61" t="n">
         <x:v>20</x:v>
@@ -3901,10 +3820,8 @@
           <x:t xml:space="preserve">프로세스의 실행과 통제 구조 이해하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C67" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정의·인스턴스·프로세스 변수·Token, 프로세스 엔진, User/Service/Agent 작업, 상태·권한·배포·감사 기록의 의미를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C67" s="53" t="str">
+        <x:v>정의·인스턴스·프로세스 변수·Token, 프로세스 엔진, User/Service/Agent 작업, 상태·권한·배포·감사 기록의 의미를 살펴본다.</x:v>
       </x:c>
       <x:c r="D67" s="54" t="n">
         <x:v>20</x:v>
@@ -3921,10 +3838,8 @@
           <x:t xml:space="preserve">업무 설계 도구의 기본 사용법 익히기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C68" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io에서 요소 배치·연결·수정·속성 확인, .bpmn 저장·불러오기를 직접 실행한다.</x:t>
-        </x:is>
+      <x:c r="C68" s="60" t="str">
+        <x:v>bpmn.io에서 요소 배치·연결·수정·속성 확인, .bpmn 저장·불러오기를 직접 실행한다.</x:v>
       </x:c>
       <x:c r="D68" s="61" t="n">
         <x:v>20</x:v>
@@ -3941,10 +3856,8 @@
           <x:t xml:space="preserve">간단한 승인 업무 흐름 그려보기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C69" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시작→요청 확인→승인 여부→승인/반려 종료를 그려 Event·Task·Gateway와 각 경로 연결을 확인한다.</x:t>
-        </x:is>
+      <x:c r="C69" s="53" t="str">
+        <x:v>시작→요청 확인→승인 여부→승인/반려 종료를 그려 Event·Task·Gateway와 각 경로 연결을 확인한다.</x:v>
       </x:c>
       <x:c r="D69" s="54" t="n">
         <x:v>15</x:v>
@@ -3961,10 +3874,8 @@
           <x:t xml:space="preserve">설비 이상을 조치까지 연결하는 흐름 설계하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C70" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">쿨러 경보→진단·조치 제안 에이전트→운전원 승인→PLC 명령→효과 재확인→보고를 bpmn.io에서 작성하고 역할별 Lane을 구성한다.</x:t>
-        </x:is>
+      <x:c r="C70" s="60" t="str">
+        <x:v>쿨러 경보→진단·조치 제안 에이전트→운전원 승인→PLC 명령→효과 재확인→보고를 bpmn.io에서 작성하고 역할별 Lane을 구성한다.</x:v>
       </x:c>
       <x:c r="D70" s="61" t="n">
         <x:v>40</x:v>
@@ -3981,56 +3892,46 @@
           <x:t xml:space="preserve">승인 조건과 예외를 반영해 안전한 흐름 만들기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">승인·거절 분기, 반려 종료, 승인 지연 알림 Timer를 구성한다. 거절 시 명령이 실행되지 않으며 알림이 사람 작업을 취소하지 않는 구조를 확인한다.</x:t>
-        </x:is>
+      <x:c r="C71" s="53" t="str">
+        <x:v>승인·거절 분기, 반려 종료, 승인 지연 알림 Timer를 구성한다. 거절 시 명령이 실행되지 않으며 알림이 사람 작업을 취소하지 않는 구조를 확인한다.</x:v>
       </x:c>
       <x:c r="D71" s="54" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="72" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A72" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B72" s="62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작성한 흐름에 에이전트와 실행 기능 연결하기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C72" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD에 BPMN을 가져와 쿨러 경보 시작 조건, 기존 에이전트, 승인 역할, PLC 명령·재관측·결과 작업을 매핑한다. 포털에 없는 시스템 설정은 수업 제공 mapping.json과 검증된 API 절차를 사용한다.</x:t>
-        </x:is>
+      <x:c r="B72" s="62" t="str">
+        <x:v>작성한 BPMN과 등록된 작업의 실행 연결 비교하기</x:v>
+      </x:c>
+      <x:c r="C72" s="60" t="str">
+        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</x:v>
       </x:c>
       <x:c r="D72" s="61" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="73" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A73" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B73" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">연결 오류를 검사하고 실행 가능한 정의로 배포하기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C73" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">실제 사전 검사에서 잡히는 필수 작업 부품 누락·분기 조건 누락 사례를 확인하고 수정한다. 정상적으로 검사 통과한 정의를 등록·배포한다.</x:t>
-        </x:is>
+      <x:c r="B73" s="55" t="str">
+        <x:v>BPMN의 역할·분기·종료 연결 검사하고 수정하기</x:v>
+      </x:c>
+      <x:c r="C73" s="53" t="str">
+        <x:v>자신의 BPMN에서 승인·반려 경로와 종료 연결을 따라가며 누락을 찾고 수정한다. 제공 기준 BPMN·매핑 자료와 비교하여 작업별 담당 역할과 실행 기능이 빠지지 않았는지 확인한다. 수정한 그림을 저장하고 다시 열어 연결을 확인한다.</x:v>
       </x:c>
       <x:c r="D73" s="54" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="74" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A74" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4041,10 +3942,8 @@
           <x:t xml:space="preserve">실제 설비 이벤트로 프로세스의 처리 결과 검증하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C74" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">쿨러 열화 버튼으로 자신의 프로세스 인스턴스를 시작하고 에이전트·승인·설비 명령·효과 확인·종료를 확인한다. 정상 처리 건과 승인 대기 상태를 구분한다.</x:t>
-        </x:is>
+      <x:c r="C74" s="60" t="str">
+        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다. 명령이 실행된 시점과 그 전에 필요한 승인·근거를 실행 기록에서 짚는다.</x:v>
       </x:c>
       <x:c r="D74" s="61" t="n">
         <x:v>20</x:v>
@@ -4101,7 +4000,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="79" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A79" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -4112,10 +4011,8 @@
           <x:t xml:space="preserve">여러 업무의 시작 조건과 실행 결과를 일관되게 관리하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C79" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정기 점검 도래와 재고 부족 시작 이벤트, 승인자·시스템 차이, 프로세스 정의 재사용·인스턴스 상태·배포·오류·반려 기록을 압축 설명한다.</x:t>
-        </x:is>
+      <x:c r="C79" s="53" t="str">
+        <x:v>정기 점검 도래와 재고 부족 시작 이벤트, 승인자·시스템 차이, 프로세스 정의 재사용·인스턴스 상태·배포·오류·반려 기록을 사례로 살펴본다.</x:v>
       </x:c>
       <x:c r="D79" s="54" t="n">
         <x:v>20</x:v>
@@ -4132,16 +4029,14 @@
           <x:t xml:space="preserve">정기 점검부터 작업지시까지 이어지는 프로세스 설계하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C80" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인·거절→CMMS 오더→생산팀 공지→종료를 그린다. 공통 역할·승인 구조에 기반해 작업과 분기 조건을 완성한다.</x:t>
-        </x:is>
+      <x:c r="C80" s="60" t="str">
+        <x:v>bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인·거절→CMMS 오더→생산팀 공지→종료를 그린다. 공통 역할·승인 구조에 기반해 작업과 분기 조건을 완성한다.</x:v>
       </x:c>
       <x:c r="D80" s="61" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="81" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A81" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4152,10 +4047,8 @@
           <x:t xml:space="preserve">정비 프로세스를 실행하고 승인 조건 검증하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C81" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HYD에 정비 BPMN을 연결·검사·배포하고 정기 점검 이벤트로 실행한다. 승인 시 작업지시·공지가 진행되고 반려 시 오더가 생성되지 않는 차이를 확인한다. 연결 값 파일 지원 범위를 준수한다.</x:t>
-        </x:is>
+      <x:c r="C81" s="53" t="str">
+        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다. 작업지시가 발행된 상태와 실제 정비가 끝난 상태를 구분한다.</x:v>
       </x:c>
       <x:c r="D81" s="54" t="n">
         <x:v>45</x:v>
@@ -4172,16 +4065,14 @@
           <x:t xml:space="preserve">재고 부족부터 발주·입고까지 이어지는 프로세스 설계하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C82" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bpmn.io에서 재고 부족→기존 구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→즉시 입고 반영→종료를 작성한다. ERP와 재고 기능은 HYD 시뮬레이션으로 다룬다.</x:t>
-        </x:is>
+      <x:c r="C82" s="60" t="str">
+        <x:v>bpmn.io에서 재고 부족→기존 구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→즉시 입고 반영→종료를 작성한다. ERP와 재고 기능은 HYD 시뮬레이션으로 다룬다.</x:v>
       </x:c>
       <x:c r="D82" s="61" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="83" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A83" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4192,10 +4083,8 @@
           <x:t xml:space="preserve">구매 프로세스를 실행하고 처리 결과 검증하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C83" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">작성한 BPMN을 매핑·사전 검사·배포하고 재고 보충 이벤트로 실행한다. 승인 시 발주·통지·재고 반영, 거절 시 발주 차단을 확인한다. 기존 처리 결과를 근거로 검증한다.</x:t>
-        </x:is>
+      <x:c r="C83" s="53" t="str">
+        <x:v>포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다. 발주 수량과 입고 후 재고를 대조하고, 실제 거래가 아닌 수업용 시뮬레이션 결과임을 구분한다.</x:v>
       </x:c>
       <x:c r="D83" s="54" t="n">
         <x:v>45</x:v>
@@ -4212,10 +4101,8 @@
           <x:t xml:space="preserve">프로세스 설계·실행·검증 과정 정리하기 — Wrap-up</x:t>
         </x:is>
       </x:c>
-      <x:c r="C84" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BPMN 모델, 엔진의 정의·인스턴스, 이벤트·에이전트·사람·시스템의 역할과 온톨로지부터 프로세스까지의 학습 연결을 복습한다. 신규 실습 없음.</x:t>
-        </x:is>
+      <x:c r="C84" s="60" t="str">
+        <x:v>BPMN 모델, 엔진의 정의·인스턴스, 이벤트·에이전트·사람·시스템의 역할과 온톨로지부터 프로세스까지의 학습 연결을 복습한다. 신규 실습 없음.</x:v>
       </x:c>
       <x:c r="D84" s="61" t="n">
         <x:v>30</x:v>
@@ -4281,10 +4168,8 @@
           <x:t xml:space="preserve">현장 지식이 AI의 판단 근거가 되는 과정 복습하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C89" s="53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">온톨로지·스키마·그래프·SOP·DMN·BSC/KPI·매뉴얼 인제스천에서 만든 공용 지식이 에이전트 도구 조회로 어떻게 쓰이는지 되짚는다.</x:t>
-        </x:is>
+      <x:c r="C89" s="53" t="str">
+        <x:v>온톨로지·스키마·그래프·SOP·DMN·BSC/KPI·매뉴얼 인제스천에서 만든 공용 지식이 에이전트 도구 조회로 어떻게 쓰이는지 되짚는다.</x:v>
       </x:c>
       <x:c r="D89" s="54" t="n">
         <x:v>30</x:v>
@@ -4301,10 +4186,8 @@
           <x:t xml:space="preserve">에이전트가 사람과 시스템을 통해 업무를 완료하는 구조 복습하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C90" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Agent·Skill·MCP·HITL·SDD·BDD, BPMN 정의·인스턴스·작업 담당·승인·시스템 작업의 차이를 전체 처리 건 시나리오로 연결한다.</x:t>
-        </x:is>
+      <x:c r="C90" s="60" t="str">
+        <x:v>Agent·Skill·MCP·HITL·SDD·BDD, BPMN 정의·인스턴스·작업 담당·승인·시스템 작업의 차이를 전체 처리 건 시나리오로 연결한다.</x:v>
       </x:c>
       <x:c r="D90" s="61" t="n">
         <x:v>30</x:v>
@@ -4336,7 +4219,7 @@
         <x:v>보충 매뉴얼을 추출·검토하여 기존 지식에 추가하기</x:v>
       </x:c>
       <x:c r="C92" s="60" t="str">
-        <x:v>강사가 제공한 설비 점검·이상 확인 보충 매뉴얼에서 절차·조건·근거를 추출하고 원문 대조 후 적재한다. 기존 제조 스키마와 지식은 유지하며 새 문서로 추가한다. 동일 조건의 추출 결과를 재사용할 때는 이를 표시한다. 임의 문서는 허용하지 않는다.</x:v>
+        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다.</x:v>
       </x:c>
       <x:c r="D92" s="61" t="n">
         <x:v>30</x:v>
@@ -4352,13 +4235,13 @@
         <x:v>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</x:v>
       </x:c>
       <x:c r="C93" s="53" t="str">
-        <x:v>기존 지식과 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 완료 메모와 열린 작업지시, 부품 도착 예정과 실제 재고의 불일치를 확인 사항으로 남긴다. 최신 값은 원천에서 조회하고 미확인 업무를 완료로 추정하지 않는다.</x:v>
+        <x:v>교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
       </x:c>
       <x:c r="D93" s="54" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="94" s="1" customFormat="1" ht="92" customHeight="1">
       <x:c r="A94" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4368,7 +4251,7 @@
         <x:v>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</x:v>
       </x:c>
       <x:c r="C94" s="60" t="str">
-        <x:v>bpmn.io에서 자료 조회→인계안 작성→인계자 검토→인수자 확인 또는 보완 요청→완료 기록을 설계한다. 포털에서 별도 정의·시작 폼·에이전트·역할을 연결해 등록한다. 설비·교대를 입력해 시작하고 정상·불일치·보완 경로와 인계 기록을 확인한다.</x:v>
+        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
       </x:c>
       <x:c r="D94" s="61" t="n">
         <x:v>30</x:v>
@@ -4385,10 +4268,8 @@
           <x:t xml:space="preserve">ProcessGPT 시연으로 지식·에이전트·프로세스의 연결 확인하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C95" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">[강사 시연] 지금까지 만든 지식·에이전트·프로세스와 HYD 포털보다 고도화된 제품인 ProcessGPT를 강사가 직접 보여 준다. ProcessGPT와 HYD의 관계, 프로세스 정의·실행 인스턴스·사람 작업·에이전트 활동 기능을 비교하면서 실제 제품과 수업용 구현의 경계를 설명한다.</x:t>
-        </x:is>
+      <x:c r="C95" s="60" t="str">
+        <x:v>ProcessGPT 시연을 보며 지식 조회·에이전트 판단·사람 작업·프로세스 실행이 연결되는 모습을 확인한다. 프로세스 정의·실행 인스턴스·작업함을 HYD 수업용 구현과 비교하고, 실제 제품의 업무 통제와 실행 기록을 살펴본다.</x:v>
       </x:c>
       <x:c r="D95" s="61" t="n">
         <x:v>40</x:v>
@@ -4405,10 +4286,8 @@
           <x:t xml:space="preserve">제작 결과를 Notion 학습노트에 기록하기</x:t>
         </x:is>
       </x:c>
-      <x:c r="C96" s="60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">첫날 만든 Notion 공간에 핵심 개념·실습 결과·참고 출처를 정리한다. 사전 검증된 Notion MCP 쓰기 권한이 있을 때만 연동을 시연하며 그렇지 않으면 준비한 Markdown을 직접 붙여 완성한다.</x:t>
-        </x:is>
+      <x:c r="C96" s="60" t="str">
+        <x:v>Notion 학습노트에 핵심 개념·실습 결과·참고 출처를 연결한다. 수업 환경에서 사용 가능한 경우 MCP로 기록을 반영하고, 그렇지 않은 경우 작성한 Markdown을 직접 붙여 학습노트를 완성한다.</x:v>
       </x:c>
       <x:c r="D96" s="61" t="n">
         <x:v>20</x:v>
@@ -4904,1634 +4783,1400 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="46" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="108" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13" style="1" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="43" style="1" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="110" style="1" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" style="1" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" s="1" customFormat="1" ht="34" customHeight="1">
-      <x:c r="A1" s="84" t="str">
-        <x:v>HYD 제조 AI | 통합반 오프라인 10회 실라버스</x:v>
-      </x:c>
-      <x:c r="B1"/>
-      <x:c r="C1"/>
-      <x:c r="D1" s="84"/>
-    </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="40" customHeight="1">
-      <x:c r="A2" s="66" t="str">
-        <x:v>2026-10-26 개편 | 온라인 선행 학습·가이드 자율 실습 | 이론 최대50분·복습 없음 | 매회 수업200분+휴식40분</x:v>
-      </x:c>
-      <x:c r="B2"/>
-      <x:c r="C2"/>
-      <x:c r="D2" s="49" t="n">
-        <x:f>SUM(D13,D24,D35,D47,D58,D69,D81,D91,D103,D115)</x:f>
+    <x:row r="1" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A1" s="137" t="str">
+        <x:v>HYD 제조 AI | 통합반 오프라인 정규 10회 | 50분 수업 단위</x:v>
+      </x:c>
+      <x:c r="B1" s="137"/>
+      <x:c r="C1" s="137"/>
+      <x:c r="D1" s="137"/>
+    </x:row>
+    <x:row r="2" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A2" s="135" t="str">
+        <x:v>온라인 실습에서 주요 활동을 선별해 직접 수행합니다. 기본 편성은 수업200분·휴식40분이며, 강사가 학생 진행에 따라 시간을 조절합니다. 이론이 있는 회차는50분, 마지막 두 회차는 실습 중심입니다.</x:v>
+      </x:c>
+      <x:c r="B2" s="135"/>
+      <x:c r="C2" s="135"/>
+      <x:c r="D2" s="135"/>
+    </x:row>
+    <x:row r="3" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A3" s="135"/>
+      <x:c r="B3" s="135"/>
+      <x:c r="C3" s="135"/>
+      <x:c r="D3" s="135"/>
+    </x:row>
+    <x:row r="4" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A4" s="138" t="str">
+        <x:v>01회차 | 설비 정보를 관계와 모델로 표현하기</x:v>
+      </x:c>
+      <x:c r="B4" s="138"/>
+      <x:c r="C4" s="138"/>
+      <x:c r="D4" s="138"/>
+    </x:row>
+    <x:row r="5" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A5" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B5" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C5" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D5" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A6" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B6" s="141" t="str">
+        <x:v>설비 정보와 관계 모델 이해하기</x:v>
+      </x:c>
+      <x:c r="C6" s="141" t="str">
+        <x:v>설비·센서·부품이 각각 어떤 정보를 나타내는지 구분한다. 쿨러의 온도 변화가 센서 값, 이상 징후, 원인 후보, 조치 판단으로 이어지는 경로를 살펴본다. 같은 종류와 개별 대상을 클래스·인스턴스로 나누고, 식별자·속성·관계 방향을 설비 사례에 적용한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A7" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B7" s="143" t="str">
+        <x:v>관계도를 그리고 최소 모델 만들기</x:v>
+      </x:c>
+      <x:c r="C7" s="143" t="str">
+        <x:v>arrows.app에서 쿨러·센서·부품·고장·조치를 노드로 만들고 관계를 연결한다. 각 화살표를 문장으로 읽어 방향을 확인한다. 제공 목록과 관계도를 대조해 클래스·고유 ID·속성을 갖춘 schema.json과 예시 인스턴스를 작성한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A8" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B8" s="141" t="str">
+        <x:v>Cypher로 그래프 생성·조회·수정·삭제하기</x:v>
+      </x:c>
+      <x:c r="C8" s="141" t="str">
+        <x:v>별도 Neo4j 랩 DB에서 작은 예제를 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 생성·조회·수정한다. 그래프의 노드와 관계를 눌러 속성을 확인하고 표 결과와 비교한다. DELETE·DETACH DELETE로 연습 데이터만 정리하고 재조회한다.</x:v>
+      </x:c>
+      <x:c r="D8" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A9" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B9" s="143" t="str">
+        <x:v>설비 모델을 적재하고 질문별 결과 확인하기</x:v>
+      </x:c>
+      <x:c r="C9" s="143" t="str">
+        <x:v>작성한 설비 모델을 제공 절차로 별도 랩 DB에 적재한다. 설비의 센서·부품을 조회해 원자료와 비교하고 빠진 관계·식별자를 수정한다. 포털 기준 지도를 열어 자신의 모델과 연결 방향을 비교한다. 관계도·모델·조회 결과를 저장한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A10" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B10" s="139"/>
+      <x:c r="C10" s="139"/>
+      <x:c r="D10" s="139" t="n">
+        <x:f>SUM(D6:D9)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A11" s="135"/>
+      <x:c r="B11" s="135"/>
+      <x:c r="C11" s="135"/>
+      <x:c r="D11" s="135"/>
+    </x:row>
+    <x:row r="12" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A12" s="138" t="str">
+        <x:v>02회차 | 설비 모델을 완성하고 작업 절차 연결하기</x:v>
+      </x:c>
+      <x:c r="B12" s="138"/>
+      <x:c r="C12" s="138"/>
+      <x:c r="D12" s="138"/>
+    </x:row>
+    <x:row r="13" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A13" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B13" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C13" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D13" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A14" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B14" s="141" t="str">
+        <x:v>식별자·적재·SOP 연결 원리 이해하기</x:v>
+      </x:c>
+      <x:c r="C14" s="141" t="str">
+        <x:v>고유 식별자로 같은 대상을 구분하는 방법과 반복 적재 시 중복을 막는 원리를 살펴본다. 필수값·자료형·관계 끝점 제약을 설비 모델에 대어 확인하고, 고장·조치와 SOP의 전제·금지·완료 조건이 연결되는 구조를 이해한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A15" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B15" s="143" t="str">
+        <x:v>모델을 보완하고 적재·조회 검증하기</x:v>
+      </x:c>
+      <x:c r="C15" s="143" t="str">
+        <x:v>설비 모델의 고유 ID·자료형·필수값·관계 끝점을 원자료와 대조해 보완한다. 모델을 적재하고 설비별 센서·부품을 조회한다. 같은 자료를 다시 적재한 뒤 노드와 관계가 불필요하게 늘어나지 않았는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D15" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A16" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B16" s="141" t="str">
+        <x:v>새 설비와 공용 부품으로 모델 확장하기</x:v>
+      </x:c>
+      <x:c r="C16" s="141" t="str">
+        <x:v>제공된 새 설비와 공용 부품을 기존 모델에 추가한다. 공용 부품이 여러 설비와 올바르게 연결되는지 조회하고, 기존 설비의 센서·부품 관계가 유지되는지 비교한다.</x:v>
+      </x:c>
+      <x:c r="D16" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A17" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B17" s="143" t="str">
+        <x:v>SOP를 모델에 연결하고 결과 완성하기</x:v>
+      </x:c>
+      <x:c r="C17" s="143" t="str">
+        <x:v>제공 SOP에서 작업의 전제·금지·수행 단계·완료 조건을 구분한다. 고장 유형과 조치 방법을 기존 설비 모델의 식별자에 연결하고, 선택한 고장에 적용할 절차와 금지 조건을 조회해 원문과 비교한다.</x:v>
+      </x:c>
+      <x:c r="D17" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A18" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B18" s="139"/>
+      <x:c r="C18" s="139"/>
+      <x:c r="D18" s="139" t="n">
+        <x:f>SUM(D14:D17)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A19" s="135"/>
+      <x:c r="B19" s="135"/>
+      <x:c r="C19" s="135"/>
+      <x:c r="D19" s="135"/>
+    </x:row>
+    <x:row r="20" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A20" s="138" t="str">
+        <x:v>03회차 | 안전한 조치와 성과 비교 기능 만들기</x:v>
+      </x:c>
+      <x:c r="B20" s="138"/>
+      <x:c r="C20" s="138"/>
+      <x:c r="D20" s="138"/>
+    </x:row>
+    <x:row r="21" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A21" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B21" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C21" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D21" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A22" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B22" s="141" t="str">
+        <x:v>안전한 판단 규칙과 성과 비교 기준 이해하기</x:v>
+      </x:c>
+      <x:c r="C22" s="141" t="str">
+        <x:v>SOP의 작업 순서와 DMN의 판단 조건을 구분한다. 입력값·단위·연산자·경계값으로 조치 허용·제외를 표현하고, 허용된 후보끼리 비용·생산·품질·에너지 성과를 비교하는 이유를 사례로 확인한다.</x:v>
+      </x:c>
+      <x:c r="D22" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A23" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B23" s="143" t="str">
+        <x:v>SOP 조건표를 만들고 조치 차이 확인하기</x:v>
+      </x:c>
+      <x:c r="C23" s="143" t="str">
+        <x:v>포털 What-if에서 운전 조건을 바꿔 조치 허용·제외와 순위 변화를 비교한다. 제공 SOP에서 입력·단위·경계·출처를 뽑아 결정표를 작성하고, 각 조건이 어떤 조치를 허용하거나 제외하는지 표시한다.</x:v>
+      </x:c>
+      <x:c r="D23" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A24" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B24" s="141" t="str">
+        <x:v>조건별 판정 기능 구현하기</x:v>
+      </x:c>
+      <x:c r="C24" s="141" t="str">
+        <x:v>VS Code에서 결정표를 입력으로 사용해 조치의 허용·제외와 사유를 반환하는 기능을 만든다. 정상 조건, 경계값, 여러 규칙이 동시에 맞는 경우, 금지 조건을 입력해 실제 결과를 조건표와 대조한다.</x:v>
+      </x:c>
+      <x:c r="D24" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A25" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B25" s="143" t="str">
+        <x:v>성과를 비교하고 경계·누락 입력 검증하기</x:v>
+      </x:c>
+      <x:c r="C25" s="143" t="str">
+        <x:v>허용된 조치 후보만 비용·생산 영향·품질·에너지 기준으로 비교한다. 경계값이나 필수 정보 누락에 따라 결과가 달라지는지 확인하고, 선택 이유와 추가 확인 사항을 출력한다. 추천 결과와 사람의 실행 승인을 구분한다.</x:v>
+      </x:c>
+      <x:c r="D25" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A26" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B26" s="139"/>
+      <x:c r="C26" s="139"/>
+      <x:c r="D26" s="139" t="n">
+        <x:f>SUM(D22:D25)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" s="1" customFormat="1" ht="36" customHeight="1">
+      <x:c r="A27" s="135"/>
+      <x:c r="B27" s="135"/>
+      <x:c r="C27" s="135"/>
+      <x:c r="D27" s="135"/>
+    </x:row>
+    <x:row r="28" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A28" s="138" t="str">
+        <x:v>04회차 | 문서를 지식으로 추출하고 검토하기</x:v>
+      </x:c>
+      <x:c r="B28" s="138"/>
+      <x:c r="C28" s="138"/>
+      <x:c r="D28" s="138"/>
+    </x:row>
+    <x:row r="29" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A29" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B29" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C29" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D29" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A30" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B30" s="141" t="str">
+        <x:v>문서 추출·검토·출처 관리 원리 이해하기</x:v>
+      </x:c>
+      <x:c r="C30" s="141" t="str">
+        <x:v>매뉴얼 원문, AI가 추출한 후보, 검토를 거친 지식을 구분한다. 부정 조건·단위·작업 순서가 잘못 추출된 사례를 원문과 대조하고, 문서 ID·페이지·인용 구간을 지식과 함께 보존하는 이유를 이해한다.</x:v>
+      </x:c>
+      <x:c r="D30" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A31" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B31" s="143" t="str">
+        <x:v>문서 등록을 경험하고 추출 기능 만들기</x:v>
+      </x:c>
+      <x:c r="C31" s="143" t="str">
+        <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 문서의 표·작업 절차·수치·단위·금지 조건을 구조화하는 기능을 만들고 문서 ID·페이지 또는 구간·인용을 함께 출력한다.</x:v>
+      </x:c>
+      <x:c r="D31" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A32" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B32" s="141" t="str">
+        <x:v>원문을 대조하고 승인 지식 그래프에 반영하기</x:v>
+      </x:c>
+      <x:c r="C32" s="141" t="str">
+        <x:v>추출 후보의 조건·단위·순서를 원문과 비교해 채택·수정·제외한다. 채택한 항목을 기존 랩 그래프의 클래스와 식별자에 맞춰 적재하고, 고장→원인→조치→근거 문서 관계를 조회한다.</x:v>
+      </x:c>
+      <x:c r="D32" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A33" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B33" s="143" t="str">
+        <x:v>다른 문서에 적용하고 결과 검증하기</x:v>
+      </x:c>
+      <x:c r="C33" s="143" t="str">
+        <x:v>제공된 다른 매뉴얼에 같은 추출 기능을 적용한다. 빠진 조건이나 잘못 연결된 대상이 있는지 원문과 대조하고 수정한다. 그래프에 반영한 지식에서 문서 출처를 다시 찾아 검토 결과와 일치하는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D33" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A34" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B34" s="139"/>
+      <x:c r="C34" s="139"/>
+      <x:c r="D34" s="139" t="n">
+        <x:f>SUM(D30:D33)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A35" s="135"/>
+      <x:c r="B35" s="135"/>
+      <x:c r="C35" s="135"/>
+      <x:c r="D35" s="135"/>
+    </x:row>
+    <x:row r="36" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A36" s="138" t="str">
+        <x:v>05회차 | 서로 다른 일을 하는 에이전트 만들기</x:v>
+      </x:c>
+      <x:c r="B36" s="138"/>
+      <x:c r="C36" s="138"/>
+      <x:c r="D36" s="138"/>
+    </x:row>
+    <x:row r="37" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A37" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B37" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C37" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D37" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A38" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B38" s="141" t="str">
+        <x:v>에이전트의 근거·도구·종료 조건 이해하기</x:v>
+      </x:c>
+      <x:c r="C38" s="141" t="str">
+        <x:v>LLM의 답변, RAG의 근거 검색, 에이전트의 목표·도구·반복 실행을 구분한다. 설비 지식과 현재 센서 값을 각각 어디서 얻는지 살펴보고, 근거 부족이나 도구 오류가 생겼을 때 멈추거나 확인을 요청할 조건을 정한다.</x:v>
+      </x:c>
+      <x:c r="D38" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A39" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B39" s="143" t="str">
+        <x:v>설비 원인과 점검 순서 에이전트 만들기</x:v>
+      </x:c>
+      <x:c r="C39" s="143" t="str">
+        <x:v>포털 에이전트의 목표·도구·근거를 확인한다. VS Code에서 설비·센서·고장·SOP 관계와 센서 입력을 읽어 원인 후보·증거·다음 점검 순서를 제안하는 에이전트를 만든다. 확인되지 않은 원인이 가설로 표시되는지 검토한다.</x:v>
+      </x:c>
+      <x:c r="D39" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="92" customHeight="1">
+      <x:c r="A40" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B40" s="141" t="str">
+        <x:v>품질 접수 후속 업무 에이전트 만들기</x:v>
+      </x:c>
+      <x:c r="C40" s="141" t="str">
+        <x:v>제공 불량 접수 메시지와 분류 기준으로 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 에이전트를 만든다. 원인이 확정되지 않은 사례를 입력해 단정 대신 조사 요청을 남기는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D40" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A41" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B41" s="143" t="str">
+        <x:v>센서 시각화와 에이전트 결과 검증하기</x:v>
+      </x:c>
+      <x:c r="C41" s="143" t="str">
+        <x:v>센서 CSV의 시간·온도·압력 변화를 읽어 이상 구간을 시각화한다. 관련 태그와 조회 기간을 함께 표시하고 원자료와 비교한다. 원인 점검·품질 대응·시각화 결과에서 근거와 미확인 사항이 구분되는지 검토한다.</x:v>
+      </x:c>
+      <x:c r="D41" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A42" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B42" s="139"/>
+      <x:c r="C42" s="139"/>
+      <x:c r="D42" s="139" t="n">
+        <x:f>SUM(D38:D41)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A43" s="135"/>
+      <x:c r="B43" s="135"/>
+      <x:c r="C43" s="135"/>
+      <x:c r="D43" s="135"/>
+    </x:row>
+    <x:row r="44" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A44" s="138" t="str">
+        <x:v>06회차 | 스킬과 MCP로 반복 작업 처리하기</x:v>
+      </x:c>
+      <x:c r="B44" s="138"/>
+      <x:c r="C44" s="138"/>
+      <x:c r="D44" s="138"/>
+    </x:row>
+    <x:row r="45" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A45" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B45" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C45" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D45" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A46" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B46" s="141" t="str">
+        <x:v>스킬·MCP·접근 범위 이해하기</x:v>
+      </x:c>
+      <x:c r="C46" s="141" t="str">
+        <x:v>SKILL.md에 담는 목적·입력·출력·절차와 MCP 도구의 역할을 구분한다. 파일·Git·시간 도구의 입력과 반환값을 살펴보고, 읽기·쓰기 권한과 접근 가능한 경로가 작업에 미치는 영향을 확인한다.</x:v>
+      </x:c>
+      <x:c r="D46" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A47" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B47" s="143" t="str">
+        <x:v>도구를 연결하고 회의록 스킬 만들기</x:v>
+      </x:c>
+      <x:c r="C47" s="143" t="str">
+        <x:v>준비된 MCP의 연결과 호출 결과를 확인한다. 회의록에서 결정사항·담당자·기한·출처를 추출하는 SKILL.md를 작성하고, 담당자나 기한이 없는 항목은 미정으로 남기는지 원문과 비교한다.</x:v>
+      </x:c>
+      <x:c r="D47" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A48" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B48" s="141" t="str">
+        <x:v>파일·Git·시간 도구를 조합해 작업하기</x:v>
+      </x:c>
+      <x:c r="C48" s="141" t="str">
+        <x:v>파일 내용 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청으로 연결한다. 각 도구의 반환값이 결과에 어떻게 사용됐는지 확인하고, 업무 목록의 변경 내용과 시점을 원자료에 대어 검증한다.</x:v>
+      </x:c>
+      <x:c r="D48" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="92" customHeight="1">
+      <x:c r="A49" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B49" s="143" t="str">
+        <x:v>대화형 학습 코치를 만들고 검증하기</x:v>
+      </x:c>
+      <x:c r="C49" s="143" t="str">
+        <x:v>제공 학습 자료를 바탕으로 문항 생성→답변 입력→정답·원문 근거 피드백으로 이어지는 대화형 학습 코치를 만든다. 답변을 달리 입력해 피드백이 바뀌는지 확인하고, 피드백의 출처가 학습 자료에 있는지 대조한다.</x:v>
+      </x:c>
+      <x:c r="D49" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A50" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B50" s="139"/>
+      <x:c r="C50" s="139"/>
+      <x:c r="D50" s="139" t="n">
+        <x:f>SUM(D46:D49)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" s="1" customFormat="1" ht="26" customHeight="1">
+      <x:c r="A51" s="135"/>
+      <x:c r="B51" s="135"/>
+      <x:c r="C51" s="135"/>
+      <x:c r="D51" s="135"/>
+    </x:row>
+    <x:row r="52" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A52" s="138" t="str">
+        <x:v>07회차 | 사람 확인·명세·검증으로 결과 완성하기</x:v>
+      </x:c>
+      <x:c r="B52" s="138"/>
+      <x:c r="C52" s="138"/>
+      <x:c r="D52" s="138"/>
+    </x:row>
+    <x:row r="53" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A53" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B53" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C53" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D53" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A54" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B54" s="141" t="str">
+        <x:v>질문·승인·명세·행동 검증 이해하기</x:v>
+      </x:c>
+      <x:c r="C54" s="141" t="str">
+        <x:v>정보 확인 질문과 사람의 승인을 구분한다. 입력·출력·금지 조건·수용 기준을 명세로 표현하고, Given/When/Then으로 기대 행동을 정하는 방법을 익힌다. 새 기능의 동작과 기존 기능 보존을 함께 확인하는 이유를 이해한다.</x:v>
+      </x:c>
+      <x:c r="D54" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A55" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B55" s="143" t="str">
+        <x:v>질문과 재개·작성과 검토 흐름 구현하기</x:v>
+      </x:c>
+      <x:c r="C55" s="143" t="str">
+        <x:v>포털의 승인 대기·승인·반려 상태를 비교한다. 품질 후속 업무 요청에 필수 정보가 빠졌을 때 질문하고 답변을 받은 뒤 다시 판단하는 흐름을 만든다. 작성·검토 에이전트의 결과와 사람의 최종 승인을 구분한다.</x:v>
+      </x:c>
+      <x:c r="D55" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A56" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B56" s="141" t="str">
+        <x:v>변경 요구를 명세하고 기능 구현하기</x:v>
+      </x:c>
+      <x:c r="C56" s="141" t="str">
+        <x:v>같은 업무 요청 프로젝트에서 변경할 기능을 정하고 입력·출력·금지 조건·완료 기준을 spec.md로 작성한다. AI 코딩 도구로 변경을 구현한 뒤 기존 일반 요청과 변경 요청의 출력을 비교한다.</x:v>
+      </x:c>
+      <x:c r="D56" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A57" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B57" s="143" t="str">
+        <x:v>행동을 검증하고 인수인계 결과 만들기</x:v>
+      </x:c>
+      <x:c r="C57" s="143" t="str">
+        <x:v>정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성해 실제 출력과 비교한다. 제공 센서·정비·부품 자료를 연결해 완료·미완료·다음 조치·근거 시각을 담은 인수인계 결과를 만들고 원자료와 대조한다.</x:v>
+      </x:c>
+      <x:c r="D57" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="28" customHeight="1">
+      <x:c r="A58" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B58" s="139"/>
+      <x:c r="C58" s="139"/>
+      <x:c r="D58" s="139" t="n">
+        <x:f>SUM(D54:D57)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" s="1" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A59" s="135"/>
+      <x:c r="B59" s="135"/>
+      <x:c r="C59" s="135"/>
+      <x:c r="D59" s="135"/>
+    </x:row>
+    <x:row r="60" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A60" s="138" t="str">
+        <x:v>08회차 | 설비 대응 프로세스를 설계하고 연결하기</x:v>
+      </x:c>
+      <x:c r="B60" s="138"/>
+      <x:c r="C60" s="138"/>
+      <x:c r="D60" s="138"/>
+    </x:row>
+    <x:row r="61" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A61" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B61" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C61" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D61" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A62" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B62" s="141" t="str">
+        <x:v>BPMN 역할·분기·지연·실행 연결 이해하기</x:v>
+      </x:c>
+      <x:c r="C62" s="141" t="str">
+        <x:v>시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
+      </x:c>
+      <x:c r="D62" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A63" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B63" s="143" t="str">
+        <x:v>기본 승인 흐름에서 설비 대응 흐름 만들기</x:v>
+      </x:c>
+      <x:c r="C63" s="143" t="str">
+        <x:v>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</x:v>
+      </x:c>
+      <x:c r="D63" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A64" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B64" s="141" t="str">
+        <x:v>승인·거절·지연 경로 완성하기</x:v>
+      </x:c>
+      <x:c r="C64" s="141" t="str">
+        <x:v>승인·거절 분기와 각각의 종료 경로를 연결한다. 거절 경로에서 설비 명령으로 진행되지 않는지 확인하고, 승인 작업을 취소하지 않는 지연 알림 Timer를 추가한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검한다.</x:v>
+      </x:c>
+      <x:c r="D64" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A65" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B65" s="143" t="str">
+        <x:v>BPMN과 등록된 실행 연결 비교하기</x:v>
+      </x:c>
+      <x:c r="C65" s="143" t="str">
+        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</x:v>
+      </x:c>
+      <x:c r="D65" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A66" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B66" s="139"/>
+      <x:c r="C66" s="139"/>
+      <x:c r="D66" s="139" t="n">
+        <x:f>SUM(D62:D65)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A67" s="135"/>
+      <x:c r="B67" s="135"/>
+      <x:c r="C67" s="135"/>
+      <x:c r="D67" s="135"/>
+    </x:row>
+    <x:row r="68" ht="38" customHeight="1">
+      <x:c r="A68" s="138" t="str">
+        <x:v>09회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</x:v>
+      </x:c>
+      <x:c r="B68" s="138"/>
+      <x:c r="C68" s="138"/>
+      <x:c r="D68" s="138"/>
+    </x:row>
+    <x:row r="69" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A69" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B69" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C69" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D69" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A70" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B70" s="141" t="str">
+        <x:v>실행 상태를 이해하고 정상·예외 경로 확인하기</x:v>
+      </x:c>
+      <x:c r="C70" s="141" t="str">
+        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+      </x:c>
+      <x:c r="D70" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A71" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B71" s="143" t="str">
+        <x:v>BPMN을 보완하고 교대 인수인계 요구 정하기</x:v>
+      </x:c>
+      <x:c r="C71" s="143" t="str">
+        <x:v>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</x:v>
+      </x:c>
+      <x:c r="D71" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" s="1" customFormat="1" ht="98" customHeight="1">
+      <x:c r="A72" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B72" s="141" t="str">
+        <x:v>보충 지식과 인수인계 에이전트 구성하기</x:v>
+      </x:c>
+      <x:c r="C72" s="141" t="str">
+        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
+      </x:c>
+      <x:c r="D72" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A73" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B73" s="143" t="str">
+        <x:v>제공 인수인계 BPMN의 에이전트 배정·등록하기</x:v>
+      </x:c>
+      <x:c r="C73" s="143" t="str">
+        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
+      </x:c>
+      <x:c r="D73" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A74" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B74" s="139"/>
+      <x:c r="C74" s="139"/>
+      <x:c r="D74" s="139" t="n">
+        <x:f>SUM(D70:D73)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A75" s="135"/>
+      <x:c r="B75" s="135"/>
+      <x:c r="C75" s="135"/>
+      <x:c r="D75" s="135"/>
+    </x:row>
+    <x:row r="76" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A76" s="138" t="str">
+        <x:v>10회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</x:v>
+      </x:c>
+      <x:c r="B76" s="138"/>
+      <x:c r="C76" s="138"/>
+      <x:c r="D76" s="138"/>
+    </x:row>
+    <x:row r="77" ht="28" customHeight="1">
+      <x:c r="A77" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B77" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C77" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D77" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A78" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B78" s="141" t="str">
+        <x:v>업무별 시작 조건을 비교하고 정비 흐름 설계하기</x:v>
+      </x:c>
+      <x:c r="C78" s="141" t="str">
+        <x:v>냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
+      </x:c>
+      <x:c r="D78" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A79" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B79" s="143" t="str">
+        <x:v>등록된 정비 흐름을 실행하고 결과 검증하기</x:v>
+      </x:c>
+      <x:c r="C79" s="143" t="str">
+        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
+      </x:c>
+      <x:c r="D79" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A80" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B80" s="141" t="str">
+        <x:v>구매 흐름을 설계하고 실행 검증하기</x:v>
+      </x:c>
+      <x:c r="C80" s="141" t="str">
+        <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
+      </x:c>
+      <x:c r="D80" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A81" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B81" s="143" t="str">
+        <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
+      </x:c>
+      <x:c r="C81" s="143" t="str">
+        <x:v>교대 인수인계 흐름에 설비·교대 정보를 입력하고 정상·기록 불일치·정보 누락 사례를 실행한다. 인계자 검토, 인수자의 보완 요청과 확인을 거쳐 인계 내용·근거·완료 기록을 대조한다(30분). ProcessGPT 시연을 보며 자신이 만든 지식·에이전트·업무 흐름이 제품의 작업함과 실행 기록에 어떻게 연결되는지 비교한다(20분).</x:v>
+      </x:c>
+      <x:c r="D81" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A82" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B82" s="139"/>
+      <x:c r="C82" s="139"/>
+      <x:c r="D82" s="139" t="n">
+        <x:f>SUM(D78:D81)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A83" s="135"/>
+      <x:c r="B83" s="135"/>
+      <x:c r="C83" s="135"/>
+      <x:c r="D83" s="135"/>
+    </x:row>
+    <x:row r="84" s="1" customFormat="1" ht="36" customHeight="1">
+      <x:c r="A84" s="135" t="str">
+        <x:v>전체 수업 시간(분)</x:v>
+      </x:c>
+      <x:c r="B84" s="135"/>
+      <x:c r="C84" s="135"/>
+      <x:c r="D84" s="135" t="n">
+        <x:f>SUM(D10,D18,D26,D34,D42,D50,D58,D66,D74,D82)</x:f>
         <x:v>2000</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A3"/>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3"/>
-    </x:row>
-    <x:row r="4" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A4" s="43" t="str">
-        <x:v>01회차 | 설비 정보를 관계와 모델로 표현하기</x:v>
-      </x:c>
-      <x:c r="B4"/>
-      <x:c r="C4"/>
-      <x:c r="D4" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A5" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B5" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C5" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D5" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A6" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B6" s="126" t="str">
-        <x:v>설비·레이어·온톨로지·식별자의 연결</x:v>
-      </x:c>
-      <x:c r="C6" s="127" t="str">
-        <x:v>설비·레이어·온톨로지·식별자의 연결을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 각 과정 온라인 1 + 2의 모델 기초. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D6" s="128" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A7" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B7" s="130" t="str">
-        <x:v>ARROWS에서 설비·원인·조치 관계 작성</x:v>
-      </x:c>
-      <x:c r="C7" s="131" t="str">
-        <x:v>쿨러·센서·부품·고장·조치를 연결하고 관계 방향을 문장으로 확인한 뒤 JSON을 저장한다.</x:v>
-      </x:c>
-      <x:c r="D7" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A8" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B8" s="130" t="str">
-        <x:v>제공 자료로 최소 스키마·인스턴스 작성</x:v>
-      </x:c>
-      <x:c r="C8" s="131" t="str">
-        <x:v>제공 목록과 관계도를 대조해 고유 ID·클래스·속성을 갖춘 최소 schema.json과 인스턴스를 만든다.</x:v>
-      </x:c>
-      <x:c r="D8" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A9" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B9" s="130" t="str">
-        <x:v>제공 절차로 랩 그래프 적재·질문 결과 확인</x:v>
-      </x:c>
-      <x:c r="C9" s="131" t="str">
-        <x:v>제공 적재 절차를 별도 랩 DB에서 수행하고 질문별 조회 결과를 원자료와 비교한다. Cypher 문법 수업은 별도로 하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D9" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A10" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B10" s="130" t="str">
-        <x:v>포털 기준 지도와 필요한 관계 비교</x:v>
-      </x:c>
-      <x:c r="C10" s="131" t="str">
-        <x:v>포털의 공통 기준 지도에서 필요한 연결만 확인하고 개인 모델과 비교한다. 자동 동기화는 전제하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D10" s="132" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A11" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B11" s="130" t="str">
-        <x:v>본인 모델의 누락 수정·질문별 결과 완성</x:v>
-      </x:c>
-      <x:c r="C11" s="131" t="str">
-        <x:v>누락된 관계·속성·방향을 보완하고 질문별 답을 다시 확인한다.</x:v>
-      </x:c>
-      <x:c r="D11" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A12" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B12" s="130" t="str">
-        <x:v>개별 진행 차이 대응·저장·다음 입력 준비</x:v>
-      </x:c>
-      <x:c r="C12" s="131" t="str">
-        <x:v>막힌 부분을 해결하고 관계도·모델·질의 결과를 저장해 다음 회차 입력으로 준비한다.</x:v>
-      </x:c>
-      <x:c r="D12" s="132" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A13" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13" s="49" t="n">
-        <x:f>SUM(D6:D12)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A14" s="66" t="str">
-        <x:v>완료 결과: 두 반 동일: 관계도, 최소 모델, 질문별 확인 결과. Neo4j 문법 수업은 별도로 편성하지 않는다. 온라인 2 전체 설계를 1회차에 모두 끝내지 않는다.</x:v>
-      </x:c>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14" s="49"/>
-    </x:row>
-    <x:row r="15" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-    </x:row>
-    <x:row r="16" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A16" s="43" t="str">
-        <x:v>02회차 | 설비 모델을 완성하고 작업 절차 연결하기</x:v>
-      </x:c>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A17" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C17" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A18" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B18" s="126" t="str">
-        <x:v>식별자·중복 없는 적재·SOP 연결</x:v>
-      </x:c>
-      <x:c r="C18" s="127" t="str">
-        <x:v>식별자·중복 없는 적재·SOP 연결을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인2 + 온라인3 SOP. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D18" s="128" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A19" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B19" s="130" t="str">
-        <x:v>앞 회차 모델의 제약 보완</x:v>
-      </x:c>
-      <x:c r="C19" s="131" t="str">
-        <x:v>앞 모델의 식별자·자료형·필수값·관계 끝점을 보완한다.</x:v>
-      </x:c>
-      <x:c r="D19" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A20" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B20" s="130" t="str">
-        <x:v>자기 모델 적재·조회·반복 적용 확인</x:v>
-      </x:c>
-      <x:c r="C20" s="131" t="str">
-        <x:v>자기 모델을 적재하고 원자료 질문의 답과 반복 적재 시 중복 여부를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D20" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A21" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B21" s="130" t="str">
-        <x:v>새 설비·공용 부품 적용</x:v>
-      </x:c>
-      <x:c r="C21" s="131" t="str">
-        <x:v>새 설비와 공용 부품을 추가하고 기존 관계가 보존되는지 조회한다.</x:v>
-      </x:c>
-      <x:c r="D21" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A22" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B22" s="130" t="str">
-        <x:v>SOP 구조화·모델 연결</x:v>
-      </x:c>
-      <x:c r="C22" s="131" t="str">
-        <x:v>제공 SOP의 전제·금지·완료 조건을 구조화해 고장·조치와 연결한다.</x:v>
-      </x:c>
-      <x:c r="D22" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A23" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B23" s="130" t="str">
-        <x:v>개별 수정·결과 보존</x:v>
-      </x:c>
-      <x:c r="C23" s="131" t="str">
-        <x:v>오류를 수정하고 스키마·인스턴스·질의·SOP를 저장한다.</x:v>
-      </x:c>
-      <x:c r="D23" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A24" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24" s="49" t="n">
-        <x:f>SUM(D18:D23)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A25" s="66" t="str">
-        <x:v>완료 결과: 완성 모델과 SOP. 앞 회차에서 만든 파일을 이어 쓰고 설계를 처음부터 반복하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25" s="49"/>
-    </x:row>
-    <x:row r="26" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-    </x:row>
-    <x:row r="27" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A27" s="43" t="str">
-        <x:v>03회차 | 안전한 조치와 성과 비교 기능 만들기</x:v>
-      </x:c>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A28" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B28" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C28" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D28" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A29" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B29" s="126" t="str">
-        <x:v>결정표·경계·허용 후보·성과 비교</x:v>
-      </x:c>
-      <x:c r="C29" s="127" t="str">
-        <x:v>결정표·경계·허용 후보·성과 비교을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인3. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D29" s="128" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A30" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B30" s="130" t="str">
-        <x:v>포털 What-if 핵심 비교</x:v>
-      </x:c>
-      <x:c r="C30" s="131" t="str">
-        <x:v>포털의 제공 사례에서 조건 전후의 제외·순위 차이를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D30" s="132" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A31" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B31" s="130" t="str">
-        <x:v>SOP에서 결정표 작성</x:v>
-      </x:c>
-      <x:c r="C31" s="131" t="str">
-        <x:v>SOP의 조건·단위·경계·출처로 결정표를 작성한다.</x:v>
-      </x:c>
-      <x:c r="D31" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A32" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B32" s="130" t="str">
-        <x:v>판정 기능 구현</x:v>
-      </x:c>
-      <x:c r="C32" s="131" t="str">
-        <x:v>조건표로 허용·제외와 사유를 반환하는 코드를 구현한다.</x:v>
-      </x:c>
-      <x:c r="D32" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A33" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B33" s="130" t="str">
-        <x:v>허용 후보의 비용·성과 비교</x:v>
-      </x:c>
-      <x:c r="C33" s="131" t="str">
-        <x:v>허용 후보만 비용·생산·품질·에너지 기준으로 비교한다.</x:v>
-      </x:c>
-      <x:c r="D33" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A34" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B34" s="130" t="str">
-        <x:v>경계·금지·누락 확인 및 개별 수정</x:v>
-      </x:c>
-      <x:c r="C34" s="131" t="str">
-        <x:v>경계·금지·누락 입력을 확인하고 추천과 실행 승인을 구별해 결과를 저장한다.</x:v>
-      </x:c>
-      <x:c r="D34" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A35" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35" s="49" t="n">
-        <x:f>SUM(D29:D34)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A36" s="66" t="str">
-        <x:v>완료 결과: 조건표·판정 코드·근거 있는 비교 결과. 포털 관찰은 짧게, 실제 구현을 중심으로 한다.</x:v>
-      </x:c>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36" s="49"/>
-    </x:row>
-    <x:row r="37" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-    </x:row>
-    <x:row r="38" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A38" s="43" t="str">
-        <x:v>04회차 | 문서를 지식으로 추출하고 검토하기</x:v>
-      </x:c>
-      <x:c r="B38"/>
-      <x:c r="C38"/>
-      <x:c r="D38" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A39" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B39" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C39" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D39" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="65" customHeight="1">
-      <x:c r="A40" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B40" s="126" t="str">
-        <x:v>원문·추출 후보·승인 지식과 출처</x:v>
-      </x:c>
-      <x:c r="C40" s="127" t="str">
-        <x:v>원문·추출 후보·승인 지식과 출처을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인4. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D40" s="128" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A41" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B41" s="130" t="str">
-        <x:v>포털 등록·추출·검토 흐름 경험</x:v>
-      </x:c>
-      <x:c r="C41" s="131" t="str">
-        <x:v>공통 포털에서 문서를 등록하고 추출 후보를 원문과 대조한다.</x:v>
-      </x:c>
-      <x:c r="D41" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A42" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B42" s="130" t="str">
-        <x:v>VS Code 문서 추출 기능 제작</x:v>
-      </x:c>
-      <x:c r="C42" s="131" t="str">
-        <x:v>표·절차·단위·금지 조건과 출처를 구조화해 추출하는 로컬 기능을 만든다.</x:v>
-      </x:c>
-      <x:c r="D42" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A43" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B43" s="130" t="str">
-        <x:v>원문 대조·수정·채택</x:v>
-      </x:c>
-      <x:c r="C43" s="131" t="str">
-        <x:v>추출 후보를 원문과 비교하고 수정·채택한다.</x:v>
-      </x:c>
-      <x:c r="D43" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A44" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B44" s="130" t="str">
-        <x:v>그래프 반영·출처 조회</x:v>
-      </x:c>
-      <x:c r="C44" s="131" t="str">
-        <x:v>채택한 지식만 기존 랩 그래프에 반영하고 원문 출처를 조회한다.</x:v>
-      </x:c>
-      <x:c r="D44" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A45" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B45" s="130" t="str">
-        <x:v>제공된 다른 문서에 적용·결과 확인</x:v>
-      </x:c>
-      <x:c r="C45" s="131" t="str">
-        <x:v>제공된 다른 문서에 기능을 적용하고 결과를 원문과 확인한다.</x:v>
-      </x:c>
-      <x:c r="D45" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A46" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B46" s="130" t="str">
-        <x:v>개별 오류 해결</x:v>
-      </x:c>
-      <x:c r="C46" s="131" t="str">
-        <x:v>적재·추출 오류를 수정하고 검토 결과를 저장한다.</x:v>
-      </x:c>
-      <x:c r="D46" s="132" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A47" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B47"/>
-      <x:c r="C47"/>
-      <x:c r="D47" s="49" t="n">
-        <x:f>SUM(D40:D46)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A48" s="66" t="str">
-        <x:v>완료 결과: 검토된 지식과 출처. 반복 기록 양식을 늘리지 않고 결과에서 원문을 확인한다.</x:v>
-      </x:c>
-      <x:c r="B48"/>
-      <x:c r="C48"/>
-      <x:c r="D48" s="49"/>
-    </x:row>
-    <x:row r="49" ht="12" customHeight="1">
-      <x:c r="A49"/>
-      <x:c r="B49"/>
-      <x:c r="C49"/>
-      <x:c r="D49"/>
-    </x:row>
-    <x:row r="50" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A50" s="43" t="str">
-        <x:v>05회차 | 서로 다른 일을 하는 에이전트 만들기</x:v>
-      </x:c>
-      <x:c r="B50"/>
-      <x:c r="C50"/>
-      <x:c r="D50" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A51" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B51" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C51" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D51" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A52" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B52" s="126" t="str">
-        <x:v>근거·도구·반복 실행·종료 조건</x:v>
-      </x:c>
-      <x:c r="C52" s="127" t="str">
-        <x:v>근거·도구·반복 실행·종료 조건을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인5. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D52" s="128" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A53" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B53" s="130" t="str">
-        <x:v>포털 에이전트 구성 확인</x:v>
-      </x:c>
-      <x:c r="C53" s="131" t="str">
-        <x:v>포털의 공통 에이전트 구성과 도구·근거를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D53" s="132" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A54" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B54" s="130" t="str">
-        <x:v>원인 후보·점검 순서 에이전트</x:v>
-      </x:c>
-      <x:c r="C54" s="131" t="str">
-        <x:v>설비 지식과 센서 증거로 원인 후보·추가 점검을 출력한다.</x:v>
-      </x:c>
-      <x:c r="D54" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A55" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B55" s="130" t="str">
-        <x:v>품질 접수 후속 업무 에이전트</x:v>
-      </x:c>
-      <x:c r="C55" s="131" t="str">
-        <x:v>불량 접수와 기준으로 유형·추가 정보·담당 업무·대응 초안을 만든다. 이후 명세 랩에서 이 프로젝트를 이어 쓴다.</x:v>
-      </x:c>
-      <x:c r="D55" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A56" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B56" s="130" t="str">
-        <x:v>센서 시계열 분석·시각화</x:v>
-      </x:c>
-      <x:c r="C56" s="131" t="str">
-        <x:v>제공 센서 CSV에서 변화·이상 구간을 분석하고 시각화한다.</x:v>
-      </x:c>
-      <x:c r="D56" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A57" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B57" s="130" t="str">
-        <x:v>세 결과 확인·개별 수정·저장</x:v>
-      </x:c>
-      <x:c r="C57" s="131" t="str">
-        <x:v>세 결과를 각각 자료와 대조하고 미확인을 표시해 저장한다.</x:v>
-      </x:c>
-      <x:c r="D57" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="28" customHeight="1">
-      <x:c r="A58" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B58"/>
-      <x:c r="C58"/>
-      <x:c r="D58" s="49" t="n">
-        <x:f>SUM(D52:D57)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A59" s="66" t="str">
-        <x:v>완료 결과: 원인 점검·품질 대응·시계열 그림의 서로 다른 결과. 같은 사례를 조건만 바꾸며 세 번 반복하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B59"/>
-      <x:c r="C59"/>
-      <x:c r="D59" s="49"/>
-    </x:row>
-    <x:row r="60" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A60"/>
-      <x:c r="B60"/>
-      <x:c r="C60"/>
-      <x:c r="D60"/>
-    </x:row>
-    <x:row r="61" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A61" s="43" t="str">
-        <x:v>06회차 | 스킬과 MCP로 반복 작업 처리하기</x:v>
-      </x:c>
-      <x:c r="B61"/>
-      <x:c r="C61"/>
-      <x:c r="D61" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A62" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B62" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C62" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D62" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A63" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B63" s="126" t="str">
-        <x:v>스킬과 도구의 역할·입출력·접근 범위</x:v>
-      </x:c>
-      <x:c r="C63" s="127" t="str">
-        <x:v>스킬과 도구의 역할·입출력·접근 범위을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인6. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D63" s="128" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A64" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B64" s="130" t="str">
-        <x:v>준비된 MCP 연결·호출 확인</x:v>
-      </x:c>
-      <x:c r="C64" s="131" t="str">
-        <x:v>포털 읽기 도구와 준비된 파일·Git·시간 MCP의 연결·입력·반환값을 확인한다.</x:v>
-      </x:c>
-      <x:c r="D64" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A65" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B65" s="130" t="str">
-        <x:v>회의록 업무 목록 스킬</x:v>
-      </x:c>
-      <x:c r="C65" s="131" t="str">
-        <x:v>회의록에서 결정·담당·기한·출처를 추출하는 SKILL.md를 만든다.</x:v>
-      </x:c>
-      <x:c r="D65" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A66" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B66" s="130" t="str">
-        <x:v>파일·Git·시간 도구 조합</x:v>
-      </x:c>
-      <x:c r="C66" s="131" t="str">
-        <x:v>파일 내용·변경 이력·시간을 연결해 작업 결과를 저장한다.</x:v>
-      </x:c>
-      <x:c r="D66" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A67" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B67" s="130" t="str">
-        <x:v>제공 학습 자료로 대화형 학습 코치</x:v>
-      </x:c>
-      <x:c r="C67" s="131" t="str">
-        <x:v>제공 학습 자료로 질문·학생 입력·원문 근거 피드백의 대화형 기능을 만든다.</x:v>
-      </x:c>
-      <x:c r="D67" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="60" customHeight="1">
-      <x:c r="A68" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B68" s="130" t="str">
-        <x:v>개별 연결 오류·결과 확인</x:v>
-      </x:c>
-      <x:c r="C68" s="131" t="str">
-        <x:v>연결 오류와 결과의 출처를 확인하고 재사용할 파일을 보존한다.</x:v>
-      </x:c>
-      <x:c r="D68" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A69" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B69"/>
-      <x:c r="C69"/>
-      <x:c r="D69" s="49" t="n">
-        <x:f>SUM(D63:D68)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A70" s="66" t="str">
-        <x:v>완료 결과: 업무 목록·도구 조합 결과·학습 코치. 포털 MCP 확인은 연결 단계 안에서 공통으로 처리한다.</x:v>
-      </x:c>
-      <x:c r="B70"/>
-      <x:c r="C70"/>
-      <x:c r="D70" s="49"/>
-    </x:row>
-    <x:row r="71" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A71"/>
-      <x:c r="B71"/>
-      <x:c r="C71"/>
-      <x:c r="D71"/>
-    </x:row>
-    <x:row r="72" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A72" s="43" t="str">
-        <x:v>07회차 | 사람 확인·명세·검증으로 결과 완성하기</x:v>
-      </x:c>
-      <x:c r="B72"/>
-      <x:c r="C72"/>
-      <x:c r="D72" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A73" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B73" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C73" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D73" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A74" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B74" s="126" t="str">
-        <x:v>질문과 승인·명세·행동 검증</x:v>
-      </x:c>
-      <x:c r="C74" s="127" t="str">
-        <x:v>질문과 승인·명세·행동 검증을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인7 + 8. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D74" s="128" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A75" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B75" s="130" t="str">
-        <x:v>공통 포털 승인 상태 확인</x:v>
-      </x:c>
-      <x:c r="C75" s="131" t="str">
-        <x:v>포털의 공통 승인 대기·승인·반려 상태를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D75" s="132" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A76" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B76" s="130" t="str">
-        <x:v>기존 요청에 질문·재개 구현</x:v>
-      </x:c>
-      <x:c r="C76" s="131" t="str">
-        <x:v>5회차 후속 업무 요청 프로젝트에 필수 정보 누락 시 질문·추가 답변·재개를 구현한다.</x:v>
-      </x:c>
-      <x:c r="D76" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="60" customHeight="1">
-      <x:c r="A77" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B77" s="130" t="str">
-        <x:v>AI 작성·검토 역할 분담</x:v>
-      </x:c>
-      <x:c r="C77" s="131" t="str">
-        <x:v>AI 작성·검토 역할의 결과를 비교하고 사람의 승인과 구별한다.</x:v>
-      </x:c>
-      <x:c r="D77" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A78" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B78" s="130" t="str">
-        <x:v>요구 변경 명세·구현</x:v>
-      </x:c>
-      <x:c r="C78" s="131" t="str">
-        <x:v>같은 프로젝트의 변경 요구·입출력·수용 기준을 spec.md에 적어 구현한다.</x:v>
-      </x:c>
-      <x:c r="D78" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A79" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B79" s="130" t="str">
-        <x:v>BDD·회귀 검증</x:v>
-      </x:c>
-      <x:c r="C79" s="131" t="str">
-        <x:v>기대 결과를 Given/When/Then으로 정하고 변경 및 기존 기능을 검증한다.</x:v>
-      </x:c>
-      <x:c r="D79" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A80" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B80" s="130" t="str">
-        <x:v>제공 다중 출처로 인수인계 결과 생성</x:v>
-      </x:c>
-      <x:c r="C80" s="131" t="str">
-        <x:v>제공된 센서·정비·부품 자료에서 완료·미완료·다음 조치·근거 시각을 담은 인수인계 결과를 생성한다.</x:v>
-      </x:c>
-      <x:c r="D80" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A81" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B81"/>
-      <x:c r="C81"/>
-      <x:c r="D81" s="49" t="n">
-        <x:f>SUM(D74:D80)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A82" s="66" t="str">
-        <x:v>완료 결과: 같은 요청 프로젝트로 명세·검증을 이어 쓴다. 인수인계는 제공 자료 기반 생성 범위이며 새 DB나 플랫폼 구축이 아니다.</x:v>
-      </x:c>
-      <x:c r="B82"/>
-      <x:c r="C82"/>
-      <x:c r="D82" s="49"/>
-    </x:row>
-    <x:row r="83" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A83"/>
-      <x:c r="B83"/>
-      <x:c r="C83"/>
-      <x:c r="D83"/>
-    </x:row>
-    <x:row r="84" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A84" s="43" t="str">
-        <x:v>08회차 | 설비 대응 프로세스를 설계하고 연결하기</x:v>
-      </x:c>
-      <x:c r="B84"/>
-      <x:c r="C84"/>
-      <x:c r="D84" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
     <x:row r="85" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A85" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B85" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C85" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D85" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="65" customHeight="1">
-      <x:c r="A86" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B86" s="126" t="str">
-        <x:v>작업·역할·분기·비중단 지연과 실행 매핑</x:v>
-      </x:c>
-      <x:c r="C86" s="127" t="str">
-        <x:v>작업·역할·분기·비중단 지연과 실행 매핑을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9 / 실전 온라인6. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D86" s="128" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A87" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B87" s="130" t="str">
-        <x:v>bpmn.io 기본 승인 흐름 직접 작성</x:v>
-      </x:c>
-      <x:c r="C87" s="131" t="str">
-        <x:v>bpmn.io에서 시작·작업·승인·종료를 배치하고 파일로 저장한다.</x:v>
-      </x:c>
-      <x:c r="D87" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A88" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B88" s="130" t="str">
-        <x:v>설비 대응 흐름 작성</x:v>
-      </x:c>
-      <x:c r="C88" s="131" t="str">
-        <x:v>공통 냉각 대응 시나리오의 역할·작업·흐름을 작성한다.</x:v>
-      </x:c>
-      <x:c r="D88" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A89" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B89" s="130" t="str">
-        <x:v>승인·거절·지연 경로 완성</x:v>
-      </x:c>
-      <x:c r="C89" s="131" t="str">
-        <x:v>승인·거절 분기와 비중단 지연 경로를 완성한다.</x:v>
-      </x:c>
-      <x:c r="D89" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A90" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B90" s="130" t="str">
-        <x:v>기존 부품으로 매핑·검사·배포</x:v>
-      </x:c>
-      <x:c r="C90" s="131" t="str">
-        <x:v>기존 에이전트·역할·작업 부품에 매핑하고 검사·등록·배포한다. 공용 환경의 배포 순서를 따른다.</x:v>
-      </x:c>
-      <x:c r="D90" s="132" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A91" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B91"/>
-      <x:c r="C91"/>
-      <x:c r="D91" s="49" t="n">
-        <x:f>SUM(D86:D90)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A92" s="66" t="str">
-        <x:v>완료 결과: 두 반 공통: 기존 냉각 대응 시나리오의 BPMN·매핑·배포 기록. 임의 작업 부품이나 포털 기능을 추가하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B92"/>
-      <x:c r="C92"/>
-      <x:c r="D92" s="49"/>
-    </x:row>
-    <x:row r="93" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A93"/>
-      <x:c r="B93"/>
-      <x:c r="C93"/>
-      <x:c r="D93"/>
-    </x:row>
-    <x:row r="94" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A94" s="43" t="str">
-        <x:v>09회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</x:v>
-      </x:c>
-      <x:c r="B94"/>
-      <x:c r="C94"/>
-      <x:c r="D94" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A95" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B95" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C95" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D95" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="65" customHeight="1">
-      <x:c r="A96" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B96" s="126" t="str">
-        <x:v>정의·실행 상태·오류 위치와 복구</x:v>
-      </x:c>
-      <x:c r="C96" s="127" t="str">
-        <x:v>정의·실행 상태·오류 위치와 복구를 오늘 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9·11 / 실전 온라인6·8. 교대 인수인계의 시작 폼·역할·완료 조건을 구분한다.</x:v>
-      </x:c>
-      <x:c r="D96" s="128" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A97" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B97" s="130" t="str">
-        <x:v>배포된 공통 흐름 정상 실행</x:v>
-      </x:c>
-      <x:c r="C97" s="131" t="str">
-        <x:v>배포된 공통 흐름을 실행하고 처리 이력을 확인한다.</x:v>
-      </x:c>
-      <x:c r="D97" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A98" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B98" s="130" t="str">
-        <x:v>거절·지연·역할 제한 확인</x:v>
-      </x:c>
-      <x:c r="C98" s="131" t="str">
-        <x:v>승인 거절·지연·역할 제한을 공통 사례로 확인한다.</x:v>
-      </x:c>
-      <x:c r="D98" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A99" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B99" s="130" t="str">
-        <x:v>실제 오류 또는 제공 오류 사례 수정·재배포</x:v>
-      </x:c>
-      <x:c r="C99" s="131" t="str">
-        <x:v>실제 또는 제공된 오류 사례에서 잘못된 설정을 찾아 수정·재배포한다.</x:v>
-      </x:c>
-      <x:c r="D99" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="68" customHeight="1">
-      <x:c r="A100" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B100" s="130" t="str">
-        <x:v>교대 인수인계의 입력·근거·완료 조건 정하기</x:v>
-      </x:c>
-      <x:c r="C100" s="131" t="str">
-        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
-      </x:c>
-      <x:c r="D100" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A101" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B101" s="130" t="str">
-        <x:v>보충 매뉴얼 적재와 인수인계 에이전트 구성</x:v>
-      </x:c>
-      <x:c r="C101" s="131" t="str">
-        <x:v>제공 보충 매뉴얼의 추출 결과를 원문 대조하여 기존 제조 지식에 추가한다. 허용된 설비·정비·ERP 조회를 사용해 인계안을 만들고, 기록 불일치와 미확인 사항을 남긴다. 같은 조건의 추출 재사용은 표시한다.</x:v>
-      </x:c>
-      <x:c r="D101" s="132" t="n">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="60" customHeight="1">
-      <x:c r="A102" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B102" s="130" t="str">
-        <x:v>교대 인수인계 BPMN 설계·매핑과 중간 결과 저장</x:v>
-      </x:c>
-      <x:c r="C102" s="131" t="str">
-        <x:v>bpmn.io에서 조회·인계안·인계자 검토·인수자 확인·보완·완료 흐름을 작성한다. 포털의 별도 정의에 시작 폼·에이전트·역할을 연결하고 판본을 저장한다. 실제 실행은 다음 회차로 이어간다.</x:v>
-      </x:c>
-      <x:c r="D102" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A103" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B103"/>
-      <x:c r="C103"/>
-      <x:c r="D103" s="49" t="n">
-        <x:f>SUM(D96:D102)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" ht="58" customHeight="1">
-      <x:c r="A104" s="66" t="str">
-        <x:v>완료 결과: 추가 지식의 검토·적재 기록, 인수인계 에이전트·스킬, 별도 BPMN·매핑·시작 폼. 기존 ABC 정의는 보존한다. 임의 코드 자동 연결이나 임의 외부 도구는 요구하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B104"/>
-      <x:c r="C104"/>
-      <x:c r="D104" s="49"/>
-    </x:row>
-    <x:row r="105" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A105"/>
-    </x:row>
-    <x:row r="106" ht="36" customHeight="1">
-      <x:c r="A106" s="43" t="str">
-        <x:v>10회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</x:v>
-      </x:c>
-      <x:c r="B106"/>
-      <x:c r="C106"/>
-      <x:c r="D106" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="26" customHeight="1">
-      <x:c r="A107" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B107" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C107" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D107" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="65" customHeight="1">
-      <x:c r="A108" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B108" s="126" t="str">
-        <x:v>냉각 대응과 정비·구매의 시작·완료 조건 차이</x:v>
-      </x:c>
-      <x:c r="C108" s="127" t="str">
-        <x:v>냉각 대응과 정비·구매의 시작·완료 조건 차이을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 통합 온라인10 + 11 / 실전 온라인7 + 8. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D108" s="128" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="60" customHeight="1">
-      <x:c r="A109" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B109" s="130" t="str">
-        <x:v>기존 승인 구조를 정비 흐름으로 작성</x:v>
-      </x:c>
-      <x:c r="C109" s="131" t="str">
-        <x:v>기존 승인 패턴으로 정비 도래·계획·승인·오더·공지 흐름을 작성한다.</x:v>
-      </x:c>
-      <x:c r="D109" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="60" customHeight="1">
-      <x:c r="A110" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B110" s="130" t="str">
-        <x:v>정비 흐름 연결·실행</x:v>
-      </x:c>
-      <x:c r="C110" s="131" t="str">
-        <x:v>정비 흐름을 연결·실행하고 정상·반려 결과를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D110" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="60" customHeight="1">
-      <x:c r="A111" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B111" s="130" t="str">
-        <x:v>구매 흐름 작성</x:v>
-      </x:c>
-      <x:c r="C111" s="131" t="str">
-        <x:v>재고 부족·구매 제안·승인·발주·입고 흐름을 작성한다.</x:v>
-      </x:c>
-      <x:c r="D111" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="60" customHeight="1">
-      <x:c r="A112" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B112" s="130" t="str">
-        <x:v>구매 흐름 연결·실행</x:v>
-      </x:c>
-      <x:c r="C112" s="131" t="str">
-        <x:v>수업용 구매 흐름을 연결·실행하고 정상·반려·재고 결과를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D112" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="60" customHeight="1">
-      <x:c r="A113" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B113" s="130" t="str">
-        <x:v>교대 인수인계 흐름 실행·보완·완료 기록 확인</x:v>
-      </x:c>
-      <x:c r="C113" s="131" t="str">
-        <x:v>앞 회차의 인수인계 흐름을 설비·교대 입력으로 시작한다. 정상·기록 불일치·정보 누락 사례에서 인계자 검토와 인수자 확인 또는 보완 요청을 수행하고, 근거·판본·완료 기록을 저장한다.</x:v>
-      </x:c>
-      <x:c r="D113" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="68" customHeight="1">
-      <x:c r="A114" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B114" s="130" t="str">
-        <x:v>ProcessGPT 강사 시연: 만든 지식·에이전트·흐름을 제품 기능과 연결해 보기</x:v>
-      </x:c>
-      <x:c r="C114" s="131" t="str">
-        <x:v>준비된 ProcessGPT 화면에서 지식·에이전트·프로세스가 연결되는 모습을 강사가 시연한다. 학생 계정 설정과 별도 제품 실습은 포함하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D114" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="28" customHeight="1">
-      <x:c r="A115" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B115"/>
-      <x:c r="C115"/>
-      <x:c r="D115" s="49" t="n">
-        <x:f>SUM(D108:D114)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="58" customHeight="1">
-      <x:c r="A116" s="66" t="str">
-        <x:v>완료 결과: 정비·구매는 기존 공통 시나리오로 수행하고 교대 인수인계는 별도 정의로 실행한다. 실제 설비 제어·발주를 인계 확인과 혼동하지 않는다. ProcessGPT는 강사가 20분 시연한다. 준비·실행 시간과 완주는 별도 실측한다.</x:v>
-      </x:c>
-      <x:c r="B116"/>
-      <x:c r="C116"/>
-      <x:c r="D116" s="49"/>
-    </x:row>
-    <x:row r="117" ht="12" customHeight="1">
-      <x:c r="A117"/>
-      <x:c r="B117"/>
-      <x:c r="C117"/>
-      <x:c r="D117"/>
-    </x:row>
-    <x:row r="118" ht="28" customHeight="1">
-      <x:c r="A118" s="66" t="str">
-        <x:v>전체 수업 시간(분)</x:v>
-      </x:c>
-      <x:c r="B118"/>
-      <x:c r="C118"/>
-      <x:c r="D118" s="49" t="n">
-        <x:f>D2</x:f>
-        <x:v>2000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="28" customHeight="1">
-      <x:c r="A119" s="66" t="str">
-        <x:v>전체 휴식 시간(40분×10회)</x:v>
-      </x:c>
-      <x:c r="B119"/>
-      <x:c r="C119"/>
-      <x:c r="D119" s="49" t="n">
+      <x:c r="A85" s="135" t="str">
+        <x:v>전체 휴식 시간(분)</x:v>
+      </x:c>
+      <x:c r="B85" s="135"/>
+      <x:c r="C85" s="135"/>
+      <x:c r="D85" s="135" t="n">
         <x:f>40*10</x:f>
         <x:v>400</x:v>
       </x:c>
     </x:row>
+    <x:row r="86" ht="65" customHeight="1">
+      <x:c r="A86" s="135" t="str">
+        <x:v>전체 편성 시간(분)</x:v>
+      </x:c>
+      <x:c r="B86" s="135"/>
+      <x:c r="C86" s="135"/>
+      <x:c r="D86" s="135" t="n">
+        <x:f>SUM(D84:D85)</x:f>
+        <x:v>2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A87" s="135"/>
+      <x:c r="B87" s="135"/>
+      <x:c r="C87" s="135"/>
+      <x:c r="D87" s="135"/>
+    </x:row>
+    <x:row r="88" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A88" s="135"/>
+      <x:c r="B88" s="135"/>
+      <x:c r="C88" s="135"/>
+      <x:c r="D88" s="135"/>
+    </x:row>
+    <x:row r="89" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A89" s="135"/>
+      <x:c r="B89" s="135"/>
+      <x:c r="C89" s="135"/>
+      <x:c r="D89" s="135"/>
+    </x:row>
+    <x:row r="90" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A90" s="135"/>
+      <x:c r="B90" s="135"/>
+      <x:c r="C90" s="135"/>
+      <x:c r="D90" s="135"/>
+    </x:row>
+    <x:row r="91" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A91" s="135"/>
+      <x:c r="B91" s="135"/>
+      <x:c r="C91" s="135"/>
+      <x:c r="D91" s="135"/>
+    </x:row>
+    <x:row r="92" s="1" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A92" s="135"/>
+      <x:c r="B92" s="135"/>
+      <x:c r="C92" s="135"/>
+      <x:c r="D92" s="135"/>
+    </x:row>
+    <x:row r="93" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A93" s="135"/>
+      <x:c r="B93" s="135"/>
+      <x:c r="C93" s="135"/>
+      <x:c r="D93" s="135"/>
+    </x:row>
+    <x:row r="94" s="1" customFormat="1" ht="36" customHeight="1">
+      <x:c r="A94" s="135"/>
+      <x:c r="B94" s="135"/>
+      <x:c r="C94" s="135"/>
+      <x:c r="D94" s="135"/>
+    </x:row>
+    <x:row r="95" s="1" customFormat="1" ht="26" customHeight="1">
+      <x:c r="A95" s="135"/>
+      <x:c r="B95" s="135"/>
+      <x:c r="C95" s="135"/>
+      <x:c r="D95" s="135"/>
+    </x:row>
+    <x:row r="96" ht="65" customHeight="1">
+      <x:c r="A96" s="135"/>
+      <x:c r="B96" s="135"/>
+      <x:c r="C96" s="135"/>
+      <x:c r="D96" s="135"/>
+    </x:row>
+    <x:row r="97" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A97" s="135"/>
+      <x:c r="B97" s="135"/>
+      <x:c r="C97" s="135"/>
+      <x:c r="D97" s="135"/>
+    </x:row>
+    <x:row r="98" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A98" s="135"/>
+      <x:c r="B98" s="135"/>
+      <x:c r="C98" s="135"/>
+      <x:c r="D98" s="135"/>
+    </x:row>
+    <x:row r="99" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A99" s="135"/>
+      <x:c r="B99" s="135"/>
+      <x:c r="C99" s="135"/>
+      <x:c r="D99" s="135"/>
+    </x:row>
+    <x:row r="100" ht="68" customHeight="1">
+      <x:c r="A100" s="135"/>
+      <x:c r="B100" s="135"/>
+      <x:c r="C100" s="135"/>
+      <x:c r="D100" s="135"/>
+    </x:row>
+    <x:row r="101" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A101" s="135"/>
+      <x:c r="B101" s="135"/>
+      <x:c r="C101" s="135"/>
+      <x:c r="D101" s="135"/>
+    </x:row>
+    <x:row r="102" ht="60" customHeight="1">
+      <x:c r="A102" s="135"/>
+      <x:c r="B102" s="135"/>
+      <x:c r="C102" s="135"/>
+      <x:c r="D102" s="135"/>
+    </x:row>
+    <x:row r="103" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A103" s="135"/>
+      <x:c r="B103" s="135"/>
+      <x:c r="C103" s="135"/>
+      <x:c r="D103" s="135"/>
+    </x:row>
+    <x:row r="104" ht="58" customHeight="1">
+      <x:c r="A104" s="135"/>
+      <x:c r="B104" s="135"/>
+      <x:c r="C104" s="135"/>
+      <x:c r="D104" s="135"/>
+    </x:row>
+    <x:row r="105" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A105" s="135"/>
+      <x:c r="B105" s="135"/>
+      <x:c r="C105" s="135"/>
+      <x:c r="D105" s="135"/>
+    </x:row>
+    <x:row r="106" ht="36" customHeight="1">
+      <x:c r="A106" s="135"/>
+      <x:c r="B106" s="135"/>
+      <x:c r="C106" s="135"/>
+      <x:c r="D106" s="135"/>
+    </x:row>
+    <x:row r="107" ht="26" customHeight="1">
+      <x:c r="A107" s="135"/>
+      <x:c r="B107" s="135"/>
+      <x:c r="C107" s="135"/>
+      <x:c r="D107" s="135"/>
+    </x:row>
+    <x:row r="108" ht="65" customHeight="1">
+      <x:c r="A108" s="135"/>
+      <x:c r="B108" s="135"/>
+      <x:c r="C108" s="135"/>
+      <x:c r="D108" s="135"/>
+    </x:row>
+    <x:row r="109" ht="60" customHeight="1">
+      <x:c r="A109" s="135"/>
+      <x:c r="B109" s="135"/>
+      <x:c r="C109" s="135"/>
+      <x:c r="D109" s="135"/>
+    </x:row>
+    <x:row r="110" ht="60" customHeight="1">
+      <x:c r="A110" s="135"/>
+      <x:c r="B110" s="135"/>
+      <x:c r="C110" s="135"/>
+      <x:c r="D110" s="135"/>
+    </x:row>
+    <x:row r="111" ht="60" customHeight="1">
+      <x:c r="A111" s="135"/>
+      <x:c r="B111" s="135"/>
+      <x:c r="C111" s="135"/>
+      <x:c r="D111" s="135"/>
+    </x:row>
+    <x:row r="112" ht="60" customHeight="1">
+      <x:c r="A112" s="135"/>
+      <x:c r="B112" s="135"/>
+      <x:c r="C112" s="135"/>
+      <x:c r="D112" s="135"/>
+    </x:row>
+    <x:row r="113" ht="60" customHeight="1">
+      <x:c r="A113" s="135"/>
+      <x:c r="B113" s="135"/>
+      <x:c r="C113" s="135"/>
+      <x:c r="D113" s="135"/>
+    </x:row>
+    <x:row r="114" ht="68" customHeight="1">
+      <x:c r="A114" s="135"/>
+      <x:c r="B114" s="135"/>
+      <x:c r="C114" s="135"/>
+      <x:c r="D114" s="135"/>
+    </x:row>
+    <x:row r="115" ht="28" customHeight="1">
+      <x:c r="A115" s="135"/>
+      <x:c r="B115" s="135"/>
+      <x:c r="C115" s="135"/>
+      <x:c r="D115" s="135"/>
+    </x:row>
+    <x:row r="116" ht="58" customHeight="1">
+      <x:c r="A116" s="135"/>
+      <x:c r="B116" s="135"/>
+      <x:c r="C116" s="135"/>
+      <x:c r="D116" s="135"/>
+    </x:row>
+    <x:row r="117" ht="12" customHeight="1">
+      <x:c r="A117" s="135"/>
+      <x:c r="B117" s="135"/>
+      <x:c r="C117" s="135"/>
+      <x:c r="D117" s="135"/>
+    </x:row>
+    <x:row r="118" ht="28" customHeight="1">
+      <x:c r="A118" s="135"/>
+      <x:c r="B118" s="135"/>
+      <x:c r="C118" s="135"/>
+      <x:c r="D118" s="135"/>
+    </x:row>
+    <x:row r="119" ht="28" customHeight="1">
+      <x:c r="A119" s="135"/>
+      <x:c r="B119" s="135"/>
+      <x:c r="C119" s="135"/>
+      <x:c r="D119" s="135"/>
+    </x:row>
     <x:row r="120" ht="28" customHeight="1">
-      <x:c r="A120" s="66" t="str">
-        <x:v>전체 편성 시간(분)</x:v>
-      </x:c>
-      <x:c r="B120"/>
-      <x:c r="C120"/>
-      <x:c r="D120" s="49" t="n">
-        <x:f>SUM(D118:D119)</x:f>
-        <x:v>2400</x:v>
-      </x:c>
+      <x:c r="A120" s="135"/>
+      <x:c r="B120" s="135"/>
+      <x:c r="C120" s="135"/>
+      <x:c r="D120" s="135"/>
     </x:row>
     <x:row r="121" ht="48" customHeight="1">
-      <x:c r="A121" s="66" t="str">
-        <x:v>운영: 시간은 학생 수행의 초기 편성값이며 실측이 아니다. 온라인 배포일보다 먼저 필요한 단원은 사전 열람 자료를 제공한다. 강사는 막힌 부분을 지원한다.</x:v>
-      </x:c>
-      <x:c r="B121"/>
-      <x:c r="C121"/>
-      <x:c r="D121" s="49"/>
+      <x:c r="A121" s="135"/>
+      <x:c r="B121" s="135"/>
+      <x:c r="C121" s="135"/>
+      <x:c r="D121" s="135"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122"/>
-      <x:c r="B122"/>
-      <x:c r="C122"/>
-      <x:c r="D122"/>
+      <x:c r="A122" s="135"/>
+      <x:c r="B122" s="135"/>
+      <x:c r="C122" s="135"/>
+      <x:c r="D122" s="135"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123"/>
-      <x:c r="B123"/>
-      <x:c r="C123"/>
-      <x:c r="D123"/>
+      <x:c r="A123" s="135"/>
+      <x:c r="B123" s="135"/>
+      <x:c r="C123" s="135"/>
+      <x:c r="D123" s="135"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124"/>
-      <x:c r="B124"/>
-      <x:c r="C124"/>
-      <x:c r="D124"/>
+      <x:c r="A124" s="135"/>
+      <x:c r="B124" s="135"/>
+      <x:c r="C124" s="135"/>
+      <x:c r="D124" s="135"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125"/>
-      <x:c r="B125"/>
-      <x:c r="C125"/>
-      <x:c r="D125"/>
+      <x:c r="A125" s="135"/>
+      <x:c r="B125" s="135"/>
+      <x:c r="C125" s="135"/>
+      <x:c r="D125" s="135"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126"/>
-      <x:c r="B126"/>
-      <x:c r="C126"/>
-      <x:c r="D126"/>
+      <x:c r="A126" s="135"/>
+      <x:c r="B126" s="135"/>
+      <x:c r="C126" s="135"/>
+      <x:c r="D126" s="135"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127"/>
-      <x:c r="B127"/>
-      <x:c r="C127"/>
-      <x:c r="D127"/>
+      <x:c r="A127" s="135"/>
+      <x:c r="B127" s="135"/>
+      <x:c r="C127" s="135"/>
+      <x:c r="D127" s="135"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128"/>
-      <x:c r="B128"/>
-      <x:c r="C128"/>
-      <x:c r="D128"/>
+      <x:c r="A128" s="135"/>
+      <x:c r="B128" s="135"/>
+      <x:c r="C128" s="135"/>
+      <x:c r="D128" s="135"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129"/>
-      <x:c r="B129"/>
-      <x:c r="C129"/>
-      <x:c r="D129"/>
+      <x:c r="A129" s="135"/>
+      <x:c r="B129" s="135"/>
+      <x:c r="C129" s="135"/>
+      <x:c r="D129" s="135"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130"/>
-      <x:c r="B130"/>
-      <x:c r="C130"/>
-      <x:c r="D130"/>
+      <x:c r="A130" s="135"/>
+      <x:c r="B130" s="135"/>
+      <x:c r="C130" s="135"/>
+      <x:c r="D130" s="135"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131"/>
-      <x:c r="B131"/>
-      <x:c r="C131"/>
-      <x:c r="D131"/>
+      <x:c r="A131" s="135"/>
+      <x:c r="B131" s="135"/>
+      <x:c r="C131" s="135"/>
+      <x:c r="D131" s="135"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132"/>
-      <x:c r="B132"/>
-      <x:c r="C132"/>
-      <x:c r="D132"/>
+      <x:c r="A132" s="135"/>
+      <x:c r="B132" s="135"/>
+      <x:c r="C132" s="135"/>
+      <x:c r="D132" s="135"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133"/>
-      <x:c r="B133"/>
-      <x:c r="C133"/>
-      <x:c r="D133"/>
+      <x:c r="A133" s="135"/>
+      <x:c r="B133" s="135"/>
+      <x:c r="C133" s="135"/>
+      <x:c r="D133" s="135"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134"/>
-      <x:c r="B134"/>
-      <x:c r="C134"/>
-      <x:c r="D134"/>
+      <x:c r="A134" s="135"/>
+      <x:c r="B134" s="135"/>
+      <x:c r="C134" s="135"/>
+      <x:c r="D134" s="135"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135"/>
-      <x:c r="B135"/>
-      <x:c r="C135"/>
-      <x:c r="D135"/>
+      <x:c r="A135" s="135"/>
+      <x:c r="B135" s="135"/>
+      <x:c r="C135" s="135"/>
+      <x:c r="D135" s="135"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136"/>
-      <x:c r="B136"/>
-      <x:c r="C136"/>
-      <x:c r="D136"/>
+      <x:c r="A136" s="135"/>
+      <x:c r="B136" s="135"/>
+      <x:c r="C136" s="135"/>
+      <x:c r="D136" s="135"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137"/>
-      <x:c r="B137"/>
-      <x:c r="C137"/>
-      <x:c r="D137"/>
+      <x:c r="A137" s="135"/>
+      <x:c r="B137" s="135"/>
+      <x:c r="C137" s="135"/>
+      <x:c r="D137" s="135"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138"/>
-      <x:c r="B138"/>
-      <x:c r="C138"/>
-      <x:c r="D138"/>
+      <x:c r="A138" s="135"/>
+      <x:c r="B138" s="135"/>
+      <x:c r="C138" s="135"/>
+      <x:c r="D138" s="135"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139"/>
-      <x:c r="B139"/>
-      <x:c r="C139"/>
-      <x:c r="D139"/>
+      <x:c r="A139" s="135"/>
+      <x:c r="B139" s="135"/>
+      <x:c r="C139" s="135"/>
+      <x:c r="D139" s="135"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140"/>
-      <x:c r="B140"/>
-      <x:c r="C140"/>
-      <x:c r="D140"/>
+      <x:c r="A140" s="135"/>
+      <x:c r="B140" s="135"/>
+      <x:c r="C140" s="135"/>
+      <x:c r="D140" s="135"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141"/>
-      <x:c r="B141"/>
-      <x:c r="C141"/>
-      <x:c r="D141"/>
+      <x:c r="A141" s="135"/>
+      <x:c r="B141" s="135"/>
+      <x:c r="C141" s="135"/>
+      <x:c r="D141" s="135"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142"/>
-      <x:c r="B142"/>
-      <x:c r="C142"/>
-      <x:c r="D142"/>
+      <x:c r="A142" s="135"/>
+      <x:c r="B142" s="135"/>
+      <x:c r="C142" s="135"/>
+      <x:c r="D142" s="135"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143"/>
-      <x:c r="B143"/>
-      <x:c r="C143"/>
-      <x:c r="D143"/>
+      <x:c r="A143" s="135"/>
+      <x:c r="B143" s="135"/>
+      <x:c r="C143" s="135"/>
+      <x:c r="D143" s="135"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144"/>
-      <x:c r="B144"/>
-      <x:c r="C144"/>
-      <x:c r="D144"/>
+      <x:c r="A144" s="135"/>
+      <x:c r="B144" s="135"/>
+      <x:c r="C144" s="135"/>
+      <x:c r="D144" s="135"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145"/>
-      <x:c r="B145"/>
-      <x:c r="C145"/>
-      <x:c r="D145"/>
+      <x:c r="A145" s="135"/>
+      <x:c r="B145" s="135"/>
+      <x:c r="C145" s="135"/>
+      <x:c r="D145" s="135"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146"/>
-      <x:c r="B146"/>
-      <x:c r="C146"/>
-      <x:c r="D146"/>
+      <x:c r="A146" s="135"/>
+      <x:c r="B146" s="135"/>
+      <x:c r="C146" s="135"/>
+      <x:c r="D146" s="135"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147"/>
-      <x:c r="B147"/>
-      <x:c r="C147"/>
-      <x:c r="D147"/>
+      <x:c r="A147" s="135"/>
+      <x:c r="B147" s="135"/>
+      <x:c r="C147" s="135"/>
+      <x:c r="D147" s="135"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148"/>
-      <x:c r="B148"/>
-      <x:c r="C148"/>
-      <x:c r="D148"/>
+      <x:c r="A148" s="135"/>
+      <x:c r="B148" s="135"/>
+      <x:c r="C148" s="135"/>
+      <x:c r="D148" s="135"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149"/>
-      <x:c r="B149"/>
-      <x:c r="C149"/>
-      <x:c r="D149"/>
+      <x:c r="A149" s="135"/>
+      <x:c r="B149" s="135"/>
+      <x:c r="C149" s="135"/>
+      <x:c r="D149" s="135"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150"/>
-      <x:c r="B150"/>
-      <x:c r="C150"/>
-      <x:c r="D150"/>
+      <x:c r="A150" s="135"/>
+      <x:c r="B150" s="135"/>
+      <x:c r="C150" s="135"/>
+      <x:c r="D150" s="135"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151"/>
@@ -6697,42 +6342,31 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
-    <x:mergeCell ref="A4:C4"/>
-    <x:mergeCell ref="A13:C13"/>
-    <x:mergeCell ref="A14:D14"/>
-    <x:mergeCell ref="A16:C16"/>
-    <x:mergeCell ref="A24:C24"/>
-    <x:mergeCell ref="A25:D25"/>
-    <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A35:C35"/>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A4:D4"/>
+    <x:mergeCell ref="A10:C10"/>
+    <x:mergeCell ref="A12:D12"/>
+    <x:mergeCell ref="A18:C18"/>
+    <x:mergeCell ref="A20:D20"/>
+    <x:mergeCell ref="A26:C26"/>
+    <x:mergeCell ref="A28:D28"/>
+    <x:mergeCell ref="A34:C34"/>
     <x:mergeCell ref="A36:D36"/>
-    <x:mergeCell ref="A38:C38"/>
-    <x:mergeCell ref="A47:C47"/>
-    <x:mergeCell ref="A48:D48"/>
+    <x:mergeCell ref="A42:C42"/>
+    <x:mergeCell ref="A44:D44"/>
     <x:mergeCell ref="A50:C50"/>
+    <x:mergeCell ref="A52:D52"/>
     <x:mergeCell ref="A58:C58"/>
-    <x:mergeCell ref="A59:D59"/>
-    <x:mergeCell ref="A61:C61"/>
-    <x:mergeCell ref="A69:C69"/>
-    <x:mergeCell ref="A70:D70"/>
-    <x:mergeCell ref="A72:C72"/>
-    <x:mergeCell ref="A81:C81"/>
-    <x:mergeCell ref="A82:D82"/>
+    <x:mergeCell ref="A60:D60"/>
+    <x:mergeCell ref="A66:C66"/>
+    <x:mergeCell ref="A68:D68"/>
+    <x:mergeCell ref="A74:C74"/>
+    <x:mergeCell ref="A76:D76"/>
+    <x:mergeCell ref="A82:C82"/>
     <x:mergeCell ref="A84:C84"/>
-    <x:mergeCell ref="A91:C91"/>
-    <x:mergeCell ref="A92:D92"/>
-    <x:mergeCell ref="A94:C94"/>
-    <x:mergeCell ref="A103:C103"/>
-    <x:mergeCell ref="A104:D104"/>
-    <x:mergeCell ref="A106:C106"/>
-    <x:mergeCell ref="A115:C115"/>
-    <x:mergeCell ref="A116:D116"/>
-    <x:mergeCell ref="A118:C118"/>
-    <x:mergeCell ref="A119:C119"/>
-    <x:mergeCell ref="A120:C120"/>
-    <x:mergeCell ref="A121:D121"/>
+    <x:mergeCell ref="A85:C85"/>
+    <x:mergeCell ref="A86:C86"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6742,1549 +6376,1353 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="46" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="108" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13" style="1" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="43" style="1" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="110" style="1" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" style="1" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" s="1" customFormat="1" ht="34" customHeight="1">
-      <x:c r="A1" s="84" t="str">
-        <x:v>HYD 제조 AI | 실전반 오프라인 9회 실라버스</x:v>
-      </x:c>
-      <x:c r="B1"/>
-      <x:c r="C1"/>
-      <x:c r="D1" s="84"/>
-    </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="40" customHeight="1">
-      <x:c r="A2" s="66" t="str">
-        <x:v>2026-10-26 개편 | 온라인 선행 학습·가이드 자율 실습 | 이론 최대50분·복습 없음 | 매회 수업200분+휴식40분</x:v>
-      </x:c>
-      <x:c r="B2"/>
-      <x:c r="C2"/>
-      <x:c r="D2" s="49" t="n">
-        <x:f>SUM(D13,D24,D35,D46,D57,D68,D78,D90,D102)</x:f>
+    <x:row r="1" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A1" s="137" t="str">
+        <x:v>HYD 제조 AI | 실전반 오프라인 정규 9회 | 50분 수업 단위</x:v>
+      </x:c>
+      <x:c r="B1" s="137"/>
+      <x:c r="C1" s="137"/>
+      <x:c r="D1" s="137"/>
+    </x:row>
+    <x:row r="2" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A2" s="135" t="str">
+        <x:v>온라인 실습에서 주요 활동을 선별해 직접 수행합니다. 기본 편성은 수업200분·휴식40분이며, 강사가 학생 진행에 따라 시간을 조절합니다. 이론이 있는 회차는50분, 마지막 두 회차는 실습 중심입니다.</x:v>
+      </x:c>
+      <x:c r="B2" s="135"/>
+      <x:c r="C2" s="135"/>
+      <x:c r="D2" s="135"/>
+    </x:row>
+    <x:row r="3" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A3" s="135"/>
+      <x:c r="B3" s="135"/>
+      <x:c r="C3" s="135"/>
+      <x:c r="D3" s="135"/>
+    </x:row>
+    <x:row r="4" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A4" s="138" t="str">
+        <x:v>01회차 | 설비 정보를 관계와 모델로 표현하기</x:v>
+      </x:c>
+      <x:c r="B4" s="138"/>
+      <x:c r="C4" s="138"/>
+      <x:c r="D4" s="138"/>
+    </x:row>
+    <x:row r="5" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A5" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B5" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C5" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D5" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A6" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B6" s="141" t="str">
+        <x:v>설비 정보와 관계 모델 이해하기</x:v>
+      </x:c>
+      <x:c r="C6" s="141" t="str">
+        <x:v>설비·센서·부품이 각각 어떤 정보를 나타내는지 구분한다. 쿨러의 온도 변화가 센서 값, 이상 징후, 원인 후보, 조치 판단으로 이어지는 경로를 살펴본다. 같은 종류와 개별 대상을 클래스·인스턴스로 나누고, 식별자·속성·관계 방향을 설비 사례에 적용한다.</x:v>
+      </x:c>
+      <x:c r="D6" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A7" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B7" s="143" t="str">
+        <x:v>관계도를 그리고 최소 모델 만들기</x:v>
+      </x:c>
+      <x:c r="C7" s="143" t="str">
+        <x:v>arrows.app에서 쿨러·센서·부품·고장·조치를 노드로 만들고 관계를 연결한다. 각 화살표를 문장으로 읽어 방향을 확인한다. 제공 목록과 관계도를 대조해 클래스·고유 ID·속성을 갖춘 schema.json과 예시 인스턴스를 작성한다.</x:v>
+      </x:c>
+      <x:c r="D7" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A8" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B8" s="141" t="str">
+        <x:v>Cypher로 그래프 생성·조회·수정·삭제하기</x:v>
+      </x:c>
+      <x:c r="C8" s="141" t="str">
+        <x:v>별도 Neo4j 랩 DB에서 작은 예제를 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 생성·조회·수정한다. 그래프의 노드와 관계를 눌러 속성을 확인하고 표 결과와 비교한다. DELETE·DETACH DELETE로 연습 데이터만 정리하고 재조회한다.</x:v>
+      </x:c>
+      <x:c r="D8" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A9" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B9" s="143" t="str">
+        <x:v>설비 모델을 적재하고 질문별 결과 확인하기</x:v>
+      </x:c>
+      <x:c r="C9" s="143" t="str">
+        <x:v>작성한 설비 모델을 제공 절차로 별도 랩 DB에 적재한다. 설비의 센서·부품을 조회해 원자료와 비교하고 빠진 관계·식별자를 수정한다. 포털 기준 지도를 열어 자신의 모델과 연결 방향을 비교한다. 관계도·모델·조회 결과를 저장한다.</x:v>
+      </x:c>
+      <x:c r="D9" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A10" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B10" s="139"/>
+      <x:c r="C10" s="139"/>
+      <x:c r="D10" s="139" t="n">
+        <x:f>SUM(D6:D9)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A11" s="135"/>
+      <x:c r="B11" s="135"/>
+      <x:c r="C11" s="135"/>
+      <x:c r="D11" s="135"/>
+    </x:row>
+    <x:row r="12" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A12" s="138" t="str">
+        <x:v>02회차 | 설비 지식과 조건을 조치 검토에 활용하기</x:v>
+      </x:c>
+      <x:c r="B12" s="138"/>
+      <x:c r="C12" s="138"/>
+      <x:c r="D12" s="138"/>
+    </x:row>
+    <x:row r="13" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A13" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B13" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C13" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D13" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A14" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B14" s="141" t="str">
+        <x:v>설비 모델·조건표·판정과 승인 이해하기</x:v>
+      </x:c>
+      <x:c r="C14" s="141" t="str">
+        <x:v>설비·부품·공급 정보를 연결해 답할 질문을 정한다. SOP의 작업 조건을 결정표로 표현하는 방법을 살펴보고, 조치 후보의 허용·제외 판정과 사람의 실행 승인이 서로 다른 단계임을 이해한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A15" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B15" s="143" t="str">
+        <x:v>설비·부품·공급 정보를 연결하고 조회하기</x:v>
+      </x:c>
+      <x:c r="C15" s="143" t="str">
+        <x:v>기존 설비·부품 모델에 제공 공급 조건을 연결한다. 부품별 사용 설비와 공급 정보를 조회하는 기능을 만들고, 조회 결과의 식별자·관계·공급 조건이 원자료와 일치하는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D15" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A16" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B16" s="141" t="str">
+        <x:v>조치 조건표와 판정·성과 비교 기능 만들기</x:v>
+      </x:c>
+      <x:c r="C16" s="141" t="str">
+        <x:v>제공 SOP에서 입력·단위·연산자·경계·출처를 뽑아 조치 조건표를 만든다. 조건에 따라 허용·제외와 사유를 반환하는 기능을 구현하고, 허용 후보의 비용·생산·품질·에너지 성과를 비교한다.</x:v>
+      </x:c>
+      <x:c r="D16" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A17" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B17" s="143" t="str">
+        <x:v>선택 근거와 확인 사항을 검증해 결과 완성하기</x:v>
+      </x:c>
+      <x:c r="C17" s="143" t="str">
+        <x:v>정상·경계·금지·누락 입력을 바꾸며 조치 검토 결과를 확인한다. 선택 이유·원문 근거·추가 확인 사항을 하나의 결과로 구성하고, 정보가 빠져도 이미 확인된 제외 근거가 유지되는지 검증한다.</x:v>
+      </x:c>
+      <x:c r="D17" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A18" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B18" s="139"/>
+      <x:c r="C18" s="139"/>
+      <x:c r="D18" s="139" t="n">
+        <x:f>SUM(D14:D17)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A19" s="135"/>
+      <x:c r="B19" s="135"/>
+      <x:c r="C19" s="135"/>
+      <x:c r="D19" s="135"/>
+    </x:row>
+    <x:row r="20" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A20" s="138" t="str">
+        <x:v>03회차 | 문서 지식을 작업 확인 자료로 활용하기</x:v>
+      </x:c>
+      <x:c r="B20" s="138"/>
+      <x:c r="C20" s="138"/>
+      <x:c r="D20" s="138"/>
+    </x:row>
+    <x:row r="21" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A21" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B21" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C21" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D21" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A22" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B22" s="141" t="str">
+        <x:v>문서 추출·검토·출처 재사용 이해하기</x:v>
+      </x:c>
+      <x:c r="C22" s="141" t="str">
+        <x:v>매뉴얼의 작업 조건을 추출 후보·검토 지식·작업 확인 자료로 전환하는 과정을 살펴본다. 문서 ID·페이지·인용 구간과 개정 정보를 보존하는 이유를 이해하고, 원문에 없는 내용을 판별한다.</x:v>
+      </x:c>
+      <x:c r="D22" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A23" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B23" s="143" t="str">
+        <x:v>문서를 추출하고 원문과 대조하기</x:v>
+      </x:c>
+      <x:c r="C23" s="143" t="str">
+        <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 작업의 조건·순서·단위·금지 조건과 출처를 추출하고, 잘못 해석한 항목을 원문과 대조해 수정한다.</x:v>
+      </x:c>
+      <x:c r="D23" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A24" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B24" s="141" t="str">
+        <x:v>검토한 지식을 적재하고 출처 확인하기</x:v>
+      </x:c>
+      <x:c r="C24" s="141" t="str">
+        <x:v>채택한 지식만 기존 랩 그래프의 식별자에 맞춰 적재한다. 작업·조건·근거 문서의 관계를 조회하고, 각 지식에서 원문 페이지나 인용 구간을 찾아 검토한 내용과 일치하는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D24" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A25" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B25" s="143" t="str">
+        <x:v>작업 확인 카드를 만들고 검증하기</x:v>
+      </x:c>
+      <x:c r="C25" s="143" t="str">
+        <x:v>선택한 작업의 준비·금지·완료 조건을 담은 확인 카드를 생성하는 기능을 만든다. 카드의 각 조건을 원문과 대조해 문서 밖 절차를 제거하고, 다른 제공 작업에도 적용해 결과를 검증한다.</x:v>
+      </x:c>
+      <x:c r="D25" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A26" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B26" s="139"/>
+      <x:c r="C26" s="139"/>
+      <x:c r="D26" s="139" t="n">
+        <x:f>SUM(D22:D25)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" s="1" customFormat="1" ht="36" customHeight="1">
+      <x:c r="A27" s="135"/>
+      <x:c r="B27" s="135"/>
+      <x:c r="C27" s="135"/>
+      <x:c r="D27" s="135"/>
+    </x:row>
+    <x:row r="28" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A28" s="138" t="str">
+        <x:v>04회차 | 분석 결과를 점검 요청으로 연결하기</x:v>
+      </x:c>
+      <x:c r="B28" s="138"/>
+      <x:c r="C28" s="138"/>
+      <x:c r="D28" s="138"/>
+    </x:row>
+    <x:row r="29" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A29" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B29" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C29" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D29" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A30" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B30" s="141" t="str">
+        <x:v>원인 근거와 점검 요청 구조 이해하기</x:v>
+      </x:c>
+      <x:c r="C30" s="141" t="str">
+        <x:v>원인 후보를 뒷받침하는 설비·센서·문서 근거를 구분한다. 원인 분석 결과를 점검 대상·근거·확인 항목으로 바꾸는 방법을 살펴보고, 미확정 원인과 실제 확인된 사실을 구분한다.</x:v>
+      </x:c>
+      <x:c r="D30" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="92" customHeight="1">
+      <x:c r="A31" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B31" s="143" t="str">
+        <x:v>설비 원인과 점검 순서 기능 만들기</x:v>
+      </x:c>
+      <x:c r="C31" s="143" t="str">
+        <x:v>포털 에이전트의 도구와 근거를 확인한다. VS Code에서 설비 증거를 읽어 원인 후보와 점검 순서를 제안하는 기능을 만들고, 제안의 각 항목에 사용한 근거가 표시되는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D31" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A32" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B32" s="141" t="str">
+        <x:v>설비·문서·부품 근거 연결하기</x:v>
+      </x:c>
+      <x:c r="C32" s="141" t="str">
+        <x:v>기존 설비·문서·부품 자료의 식별자와 출처를 점검 대상에 연결한다. 제안된 점검 항목에서 관련 설비·부품·문서 근거를 찾아가고, 잘못 연결되거나 빠진 자료를 수정한다.</x:v>
+      </x:c>
+      <x:c r="D32" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A33" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B33" s="143" t="str">
+        <x:v>점검 요청 초안을 만들고 검증하기</x:v>
+      </x:c>
+      <x:c r="C33" s="143" t="str">
+        <x:v>점검 대상·근거·확인 항목을 담은 요청 초안을 만든다. 자료가 누락되거나 원인이 확정되지 않은 입력을 넣어 확인 질문이나 가설 표시가 남는지 검증한다. 근거 없는 단정을 수정해 요청 결과를 완성한다.</x:v>
+      </x:c>
+      <x:c r="D33" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A34" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B34" s="139"/>
+      <x:c r="C34" s="139"/>
+      <x:c r="D34" s="139" t="n">
+        <x:f>SUM(D30:D33)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A35" s="135"/>
+      <x:c r="B35" s="135"/>
+      <x:c r="C35" s="135"/>
+      <x:c r="D35" s="135"/>
+    </x:row>
+    <x:row r="36" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A36" s="138" t="str">
+        <x:v>05회차 | 스킬과 도구로 다음 협의 준비하기</x:v>
+      </x:c>
+      <x:c r="B36" s="138"/>
+      <x:c r="C36" s="138"/>
+      <x:c r="D36" s="138"/>
+    </x:row>
+    <x:row r="37" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A37" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B37" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C37" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D37" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A38" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B38" s="141" t="str">
+        <x:v>스킬·도구 조합·변경 근거 이해하기</x:v>
+      </x:c>
+      <x:c r="C38" s="141" t="str">
+        <x:v>재사용할 업무 지침과 실행 도구의 역할을 구분한다. 회의록의 결정·담당·기한과 Git 변경 기록·시각 정보를 연결해 완료·미결·변경 내용을 판단하는 기준을 이해한다.</x:v>
+      </x:c>
+      <x:c r="D38" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A39" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B39" s="143" t="str">
+        <x:v>도구를 연결하고 회의 후속 업무 스킬 만들기</x:v>
+      </x:c>
+      <x:c r="C39" s="143" t="str">
+        <x:v>공통 읽기 도구와 파일·Git·시간 MCP를 연결해 호출 결과를 확인한다. 제공 회의록 두 건과 점검 메모에서 결정·담당·기한·근거를 추출하는 스킬을 만들고, 없는 정보는 미정으로 남기는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D39" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="92" customHeight="1">
+      <x:c r="A40" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B40" s="141" t="str">
+        <x:v>파일·Git·시간으로 변경 자료 확인하기</x:v>
+      </x:c>
+      <x:c r="C40" s="141" t="str">
+        <x:v>파일 내용과 Git 변경 이력, 시간 정보를 대조한다. 이전 회의에서 정한 업무 중 무엇이 바뀌었는지 찾고, 변경된 내용·근거 파일·변경 시각을 연결해 기록한다.</x:v>
+      </x:c>
+      <x:c r="D40" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A41" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B41" s="143" t="str">
+        <x:v>다음 협의 안건을 만들고 검증하기</x:v>
+      </x:c>
+      <x:c r="C41" s="143" t="str">
+        <x:v>회의 업무 목록과 변경 기록을 합쳐 완료·미결·변경 사항 및 다음 협의에서 확인할 안건을 생성한다. 안건의 근거를 원문과 대조하고 같은 입력을 다시 실행해 필수 정보가 유지되는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D41" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A42" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B42" s="139"/>
+      <x:c r="C42" s="139"/>
+      <x:c r="D42" s="139" t="n">
+        <x:f>SUM(D38:D41)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A43" s="135"/>
+      <x:c r="B43" s="135"/>
+      <x:c r="C43" s="135"/>
+      <x:c r="D43" s="135"/>
+    </x:row>
+    <x:row r="44" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A44" s="138" t="str">
+        <x:v>06회차 | 활용 기능의 요구를 명세하고 검증하기</x:v>
+      </x:c>
+      <x:c r="B44" s="138"/>
+      <x:c r="C44" s="138"/>
+      <x:c r="D44" s="138"/>
+    </x:row>
+    <x:row r="45" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A45" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B45" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C45" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D45" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A46" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B46" s="141" t="str">
+        <x:v>질문·승인·명세와 기대 결과 이해하기</x:v>
+      </x:c>
+      <x:c r="C46" s="141" t="str">
+        <x:v>필수 입력이 없을 때의 질문·보류와 사람 승인을 구분한다. 기능의 입력·출력·제약·완료 기준을 명세하고, 정상·누락·변경·기존 기능을 검증할 기대 결과로 바꾸는 방법을 익힌다.</x:v>
+      </x:c>
+      <x:c r="D46" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A47" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B47" s="143" t="str">
+        <x:v>점검 요청의 질문·답변·재개 구현하기</x:v>
+      </x:c>
+      <x:c r="C47" s="143" t="str">
+        <x:v>포털의 승인·보류 상태를 확인한다. 점검 요청 초안의 필수 정보가 빠졌을 때 질문하고, 추가 답변을 반영해 다시 판단하는 흐름을 구현한다. 사람이 승인할 결과가 자동 확정되지 않는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D47" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A48" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B48" s="141" t="str">
+        <x:v>변경을 명세하고 기존 기능을 보존해 구현하기</x:v>
+      </x:c>
+      <x:c r="C48" s="141" t="str">
+        <x:v>기존 점검 요청 기능에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기능을 구현한다. 변경 전부터 유지해야 할 출력 형식과 승인 조건을 함께 대조한다.</x:v>
+      </x:c>
+      <x:c r="D48" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="92" customHeight="1">
+      <x:c r="A49" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B49" s="143" t="str">
+        <x:v>정상·누락·회귀 시나리오 검증하기</x:v>
+      </x:c>
+      <x:c r="C49" s="143" t="str">
+        <x:v>직접 정한 정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성한다. 실제 출력을 비교해 어긋난 조건을 수정하고, 기존 점검 요청과 승인 조건도 다시 실행해 회귀 오류가 없는지 확인한다.</x:v>
+      </x:c>
+      <x:c r="D49" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A50" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B50" s="139"/>
+      <x:c r="C50" s="139"/>
+      <x:c r="D50" s="139" t="n">
+        <x:f>SUM(D46:D49)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" s="1" customFormat="1" ht="65" customHeight="1">
+      <x:c r="A51" s="135"/>
+      <x:c r="B51" s="135"/>
+      <x:c r="C51" s="135"/>
+      <x:c r="D51" s="135"/>
+    </x:row>
+    <x:row r="52" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A52" s="138" t="str">
+        <x:v>07회차 | 설비 대응 프로세스를 설계하고 연결하기</x:v>
+      </x:c>
+      <x:c r="B52" s="138"/>
+      <x:c r="C52" s="138"/>
+      <x:c r="D52" s="138"/>
+    </x:row>
+    <x:row r="53" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A53" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B53" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C53" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D53" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A54" s="141" t="str">
+        <x:v>이론</x:v>
+      </x:c>
+      <x:c r="B54" s="141" t="str">
+        <x:v>BPMN 역할·분기·지연·실행 연결 이해하기</x:v>
+      </x:c>
+      <x:c r="C54" s="141" t="str">
+        <x:v>시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
+      </x:c>
+      <x:c r="D54" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A55" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B55" s="143" t="str">
+        <x:v>기본 승인 흐름에서 설비 대응 흐름 만들기</x:v>
+      </x:c>
+      <x:c r="C55" s="143" t="str">
+        <x:v>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</x:v>
+      </x:c>
+      <x:c r="D55" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A56" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B56" s="141" t="str">
+        <x:v>승인·거절·지연 경로 완성하기</x:v>
+      </x:c>
+      <x:c r="C56" s="141" t="str">
+        <x:v>승인·거절 분기와 각각의 종료 경로를 연결한다. 거절 경로에서 설비 명령으로 진행되지 않는지 확인하고, 승인 작업을 취소하지 않는 지연 알림 Timer를 추가한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검한다.</x:v>
+      </x:c>
+      <x:c r="D56" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A57" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B57" s="143" t="str">
+        <x:v>BPMN과 등록된 실행 연결 비교하기</x:v>
+      </x:c>
+      <x:c r="C57" s="143" t="str">
+        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</x:v>
+      </x:c>
+      <x:c r="D57" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A58" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B58" s="139"/>
+      <x:c r="C58" s="139"/>
+      <x:c r="D58" s="139" t="n">
+        <x:f>SUM(D54:D57)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="12" customHeight="1">
+      <x:c r="A59" s="135"/>
+      <x:c r="B59" s="135"/>
+      <x:c r="C59" s="135"/>
+      <x:c r="D59" s="135"/>
+    </x:row>
+    <x:row r="60" s="1" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A60" s="138" t="str">
+        <x:v>08회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</x:v>
+      </x:c>
+      <x:c r="B60" s="138"/>
+      <x:c r="C60" s="138"/>
+      <x:c r="D60" s="138"/>
+    </x:row>
+    <x:row r="61" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A61" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B61" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C61" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D61" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A62" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B62" s="141" t="str">
+        <x:v>실행 상태를 이해하고 정상·예외 경로 확인하기</x:v>
+      </x:c>
+      <x:c r="C62" s="141" t="str">
+        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+      </x:c>
+      <x:c r="D62" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A63" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B63" s="143" t="str">
+        <x:v>BPMN을 보완하고 교대 인수인계 요구 정하기</x:v>
+      </x:c>
+      <x:c r="C63" s="143" t="str">
+        <x:v>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</x:v>
+      </x:c>
+      <x:c r="D63" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" s="1" customFormat="1" ht="98" customHeight="1">
+      <x:c r="A64" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B64" s="141" t="str">
+        <x:v>보충 지식과 인수인계 에이전트 구성하기</x:v>
+      </x:c>
+      <x:c r="C64" s="141" t="str">
+        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
+      </x:c>
+      <x:c r="D64" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A65" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B65" s="143" t="str">
+        <x:v>제공 인수인계 BPMN의 에이전트 배정·등록하기</x:v>
+      </x:c>
+      <x:c r="C65" s="143" t="str">
+        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
+      </x:c>
+      <x:c r="D65" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A66" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B66" s="139"/>
+      <x:c r="C66" s="139"/>
+      <x:c r="D66" s="139" t="n">
+        <x:f>SUM(D62:D65)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A67" s="135"/>
+      <x:c r="B67" s="135"/>
+      <x:c r="C67" s="135"/>
+      <x:c r="D67" s="135"/>
+    </x:row>
+    <x:row r="68" ht="38" customHeight="1">
+      <x:c r="A68" s="138" t="str">
+        <x:v>09회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</x:v>
+      </x:c>
+      <x:c r="B68" s="138"/>
+      <x:c r="C68" s="138"/>
+      <x:c r="D68" s="138"/>
+    </x:row>
+    <x:row r="69" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A69" s="140" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B69" s="140" t="str">
+        <x:v>수업 단위</x:v>
+      </x:c>
+      <x:c r="C69" s="140" t="str">
+        <x:v>세부 활동과 확인할 결과</x:v>
+      </x:c>
+      <x:c r="D69" s="140" t="str">
+        <x:v>시간(분)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A70" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B70" s="141" t="str">
+        <x:v>업무별 시작 조건을 비교하고 정비 흐름 설계하기</x:v>
+      </x:c>
+      <x:c r="C70" s="141" t="str">
+        <x:v>냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
+      </x:c>
+      <x:c r="D70" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A71" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B71" s="143" t="str">
+        <x:v>등록된 정비 흐름을 실행하고 결과 검증하기</x:v>
+      </x:c>
+      <x:c r="C71" s="143" t="str">
+        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
+      </x:c>
+      <x:c r="D71" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A72" s="141" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B72" s="141" t="str">
+        <x:v>구매 흐름을 설계하고 실행 검증하기</x:v>
+      </x:c>
+      <x:c r="C72" s="141" t="str">
+        <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
+      </x:c>
+      <x:c r="D72" s="142" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" s="1" customFormat="1" ht="92" customHeight="1">
+      <x:c r="A73" s="143" t="str">
+        <x:v>실습</x:v>
+      </x:c>
+      <x:c r="B73" s="143" t="str">
+        <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
+      </x:c>
+      <x:c r="C73" s="143" t="str">
+        <x:v>교대 인수인계 흐름에 설비·교대 정보를 입력하고 정상·기록 불일치·정보 누락 사례를 실행한다. 인계자 검토, 인수자의 보완 요청과 확인을 거쳐 인계 내용·근거·완료 기록을 대조한다(30분). ProcessGPT 시연을 보며 자신이 만든 지식·에이전트·업무 흐름이 제품의 작업함과 실행 기록에 어떻게 연결되는지 비교한다(20분).</x:v>
+      </x:c>
+      <x:c r="D73" s="144" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A74" s="139" t="str">
+        <x:v>수업 합계 (휴식40분 별도)</x:v>
+      </x:c>
+      <x:c r="B74" s="139"/>
+      <x:c r="C74" s="139"/>
+      <x:c r="D74" s="139" t="n">
+        <x:f>SUM(D70:D73)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A75" s="135"/>
+      <x:c r="B75" s="135"/>
+      <x:c r="C75" s="135"/>
+      <x:c r="D75" s="135"/>
+    </x:row>
+    <x:row r="76" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A76" s="135" t="str">
+        <x:v>전체 수업 시간(분)</x:v>
+      </x:c>
+      <x:c r="B76" s="135"/>
+      <x:c r="C76" s="135"/>
+      <x:c r="D76" s="135" t="n">
+        <x:f>SUM(D10,D18,D26,D34,D42,D50,D58,D66,D74)</x:f>
         <x:v>1800</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A3"/>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3"/>
-    </x:row>
-    <x:row r="4" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A4" s="43" t="str">
-        <x:v>01회차 | 설비 정보를 관계와 모델로 표현하기</x:v>
-      </x:c>
-      <x:c r="B4"/>
-      <x:c r="C4"/>
-      <x:c r="D4" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A5" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B5" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C5" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D5" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A6" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B6" s="126" t="str">
-        <x:v>설비·레이어·온톨로지·식별자의 연결</x:v>
-      </x:c>
-      <x:c r="C6" s="127" t="str">
-        <x:v>설비·레이어·온톨로지·식별자의 연결을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 각 과정 온라인 1 + 2의 모델 기초. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D6" s="128" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A7" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B7" s="130" t="str">
-        <x:v>ARROWS에서 설비·원인·조치 관계 작성</x:v>
-      </x:c>
-      <x:c r="C7" s="131" t="str">
-        <x:v>쿨러·센서·부품·고장·조치를 연결하고 관계 방향을 문장으로 확인한 뒤 JSON을 저장한다.</x:v>
-      </x:c>
-      <x:c r="D7" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A8" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B8" s="130" t="str">
-        <x:v>제공 자료로 최소 스키마·인스턴스 작성</x:v>
-      </x:c>
-      <x:c r="C8" s="131" t="str">
-        <x:v>제공 목록과 관계도를 대조해 고유 ID·클래스·속성을 갖춘 최소 schema.json과 인스턴스를 만든다.</x:v>
-      </x:c>
-      <x:c r="D8" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A9" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B9" s="130" t="str">
-        <x:v>제공 절차로 랩 그래프 적재·질문 결과 확인</x:v>
-      </x:c>
-      <x:c r="C9" s="131" t="str">
-        <x:v>제공 적재 절차를 별도 랩 DB에서 수행하고 질문별 조회 결과를 원자료와 비교한다. Cypher 문법 수업은 별도로 하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D9" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A10" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B10" s="130" t="str">
-        <x:v>포털 기준 지도와 필요한 관계 비교</x:v>
-      </x:c>
-      <x:c r="C10" s="131" t="str">
-        <x:v>포털의 공통 기준 지도에서 필요한 연결만 확인하고 개인 모델과 비교한다. 자동 동기화는 전제하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D10" s="132" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A11" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B11" s="130" t="str">
-        <x:v>본인 모델의 누락 수정·질문별 결과 완성</x:v>
-      </x:c>
-      <x:c r="C11" s="131" t="str">
-        <x:v>누락된 관계·속성·방향을 보완하고 질문별 답을 다시 확인한다.</x:v>
-      </x:c>
-      <x:c r="D11" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A12" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B12" s="130" t="str">
-        <x:v>개별 진행 차이 대응·저장·다음 입력 준비</x:v>
-      </x:c>
-      <x:c r="C12" s="131" t="str">
-        <x:v>막힌 부분을 해결하고 관계도·모델·질의 결과를 저장해 다음 회차 입력으로 준비한다.</x:v>
-      </x:c>
-      <x:c r="D12" s="132" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A13" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13" s="49" t="n">
-        <x:f>SUM(D6:D12)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A14" s="66" t="str">
-        <x:v>완료 결과: 두 반 동일: 관계도, 최소 모델, 질문별 확인 결과. Neo4j 문법 수업은 별도로 편성하지 않는다. 온라인 2 전체 설계를 1회차에 모두 끝내지 않는다.</x:v>
-      </x:c>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14" s="49"/>
-    </x:row>
-    <x:row r="15" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-    </x:row>
-    <x:row r="16" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A16" s="43" t="str">
-        <x:v>02회차 | 설비 지식과 조건을 조치 검토에 활용하기</x:v>
-      </x:c>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A17" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C17" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A18" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B18" s="126" t="str">
-        <x:v>모델의 사용 목적·조건표·판정과 승인 구분</x:v>
-      </x:c>
-      <x:c r="C18" s="127" t="str">
-        <x:v>모델의 사용 목적·조건표·판정과 승인 구분을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인2 + 3 판단. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D18" s="128" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A19" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B19" s="130" t="str">
-        <x:v>기존 설비·부품 모델에 공급 자료 연결</x:v>
-      </x:c>
-      <x:c r="C19" s="131" t="str">
-        <x:v>기존 설비·부품 모델에 제공 공급 조건을 연결한다.</x:v>
-      </x:c>
-      <x:c r="D19" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A20" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B20" s="130" t="str">
-        <x:v>부품별 사용 설비·공급 정보 조회 결과 제작</x:v>
-      </x:c>
-      <x:c r="C20" s="131" t="str">
-        <x:v>부품별 사용 설비와 공급 정보를 조회하는 기능을 만들고 원자료와 비교한다.</x:v>
-      </x:c>
-      <x:c r="D20" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A21" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B21" s="130" t="str">
-        <x:v>SOP 조치 조건표 작성</x:v>
-      </x:c>
-      <x:c r="C21" s="131" t="str">
-        <x:v>SOP에서 입력·단위·경계·출처를 가진 조치 조건표를 작성한다.</x:v>
-      </x:c>
-      <x:c r="D21" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A22" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B22" s="130" t="str">
-        <x:v>허용·제외와 성과 비교 기능 제작</x:v>
-      </x:c>
-      <x:c r="C22" s="131" t="str">
-        <x:v>허용·제외와 사유를 구현하고 허용 후보의 성과를 비교한다.</x:v>
-      </x:c>
-      <x:c r="D22" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A23" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B23" s="130" t="str">
-        <x:v>선택 이유·추가 확인 사항을 조치 검토 결과로 완성</x:v>
-      </x:c>
-      <x:c r="C23" s="131" t="str">
-        <x:v>선택 이유·원문 근거·추가 확인 사항을 한 조치 검토 결과로 저장한다.</x:v>
-      </x:c>
-      <x:c r="D23" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A24" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24" s="49" t="n">
-        <x:f>SUM(D18:D23)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A25" s="66" t="str">
-        <x:v>완료 결과: 같은 설비 모델·판단 코어를 유지한다. 공급 정보는 조회·비교 자료이며 임의 공급사 선정 규칙을 만들지 않는다. 선택 이유에는 계산과 원문 근거를 연결한다.</x:v>
-      </x:c>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25" s="49"/>
-    </x:row>
-    <x:row r="26" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-    </x:row>
-    <x:row r="27" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A27" s="43" t="str">
-        <x:v>03회차 | 문서 지식을 작업 확인 자료로 활용하기</x:v>
-      </x:c>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A28" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B28" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C28" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D28" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A29" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B29" s="126" t="str">
-        <x:v>추출·검토·출처·지식의 재사용</x:v>
-      </x:c>
-      <x:c r="C29" s="127" t="str">
-        <x:v>추출·검토·출처·지식의 재사용을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인3 문서. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D29" s="128" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A30" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B30" s="130" t="str">
-        <x:v>공통 포털 문서 등록·검토 경험</x:v>
-      </x:c>
-      <x:c r="C30" s="131" t="str">
-        <x:v>공통 포털에서 문서 등록과 추출 후보 검토를 수행한다.</x:v>
-      </x:c>
-      <x:c r="D30" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="60" customHeight="1">
-      <x:c r="A31" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B31" s="130" t="str">
-        <x:v>제공 문서 추출·원문 검토</x:v>
-      </x:c>
-      <x:c r="C31" s="131" t="str">
-        <x:v>제공 문서를 구조화해 추출하고 조건·단위·출처를 원문과 비교한다.</x:v>
-      </x:c>
-      <x:c r="D31" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A32" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B32" s="130" t="str">
-        <x:v>검토 지식 적재·출처 확인</x:v>
-      </x:c>
-      <x:c r="C32" s="131" t="str">
-        <x:v>채택 지식을 별도 랩 그래프에 적재하고 출처를 조회한다.</x:v>
-      </x:c>
-      <x:c r="D32" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A33" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B33" s="130" t="str">
-        <x:v>선택한 작업의 준비·금지·완료 조건 카드 생성 기능</x:v>
-      </x:c>
-      <x:c r="C33" s="131" t="str">
-        <x:v>검토 지식에서 선택 작업의 준비·금지·완료 조건 카드를 생성하는 로컬 기능을 만든다.</x:v>
-      </x:c>
-      <x:c r="D33" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A34" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B34" s="130" t="str">
-        <x:v>카드와 원문 대조·개별 수정</x:v>
-      </x:c>
-      <x:c r="C34" s="131" t="str">
-        <x:v>카드를 원문과 비교해 수정하고 파일로 저장한다. 포털 화면을 추가하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D34" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A35" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35" s="49" t="n">
-        <x:f>SUM(D29:D34)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A36" s="66" t="str">
-        <x:v>완료 결과: 추출된 지식으로 작업 확인 카드를 생성한다. 문서 밖 절차를 만들지 않는다. 포털에 카드 화면을 추가하지 않고 로컬 파일로 저장한다.</x:v>
-      </x:c>
-      <x:c r="B36"/>
-      <x:c r="C36"/>
-      <x:c r="D36" s="49"/>
-    </x:row>
-    <x:row r="37" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-    </x:row>
-    <x:row r="38" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A38" s="43" t="str">
-        <x:v>04회차 | 분석 결과를 점검 요청으로 연결하기</x:v>
-      </x:c>
-      <x:c r="B38"/>
-      <x:c r="C38"/>
-      <x:c r="D38" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A39" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B39" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C39" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D39" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="65" customHeight="1">
-      <x:c r="A40" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B40" s="126" t="str">
-        <x:v>원인 근거·점검 제안·사용할 결과의 구조</x:v>
-      </x:c>
-      <x:c r="C40" s="127" t="str">
-        <x:v>원인 근거·점검 제안·사용할 결과의 구조을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인4 에이전트. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D40" s="128" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A41" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B41" s="130" t="str">
-        <x:v>공통 포털 에이전트 경험</x:v>
-      </x:c>
-      <x:c r="C41" s="131" t="str">
-        <x:v>공통 포털 에이전트의 구성·도구·근거를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D41" s="132" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A42" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B42" s="130" t="str">
-        <x:v>원인 후보·점검 순서 기능 제작</x:v>
-      </x:c>
-      <x:c r="C42" s="131" t="str">
-        <x:v>설비 증거에서 원인 후보와 점검 순서를 생성하는 기능을 만든다.</x:v>
-      </x:c>
-      <x:c r="D42" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A43" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B43" s="130" t="str">
-        <x:v>기존 설비·문서·부품 자료 연결</x:v>
-      </x:c>
-      <x:c r="C43" s="131" t="str">
-        <x:v>기존 설비·문서·부품 자료의 출처와 점검 대상 관계를 연결한다.</x:v>
-      </x:c>
-      <x:c r="D43" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A44" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B44" s="130" t="str">
-        <x:v>점검 대상·근거·확인 항목을 담은 요청 초안 제작</x:v>
-      </x:c>
-      <x:c r="C44" s="131" t="str">
-        <x:v>점검 대상·근거·확인 항목을 담은 로컬 요청 초안을 만든다.</x:v>
-      </x:c>
-      <x:c r="D44" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A45" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B45" s="130" t="str">
-        <x:v>누락·단정 여부 확인·개별 수정</x:v>
-      </x:c>
-      <x:c r="C45" s="131" t="str">
-        <x:v>누락과 근거 없는 단정을 수정해 6회차 변경·검증의 입력으로 저장한다.</x:v>
-      </x:c>
-      <x:c r="D45" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A46" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B46"/>
-      <x:c r="C46"/>
-      <x:c r="D46" s="49" t="n">
-        <x:f>SUM(D40:D45)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A47" s="66" t="str">
-        <x:v>완료 결과: 원인 분석 코어를 유지하고 점검 요청 초안까지 완성한다. 요청은 로컬 결과이며 포털 작업지시 생성·설비 조작은 하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B47"/>
-      <x:c r="C47"/>
-      <x:c r="D47" s="49"/>
-    </x:row>
-    <x:row r="48" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A48"/>
-      <x:c r="D48"/>
-    </x:row>
-    <x:row r="49" ht="36" customHeight="1">
-      <x:c r="A49" s="43" t="str">
-        <x:v>05회차 | 스킬과 도구로 다음 협의 준비하기</x:v>
-      </x:c>
-      <x:c r="B49"/>
-      <x:c r="C49"/>
-      <x:c r="D49" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A50" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B50" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C50" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D50" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A51" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B51" s="126" t="str">
-        <x:v>재사용 지침·도구 조합·변경 근거</x:v>
-      </x:c>
-      <x:c r="C51" s="127" t="str">
-        <x:v>재사용 지침·도구 조합·변경 근거을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인4 스킬·MCP. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D51" s="128" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A52" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B52" s="130" t="str">
-        <x:v>공통 도구 연결·호출 확인</x:v>
-      </x:c>
-      <x:c r="C52" s="131" t="str">
-        <x:v>공통 포털 읽기 도구와 준비된 파일·Git·시간 MCP 연결을 확인한다.</x:v>
-      </x:c>
-      <x:c r="D52" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A53" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B53" s="130" t="str">
-        <x:v>회의 결정·후속 업무 추출 스킬 제작</x:v>
-      </x:c>
-      <x:c r="C53" s="131" t="str">
-        <x:v>회의록 두 건과 점검 메모에서 결정·담당·기한·근거를 추출하는 스킬을 만든다.</x:v>
-      </x:c>
-      <x:c r="D53" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A54" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B54" s="130" t="str">
-        <x:v>파일·Git·시간으로 변경 자료 확인</x:v>
-      </x:c>
-      <x:c r="C54" s="131" t="str">
-        <x:v>파일 내용과 Git 이력·시간을 대조해 변경 내용을 찾는다.</x:v>
-      </x:c>
-      <x:c r="D54" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A55" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B55" s="130" t="str">
-        <x:v>완료·미결·변경 내용을 연결한 다음 협의 안건 생성</x:v>
-      </x:c>
-      <x:c r="C55" s="131" t="str">
-        <x:v>완료·미결·변경 사항을 연결해 다음 협의 안건을 로컬 파일로 생성한다.</x:v>
-      </x:c>
-      <x:c r="D55" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A56" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B56" s="130" t="str">
-        <x:v>원문 대조·다시 실행·개별 수정</x:v>
-      </x:c>
-      <x:c r="C56" s="131" t="str">
-        <x:v>원문과 결과를 비교하고 재실행해 수정·보존한다.</x:v>
-      </x:c>
-      <x:c r="D56" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A57" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B57"/>
-      <x:c r="C57"/>
-      <x:c r="D57" s="49" t="n">
-        <x:f>SUM(D51:D56)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A58" s="66" t="str">
-        <x:v>완료 결과: 기존 회의록 두 건·점검 메모·Git 이력으로 다음 협의 자료를 만든다. 공통 서버를 재사용하며 새 MCP 서버나 외부 계정 연동을 만들지 않는다.</x:v>
-      </x:c>
-      <x:c r="B58"/>
-      <x:c r="C58"/>
-      <x:c r="D58" s="49"/>
-    </x:row>
-    <x:row r="59" ht="12" customHeight="1">
-      <x:c r="A59"/>
-      <x:c r="B59"/>
-      <x:c r="C59"/>
-      <x:c r="D59"/>
-    </x:row>
-    <x:row r="60" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A60" s="43" t="str">
-        <x:v>06회차 | 활용 기능의 요구를 명세하고 검증하기</x:v>
-      </x:c>
-      <x:c r="B60"/>
-      <x:c r="C60"/>
-      <x:c r="D60" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A61" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B61" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C61" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D61" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A62" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B62" s="126" t="str">
-        <x:v>필수 입력·질문·승인·명세와 기대 결과</x:v>
-      </x:c>
-      <x:c r="C62" s="127" t="str">
-        <x:v>필수 입력·질문·승인·명세와 기대 결과을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 온라인5. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D62" s="128" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A63" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B63" s="130" t="str">
-        <x:v>공통 포털 승인 상태 확인</x:v>
-      </x:c>
-      <x:c r="C63" s="131" t="str">
-        <x:v>공통 포털 승인·보류 상태를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D63" s="132" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A64" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B64" s="130" t="str">
-        <x:v>점검 요청 초안의 필수 정보 확인·질문·재개</x:v>
-      </x:c>
-      <x:c r="C64" s="131" t="str">
-        <x:v>4회차 점검 요청 프로젝트에서 필수 입력을 정하고 질문·추가 답변·재판단을 구현한다.</x:v>
-      </x:c>
-      <x:c r="D64" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A65" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B65" s="130" t="str">
-        <x:v>완료 기준과 필요한 변경 한 건을 명세로 작성</x:v>
-      </x:c>
-      <x:c r="C65" s="131" t="str">
-        <x:v>같은 프로젝트의 완료 기준과 필요한 변경 한 건을 spec.md로 작성한다.</x:v>
-      </x:c>
-      <x:c r="D65" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A66" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B66" s="130" t="str">
-        <x:v>기존 기능을 보존하며 변경 구현</x:v>
-      </x:c>
-      <x:c r="C66" s="131" t="str">
-        <x:v>기존 입력·출력·승인 조건을 보존하며 변경을 구현한다.</x:v>
-      </x:c>
-      <x:c r="D66" s="132" t="n">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A67" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B67" s="130" t="str">
-        <x:v>직접 정한 기대 결과로 정상·누락·회귀 검증</x:v>
-      </x:c>
-      <x:c r="C67" s="131" t="str">
-        <x:v>직접 정한 정상·누락·변경 기대 결과를 실제 출력과 비교하고 회귀 검증한다.</x:v>
-      </x:c>
-      <x:c r="D67" s="132" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="28" customHeight="1">
-      <x:c r="A68" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B68"/>
-      <x:c r="C68"/>
-      <x:c r="D68" s="49" t="n">
-        <x:f>SUM(D62:D67)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A69" s="66" t="str">
-        <x:v>완료 결과: 새 분야로 바꾸지 않고 4회차 로컬 프로젝트를 사용한다. 예외 수 늘리기가 아니라 자신의 요구를 검증 가능한 결과로 만드는 데 차이를 둔다.</x:v>
-      </x:c>
-      <x:c r="B69"/>
-      <x:c r="C69"/>
-      <x:c r="D69" s="49"/>
-    </x:row>
-    <x:row r="70" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A70"/>
-      <x:c r="B70"/>
-      <x:c r="C70"/>
-      <x:c r="D70"/>
-    </x:row>
-    <x:row r="71" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A71" s="43" t="str">
-        <x:v>07회차 | 설비 대응 프로세스를 설계하고 연결하기</x:v>
-      </x:c>
-      <x:c r="B71"/>
-      <x:c r="C71"/>
-      <x:c r="D71" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A72" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B72" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C72" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D72" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A73" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B73" s="126" t="str">
-        <x:v>작업·역할·분기·비중단 지연과 실행 매핑</x:v>
-      </x:c>
-      <x:c r="C73" s="127" t="str">
-        <x:v>작업·역할·분기·비중단 지연과 실행 매핑을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9 / 실전 온라인6. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D73" s="128" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A74" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B74" s="130" t="str">
-        <x:v>bpmn.io 기본 승인 흐름 직접 작성</x:v>
-      </x:c>
-      <x:c r="C74" s="131" t="str">
-        <x:v>bpmn.io에서 시작·작업·승인·종료를 배치하고 파일로 저장한다.</x:v>
-      </x:c>
-      <x:c r="D74" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A75" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B75" s="130" t="str">
-        <x:v>설비 대응 흐름 작성</x:v>
-      </x:c>
-      <x:c r="C75" s="131" t="str">
-        <x:v>공통 냉각 대응 시나리오의 역할·작업·흐름을 작성한다.</x:v>
-      </x:c>
-      <x:c r="D75" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A76" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B76" s="130" t="str">
-        <x:v>승인·거절·지연 경로 완성</x:v>
-      </x:c>
-      <x:c r="C76" s="131" t="str">
-        <x:v>승인·거절 분기와 비중단 지연 경로를 완성한다.</x:v>
-      </x:c>
-      <x:c r="D76" s="132" t="n">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
     <x:row r="77" ht="60" customHeight="1">
-      <x:c r="A77" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B77" s="130" t="str">
-        <x:v>기존 부품으로 매핑·검사·배포</x:v>
-      </x:c>
-      <x:c r="C77" s="131" t="str">
-        <x:v>기존 에이전트·역할·작업 부품에 매핑하고 검사·등록·배포한다. 공용 환경의 배포 순서를 따른다.</x:v>
-      </x:c>
-      <x:c r="D77" s="132" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A78" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B78"/>
-      <x:c r="C78"/>
-      <x:c r="D78" s="49" t="n">
-        <x:f>SUM(D73:D77)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" s="1" customFormat="1" ht="58" customHeight="1">
-      <x:c r="A79" s="66" t="str">
-        <x:v>완료 결과: 두 반 공통: 기존 냉각 대응 시나리오의 BPMN·매핑·배포 기록. 임의 작업 부품이나 포털 기능을 추가하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B79"/>
-      <x:c r="C79"/>
-      <x:c r="D79" s="49"/>
-    </x:row>
-    <x:row r="80" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A80"/>
-      <x:c r="B80"/>
-      <x:c r="C80"/>
-      <x:c r="D80"/>
-    </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="36" customHeight="1">
-      <x:c r="A81" s="43" t="str">
-        <x:v>08회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</x:v>
-      </x:c>
-      <x:c r="B81"/>
-      <x:c r="C81"/>
-      <x:c r="D81" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A82" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B82" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C82" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D82" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" s="1" customFormat="1" ht="65" customHeight="1">
-      <x:c r="A83" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B83" s="126" t="str">
-        <x:v>정의·실행 상태·오류 위치와 복구</x:v>
-      </x:c>
-      <x:c r="C83" s="127" t="str">
-        <x:v>정의·실행 상태·오류 위치와 복구를 오늘 과제와 연결해 설명한다. 온라인 대응: 통합 온라인9·11 / 실전 온라인6·8. 교대 인수인계의 시작 폼·역할·완료 조건을 구분한다.</x:v>
-      </x:c>
-      <x:c r="D83" s="128" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A84" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B84" s="130" t="str">
-        <x:v>배포된 공통 흐름 정상 실행</x:v>
-      </x:c>
-      <x:c r="C84" s="131" t="str">
-        <x:v>배포된 공통 흐름을 실행하고 처리 이력을 확인한다.</x:v>
-      </x:c>
-      <x:c r="D84" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A85" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B85" s="130" t="str">
-        <x:v>거절·지연·역할 제한 확인</x:v>
-      </x:c>
-      <x:c r="C85" s="131" t="str">
-        <x:v>승인 거절·지연·역할 제한을 공통 사례로 확인한다.</x:v>
-      </x:c>
-      <x:c r="D85" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A86" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B86" s="130" t="str">
-        <x:v>실제 오류 또는 제공 오류 사례 수정·재배포</x:v>
-      </x:c>
-      <x:c r="C86" s="131" t="str">
-        <x:v>실제 또는 제공된 오류 사례에서 잘못된 설정을 찾아 수정·재배포한다.</x:v>
-      </x:c>
-      <x:c r="D86" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="68" customHeight="1">
-      <x:c r="A87" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B87" s="130" t="str">
-        <x:v>교대 인수인계의 입력·근거·완료 조건 정하기</x:v>
-      </x:c>
-      <x:c r="C87" s="131" t="str">
-        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
-      </x:c>
-      <x:c r="D87" s="132" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A88" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B88" s="130" t="str">
-        <x:v>보충 매뉴얼 적재와 인수인계 에이전트 구성</x:v>
-      </x:c>
-      <x:c r="C88" s="131" t="str">
-        <x:v>제공 보충 매뉴얼의 추출 결과를 원문 대조하여 기존 제조 지식에 추가한다. 허용된 설비·정비·ERP 조회를 사용해 인계안을 만들고, 기록 불일치와 미확인 사항을 남긴다. 같은 조건의 추출 재사용은 표시한다.</x:v>
-      </x:c>
-      <x:c r="D88" s="132" t="n">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A89" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B89" s="130" t="str">
-        <x:v>교대 인수인계 BPMN 설계·매핑과 중간 결과 저장</x:v>
-      </x:c>
-      <x:c r="C89" s="131" t="str">
-        <x:v>bpmn.io에서 조회·인계안·인계자 검토·인수자 확인·보완·완료 흐름을 작성한다. 포털의 별도 정의에 시작 폼·에이전트·역할을 연결하고 판본을 저장한다. 실제 실행은 다음 회차로 이어간다.</x:v>
-      </x:c>
-      <x:c r="D89" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" s="1" customFormat="1" ht="28" customHeight="1">
-      <x:c r="A90" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B90"/>
-      <x:c r="C90"/>
-      <x:c r="D90" s="49" t="n">
-        <x:f>SUM(D83:D89)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="58" customHeight="1">
-      <x:c r="A91" s="66" t="str">
-        <x:v>완료 결과: 추가 지식의 검토·적재 기록, 인수인계 에이전트·스킬, 별도 BPMN·매핑·시작 폼. 기존 ABC 정의는 보존한다. 임의 코드 자동 연결이나 임의 외부 도구는 요구하지 않는다.</x:v>
-      </x:c>
-      <x:c r="B91"/>
-      <x:c r="C91"/>
-      <x:c r="D91" s="49"/>
-    </x:row>
-    <x:row r="92" s="1" customFormat="1" ht="12" customHeight="1">
-      <x:c r="A92"/>
-    </x:row>
-    <x:row r="93" ht="36" customHeight="1">
-      <x:c r="A93" s="43" t="str">
-        <x:v>09회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</x:v>
-      </x:c>
-      <x:c r="B93"/>
-      <x:c r="C93"/>
-      <x:c r="D93" s="44" t="str">
-        <x:v>4H</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" s="1" customFormat="1" ht="26" customHeight="1">
-      <x:c r="A94" s="49" t="str">
-        <x:v>구분</x:v>
-      </x:c>
-      <x:c r="B94" s="49" t="str">
-        <x:v>주제</x:v>
-      </x:c>
-      <x:c r="C94" s="49" t="str">
-        <x:v>세부 학습 내용</x:v>
-      </x:c>
-      <x:c r="D94" s="49" t="str">
-        <x:v>시간(분)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="65" customHeight="1">
-      <x:c r="A95" s="125" t="str">
-        <x:v>이론</x:v>
-      </x:c>
-      <x:c r="B95" s="126" t="str">
-        <x:v>냉각 대응과 정비·구매의 시작·완료 조건 차이</x:v>
-      </x:c>
-      <x:c r="C95" s="127" t="str">
-        <x:v>냉각 대응과 정비·구매의 시작·완료 조건 차이을(를) 오늘 수행할 과제와 연결해 설명한다. 온라인 대응: 통합 온라인10 + 11 / 실전 온라인7 + 8. 복습 대신 적용에 필요한 설명으로 한정한다.</x:v>
-      </x:c>
-      <x:c r="D95" s="128" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" s="1" customFormat="1" ht="60" customHeight="1">
-      <x:c r="A96" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B96" s="130" t="str">
-        <x:v>기존 승인 구조를 정비 흐름으로 작성</x:v>
-      </x:c>
-      <x:c r="C96" s="131" t="str">
-        <x:v>기존 승인 패턴으로 정비 도래·계획·승인·오더·공지 흐름을 작성한다.</x:v>
-      </x:c>
-      <x:c r="D96" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" ht="60" customHeight="1">
-      <x:c r="A97" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B97" s="130" t="str">
-        <x:v>정비 흐름 연결·실행</x:v>
-      </x:c>
-      <x:c r="C97" s="131" t="str">
-        <x:v>정비 흐름을 연결·실행하고 정상·반려 결과를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D97" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="60" customHeight="1">
-      <x:c r="A98" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B98" s="130" t="str">
-        <x:v>구매 흐름 작성</x:v>
-      </x:c>
-      <x:c r="C98" s="131" t="str">
-        <x:v>재고 부족·구매 제안·승인·발주·입고 흐름을 작성한다.</x:v>
-      </x:c>
-      <x:c r="D98" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="60" customHeight="1">
-      <x:c r="A99" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B99" s="130" t="str">
-        <x:v>구매 흐름 연결·실행</x:v>
-      </x:c>
-      <x:c r="C99" s="131" t="str">
-        <x:v>수업용 구매 흐름을 연결·실행하고 정상·반려·재고 결과를 확인한다.</x:v>
-      </x:c>
-      <x:c r="D99" s="132" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="60" customHeight="1">
-      <x:c r="A100" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B100" s="130" t="str">
-        <x:v>교대 인수인계 흐름 실행·보완·완료 기록 확인</x:v>
-      </x:c>
-      <x:c r="C100" s="131" t="str">
-        <x:v>앞 회차의 인수인계 흐름을 설비·교대 입력으로 시작한다. 정상·기록 불일치·정보 누락 사례에서 인계자 검토와 인수자 확인 또는 보완 요청을 수행하고, 근거·판본·완료 기록을 저장한다.</x:v>
-      </x:c>
-      <x:c r="D100" s="132" t="n">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="68" customHeight="1">
-      <x:c r="A101" s="129" t="str">
-        <x:v>실습</x:v>
-      </x:c>
-      <x:c r="B101" s="130" t="str">
-        <x:v>ProcessGPT 강사 시연: 만든 지식·에이전트·흐름을 제품 기능과 연결해 보기</x:v>
-      </x:c>
-      <x:c r="C101" s="131" t="str">
-        <x:v>준비된 ProcessGPT 화면에서 지식·에이전트·프로세스가 연결되는 모습을 강사가 시연한다. 학생 계정 설정과 별도 제품 실습은 포함하지 않는다.</x:v>
-      </x:c>
-      <x:c r="D101" s="132" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="28" customHeight="1">
-      <x:c r="A102" s="66" t="str">
-        <x:v>회차 수업 합계 (휴식 40분 별도)</x:v>
-      </x:c>
-      <x:c r="B102"/>
-      <x:c r="C102"/>
-      <x:c r="D102" s="49" t="n">
-        <x:f>SUM(D95:D101)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="58" customHeight="1">
-      <x:c r="A103" s="66" t="str">
-        <x:v>완료 결과: 정비·구매는 기존 공통 시나리오로 수행하고 교대 인수인계는 별도 정의로 실행한다. 실제 설비 제어·발주를 인계 확인과 혼동하지 않는다. ProcessGPT는 강사가 20분 시연한다. 준비·실행 시간과 완주는 별도 실측한다.</x:v>
-      </x:c>
-      <x:c r="B103"/>
-      <x:c r="C103"/>
-      <x:c r="D103" s="49"/>
-    </x:row>
-    <x:row r="104" ht="12" customHeight="1">
-      <x:c r="A104"/>
-      <x:c r="B104"/>
-      <x:c r="C104"/>
-      <x:c r="D104"/>
-    </x:row>
-    <x:row r="105" ht="28" customHeight="1">
-      <x:c r="A105" s="66" t="str">
-        <x:v>전체 수업 시간(분)</x:v>
-      </x:c>
-      <x:c r="B105"/>
-      <x:c r="C105"/>
-      <x:c r="D105" s="49" t="n">
-        <x:f>D2</x:f>
-        <x:v>1800</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="28" customHeight="1">
-      <x:c r="A106" s="66" t="str">
-        <x:v>전체 휴식 시간(40분×9회)</x:v>
-      </x:c>
-      <x:c r="B106"/>
-      <x:c r="C106"/>
-      <x:c r="D106" s="49" t="n">
+      <x:c r="A77" s="135" t="str">
+        <x:v>전체 휴식 시간(분)</x:v>
+      </x:c>
+      <x:c r="B77" s="135"/>
+      <x:c r="C77" s="135"/>
+      <x:c r="D77" s="135" t="n">
         <x:f>40*9</x:f>
         <x:v>360</x:v>
       </x:c>
     </x:row>
+    <x:row r="78" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A78" s="135" t="str">
+        <x:v>전체 편성 시간(분)</x:v>
+      </x:c>
+      <x:c r="B78" s="135"/>
+      <x:c r="C78" s="135"/>
+      <x:c r="D78" s="135" t="n">
+        <x:f>SUM(D76:D77)</x:f>
+        <x:v>2160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" s="1" customFormat="1" ht="58" customHeight="1">
+      <x:c r="A79" s="135"/>
+      <x:c r="B79" s="135"/>
+      <x:c r="C79" s="135"/>
+      <x:c r="D79" s="135"/>
+    </x:row>
+    <x:row r="80" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A80" s="135"/>
+      <x:c r="B80" s="135"/>
+      <x:c r="C80" s="135"/>
+      <x:c r="D80" s="135"/>
+    </x:row>
+    <x:row r="81" s="1" customFormat="1" ht="36" customHeight="1">
+      <x:c r="A81" s="135"/>
+      <x:c r="B81" s="135"/>
+      <x:c r="C81" s="135"/>
+      <x:c r="D81" s="135"/>
+    </x:row>
+    <x:row r="82" s="1" customFormat="1" ht="26" customHeight="1">
+      <x:c r="A82" s="135"/>
+      <x:c r="B82" s="135"/>
+      <x:c r="C82" s="135"/>
+      <x:c r="D82" s="135"/>
+    </x:row>
+    <x:row r="83" s="1" customFormat="1" ht="65" customHeight="1">
+      <x:c r="A83" s="135"/>
+      <x:c r="B83" s="135"/>
+      <x:c r="C83" s="135"/>
+      <x:c r="D83" s="135"/>
+    </x:row>
+    <x:row r="84" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A84" s="135"/>
+      <x:c r="B84" s="135"/>
+      <x:c r="C84" s="135"/>
+      <x:c r="D84" s="135"/>
+    </x:row>
+    <x:row r="85" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A85" s="135"/>
+      <x:c r="B85" s="135"/>
+      <x:c r="C85" s="135"/>
+      <x:c r="D85" s="135"/>
+    </x:row>
+    <x:row r="86" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A86" s="135"/>
+      <x:c r="B86" s="135"/>
+      <x:c r="C86" s="135"/>
+      <x:c r="D86" s="135"/>
+    </x:row>
+    <x:row r="87" ht="68" customHeight="1">
+      <x:c r="A87" s="135"/>
+      <x:c r="B87" s="135"/>
+      <x:c r="C87" s="135"/>
+      <x:c r="D87" s="135"/>
+    </x:row>
+    <x:row r="88" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A88" s="135"/>
+      <x:c r="B88" s="135"/>
+      <x:c r="C88" s="135"/>
+      <x:c r="D88" s="135"/>
+    </x:row>
+    <x:row r="89" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A89" s="135"/>
+      <x:c r="B89" s="135"/>
+      <x:c r="C89" s="135"/>
+      <x:c r="D89" s="135"/>
+    </x:row>
+    <x:row r="90" s="1" customFormat="1" ht="28" customHeight="1">
+      <x:c r="A90" s="135"/>
+      <x:c r="B90" s="135"/>
+      <x:c r="C90" s="135"/>
+      <x:c r="D90" s="135"/>
+    </x:row>
+    <x:row r="91" ht="58" customHeight="1">
+      <x:c r="A91" s="135"/>
+      <x:c r="B91" s="135"/>
+      <x:c r="C91" s="135"/>
+      <x:c r="D91" s="135"/>
+    </x:row>
+    <x:row r="92" s="1" customFormat="1" ht="12" customHeight="1">
+      <x:c r="A92" s="135"/>
+      <x:c r="B92" s="135"/>
+      <x:c r="C92" s="135"/>
+      <x:c r="D92" s="135"/>
+    </x:row>
+    <x:row r="93" ht="36" customHeight="1">
+      <x:c r="A93" s="135"/>
+      <x:c r="B93" s="135"/>
+      <x:c r="C93" s="135"/>
+      <x:c r="D93" s="135"/>
+    </x:row>
+    <x:row r="94" s="1" customFormat="1" ht="26" customHeight="1">
+      <x:c r="A94" s="135"/>
+      <x:c r="B94" s="135"/>
+      <x:c r="C94" s="135"/>
+      <x:c r="D94" s="135"/>
+    </x:row>
+    <x:row r="95" ht="65" customHeight="1">
+      <x:c r="A95" s="135"/>
+      <x:c r="B95" s="135"/>
+      <x:c r="C95" s="135"/>
+      <x:c r="D95" s="135"/>
+    </x:row>
+    <x:row r="96" s="1" customFormat="1" ht="60" customHeight="1">
+      <x:c r="A96" s="135"/>
+      <x:c r="B96" s="135"/>
+      <x:c r="C96" s="135"/>
+      <x:c r="D96" s="135"/>
+    </x:row>
+    <x:row r="97" ht="60" customHeight="1">
+      <x:c r="A97" s="135"/>
+      <x:c r="B97" s="135"/>
+      <x:c r="C97" s="135"/>
+      <x:c r="D97" s="135"/>
+    </x:row>
+    <x:row r="98" ht="60" customHeight="1">
+      <x:c r="A98" s="135"/>
+      <x:c r="B98" s="135"/>
+      <x:c r="C98" s="135"/>
+      <x:c r="D98" s="135"/>
+    </x:row>
+    <x:row r="99" ht="60" customHeight="1">
+      <x:c r="A99" s="135"/>
+      <x:c r="B99" s="135"/>
+      <x:c r="C99" s="135"/>
+      <x:c r="D99" s="135"/>
+    </x:row>
+    <x:row r="100" ht="60" customHeight="1">
+      <x:c r="A100" s="135"/>
+      <x:c r="B100" s="135"/>
+      <x:c r="C100" s="135"/>
+      <x:c r="D100" s="135"/>
+    </x:row>
+    <x:row r="101" ht="68" customHeight="1">
+      <x:c r="A101" s="135"/>
+      <x:c r="B101" s="135"/>
+      <x:c r="C101" s="135"/>
+      <x:c r="D101" s="135"/>
+    </x:row>
+    <x:row r="102" ht="28" customHeight="1">
+      <x:c r="A102" s="135"/>
+      <x:c r="B102" s="135"/>
+      <x:c r="C102" s="135"/>
+      <x:c r="D102" s="135"/>
+    </x:row>
+    <x:row r="103" ht="58" customHeight="1">
+      <x:c r="A103" s="135"/>
+      <x:c r="B103" s="135"/>
+      <x:c r="C103" s="135"/>
+      <x:c r="D103" s="135"/>
+    </x:row>
+    <x:row r="104" ht="12" customHeight="1">
+      <x:c r="A104" s="135"/>
+      <x:c r="B104" s="135"/>
+      <x:c r="C104" s="135"/>
+      <x:c r="D104" s="135"/>
+    </x:row>
+    <x:row r="105" ht="28" customHeight="1">
+      <x:c r="A105" s="135"/>
+      <x:c r="B105" s="135"/>
+      <x:c r="C105" s="135"/>
+      <x:c r="D105" s="135"/>
+    </x:row>
+    <x:row r="106" ht="28" customHeight="1">
+      <x:c r="A106" s="135"/>
+      <x:c r="B106" s="135"/>
+      <x:c r="C106" s="135"/>
+      <x:c r="D106" s="135"/>
+    </x:row>
     <x:row r="107" ht="28" customHeight="1">
-      <x:c r="A107" s="66" t="str">
-        <x:v>전체 편성 시간(분)</x:v>
-      </x:c>
-      <x:c r="B107"/>
-      <x:c r="C107"/>
-      <x:c r="D107" s="49" t="n">
-        <x:f>SUM(D105:D106)</x:f>
-        <x:v>2160</x:v>
-      </x:c>
+      <x:c r="A107" s="135"/>
+      <x:c r="B107" s="135"/>
+      <x:c r="C107" s="135"/>
+      <x:c r="D107" s="135"/>
     </x:row>
     <x:row r="108" ht="48" customHeight="1">
-      <x:c r="A108" s="66" t="str">
-        <x:v>운영: 시간은 학생 수행의 초기 편성값이며 실측이 아니다. 온라인 배포일보다 먼저 필요한 단원은 사전 열람 자료를 제공한다. 강사는 막힌 부분을 지원한다.</x:v>
-      </x:c>
-      <x:c r="B108"/>
-      <x:c r="C108"/>
-      <x:c r="D108" s="49"/>
+      <x:c r="A108" s="135"/>
+      <x:c r="B108" s="135"/>
+      <x:c r="C108" s="135"/>
+      <x:c r="D108" s="135"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109"/>
-      <x:c r="B109"/>
-      <x:c r="C109"/>
-      <x:c r="D109"/>
+      <x:c r="A109" s="135"/>
+      <x:c r="B109" s="135"/>
+      <x:c r="C109" s="135"/>
+      <x:c r="D109" s="135"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110"/>
-      <x:c r="B110"/>
-      <x:c r="C110"/>
-      <x:c r="D110"/>
+      <x:c r="A110" s="135"/>
+      <x:c r="B110" s="135"/>
+      <x:c r="C110" s="135"/>
+      <x:c r="D110" s="135"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111"/>
-      <x:c r="B111"/>
-      <x:c r="C111"/>
-      <x:c r="D111"/>
+      <x:c r="A111" s="135"/>
+      <x:c r="B111" s="135"/>
+      <x:c r="C111" s="135"/>
+      <x:c r="D111" s="135"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112"/>
-      <x:c r="B112"/>
-      <x:c r="C112"/>
-      <x:c r="D112"/>
+      <x:c r="A112" s="135"/>
+      <x:c r="B112" s="135"/>
+      <x:c r="C112" s="135"/>
+      <x:c r="D112" s="135"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113"/>
-      <x:c r="B113"/>
-      <x:c r="C113"/>
-      <x:c r="D113"/>
+      <x:c r="A113" s="135"/>
+      <x:c r="B113" s="135"/>
+      <x:c r="C113" s="135"/>
+      <x:c r="D113" s="135"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114"/>
-      <x:c r="B114"/>
-      <x:c r="C114"/>
-      <x:c r="D114"/>
+      <x:c r="A114" s="135"/>
+      <x:c r="B114" s="135"/>
+      <x:c r="C114" s="135"/>
+      <x:c r="D114" s="135"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115"/>
-      <x:c r="B115"/>
-      <x:c r="C115"/>
-      <x:c r="D115"/>
+      <x:c r="A115" s="135"/>
+      <x:c r="B115" s="135"/>
+      <x:c r="C115" s="135"/>
+      <x:c r="D115" s="135"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116"/>
-      <x:c r="B116"/>
-      <x:c r="C116"/>
-      <x:c r="D116"/>
+      <x:c r="A116" s="135"/>
+      <x:c r="B116" s="135"/>
+      <x:c r="C116" s="135"/>
+      <x:c r="D116" s="135"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117"/>
-      <x:c r="B117"/>
-      <x:c r="C117"/>
-      <x:c r="D117"/>
+      <x:c r="A117" s="135"/>
+      <x:c r="B117" s="135"/>
+      <x:c r="C117" s="135"/>
+      <x:c r="D117" s="135"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118"/>
-      <x:c r="B118"/>
-      <x:c r="C118"/>
-      <x:c r="D118"/>
+      <x:c r="A118" s="135"/>
+      <x:c r="B118" s="135"/>
+      <x:c r="C118" s="135"/>
+      <x:c r="D118" s="135"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119"/>
-      <x:c r="B119"/>
-      <x:c r="C119"/>
-      <x:c r="D119"/>
+      <x:c r="A119" s="135"/>
+      <x:c r="B119" s="135"/>
+      <x:c r="C119" s="135"/>
+      <x:c r="D119" s="135"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120"/>
-      <x:c r="B120"/>
-      <x:c r="C120"/>
-      <x:c r="D120"/>
+      <x:c r="A120" s="135"/>
+      <x:c r="B120" s="135"/>
+      <x:c r="C120" s="135"/>
+      <x:c r="D120" s="135"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121"/>
-      <x:c r="B121"/>
-      <x:c r="C121"/>
-      <x:c r="D121"/>
+      <x:c r="A121" s="135"/>
+      <x:c r="B121" s="135"/>
+      <x:c r="C121" s="135"/>
+      <x:c r="D121" s="135"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122"/>
-      <x:c r="B122"/>
-      <x:c r="C122"/>
-      <x:c r="D122"/>
+      <x:c r="A122" s="135"/>
+      <x:c r="B122" s="135"/>
+      <x:c r="C122" s="135"/>
+      <x:c r="D122" s="135"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123"/>
-      <x:c r="B123"/>
-      <x:c r="C123"/>
-      <x:c r="D123"/>
+      <x:c r="A123" s="135"/>
+      <x:c r="B123" s="135"/>
+      <x:c r="C123" s="135"/>
+      <x:c r="D123" s="135"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124"/>
-      <x:c r="B124"/>
-      <x:c r="C124"/>
-      <x:c r="D124"/>
+      <x:c r="A124" s="135"/>
+      <x:c r="B124" s="135"/>
+      <x:c r="C124" s="135"/>
+      <x:c r="D124" s="135"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125"/>
-      <x:c r="B125"/>
-      <x:c r="C125"/>
-      <x:c r="D125"/>
+      <x:c r="A125" s="135"/>
+      <x:c r="B125" s="135"/>
+      <x:c r="C125" s="135"/>
+      <x:c r="D125" s="135"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126"/>
-      <x:c r="B126"/>
-      <x:c r="C126"/>
-      <x:c r="D126"/>
+      <x:c r="A126" s="135"/>
+      <x:c r="B126" s="135"/>
+      <x:c r="C126" s="135"/>
+      <x:c r="D126" s="135"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127"/>
-      <x:c r="B127"/>
-      <x:c r="C127"/>
-      <x:c r="D127"/>
+      <x:c r="A127" s="135"/>
+      <x:c r="B127" s="135"/>
+      <x:c r="C127" s="135"/>
+      <x:c r="D127" s="135"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128"/>
-      <x:c r="B128"/>
-      <x:c r="C128"/>
-      <x:c r="D128"/>
+      <x:c r="A128" s="135"/>
+      <x:c r="B128" s="135"/>
+      <x:c r="C128" s="135"/>
+      <x:c r="D128" s="135"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129"/>
-      <x:c r="B129"/>
-      <x:c r="C129"/>
-      <x:c r="D129"/>
+      <x:c r="A129" s="135"/>
+      <x:c r="B129" s="135"/>
+      <x:c r="C129" s="135"/>
+      <x:c r="D129" s="135"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130"/>
-      <x:c r="B130"/>
-      <x:c r="C130"/>
-      <x:c r="D130"/>
+      <x:c r="A130" s="135"/>
+      <x:c r="B130" s="135"/>
+      <x:c r="C130" s="135"/>
+      <x:c r="D130" s="135"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131"/>
-      <x:c r="B131"/>
-      <x:c r="C131"/>
-      <x:c r="D131"/>
+      <x:c r="A131" s="135"/>
+      <x:c r="B131" s="135"/>
+      <x:c r="C131" s="135"/>
+      <x:c r="D131" s="135"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132"/>
-      <x:c r="B132"/>
-      <x:c r="C132"/>
-      <x:c r="D132"/>
+      <x:c r="A132" s="135"/>
+      <x:c r="B132" s="135"/>
+      <x:c r="C132" s="135"/>
+      <x:c r="D132" s="135"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133"/>
-      <x:c r="B133"/>
-      <x:c r="C133"/>
-      <x:c r="D133"/>
+      <x:c r="A133" s="135"/>
+      <x:c r="B133" s="135"/>
+      <x:c r="C133" s="135"/>
+      <x:c r="D133" s="135"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134"/>
-      <x:c r="B134"/>
-      <x:c r="C134"/>
-      <x:c r="D134"/>
+      <x:c r="A134" s="135"/>
+      <x:c r="B134" s="135"/>
+      <x:c r="C134" s="135"/>
+      <x:c r="D134" s="135"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135"/>
-      <x:c r="B135"/>
-      <x:c r="C135"/>
-      <x:c r="D135"/>
+      <x:c r="A135" s="135"/>
+      <x:c r="B135" s="135"/>
+      <x:c r="C135" s="135"/>
+      <x:c r="D135" s="135"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136"/>
-      <x:c r="B136"/>
-      <x:c r="C136"/>
-      <x:c r="D136"/>
+      <x:c r="A136" s="135"/>
+      <x:c r="B136" s="135"/>
+      <x:c r="C136" s="135"/>
+      <x:c r="D136" s="135"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137"/>
-      <x:c r="B137"/>
-      <x:c r="C137"/>
-      <x:c r="D137"/>
+      <x:c r="A137" s="135"/>
+      <x:c r="B137" s="135"/>
+      <x:c r="C137" s="135"/>
+      <x:c r="D137" s="135"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138"/>
-      <x:c r="B138"/>
-      <x:c r="C138"/>
-      <x:c r="D138"/>
+      <x:c r="A138" s="135"/>
+      <x:c r="B138" s="135"/>
+      <x:c r="C138" s="135"/>
+      <x:c r="D138" s="135"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139"/>
-      <x:c r="B139"/>
-      <x:c r="C139"/>
-      <x:c r="D139"/>
+      <x:c r="A139" s="135"/>
+      <x:c r="B139" s="135"/>
+      <x:c r="C139" s="135"/>
+      <x:c r="D139" s="135"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140"/>
-      <x:c r="B140"/>
-      <x:c r="C140"/>
-      <x:c r="D140"/>
+      <x:c r="A140" s="135"/>
+      <x:c r="B140" s="135"/>
+      <x:c r="C140" s="135"/>
+      <x:c r="D140" s="135"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141"/>
-      <x:c r="B141"/>
-      <x:c r="C141"/>
-      <x:c r="D141"/>
+      <x:c r="A141" s="135"/>
+      <x:c r="B141" s="135"/>
+      <x:c r="C141" s="135"/>
+      <x:c r="D141" s="135"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142"/>
-      <x:c r="B142"/>
-      <x:c r="C142"/>
-      <x:c r="D142"/>
+      <x:c r="A142" s="135"/>
+      <x:c r="B142" s="135"/>
+      <x:c r="C142" s="135"/>
+      <x:c r="D142" s="135"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143"/>
-      <x:c r="B143"/>
-      <x:c r="C143"/>
-      <x:c r="D143"/>
+      <x:c r="A143" s="135"/>
+      <x:c r="B143" s="135"/>
+      <x:c r="C143" s="135"/>
+      <x:c r="D143" s="135"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144"/>
-      <x:c r="B144"/>
-      <x:c r="C144"/>
-      <x:c r="D144"/>
+      <x:c r="A144" s="135"/>
+      <x:c r="B144" s="135"/>
+      <x:c r="C144" s="135"/>
+      <x:c r="D144" s="135"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145"/>
-      <x:c r="B145"/>
-      <x:c r="C145"/>
-      <x:c r="D145"/>
+      <x:c r="A145" s="135"/>
+      <x:c r="B145" s="135"/>
+      <x:c r="C145" s="135"/>
+      <x:c r="D145" s="135"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146"/>
-      <x:c r="B146"/>
-      <x:c r="C146"/>
-      <x:c r="D146"/>
+      <x:c r="A146" s="135"/>
+      <x:c r="B146" s="135"/>
+      <x:c r="C146" s="135"/>
+      <x:c r="D146" s="135"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147"/>
-      <x:c r="B147"/>
-      <x:c r="C147"/>
-      <x:c r="D147"/>
+      <x:c r="A147" s="135"/>
+      <x:c r="B147" s="135"/>
+      <x:c r="C147" s="135"/>
+      <x:c r="D147" s="135"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148"/>
-      <x:c r="B148"/>
-      <x:c r="C148"/>
-      <x:c r="D148"/>
+      <x:c r="A148" s="135"/>
+      <x:c r="B148" s="135"/>
+      <x:c r="C148" s="135"/>
+      <x:c r="D148" s="135"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149"/>
-      <x:c r="B149"/>
-      <x:c r="C149"/>
-      <x:c r="D149"/>
+      <x:c r="A149" s="135"/>
+      <x:c r="B149" s="135"/>
+      <x:c r="C149" s="135"/>
+      <x:c r="D149" s="135"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150"/>
-      <x:c r="B150"/>
-      <x:c r="C150"/>
-      <x:c r="D150"/>
+      <x:c r="A150" s="135"/>
+      <x:c r="B150" s="135"/>
+      <x:c r="C150" s="135"/>
+      <x:c r="D150" s="135"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151"/>
@@ -8450,39 +7888,29 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
-    <x:mergeCell ref="A4:C4"/>
-    <x:mergeCell ref="A13:C13"/>
-    <x:mergeCell ref="A14:D14"/>
-    <x:mergeCell ref="A16:C16"/>
-    <x:mergeCell ref="A24:C24"/>
-    <x:mergeCell ref="A25:D25"/>
-    <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A35:C35"/>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A4:D4"/>
+    <x:mergeCell ref="A10:C10"/>
+    <x:mergeCell ref="A12:D12"/>
+    <x:mergeCell ref="A18:C18"/>
+    <x:mergeCell ref="A20:D20"/>
+    <x:mergeCell ref="A26:C26"/>
+    <x:mergeCell ref="A28:D28"/>
+    <x:mergeCell ref="A34:C34"/>
     <x:mergeCell ref="A36:D36"/>
-    <x:mergeCell ref="A38:C38"/>
-    <x:mergeCell ref="A46:C46"/>
-    <x:mergeCell ref="A47:D47"/>
-    <x:mergeCell ref="A49:C49"/>
-    <x:mergeCell ref="A57:C57"/>
-    <x:mergeCell ref="A58:D58"/>
-    <x:mergeCell ref="A60:C60"/>
-    <x:mergeCell ref="A68:C68"/>
-    <x:mergeCell ref="A69:D69"/>
-    <x:mergeCell ref="A71:C71"/>
+    <x:mergeCell ref="A42:C42"/>
+    <x:mergeCell ref="A44:D44"/>
+    <x:mergeCell ref="A50:C50"/>
+    <x:mergeCell ref="A52:D52"/>
+    <x:mergeCell ref="A58:C58"/>
+    <x:mergeCell ref="A60:D60"/>
+    <x:mergeCell ref="A66:C66"/>
+    <x:mergeCell ref="A68:D68"/>
+    <x:mergeCell ref="A74:C74"/>
+    <x:mergeCell ref="A76:C76"/>
+    <x:mergeCell ref="A77:C77"/>
     <x:mergeCell ref="A78:C78"/>
-    <x:mergeCell ref="A79:D79"/>
-    <x:mergeCell ref="A81:C81"/>
-    <x:mergeCell ref="A90:C90"/>
-    <x:mergeCell ref="A91:D91"/>
-    <x:mergeCell ref="A93:C93"/>
-    <x:mergeCell ref="A102:C102"/>
-    <x:mergeCell ref="A103:D103"/>
-    <x:mergeCell ref="A105:C105"/>
-    <x:mergeCell ref="A106:C106"/>
-    <x:mergeCell ref="A107:C107"/>
-    <x:mergeCell ref="A108:D108"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Rb671491d80264b7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R7f4a1a1f640b4bb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R86cff5214ecc4afa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Raaeb30ffe83747c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R8bf50ea5b26f4890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R604ce3e088134b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="Rf4d11f162fb44998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rbb8e2240d91e468a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -974,7 +974,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="65" customHeight="1">
+    <x:row r="6" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A6" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -986,7 +986,7 @@
         </x:is>
       </x:c>
       <x:c r="C6" s="19" t="str">
-        <x:v>단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 살펴본다.</x:v>
+        <x:v>HYD의 전체 흐름을 보고 이후 실습에서 만들 지식·에이전트·업무 연결의 목표를 확인한다. 단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 살펴본다.</x:v>
       </x:c>
       <x:c r="D6" s="25" t="n">
         <x:v>10</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="12" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A12" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1094,7 +1094,7 @@
         </x:is>
       </x:c>
       <x:c r="C12" s="19" t="str">
-        <x:v>arrows.app의 노드·관계·레이블 작성 방법을 익힌다. 간단한 설비 이상 사례를 바탕으로 설비·센서·증상·원인·조치를 배치하고 각각의 연결 관계를 직접 그린다. 어떤 대상이 다른 대상과 연결되는지, 관계의 방향을 어떻게 표현하는지 살펴본다. 완성한 관계도를 통해 단순히 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 복잡한 온톨로지 스키마와 제약은 다음 학습에서 다룬다.</x:v>
+        <x:v>arrows.app의 노드·관계·레이블 작성 방법을 익힌다. 간단한 설비 이상 사례를 바탕으로 설비·센서·증상·원인·조치를 배치하고 각각의 연결 관계를 직접 그린다. 어떤 대상이 다른 대상과 연결되는지, 관계의 방향을 어떻게 표현하는지 살펴본다. 완성한 관계도를 통해 단순히 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 복잡한 온톨로지 스키마와 제약은 다음 학습에서 다룬다. 이 관계를 다음 회차에서 식별자와 속성을 갖춘 모델로 옮겨 실제 질의로 확인한다.</x:v>
       </x:c>
       <x:c r="D12" s="25" t="n">
         <x:v>30</x:v>
@@ -1151,7 +1151,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="17" s="1" customFormat="1" ht="93.5" customHeight="1">
+    <x:row r="17" s="1" customFormat="1" ht="136" customHeight="1">
       <x:c r="A17" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1163,7 +1163,7 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="27" t="str">
-        <x:v>온톨로지에서 클래스·인스턴스·속성·관계의 정확한 정의와 역할을 학습한다. 클래스가 공통 특성을 가진 대상의 유형을 표현하고, 인스턴스는 그 유형에 속하는 실제 개별 대상을 나타낸다는 점을 살펴본다. 설비·센서·부품과 HYD-01·TS1·쿨러를 비교하며 구분한다. 클래스 계층과 상속의 기초, 데이터 속성과 객체 간 관계의 차이, 속성값과 인스턴스의 구별, 관계 유형·방향·카디널리티(1:1, 1:N, N:M)를 배운다. 언제 새로운 클래스를 정의하고 언제 속성이나 관계로 표현해야 하는지 구체적인 설비 사례로 비교한다.</x:v>
+        <x:v>앞서 그린 관계도에 같은 대상의 식별 기준을 정하고, 질문에 답할 수 있는 그래프를 만든다. 온톨로지에서 클래스·인스턴스·속성·관계의 정확한 정의와 역할을 학습한다. 클래스가 공통 특성을 가진 대상의 유형을 표현하고, 인스턴스는 그 유형에 속하는 실제 개별 대상을 나타낸다는 점을 살펴본다. 설비·센서·부품과 HYD-01·TS1·쿨러를 비교하며 구분한다. 클래스 계층과 상속의 기초, 데이터 속성과 객체 간 관계의 차이, 속성값과 인스턴스의 구별, 관계 유형·방향·카디널리티(1:1, 1:N, N:M)를 배운다. 언제 새로운 클래스를 정의하고 언제 속성이나 관계로 표현해야 하는지 구체적인 설비 사례로 비교한다.</x:v>
       </x:c>
       <x:c r="D17" s="33" t="n">
         <x:v>50</x:v>
@@ -1257,7 +1257,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" s="1" customFormat="1" ht="65" customHeight="1">
+    <x:row r="23" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A23" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1267,7 +1267,7 @@
         <x:v>설계한 온톨로지를 그래프 DB에 구현하고 검증하기</x:v>
       </x:c>
       <x:c r="C23" s="27" t="str">
-        <x:v>앞 실습의 스키마·인스턴스·요구사항·원자료 검토 기록을 이어 쓴다. VS Code의 GitHub Copilot·Codex로 Cypher를 작성하고 별도 랩 DB에 적재한다. 식별자·관계 끝점·방향과 원자료 질문의 답, 반복 적재 시 중복 여부를 확인한다. 오류가 있으면 근거에 따라 수정하고 질의·결과를 저장한다.</x:v>
+        <x:v>앞 실습의 스키마·인스턴스·요구사항·원자료 검토 기록을 이어 쓴다. VS Code의 GitHub Copilot·Codex로 Cypher를 작성하고 별도 랩 DB에 적재한다. 식별자·관계 끝점·방향과 원자료 질문의 답, 반복 적재 시 중복 여부를 확인한다. 오류가 있으면 근거에 따라 수정하고 질의·결과를 저장한다. 확인한 설비 식별자와 관계는 다음 회차에서 작업 절차와 조치 조건을 연결하는 기준이 된다.</x:v>
       </x:c>
       <x:c r="D23" s="33" t="n">
         <x:v>40</x:v>
@@ -1324,7 +1324,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="28" s="1" customFormat="1" ht="93.5" customHeight="1">
+    <x:row r="28" s="1" customFormat="1" ht="136" customHeight="1">
       <x:c r="A28" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1336,7 +1336,7 @@
         </x:is>
       </x:c>
       <x:c r="C28" s="19" t="str">
-        <x:v>설비 고장 원인을 진단하는 것과 실제 조치 방법을 결정하는 것이 서로 다른 단계임을 이해한다. SOP(Standard Operating Procedure)의 목적과 역할을 배우고, 적용 대상·작업 전제 조건·안전 조건·준비사항·수행 단계·금지 사항·담당 역할·완료 확인 기준 등 SOP의 구성요소를 살펴본다. 작업 절차의 순서와 조건을 구분하고, 동일한 조치도 설비 운전 상태에 따라 수행 가능 여부가 달라지는 이유를 학습한다. HYD 온톨로지에서 고장 유형·원인·조치 방법(Skill)·작업 단계(Step)·근거 매뉴얼이 연결되는 구조와, 즉시 완화·근본 조치·예방 조치의 차이를 살펴본다.</x:v>
+        <x:v>설비 관계를 안다는 것만으로 조치를 실행할 수 없으므로, 허용 조건과 선택 근거를 구분한다. 설비 고장 원인을 진단하는 것과 실제 조치 방법을 결정하는 것이 서로 다른 단계임을 이해한다. SOP(Standard Operating Procedure)의 목적과 역할을 배우고, 적용 대상·작업 전제 조건·안전 조건·준비사항·수행 단계·금지 사항·담당 역할·완료 확인 기준 등 SOP의 구성요소를 살펴본다. 작업 절차의 순서와 조건을 구분하고, 동일한 조치도 설비 운전 상태에 따라 수행 가능 여부가 달라지는 이유를 학습한다. HYD 온톨로지에서 고장 유형·원인·조치 방법(Skill)·작업 단계(Step)·근거 매뉴얼이 연결되는 구조와, 즉시 완화·근본 조치·예방 조치의 차이를 살펴본다.</x:v>
       </x:c>
       <x:c r="D28" s="25" t="n">
         <x:v>35</x:v>
@@ -1396,7 +1396,7 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="32" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A32" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1408,13 +1408,13 @@
         </x:is>
       </x:c>
       <x:c r="C32" s="19" t="str">
-        <x:v>VS Code에서 GitHub Copilot·Codex를 활용해 이미 작업 조건이 정리된 랩 전용 SOP 자료를 사용한다. 2일차에 만든 설비 모델과 식별자를 재사용하고, 제공된 고장 유형과 조치 방법을 연결한다. 작업의 적용 조건·금지 조건·수행 단계·완료 기준을 구분해 구조화하고, 이를 DMN 형태의 입력 조건과 판단 결과로 구성한다. 조치 방법과 단계, 판단 규칙의 의미적 관계를 정리해 SOP 구조와 결정표 자료를 완성한다. 이 과정에서는 원문 문서를 자동 추출하는 인제스천을 구현하지 않는다.</x:v>
+        <x:v>VS Code에서 GitHub Copilot·Codex를 활용해 이미 작업 조건이 정리된 랩 전용 SOP 자료를 사용한다. 제공된 이전 단계의 설비 모델과 식별자를 재사용하고, 제공된 고장 유형과 조치 방법을 연결한다. 작업의 적용 조건·금지 조건·수행 단계·완료 기준을 구분해 구조화하고, 이를 DMN 형태의 입력 조건과 판단 결과로 구성한다. 조치 방법과 단계, 판단 규칙의 의미적 관계를 정리해 SOP 구조와 결정표 자료를 완성한다. 이 과정에서는 원문 문서를 자동 추출하는 인제스천을 구현하지 않는다.</x:v>
       </x:c>
       <x:c r="D32" s="25" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="33" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A33" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1426,7 +1426,7 @@
         </x:is>
       </x:c>
       <x:c r="C33" s="27" t="str">
-        <x:v>VS Code에서 앞서 작성한 결정표를 활용해 GitHub Copilot·Codex로 간단한 조치 판정 기능을 제작한다. 설비 상태·운전 조건·금지 조건 등 입력값에 따라 가능한 조치와 제외해야 하는 조치를 구분하도록 구현한다. 제공된 효과·비용·성과 지표 값을 이용해 허용된 조치 후보를 비교하고 선택 이유를 표시한다. 정상 조건·경계값·복수 규칙 일치·조치 불가 상황을 실행해 결과를 확인하고, 조건을 변경했을 때 판단이 어떻게 달라지는지 살펴본다.</x:v>
+        <x:v>VS Code에서 앞서 작성한 결정표를 활용해 GitHub Copilot·Codex로 간단한 조치 판정 기능을 제작한다. 설비 상태·운전 조건·금지 조건 등 입력값에 따라 가능한 조치와 제외해야 하는 조치를 구분하도록 구현한다. 제공된 효과·비용·성과 지표 값을 이용해 허용된 조치 후보를 비교하고 선택 이유를 표시한다. 정상 조건·경계값·복수 규칙 일치·조치 불가 상황을 실행해 결과를 확인하고, 조건을 변경했을 때 판단이 어떻게 달라지는지 살펴본다. 다음 회차에는 이 조건의 근거가 된 매뉴얼에서 지식을 추출하고 원문과 대조한다.</x:v>
       </x:c>
       <x:c r="D33" s="33" t="n">
         <x:v>50</x:v>
@@ -1483,7 +1483,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="38" s="1" customFormat="1" ht="145" customHeight="1">
+    <x:row r="38" s="1" customFormat="1" ht="208" customHeight="1">
       <x:c r="A38" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1495,7 +1495,7 @@
         </x:is>
       </x:c>
       <x:c r="C38" s="19" t="str">
-        <x:v>인제스천(Ingestion)의 의미와 필요성을 학습하고, 매뉴얼·SOP 문서·업무 DB 등 서로 다른 형태의 원천 자료를 지식으로 전환하는 전체 과정을 이해한다. 원천 확보와 보관 → 문서 내용 분석 → 증상·원인·부품·조치·판단 조건 등 지식 후보 추출 → 기존 온톨로지 스키마와 식별자에 매핑 → 원문 근거 대조와 사람 검토 → 승인된 지식 적재 → 그래프 관계·출처 조회의 단계별 역할을 살펴본다. LLM의 문서 이해 및 구조화 출력 원리를 살펴보고, 추출 과정에서 발생할 수 있는 부정 조건 누락·수치/단위 오류·잘못된 관계 추론·근거 없는 내용 생성의 위험을 배운다. 원문 페이지·문단·인용 구간, 문서 식별자와 개정 이력, 지식 소유 관계 및 변경 추적이 필요한 이유를 살펴본다. 검색해 문서를 참고하는 방식과 구조화된 지식으로 등록하는 방식의 차이도 이해한다. 마지막으로 설비의 원인·절차·규칙처럼 상대적으로 안정적인 지식과 센서·재고·운전시간처럼 지속적으로 변하는 값을 구분하고, 실제 값은 업무 DB·시계열 DB 등 원천에서 조회하도록 연결하는 원리를 살펴본다.</x:v>
+        <x:v>앞서 사용한 조치 조건을 문서에서 찾아 검토하고, 다시 출처를 확인할 수 있는 지식으로 만든다. 인제스천(Ingestion)의 의미와 필요성을 학습하고, 매뉴얼·SOP 문서·업무 DB 등 서로 다른 형태의 원천 자료를 지식으로 전환하는 전체 과정을 이해한다. 원천 확보와 보관 → 문서 내용 분석 → 증상·원인·부품·조치·판단 조건 등 지식 후보 추출 → 기존 온톨로지 스키마와 식별자에 매핑 → 원문 근거 대조와 사람 검토 → 승인된 지식 적재 → 그래프 관계·출처 조회의 단계별 역할을 살펴본다. LLM의 문서 이해 및 구조화 출력 원리를 살펴보고, 추출 과정에서 발생할 수 있는 부정 조건 누락·수치/단위 오류·잘못된 관계 추론·근거 없는 내용 생성의 위험을 배운다. 원문 페이지·문단·인용 구간, 문서 식별자와 개정 이력, 지식 소유 관계 및 변경 추적이 필요한 이유를 살펴본다. 검색해 문서를 참고하는 방식과 구조화된 지식으로 등록하는 방식의 차이도 이해한다. 마지막으로 설비의 원인·절차·규칙처럼 상대적으로 안정적인 지식과 센서·재고·운전시간처럼 지속적으로 변하는 값을 구분하고, 실제 값은 업무 DB·시계열 DB 등 원천에서 조회하도록 연결하는 원리를 살펴본다.</x:v>
       </x:c>
       <x:c r="D38" s="25" t="n">
         <x:v>40</x:v>
@@ -1507,10 +1507,8 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B39" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">현장 매뉴얼에서 판단 근거를 추출하고 검증된 지식으로 등록하기</x:t>
-        </x:is>
+      <x:c r="B39" s="31" t="str">
+        <x:v>매뉴얼 원문과 등록된 지식의 조건·출처 대조하기</x:v>
       </x:c>
       <x:c r="C39" s="27" t="str">
         <x:v>제공 매뉴얼의 원문과 포털에 등록된 추출·검토 결과를 나란히 확인한다. 작업 순서·단위·금지 조건·대상 설비를 비교하고 수정하거나 제외할 후보를 표시한다. 지식 지도에서 채택된 항목의 설비·조치·출처 연결을 찾는다. 직접 추가 적재는 마지막 교대 실습에서 제공 보충 매뉴얼로 수행한다.</x:v>
@@ -1537,7 +1535,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="41" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A41" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1549,13 +1547,13 @@
         </x:is>
       </x:c>
       <x:c r="C41" s="27" t="str">
-        <x:v>VS Code에서 앞서 추출한 지식 후보를 원문과 대조해 채택·수정·제외한다. 2일차에 만든 모델과 3일차에 학습한 조치·규칙의 구조를 재사용하여 후보를 해당 클래스·인스턴스·관계에 매핑한다. GitHub Copilot·Codex로 기존 식별자를 활용한 그래프 DB 적재 코드를 구현하고, 검토한 항목만 랩 전용 그래프 DB에 반영한다. 이후 고장 유형에서 원인·조치·판단 규칙·원문 출처로 이어지는 관계를 조회하고, 문서에서 추출한 지식이 앞서 만든 그래프에 보강된 결과를 확인한다.</x:v>
+        <x:v>VS Code에서 앞서 추출한 지식 후보를 원문과 대조해 채택·수정·제외한다. 제공된 이전 단계의 모델과 3일차에 학습한 조치·규칙의 구조를 재사용하여 후보를 해당 클래스·인스턴스·관계에 매핑한다. GitHub Copilot·Codex로 기존 식별자를 활용한 그래프 DB 적재 코드를 구현하고, 검토한 항목만 랩 전용 그래프 DB에 반영한다. 이후 고장 유형에서 원인·조치·판단 규칙·원문 출처로 이어지는 관계를 조회하고, 문서에서 추출한 지식이 앞서 만든 그래프에 보강된 결과를 확인한다.</x:v>
       </x:c>
       <x:c r="D41" s="33" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="42" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A42" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1567,7 +1565,7 @@
         </x:is>
       </x:c>
       <x:c r="C42" s="19" t="str">
-        <x:v>1일차 온톨로지의 필요성에서 시작해 2일차 클래스·인스턴스·속성·관계·스키마와 그래프 DB, 3일차 SOP·DMN·BSC/KPI의 조치·판단·성과 체계, 4일차 원천 자료 추출·검토·인제스천·출처 관리를 하나의 흐름으로 복습한다. 각 단계의 입력과 결과물, 지식 구조와 실제 데이터의 차이, 판단 규칙과 근거 문서의 관계를 되짚는다. 이렇게 구축된 지식과 규칙이 이후 에이전트의 업무 판단과 도구 활용에 어떤 역할을 하는지 연결해 살펴본다. 새로운 실습은 진행하지 않는다.</x:v>
+        <x:v>1일차 온톨로지의 필요성에서 시작해 2일차 클래스·인스턴스·속성·관계·스키마와 그래프 DB, 3일차 SOP·DMN·BSC/KPI의 조치·판단·성과 체계, 4일차 원천 자료 추출·검토·인제스천·출처 관리를 하나의 흐름으로 복습한다. 각 단계의 입력과 결과물, 지식 구조와 실제 데이터의 차이, 판단 규칙과 근거 문서의 관계를 되짚는다. 이렇게 구축된 지식과 규칙이 이후 에이전트의 업무 판단과 도구 활용에 어떤 역할을 하는지 연결해 살펴본다. 새로운 실습은 진행하지 않는다. 검토한 지식은 다음 회차 에이전트가 원인 후보와 점검 순서를 제안할 때 사용하는 근거가 된다.</x:v>
       </x:c>
       <x:c r="D42" s="25" t="n">
         <x:v>30</x:v>
@@ -1619,7 +1617,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="47" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="47" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A47" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1631,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c r="C47" s="53" t="str">
-        <x:v>LLM의 응답 생성, RAG의 근거 검색, Agent의 목표 지향 작업 수행을 구분한다. 요청 해석→계획→도구 선택·호출→결과 관찰→필요 시 재시도→종료의 실행 고리를 살펴보고, 단순 답변과 점검·요청 등 업무 산출물 생성의 차이를 쿨러 사례로 연결한다.</x:v>
+        <x:v>지식 조회 결과를 실제 요청의 답과 점검 제안으로 바꾸고, 근거 없는 단정을 찾아낸다. LLM의 응답 생성, RAG의 근거 검색, Agent의 목표 지향 작업 수행을 구분한다. 요청 해석→계획→도구 선택·호출→결과 관찰→필요 시 재시도→종료의 실행 고리를 살펴보고, 단순 답변과 점검·요청 등 업무 산출물 생성의 차이를 쿨러 사례로 연결한다.</x:v>
       </x:c>
       <x:c r="D47" s="54" t="n">
         <x:v>40</x:v>
@@ -1707,7 +1705,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="52" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A52" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1719,7 +1717,7 @@
         </x:is>
       </x:c>
       <x:c r="C52" s="60" t="str">
-        <x:v>기존 HYD 센서 시계열 또는 사전 배포 CSV에서 온도·압력·시간 변화와 상승 구간을 비교하고 도표를 생성한다. 이상 구간·관련 태그·조회 기간을 근거와 함께 요약하되 상관관계로 고장 원인을 단정하지 않는 출력을 점검한다.</x:v>
+        <x:v>기존 HYD 센서 시계열 또는 사전 배포 CSV에서 온도·압력·시간 변화와 상승 구간을 비교하고 도표를 생성한다. 이상 구간·관련 태그·조회 기간을 근거와 함께 요약하되 상관관계로 고장 원인을 단정하지 않는 출력을 점검한다. 다음 회차에는 반복하는 작업 방법을 스킬로 정리하고 필요한 도구를 연결한다.</x:v>
       </x:c>
       <x:c r="D52" s="61" t="n">
         <x:v>40</x:v>
@@ -1771,7 +1769,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="57" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="57" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A57" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1783,7 +1781,7 @@
         </x:is>
       </x:c>
       <x:c r="C57" s="53" t="str">
-        <x:v>Agent Skill의 목적, SKILL.md의 작업 목적·호출 조건·입력·출력·순서·예외 지침, SOP의 현장 작업 절차와 에이전트 실행 지침의 차이를 살펴본다. 재사용 지침과 한번의 프롬프트를 구분한다.</x:v>
+        <x:v>앞서 만든 에이전트가 같은 작업을 반복할 수 있도록 지침과 도구의 역할을 구분한다. Agent Skill의 목적, SKILL.md의 작업 목적·호출 조건·입력·출력·순서·예외 지침, SOP의 현장 작업 절차와 에이전트 실행 지침의 차이를 살펴본다. 재사용 지침과 한번의 프롬프트를 구분한다.</x:v>
       </x:c>
       <x:c r="D57" s="54" t="n">
         <x:v>35</x:v>
@@ -1807,7 +1805,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="59" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A59" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1819,7 +1817,7 @@
         </x:is>
       </x:c>
       <x:c r="C59" s="53" t="str">
-        <x:v>도구별 읽기/쓰기 권한, 파일 접근 범위, 인증 비밀값, 외부 응답의 불완전성, 실패·타임아웃과 근거 표시를 살펴본다. HYD 포털에서 학생이 등록한 서버는 연결 검사 후 읽기 전용 도구를 선택해 사용하는 범위를 확인한다.</x:v>
+        <x:v>도구별 읽기·쓰기 권한, 파일 접근 범위, 인증 정보, 실패·시간 초과와 근거 표시를 살펴본다. 포털에서 허용된 수업 도구 사용과 로컬 VS Code의 MCP 연결을 구분한다. 포털에 임의 서버를 추가하는 기능은 사용하지 않는다.</x:v>
       </x:c>
       <x:c r="D59" s="54" t="n">
         <x:v>20</x:v>
@@ -1877,7 +1875,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="63" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A63" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1889,7 +1887,7 @@
         </x:is>
       </x:c>
       <x:c r="C63" s="53" t="str">
-        <x:v>Notion에서 내보낸 Markdown 학습노트나 제공 매뉴얼로 문항 생성→학생 답변 입력→정답·출처 기반 피드백→다음 문항 제공의 대화를 구성한다. 텍스트 파일 기반으로 우선 완주하며 실서비스 Notion API 연동은 필수로 가정하지 않는다.</x:v>
+        <x:v>Notion에서 내보낸 Markdown 학습노트나 제공 매뉴얼로 문항 생성→학생 답변 입력→정답·출처 기반 피드백→다음 문항 제공의 대화를 구성한다. 텍스트 파일 기반으로 우선 완주하며 실서비스 Notion API 연동은 필수로 가정하지 않는다. 다음 회차에는 정보가 부족한 요청을 질문으로 보완하고 기능 변경의 조건을 명세한다.</x:v>
       </x:c>
       <x:c r="D63" s="54" t="n">
         <x:v>45</x:v>
@@ -1941,7 +1939,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="68" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="68" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A68" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1953,7 +1951,7 @@
         </x:is>
       </x:c>
       <x:c r="C68" s="53" t="str">
-        <x:v>HITL의 정의, 자동 처리와 승인·보류·거절의 구분, 승인권자와 권한의 경계, 사람의 책임과 결정 기록을 살펴본다. AI의 자기 검토와 실제 사람 승인 절차는 다른 것임을 구분한다.</x:v>
+        <x:v>앞서 만든 업무 요청 기능이 정보 누락이나 새 요구를 만났을 때 지켜야 할 동작을 정한다. HITL의 정의, 자동 처리와 승인·보류·거절의 구분, 승인권자와 권한의 경계, 사람의 책임과 결정 기록을 살펴본다. AI의 자기 검토와 실제 사람 승인 절차는 다른 것임을 구분한다.</x:v>
       </x:c>
       <x:c r="D68" s="54" t="n">
         <x:v>20</x:v>
@@ -1977,7 +1975,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="70" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A70" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1989,7 +1987,7 @@
         </x:is>
       </x:c>
       <x:c r="C70" s="53" t="str">
-        <x:v>5회차에서 만든 후속 업무 요청 결과와 처리 프로젝트를 재사용한다. 해당 업무의 필수 정보가 빠지면 확정하지 않고 확인 질문을 생성하며, 추가 입력 후 다시 판단해 상태 변화를 기록한다.</x:v>
+        <x:v>제공된 5회차 완성 시작본의 후속 업무 요청 결과와 처리 프로젝트를 재사용한다. 해당 업무의 필수 정보가 빠지면 확정하지 않고 확인 질문을 생성하며, 추가 입력 후 다시 판단해 상태 변화를 기록한다.</x:v>
       </x:c>
       <x:c r="D70" s="54" t="n">
         <x:v>45</x:v>
@@ -2047,7 +2045,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="74" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A74" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2059,7 +2057,7 @@
         </x:is>
       </x:c>
       <x:c r="C74" s="53" t="str">
-        <x:v>같은 프로젝트의 spec.md에 일반·긴급 요청, 필수 정보 누락 시 보류, 승인 없이 확정 금지, 결과 형식·수용 기준을 명시한다. 구현 후 두 요청을 재실행하고 실제 출력과 명세의 기대 결과를 비교한다.</x:v>
+        <x:v>같은 프로젝트의 spec.md에 일반·긴급 요청, 필수 정보 누락 시 보류, 승인 없이 확정 금지, 결과 형식·수용 기준을 명시한다. 구현 후 두 요청을 재실행하고 실제 출력과 명세의 기대 결과를 비교한다. 이 명세와 출력 사례를 다음 회차에서 실행 가능한 검증 시나리오로 바꾼다.</x:v>
       </x:c>
       <x:c r="D74" s="54" t="n">
         <x:v>25</x:v>
@@ -2111,7 +2109,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="79" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A79" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2123,13 +2121,13 @@
         </x:is>
       </x:c>
       <x:c r="C79" s="53" t="str">
-        <x:v>BDD의 Given/When/Then 구조, 요구 명세(SDD)와 행동 검증(BDD)의 차이, 정상·경계·예외·회귀 테스트를 살펴본다. 자연어 시나리오가 실행 가능한 검증 입력·기대 결과와 연결돼야 하는 이유를 살펴본다.</x:v>
+        <x:v>앞서 정한 명세가 실제 출력에서도 지켜지는지 확인하고 여러 출처를 연결한 결과를 검증한다. BDD의 Given/When/Then 구조, 요구 명세(SDD)와 행동 검증(BDD)의 차이, 정상·경계·예외·회귀 테스트를 살펴본다. 자연어 시나리오가 실행 가능한 검증 입력·기대 결과와 연결돼야 하는 이유를 살펴본다.</x:v>
       </x:c>
       <x:c r="D79" s="54" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="80" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A80" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2141,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c r="C80" s="60" t="str">
-        <x:v>7일차 spec.md와 동일 에이전트를 활용한다. 일반 정비, 긴급 정비, 필수 정보 누락, 승인 거절, 도구 오류에 대해 Given·When·Then과 입력값·기대 상태·출력 계약을 작성한다.</x:v>
+        <x:v>제공된 7일차 시작본의 spec.md와 동일 에이전트를 활용한다. 일반 정비, 긴급 정비, 필수 정보 누락, 승인 거절, 도구 오류에 대해 Given·When·Then과 입력값·기대 상태·출력 계약을 작성한다.</x:v>
       </x:c>
       <x:c r="D80" s="61" t="n">
         <x:v>40</x:v>
@@ -2201,7 +2199,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="84" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A84" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2213,7 +2211,7 @@
         </x:is>
       </x:c>
       <x:c r="C84" s="60" t="str">
-        <x:v>에이전트의 목표와 도구, Skill·MCP의 구분, HITL, SDD·BDD와 회귀 검증, 응용별 산출물의 차이를 복습한다. 신규 실습·과제 없이 배운 내용을 정리한다.</x:v>
+        <x:v>에이전트의 목표와 도구, Skill·MCP의 구분, HITL, SDD·BDD와 회귀 검증, 응용별 산출물의 차이를 복습한다. 신규 실습·과제 없이 배운 내용을 정리한다. 다음 회차에는 검증한 작업을 사람의 승인과 함께 하나의 BPMN 흐름으로 표현한다.</x:v>
       </x:c>
       <x:c r="D84" s="61" t="n">
         <x:v>30</x:v>
@@ -2265,7 +2263,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="89" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="89" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A89" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2277,7 +2275,7 @@
         </x:is>
       </x:c>
       <x:c r="C89" s="53" t="str">
-        <x:v>비즈니스 프로세스의 정의, Task와 End-to-End의 차이, 시작 조건·입력·출력·책임자·완료 조건을 살펴본다. BPM의 분석→설계→실행→모니터링→개선과 AS-IS/TO-BE를 다루고 에이전트만으로 전체 업무 순서와 책임이 보장되지 않는 이유를 연결한다.</x:v>
+        <x:v>개별 에이전트의 답을 넘어서 작업 순서·담당자·승인·완료를 하나의 흐름으로 표현한다. 비즈니스 프로세스의 정의, Task와 End-to-End의 차이, 시작 조건·입력·출력·책임자·완료 조건을 살펴본다. BPM의 분석→설계→실행→모니터링→개선과 AS-IS/TO-BE를 다루고 에이전트만으로 전체 업무 순서와 책임이 보장되지 않는 이유를 연결한다.</x:v>
       </x:c>
       <x:c r="D89" s="54" t="n">
         <x:v>35</x:v>
@@ -2371,7 +2369,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="95" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A95" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2383,7 +2381,7 @@
         </x:is>
       </x:c>
       <x:c r="C95" s="53" t="str">
-        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다. 이 승인·반려 패턴을 다음 회차의 정기 점검과 재고 보충 흐름에 적용한다.</x:v>
       </x:c>
       <x:c r="D95" s="54" t="n">
         <x:v>35</x:v>
@@ -2435,7 +2433,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="100" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="100" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A100" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2447,7 +2445,7 @@
         </x:is>
       </x:c>
       <x:c r="C100" s="53" t="str">
-        <x:v>설비 경보, 정기 점검 도래, 재고 부족이라는 시작 조건과 에이전트·승인자·실행 시스템의 차이를 비교한다. 프로세스 정의·인스턴스·배포, 대기와 완료 상태, 실행 기록·모니터링·병목·지표를 설명하고 같은 BPMN 패턴의 재사용 원리를 정리한다.</x:v>
+        <x:v>앞서 익힌 승인 흐름을 정비와 구매에 적용하며 시작 조건과 처리 결과의 차이를 비교한다. 설비 경보, 정기 점검 도래, 재고 부족이라는 시작 조건과 에이전트·승인자·실행 시스템의 차이를 비교한다. 프로세스 정의·인스턴스·배포, 대기와 완료 상태, 실행 기록·모니터링·병목·지표를 설명하고 같은 BPMN 패턴의 재사용 원리를 정리한다.</x:v>
       </x:c>
       <x:c r="D100" s="54" t="n">
         <x:v>35</x:v>
@@ -2525,7 +2523,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="105" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A105" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2537,7 +2535,7 @@
         </x:is>
       </x:c>
       <x:c r="C105" s="60" t="str">
-        <x:v>설비 조치·정기 점검·재고 보충의 시작 이벤트, 에이전트 판단, 사람 승인·반려, 시스템 처리와 종료 기록을 되짚는다. 온톨로지→에이전트→프로세스의 연결을 복습하며 새로운 실습은 하지 않는다.</x:v>
+        <x:v>설비 조치·정기 점검·재고 보충의 시작 이벤트, 에이전트 판단, 사람 승인·반려, 시스템 처리와 종료 기록을 되짚는다. 온톨로지→에이전트→프로세스의 연결을 복습하며 새로운 실습은 하지 않는다. 다음 회차에는 설비·정비·재고 기록을 교대 인계안으로 묶고 사람이 검토·확인하는 흐름을 완성한다.</x:v>
       </x:c>
       <x:c r="D105" s="61" t="n">
         <x:v>30</x:v>
@@ -2587,7 +2585,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="110" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="110" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A110" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2599,7 +2597,7 @@
         </x:is>
       </x:c>
       <x:c r="C110" s="53" t="str">
-        <x:v>설비·센서·고장 관계를 정의하는 클래스·인스턴스·스키마, 그래프 질의, SOP·DMN·BSC/KPI, 문서 인제스천과 출처, 정적 지식과 현재 DB 값의 구분을 되짚는다. 앞선 영역 Wrap-up의 단순 반복보다 에이전트 입력으로 연결되는 구조를 중심으로 정리한다.</x:v>
+        <x:v>그동안 만든 지식·에이전트·업무 흐름을 교대 인수인계 한 건에 연결한다. 설비·센서·고장 관계를 정의하는 클래스·인스턴스·스키마, 그래프 질의, SOP·DMN·BSC/KPI, 문서 인제스천과 출처, 정적 지식과 현재 DB 값의 구분을 되짚는다. 앞선 영역 Wrap-up의 단순 반복보다 에이전트 입력으로 연결되는 구조를 중심으로 정리한다.</x:v>
       </x:c>
       <x:c r="D110" s="54" t="n">
         <x:v>30</x:v>
@@ -2705,7 +2703,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="117" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A117" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2717,7 +2715,7 @@
         </x:is>
       </x:c>
       <x:c r="C117" s="60" t="str">
-        <x:v>첫날 준비한 Notion 학습노트에 개념·참고 자료·실습 산출물·검증 결과를 연결해 기록한다. 수업 계정에서 Notion 연결과 쓰기 권한이 검증된 경우 MCP 연동을 시연하고, 미연결 환경에서는 준비한 Markdown을 Notion에 직접 정리한다.</x:v>
+        <x:v>첫날 준비한 Notion 학습노트에 개념·참고 자료·실습 산출물·검증 결과를 연결해 기록한다. 수업 계정에서 Notion 연결과 쓰기 권한이 검증된 경우 MCP 연동을 시연하고, 미연결 환경에서는 준비한 Markdown을 Notion에 직접 정리한다. 관계 모델·판단 근거·명세·검증 결과·인계 기록을 함께 찾아볼 수 있게 정리하며 과정을 마친다.</x:v>
       </x:c>
       <x:c r="D117" s="61" t="n">
         <x:v>20</x:v>
@@ -2872,7 +2870,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="6" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A6" s="56" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -2880,7 +2878,7 @@
         <x:v>학습 내용을 지식 자산으로 전환하는 방법 이해하기</x:v>
       </x:c>
       <x:c r="C6" s="53" t="str">
-        <x:v>단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 살펴본다.</x:v>
+        <x:v>HYD의 전체 흐름을 보고 이후 실습에서 만들 지식·에이전트·업무 연결의 목표를 확인한다. 단순히 내용을 기록하는 것과 나중에 다시 찾아 활용할 수 있는 지식 자산으로 축적하는 것의 차이를 이해한다. 학습한 개념, 핵심 원리, 참고 자료와 출처, 실습 과정 및 결과를 체계적으로 연결해 기록하는 이유를 배운다. Notion을 활용해 수업이 끝난 뒤에도 지식을 검색·보완·재사용할 수 있는 개인 학습 체계를 마련하는 목적을 살펴본다.</x:v>
       </x:c>
       <x:c r="D6" s="54" t="n">
         <x:v>10</x:v>
@@ -2956,7 +2954,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="12" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A12" s="64" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -2964,7 +2962,7 @@
         <x:v>설비 이상과 원인·조치의 관계를 시각화하기</x:v>
       </x:c>
       <x:c r="C12" s="53" t="str">
-        <x:v>arrows.app의 노드·관계·레이블 작성 방법을 익힌다. 간단한 설비 이상 사례를 바탕으로 설비·센서·증상·원인·조치를 배치하고 각각의 연결 관계를 직접 그린다. 어떤 대상이 다른 대상과 연결되는지, 관계의 방향을 어떻게 표현하는지 살펴본다. 완성한 관계도를 통해 단순히 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 복잡한 온톨로지 스키마와 제약은 다음 학습에서 다룬다.</x:v>
+        <x:v>arrows.app의 노드·관계·레이블 작성 방법을 익힌다. 간단한 설비 이상 사례를 바탕으로 설비·센서·증상·원인·조치를 배치하고 각각의 연결 관계를 직접 그린다. 어떤 대상이 다른 대상과 연결되는지, 관계의 방향을 어떻게 표현하는지 살펴본다. 완성한 관계도를 통해 단순히 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 복잡한 온톨로지 스키마와 제약은 다음 학습에서 다룬다. 이 관계를 다음 회차에서 식별자와 속성을 갖춘 모델로 옮겨 실제 질의로 확인한다.</x:v>
       </x:c>
       <x:c r="D12" s="54" t="n">
         <x:v>30</x:v>
@@ -3021,7 +3019,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="17" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="17" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A17" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3033,13 +3031,13 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="53" t="str">
-        <x:v>클래스·인스턴스·속성·관계, 관계 방향, 카디널리티를 HYD 설비와 센서 실례로 살펴본다. 같은 종류의 설비와 실제 설비 1대를 구별한다.</x:v>
+        <x:v>관계도에서 부품이 쓰이는 설비와 공급 정보를 찾고, 작업 조건을 판단에 쓸 수 있는 형태로 바꾼다. 클래스·인스턴스·속성·관계, 관계 방향, 카디널리티를 HYD 설비와 센서 실례로 살펴본다. 같은 종류의 설비와 실제 설비 1대를 구별한다.</x:v>
       </x:c>
       <x:c r="D17" s="54" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="18" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A18" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3051,7 +3049,7 @@
         </x:is>
       </x:c>
       <x:c r="C18" s="60" t="str">
-        <x:v>고유 식별자, 자료형, 필수값, 레이블, 노드 간 관계·제약, 스키마와 인스턴스의 역할 차이를 살펴본다. 중복 부품 명칭과 동일 설비 구분 문제를 예로 든다.</x:v>
+        <x:v>고유 식별자, 자료형, 필수값, 레이블, 노드 간 관계·제약, 스키마와 인스턴스의 역할 차이를 살펴본다. 중복 부품 명칭과 고유 식별자로 대상을 구분한 결과를 비교한다.</x:v>
       </x:c>
       <x:c r="D18" s="61" t="n">
         <x:v>20</x:v>
@@ -3159,7 +3157,7 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="25" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A25" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3169,7 +3167,7 @@
         <x:v>작업 기준의 복합 조건과 예외를 조치 조건표로 표현하기</x:v>
       </x:c>
       <x:c r="C25" s="53" t="str">
-        <x:v>제공 SOP에서 경고·감점·제외를 구분해 입력·단위·연산자·경계·출력·출처를 조건표로 작성한다. 복수 사유를 함께 남기고, 입력 누락이 있어도 확인된 제외 근거는 보존한다. 후보 유지와 실행 승인을 구별한다.</x:v>
+        <x:v>제공 SOP에서 경고·감점·제외를 구분해 입력·단위·연산자·경계·출력·출처를 조건표로 작성한다. 복수 사유를 함께 남기고, 입력 누락이 있어도 확인된 제외 근거는 보존한다. 후보 유지와 실행 승인을 구별한다. 다음 회차에는 이 조건표로 조치 검토 결과를 만들고 매뉴얼 근거를 연결한다.</x:v>
       </x:c>
       <x:c r="D25" s="54" t="n">
         <x:v>40</x:v>
@@ -3226,7 +3224,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="30" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="30" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A30" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3238,7 +3236,7 @@
         </x:is>
       </x:c>
       <x:c r="C30" s="53" t="str">
-        <x:v>BSC 4관점과 전략 목표·KPI의 역할, 안전을 만족한 후보 사이에서 예상 비용·생산 영향·품질·에너지 측면을 비교하는 이유, What-if 분석의 개념을 살펴본다.</x:v>
+        <x:v>조건표에 따른 조치 선택과 문서의 원문 근거를 연결해 검토 결과와 작업 확인 카드를 만든다. BSC 4관점과 전략 목표·KPI의 역할, 안전을 만족한 후보 사이에서 예상 비용·생산 영향·품질·에너지 측면을 비교하는 이유, What-if 분석의 개념을 살펴본다.</x:v>
       </x:c>
       <x:c r="D30" s="54" t="n">
         <x:v>20</x:v>
@@ -3302,10 +3300,8 @@
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B34" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">현장 매뉴얼을 검토해 근거 있는 지식으로 등록하기</x:t>
-        </x:is>
+      <x:c r="B34" s="55" t="str">
+        <x:v>매뉴얼 근거를 대조하고 작업 확인 항목 정리하기</x:v>
       </x:c>
       <x:c r="C34" s="53" t="str">
         <x:v>제공 매뉴얼의 원문과 포털에 등록된 추출·검토 결과를 나란히 확인한다. 작업 순서·단위·금지 조건·대상 설비를 비교하고 수정하거나 제외할 후보를 표시한다. 지식 지도에서 채택된 항목의 설비·조치·출처 연결을 찾는다. 직접 추가 적재는 마지막 교대 실습에서 제공 보충 매뉴얼로 수행한다. 선택한 작업에 필요한 준비·금지·완료 조건을 원문 근거와 함께 정리한다.</x:v>
@@ -3346,7 +3342,7 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="37" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A37" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3358,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c r="C37" s="60" t="str">
-        <x:v>온톨로지 WHY→클래스·스키마→그래프 DB→SOP·DMN→BSC·KPI→매뉴얼 인제스천의 역할과 다음 에이전트 학습으로 이어지는 지식 자산을 복습한다. 신규 실습 없음.</x:v>
+        <x:v>온톨로지 WHY→클래스·스키마→그래프 DB→SOP·DMN→BSC·KPI→매뉴얼 인제스천의 역할과 다음 에이전트 학습으로 이어지는 지식 자산을 복습한다. 신규 실습 없음. 검토한 근거와 확인 항목은 다음 회차 점검 요청을 작성하는 에이전트의 입력으로 활용한다.</x:v>
       </x:c>
       <x:c r="D37" s="61" t="n">
         <x:v>30</x:v>
@@ -3415,7 +3411,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="42" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="42" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A42" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3427,7 +3423,7 @@
         </x:is>
       </x:c>
       <x:c r="C42" s="53" t="str">
-        <x:v>LLM·RAG·Agent의 목표·도구·반복 실행 차이, 온톨로지·업무 DB·SOP를 근거로 선택하는 과정과 실패 시 확인해야 할 실행 기록을 사례로 살펴본다.</x:v>
+        <x:v>설비·문서 근거를 점검 요청으로 연결하고 반복하는 후속 업무를 스킬과 도구로 처리한다. LLM·RAG·Agent의 목표·도구·반복 실행 차이, 온톨로지·업무 DB·SOP를 근거로 선택하는 과정과 실패 시 확인해야 할 실행 기록을 사례로 살펴본다.</x:v>
       </x:c>
       <x:c r="D42" s="54" t="n">
         <x:v>30</x:v>
@@ -3517,7 +3513,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="48" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A48" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3527,7 +3523,7 @@
         <x:v>파일·Git·시간 도구로 다음 협의 안건 만들기</x:v>
       </x:c>
       <x:c r="C48" s="53" t="str">
-        <x:v>공통 HYD 읽기 도구 연결을 확인하고 준비된 파일·Git·시간 MCP를 VS Code에서 호출한다. 앞 업무 목록과 변경 이력을 연결해 완료·미결·변경 내용 및 다음 확인 안건을 생성한다. 원자료와 대조해 로컬 파일로 저장한다. 새 서버나 외부 계정 연동은 만들지 않는다.</x:v>
+        <x:v>공통 HYD 읽기 도구 연결을 확인하고 준비된 파일·Git·시간 MCP를 VS Code에서 호출한다. 앞 업무 목록과 변경 이력을 연결해 완료·미결·변경 내용 및 다음 확인 안건을 생성한다. 원자료와 대조해 로컬 파일로 저장한다. 새 서버나 외부 계정 연동은 만들지 않는다. 다음 회차에는 점검 요청의 정보 누락을 질문으로 보완하고 기능 변경 전후의 동작을 검증한다.</x:v>
       </x:c>
       <x:c r="D48" s="54" t="n">
         <x:v>45</x:v>
@@ -3584,7 +3580,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="53" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="53" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A53" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3596,7 +3592,7 @@
         </x:is>
       </x:c>
       <x:c r="C53" s="53" t="str">
-        <x:v>HITL의 승인·보류·거절, 역할별 책임·감사 기록, AI의 자체 검토와 사람 결정의 차이를 살펴본다.</x:v>
+        <x:v>점검 요청을 바로 확정할 수 없는 경우를 구분하고, 새 요구를 반영해도 기존 조건을 지키게 한다. HITL의 승인·보류·거절, 역할별 책임·감사 기록, AI의 자체 검토와 사람 결정의 차이를 살펴본다.</x:v>
       </x:c>
       <x:c r="D53" s="54" t="n">
         <x:v>20</x:v>
@@ -3620,7 +3616,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="55" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A55" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3630,7 +3626,7 @@
         <x:v>점검 요청의 부족한 정보를 질문하고 재개하기</x:v>
       </x:c>
       <x:c r="C55" s="53" t="str">
-        <x:v>4회차 점검 요청 초안 프로젝트의 필수 입력과 완료 기준을 정한다. 누락 시 보류·질문·추가 답변 반영·재판단을 구현하고 근거와 처리 상태를 보존한다. 사람 승인이 필요한 결과를 자동 확정하지 않는다.</x:v>
+        <x:v>제공된 4회차 점검 요청 시작본의 필수 입력과 완료 기준을 정한다. 누락 시 보류·질문·추가 답변 반영·재판단을 구현하고 근거와 처리 상태를 보존한다. 사람 승인이 필요한 결과를 자동 확정하지 않는다.</x:v>
       </x:c>
       <x:c r="D55" s="54" t="n">
         <x:v>35</x:v>
@@ -3704,7 +3700,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="60" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A60" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3716,7 +3712,7 @@
         </x:is>
       </x:c>
       <x:c r="C60" s="60" t="str">
-        <x:v>Agent·Skill·MCP·HITL·SDD·BDD가 각각 해결하는 문제와 구현 산출물을 복습하고 BPMN 업무 연결을 예고한다. 새로운 실습 없음.</x:v>
+        <x:v>Agent·Skill·MCP·HITL·SDD·BDD가 각각 해결하는 문제와 구현 산출물을 복습하고 BPMN 업무 연결을 예고한다. 새로운 실습 없음. 검증한 개별 작업을 다음 회차에서 사람의 승인과 연결한 BPMN 흐름으로 표현한다.</x:v>
       </x:c>
       <x:c r="D60" s="61" t="n">
         <x:v>30</x:v>
@@ -3773,7 +3769,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="65" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="65" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A65" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3785,7 +3781,7 @@
         </x:is>
       </x:c>
       <x:c r="C65" s="53" t="str">
-        <x:v>End-to-End 업무, 시작·입력·담당·완료와 BPM의 분석·설계·실행·모니터링·개선, 에이전트의 단일 작업과 오케스트레이션의 전체 흐름 책임을 살펴본다.</x:v>
+        <x:v>개별 판단이 실제 조치로 이어지려면 어떤 역할·승인·실행 연결이 필요한지 흐름과 기록을 대조한다. End-to-End 업무, 시작·입력·담당·완료와 BPM의 분석·설계·실행·모니터링·개선, 에이전트의 단일 작업과 오케스트레이션의 전체 흐름 책임을 살펴본다.</x:v>
       </x:c>
       <x:c r="D65" s="54" t="n">
         <x:v>20</x:v>
@@ -3931,7 +3927,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="74" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A74" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3943,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c r="C74" s="60" t="str">
-        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다. 명령이 실행된 시점과 그 전에 필요한 승인·근거를 실행 기록에서 짚는다.</x:v>
+        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다. 명령이 실행된 시점과 그 전에 필요한 승인·근거를 실행 기록에서 짚는다. 같은 패턴을 다음 회차 정비·구매에 적용하고 업무별 완료 결과를 비교한다.</x:v>
       </x:c>
       <x:c r="D74" s="61" t="n">
         <x:v>20</x:v>
@@ -4000,7 +3996,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="79" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="79" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A79" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -4012,7 +4008,7 @@
         </x:is>
       </x:c>
       <x:c r="C79" s="53" t="str">
-        <x:v>정기 점검 도래와 재고 부족 시작 이벤트, 승인자·시스템 차이, 프로세스 정의 재사용·인스턴스 상태·배포·오류·반려 기록을 사례로 살펴본다.</x:v>
+        <x:v>설비 제어와 정비·구매 처리가 끝나는 지점을 구분하고 각 결과를 실행 기록에서 확인한다. 정기 점검 도래와 재고 부족 시작 이벤트, 승인자·시스템 차이, 프로세스 정의 재사용·인스턴스 상태·배포·오류·반려 기록을 사례로 살펴본다.</x:v>
       </x:c>
       <x:c r="D79" s="54" t="n">
         <x:v>20</x:v>
@@ -4090,7 +4086,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="84" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A84" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -4102,7 +4098,7 @@
         </x:is>
       </x:c>
       <x:c r="C84" s="60" t="str">
-        <x:v>BPMN 모델, 엔진의 정의·인스턴스, 이벤트·에이전트·사람·시스템의 역할과 온톨로지부터 프로세스까지의 학습 연결을 복습한다. 신규 실습 없음.</x:v>
+        <x:v>BPMN 모델, 엔진의 정의·인스턴스, 이벤트·에이전트·사람·시스템의 역할과 온톨로지부터 프로세스까지의 학습 연결을 복습한다. 신규 실습 없음. 다음 회차에는 이 기록의 미완료·불일치를 인계안으로 모아 사람의 검토·확인까지 연결한다.</x:v>
       </x:c>
       <x:c r="D84" s="61" t="n">
         <x:v>30</x:v>
@@ -4157,7 +4153,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="89" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="89" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A89" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -4169,7 +4165,7 @@
         </x:is>
       </x:c>
       <x:c r="C89" s="53" t="str">
-        <x:v>온톨로지·스키마·그래프·SOP·DMN·BSC/KPI·매뉴얼 인제스천에서 만든 공용 지식이 에이전트 도구 조회로 어떻게 쓰이는지 되짚는다.</x:v>
+        <x:v>지식·도구·에이전트·승인 흐름을 교대 인수인계 한 건에 연결하여 결과와 근거를 확인한다. 온톨로지·스키마·그래프·SOP·DMN·BSC/KPI·매뉴얼 인제스천에서 만든 공용 지식이 에이전트 도구 조회로 어떻게 쓰이는지 되짚는다.</x:v>
       </x:c>
       <x:c r="D89" s="54" t="n">
         <x:v>30</x:v>
@@ -4275,7 +4271,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="96" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A96" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4287,7 +4283,7 @@
         </x:is>
       </x:c>
       <x:c r="C96" s="60" t="str">
-        <x:v>Notion 학습노트에 핵심 개념·실습 결과·참고 출처를 연결한다. 수업 환경에서 사용 가능한 경우 MCP로 기록을 반영하고, 그렇지 않은 경우 작성한 Markdown을 직접 붙여 학습노트를 완성한다.</x:v>
+        <x:v>Notion 학습노트에 핵심 개념·실습 결과·참고 출처를 연결한다. 수업 환경에서 사용 가능한 경우 MCP로 기록을 반영하고, 그렇지 않은 경우 작성한 Markdown을 직접 붙여 학습노트를 완성한다. 조회·판단·검토·실행 확인에 사용한 자료와 산출물을 연결해 이후에도 다시 활용할 수 있게 정리한다.</x:v>
       </x:c>
       <x:c r="D96" s="61" t="n">
         <x:v>20</x:v>
@@ -4791,15 +4787,15 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="38" customHeight="1">
       <x:c r="A1" s="137" t="str">
-        <x:v>HYD 제조 AI | 통합반 오프라인 정규 10회 | 50분 수업 단위</x:v>
+        <x:v>HYD 제조 AI | 통합반 오프라인 정규 10회 | 수업 계획</x:v>
       </x:c>
       <x:c r="B1" s="137"/>
       <x:c r="C1" s="137"/>
       <x:c r="D1" s="137"/>
     </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="38" customHeight="1">
+    <x:row r="2" s="1" customFormat="1" ht="48" customHeight="1">
       <x:c r="A2" s="135" t="str">
-        <x:v>온라인 실습에서 주요 활동을 선별해 직접 수행합니다. 기본 편성은 수업200분·휴식40분이며, 강사가 학생 진행에 따라 시간을 조절합니다. 이론이 있는 회차는50분, 마지막 두 회차는 실습 중심입니다.</x:v>
+        <x:v>온라인 선행학습 후 목적·핵심 개념을 연결하고 주요 실습을 직접 수행합니다. 수업200분·휴식40분의 기본 배정이며 실제 진행은 강사가 조절합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</x:v>
       </x:c>
       <x:c r="B2" s="135"/>
       <x:c r="C2" s="135"/>
@@ -4813,7 +4809,7 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="38" customHeight="1">
       <x:c r="A4" s="138" t="str">
-        <x:v>01회차 | 설비 정보를 관계와 모델로 표현하기</x:v>
+        <x:v>01회차 | HYD 전체 흐름을 확인하고 설비 관계 표현하기</x:v>
       </x:c>
       <x:c r="B4" s="138"/>
       <x:c r="C4" s="138"/>
@@ -4833,32 +4829,32 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="6" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A6" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
       <x:c r="B6" s="141" t="str">
-        <x:v>설비 정보와 관계 모델 이해하기</x:v>
+        <x:v>HYD 시스템과 이번 과정의 학습 목표 이해하기</x:v>
       </x:c>
       <x:c r="C6" s="141" t="str">
-        <x:v>설비·센서·부품이 각각 어떤 정보를 나타내는지 구분한다. 쿨러의 온도 변화가 센서 값, 이상 징후, 원인 후보, 조치 판단으로 이어지는 경로를 살펴본다. 같은 종류와 개별 대상을 클래스·인스턴스로 나누고, 식별자·속성·관계 방향을 설비 사례에 적용한다.</x:v>
+        <x:v>HYD의 완성 흐름을 먼저 확인하고, 판단 근거를 표현하는 관계도와 그래프를 직접 다룬다. HYD가 유압 설비와 업무 시스템을 연결한 수업용 시스템임을 이해한다. 설비·센서 데이터 수집→상태 관찰→지식에 근거한 판단→사람 승인→조치→결과 확인의 전체 구조를 살펴본다. 포털에서 확인할 설비 화면·지식 지도·에이전트·작업함의 역할을 구분한다. 이번 과정에서 관계 모델을 만들고, 근거를 조회하는 에이전트와 업무 흐름으로 연결할 학습 목표를 확인한다.</x:v>
       </x:c>
       <x:c r="D6" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="125" customHeight="1">
       <x:c r="A7" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B7" s="143" t="str">
-        <x:v>관계도를 그리고 최소 모델 만들기</x:v>
+        <x:v>포털 시연으로 완성 흐름을 확인하고 관계도 그리기</x:v>
       </x:c>
       <x:c r="C7" s="143" t="str">
-        <x:v>arrows.app에서 쿨러·센서·부품·고장·조치를 노드로 만들고 관계를 연결한다. 각 화살표를 문장으로 읽어 방향을 확인한다. 제공 목록과 관계도를 대조해 클래스·고유 ID·속성을 갖춘 schema.json과 예시 인스턴스를 작성한다.</x:v>
+        <x:v>강사가 실제 HYD 포털을 열어 보여 주는 설비 상태·센서 값과 쿨러 열화 시나리오를 따라간다. 경보 발생→에이전트의 원인·조치 추천→운전원 승인→설비 명령→센서 값 재확인과 완료 기록을 보고, 추천·승인·실행의 차이를 구분한다. 지식 지도에서 판단에 사용된 설비·센서·고장·조치 연결을 확인한다. 이어 arrows.app에서 방금 본 대상을 노드와 관계로 그려 각 화살표를 문장으로 읽는다.</x:v>
       </x:c>
       <x:c r="D7" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="92" customHeight="1">
@@ -4875,15 +4871,15 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="9" s="1" customFormat="1" ht="150" customHeight="1">
       <x:c r="A9" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B9" s="143" t="str">
-        <x:v>설비 모델을 적재하고 질문별 결과 확인하기</x:v>
+        <x:v>관계도를 설비 모델로 옮기고 적재·조회 결과 확인하기</x:v>
       </x:c>
       <x:c r="C9" s="143" t="str">
-        <x:v>작성한 설비 모델을 제공 절차로 별도 랩 DB에 적재한다. 설비의 센서·부품을 조회해 원자료와 비교하고 빠진 관계·식별자를 수정한다. 포털 기준 지도를 열어 자신의 모델과 연결 방향을 비교한다. 관계도·모델·조회 결과를 저장한다.</x:v>
+        <x:v>VS Code에서 탐색기의 자료 위치와 터미널 실행 방법을 확인한다. 앞서 그린 관계도와 제공 자료를 대조해 클래스와 개별 설비를 구분한다. 제공 파일 형식에 맞춰 고유 ID·속성·관계 방향을 갖춘 작은 schema.json과 예시 인스턴스를 작성한다. 제공 절차로 별도 랩 DB에 적재한 뒤 설비의 센서·부품을 조회하고 원자료와 비교한다. 빠진 관계나 잘못된 식별자를 수정하고 관계도·모델·조회 결과를 저장한다. 다음 회차에는 이 작은 모델을 여러 설비와 공용 부품으로 확장하고 SOP를 연결한다. Notion 학습노트의 해당 주제에 관계도와 확인 결과를 연결한다.</x:v>
       </x:c>
       <x:c r="D9" s="144" t="n">
         <x:v>50</x:v>
@@ -4928,7 +4924,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="14" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A14" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -4936,10 +4932,10 @@
         <x:v>식별자·적재·SOP 연결 원리 이해하기</x:v>
       </x:c>
       <x:c r="C14" s="141" t="str">
-        <x:v>고유 식별자로 같은 대상을 구분하는 방법과 반복 적재 시 중복을 막는 원리를 살펴본다. 필수값·자료형·관계 끝점 제약을 설비 모델에 대어 확인하고, 고장·조치와 SOP의 전제·금지·완료 조건이 연결되는 구조를 이해한다.</x:v>
+        <x:v>앞서 만든 작은 모델을 다시 적재해도 중복되지 않게 하고 작업 절차를 연결한다. 고유 식별자로 같은 대상을 구분하는 방법과 반복 적재 시 중복을 막는 원리를 살펴본다. 필수값·자료형·관계 끝점 제약을 설비 모델에 대어 확인하고, 고장·조치와 SOP의 전제·금지·완료 조건이 연결되는 구조를 이해한다.</x:v>
       </x:c>
       <x:c r="D14" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
@@ -4953,7 +4949,7 @@
         <x:v>설비 모델의 고유 ID·자료형·필수값·관계 끝점을 원자료와 대조해 보완한다. 모델을 적재하고 설비별 센서·부품을 조회한다. 같은 자료를 다시 적재한 뒤 노드와 관계가 불필요하게 늘어나지 않았는지 확인한다.</x:v>
       </x:c>
       <x:c r="D15" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1" ht="92" customHeight="1">
@@ -4970,7 +4966,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="17" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A17" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -4978,10 +4974,10 @@
         <x:v>SOP를 모델에 연결하고 결과 완성하기</x:v>
       </x:c>
       <x:c r="C17" s="143" t="str">
-        <x:v>제공 SOP에서 작업의 전제·금지·수행 단계·완료 조건을 구분한다. 고장 유형과 조치 방법을 기존 설비 모델의 식별자에 연결하고, 선택한 고장에 적용할 절차와 금지 조건을 조회해 원문과 비교한다.</x:v>
+        <x:v>제공 SOP에서 작업의 전제·금지·수행 단계·완료 조건을 구분한다. 고장 유형과 조치 방법을 기존 설비 모델의 식별자에 연결하고, 선택한 고장에 적용할 절차와 금지 조건을 조회해 원문과 비교한다. 다음 회차에는 연결한 SOP 조건으로 조치의 허용·제외와 성과를 판정한다.</x:v>
       </x:c>
       <x:c r="D17" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5023,7 +5019,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="22" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A22" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5031,10 +5027,10 @@
         <x:v>안전한 판단 규칙과 성과 비교 기준 이해하기</x:v>
       </x:c>
       <x:c r="C22" s="141" t="str">
-        <x:v>SOP의 작업 순서와 DMN의 판단 조건을 구분한다. 입력값·단위·연산자·경계값으로 조치 허용·제외를 표현하고, 허용된 후보끼리 비용·생산·품질·에너지 성과를 비교하는 이유를 사례로 확인한다.</x:v>
+        <x:v>관계와 절차를 읽는 데서 나아가 입력 조건에 따라 가능한 조치와 그 이유를 반환한다. SOP의 작업 순서와 DMN의 판단 조건을 구분한다. 입력값·단위·연산자·경계값으로 조치 허용·제외를 표현하고, 허용된 후보끼리 비용·생산·품질·에너지 성과를 비교하는 이유를 사례로 확인한다.</x:v>
       </x:c>
       <x:c r="D22" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5048,7 +5044,7 @@
         <x:v>포털 What-if에서 운전 조건을 바꿔 조치 허용·제외와 순위 변화를 비교한다. 제공 SOP에서 입력·단위·경계·출처를 뽑아 결정표를 작성하고, 각 조건이 어떤 조치를 허용하거나 제외하는지 표시한다.</x:v>
       </x:c>
       <x:c r="D23" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5062,10 +5058,10 @@
         <x:v>VS Code에서 결정표를 입력으로 사용해 조치의 허용·제외와 사유를 반환하는 기능을 만든다. 정상 조건, 경계값, 여러 규칙이 동시에 맞는 경우, 금지 조건을 입력해 실제 결과를 조건표와 대조한다.</x:v>
       </x:c>
       <x:c r="D24" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A25" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5073,10 +5069,10 @@
         <x:v>성과를 비교하고 경계·누락 입력 검증하기</x:v>
       </x:c>
       <x:c r="C25" s="143" t="str">
-        <x:v>허용된 조치 후보만 비용·생산 영향·품질·에너지 기준으로 비교한다. 경계값이나 필수 정보 누락에 따라 결과가 달라지는지 확인하고, 선택 이유와 추가 확인 사항을 출력한다. 추천 결과와 사람의 실행 승인을 구분한다.</x:v>
+        <x:v>허용된 조치 후보만 비용·생산 영향·품질·에너지 기준으로 비교한다. 경계값이나 필수 정보 누락에 따라 결과가 달라지는지 확인하고, 선택 이유와 추가 확인 사항을 출력한다. 추천 결과와 사람의 실행 승인을 구분한다. 다음 회차에는 사용한 조건의 원문을 추출·검토하여 근거 지식을 보강한다.</x:v>
       </x:c>
       <x:c r="D25" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5118,7 +5114,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="30" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A30" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5126,10 +5122,10 @@
         <x:v>문서 추출·검토·출처 관리 원리 이해하기</x:v>
       </x:c>
       <x:c r="C30" s="141" t="str">
-        <x:v>매뉴얼 원문, AI가 추출한 후보, 검토를 거친 지식을 구분한다. 부정 조건·단위·작업 순서가 잘못 추출된 사례를 원문과 대조하고, 문서 ID·페이지·인용 구간을 지식과 함께 보존하는 이유를 이해한다.</x:v>
+        <x:v>판단에 쓰는 조건을 원문까지 확인할 수 있도록 문서 추출·검토·적재를 연결한다. 매뉴얼 원문, AI가 추출한 후보, 검토를 거친 지식을 구분한다. 부정 조건·단위·작업 순서가 잘못 추출된 사례를 원문과 대조하고, 문서 ID·페이지·인용 구간을 지식과 함께 보존하는 이유를 이해한다.</x:v>
       </x:c>
       <x:c r="D30" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5137,13 +5133,13 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B31" s="143" t="str">
-        <x:v>문서 등록을 경험하고 추출 기능 만들기</x:v>
+        <x:v>등록된 문서 지식을 검토하고 로컬 추출 기능 만들기</x:v>
       </x:c>
       <x:c r="C31" s="143" t="str">
         <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 문서의 표·작업 절차·수치·단위·금지 조건을 구조화하는 기능을 만들고 문서 ID·페이지 또는 구간·인용을 함께 출력한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5157,10 +5153,10 @@
         <x:v>추출 후보의 조건·단위·순서를 원문과 비교해 채택·수정·제외한다. 채택한 항목을 기존 랩 그래프의 클래스와 식별자에 맞춰 적재하고, 고장→원인→조치→근거 문서 관계를 조회한다.</x:v>
       </x:c>
       <x:c r="D32" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A33" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5168,10 +5164,10 @@
         <x:v>다른 문서에 적용하고 결과 검증하기</x:v>
       </x:c>
       <x:c r="C33" s="143" t="str">
-        <x:v>제공된 다른 매뉴얼에 같은 추출 기능을 적용한다. 빠진 조건이나 잘못 연결된 대상이 있는지 원문과 대조하고 수정한다. 그래프에 반영한 지식에서 문서 출처를 다시 찾아 검토 결과와 일치하는지 확인한다.</x:v>
+        <x:v>제공된 다른 매뉴얼에 같은 추출 기능을 적용한다. 빠진 조건이나 잘못 연결된 대상이 있는지 원문과 대조하고 수정한다. 그래프에 반영한 지식에서 문서 출처를 다시 찾아 검토 결과와 일치하는지 확인한다. 이 검토 지식과 센서 자료를 다음 회차 에이전트의 근거로 사용한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5213,7 +5209,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="38" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A38" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5221,10 +5217,10 @@
         <x:v>에이전트의 근거·도구·종료 조건 이해하기</x:v>
       </x:c>
       <x:c r="C38" s="141" t="str">
-        <x:v>LLM의 답변, RAG의 근거 검색, 에이전트의 목표·도구·반복 실행을 구분한다. 설비 지식과 현재 센서 값을 각각 어디서 얻는지 살펴보고, 근거 부족이나 도구 오류가 생겼을 때 멈추거나 확인을 요청할 조건을 정한다.</x:v>
+        <x:v>검토한 지식과 현재 입력을 이용해 원인 후보·후속 업무·이상 구간을 확인한다. LLM의 답변, RAG의 근거 검색, 에이전트의 목표·도구·반복 실행을 구분한다. 설비 지식과 현재 센서 값을 각각 어디서 얻는지 살펴보고, 근거 부족이나 도구 오류가 생겼을 때 멈추거나 확인을 요청할 조건을 정한다.</x:v>
       </x:c>
       <x:c r="D38" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5238,7 +5234,7 @@
         <x:v>포털 에이전트의 목표·도구·근거를 확인한다. VS Code에서 설비·센서·고장·SOP 관계와 센서 입력을 읽어 원인 후보·증거·다음 점검 순서를 제안하는 에이전트를 만든다. 확인되지 않은 원인이 가설로 표시되는지 검토한다.</x:v>
       </x:c>
       <x:c r="D39" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="92" customHeight="1">
@@ -5252,10 +5248,10 @@
         <x:v>제공 불량 접수 메시지와 분류 기준으로 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 에이전트를 만든다. 원인이 확정되지 않은 사례를 입력해 단정 대신 조사 요청을 남기는지 확인한다.</x:v>
       </x:c>
       <x:c r="D40" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A41" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5263,10 +5259,10 @@
         <x:v>센서 시각화와 에이전트 결과 검증하기</x:v>
       </x:c>
       <x:c r="C41" s="143" t="str">
-        <x:v>센서 CSV의 시간·온도·압력 변화를 읽어 이상 구간을 시각화한다. 관련 태그와 조회 기간을 함께 표시하고 원자료와 비교한다. 원인 점검·품질 대응·시각화 결과에서 근거와 미확인 사항이 구분되는지 검토한다.</x:v>
+        <x:v>센서 CSV의 시간·온도·압력 변화를 읽어 이상 구간을 시각화한다. 관련 태그와 조회 기간을 함께 표시하고 원자료와 비교한다. 원인 점검·품질 대응·시각화 결과에서 근거와 미확인 사항이 구분되는지 검토한다. 다음 회차에는 반복 작업의 지침을 스킬로 만들고 파일·Git·시간 도구를 조합한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5308,7 +5304,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="46" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A46" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5316,10 +5312,10 @@
         <x:v>스킬·MCP·접근 범위 이해하기</x:v>
       </x:c>
       <x:c r="C46" s="141" t="str">
-        <x:v>SKILL.md에 담는 목적·입력·출력·절차와 MCP 도구의 역할을 구분한다. 파일·Git·시간 도구의 입력과 반환값을 살펴보고, 읽기·쓰기 권한과 접근 가능한 경로가 작업에 미치는 영향을 확인한다.</x:v>
+        <x:v>에이전트의 반복 작업을 재사용 지침과 도구 호출로 나누어 구성한다. SKILL.md에 담는 목적·입력·출력·절차와 MCP 도구의 역할을 구분한다. 파일·Git·시간 도구의 입력과 반환값을 살펴보고, 읽기·쓰기 권한과 접근 가능한 경로가 작업에 미치는 영향을 확인한다.</x:v>
       </x:c>
       <x:c r="D46" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5333,7 +5329,7 @@
         <x:v>준비된 MCP의 연결과 호출 결과를 확인한다. 회의록에서 결정사항·담당자·기한·출처를 추출하는 SKILL.md를 작성하고, 담당자나 기한이 없는 항목은 미정으로 남기는지 원문과 비교한다.</x:v>
       </x:c>
       <x:c r="D47" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5347,10 +5343,10 @@
         <x:v>파일 내용 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청으로 연결한다. 각 도구의 반환값이 결과에 어떻게 사용됐는지 확인하고, 업무 목록의 변경 내용과 시점을 원자료에 대어 검증한다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="92" customHeight="1">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="108" customHeight="1">
       <x:c r="A49" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5358,10 +5354,10 @@
         <x:v>대화형 학습 코치를 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C49" s="143" t="str">
-        <x:v>제공 학습 자료를 바탕으로 문항 생성→답변 입력→정답·원문 근거 피드백으로 이어지는 대화형 학습 코치를 만든다. 답변을 달리 입력해 피드백이 바뀌는지 확인하고, 피드백의 출처가 학습 자료에 있는지 대조한다.</x:v>
+        <x:v>제공 학습 자료를 바탕으로 문항 생성→답변 입력→정답·원문 근거 피드백으로 이어지는 대화형 학습 코치를 만든다. 답변을 달리 입력해 피드백이 바뀌는지 확인하고, 피드백의 출처가 학습 자료에 있는지 대조한다. 다음 회차에는 정보 누락과 요구 변경에도 결과를 확인할 수 있도록 질문·명세·검증을 연결한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5403,7 +5399,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="54" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A54" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5411,21 +5407,21 @@
         <x:v>질문·승인·명세·행동 검증 이해하기</x:v>
       </x:c>
       <x:c r="C54" s="141" t="str">
-        <x:v>정보 확인 질문과 사람의 승인을 구분한다. 입력·출력·금지 조건·수용 기준을 명세로 표현하고, Given/When/Then으로 기대 행동을 정하는 방법을 익힌다. 새 기능의 동작과 기존 기능 보존을 함께 확인하는 이유를 이해한다.</x:v>
+        <x:v>앞서 만든 업무 요청 기능의 누락 입력과 변경 요구를 다루고 기존 동작이 유지되는지 확인한다. 정보 확인 질문과 사람의 승인을 구분한다. 입력·출력·금지 조건·수용 기준을 명세로 표현하고, Given/When/Then으로 기대 행동을 정하는 방법을 익힌다. 새 기능의 동작과 기존 기능 보존을 함께 확인하는 이유를 이해한다.</x:v>
       </x:c>
       <x:c r="D54" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A55" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B55" s="143" t="str">
-        <x:v>질문과 재개·작성과 검토 흐름 구현하기</x:v>
+        <x:v>질문·답변·재개를 구현하고 작성·검토 결과 비교하기</x:v>
       </x:c>
       <x:c r="C55" s="143" t="str">
-        <x:v>포털의 승인 대기·승인·반려 상태를 비교한다. 품질 후속 업무 요청에 필수 정보가 빠졌을 때 질문하고 답변을 받은 뒤 다시 판단하는 흐름을 만든다. 작성·검토 에이전트의 결과와 사람의 최종 승인을 구분한다.</x:v>
+        <x:v>포털의 승인 대기·승인·반려 상태를 확인한다. 제공된 품질 후속 업무 시작본에서 필수 정보가 빠지면 질문하고 답변 뒤 다시 판단하도록 구현한다. 제공 작성·검토 결과를 대조해 AI 검토와 사람의 최종 승인을 구분한다.</x:v>
       </x:c>
       <x:c r="D55" s="144" t="n">
         <x:v>50</x:v>
@@ -5442,10 +5438,10 @@
         <x:v>같은 업무 요청 프로젝트에서 변경할 기능을 정하고 입력·출력·금지 조건·완료 기준을 spec.md로 작성한다. AI 코딩 도구로 변경을 구현한 뒤 기존 일반 요청과 변경 요청의 출력을 비교한다.</x:v>
       </x:c>
       <x:c r="D56" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A57" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5453,10 +5449,10 @@
         <x:v>행동을 검증하고 인수인계 결과 만들기</x:v>
       </x:c>
       <x:c r="C57" s="143" t="str">
-        <x:v>정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성해 실제 출력과 비교한다. 제공 센서·정비·부품 자료를 연결해 완료·미완료·다음 조치·근거 시각을 담은 인수인계 결과를 만들고 원자료와 대조한다.</x:v>
+        <x:v>정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성해 실제 출력과 비교한다. 제공 센서·정비·부품 자료를 연결해 완료·미완료·다음 조치·근거 시각을 담은 인수인계 결과를 만들고 원자료와 대조한다. 다음 회차에는 검증한 작업을 사람의 승인과 함께 BPMN으로 표현한다.</x:v>
       </x:c>
       <x:c r="D57" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
@@ -5498,7 +5494,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="62" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A62" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5506,10 +5502,10 @@
         <x:v>BPMN 역할·분기·지연·실행 연결 이해하기</x:v>
       </x:c>
       <x:c r="C62" s="141" t="str">
-        <x:v>시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
+        <x:v>개별 작업의 결과가 다음 작업으로 넘어가는 조건과 담당 역할을 그림으로 명확히 한다. 시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
       </x:c>
       <x:c r="D62" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5523,7 +5519,7 @@
         <x:v>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</x:v>
       </x:c>
       <x:c r="D63" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5537,10 +5533,10 @@
         <x:v>승인·거절 분기와 각각의 종료 경로를 연결한다. 거절 경로에서 설비 명령으로 진행되지 않는지 확인하고, 승인 작업을 취소하지 않는 지연 알림 Timer를 추가한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검한다.</x:v>
       </x:c>
       <x:c r="D64" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A65" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5548,10 +5544,10 @@
         <x:v>BPMN과 등록된 실행 연결 비교하기</x:v>
       </x:c>
       <x:c r="C65" s="143" t="str">
-        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</x:v>
+        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다. 다음 회차에는 등록된 흐름을 실행해 이 그림과 실제 처리 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D65" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5593,7 +5589,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="70" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A70" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5601,10 +5597,10 @@
         <x:v>실행 상태를 이해하고 정상·예외 경로 확인하기</x:v>
       </x:c>
       <x:c r="C70" s="141" t="str">
-        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+        <x:v>앞서 그린 BPMN과 실제 실행을 비교하고 같은 구조를 교대 검토·확인 흐름에 연결한다. 포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D70" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5618,7 +5614,7 @@
         <x:v>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</x:v>
       </x:c>
       <x:c r="D71" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1" ht="98" customHeight="1">
@@ -5632,10 +5628,10 @@
         <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
       </x:c>
       <x:c r="D72" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A73" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5643,7 +5639,7 @@
         <x:v>제공 인수인계 BPMN의 에이전트 배정·등록하기</x:v>
       </x:c>
       <x:c r="C73" s="143" t="str">
-        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
+        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 시작 폼의 설비·교대 입력과 각 단계 배정을 확인한다. 다음 회차에는 정비·구매의 실행 결과를 확인하고 준비한 교대 흐름을 끝까지 수행한다.</x:v>
       </x:c>
       <x:c r="D73" s="144" t="n">
         <x:v>50</x:v>
@@ -5688,7 +5684,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="78" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A78" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5696,10 +5692,10 @@
         <x:v>업무별 시작 조건을 비교하고 정비 흐름 설계하기</x:v>
       </x:c>
       <x:c r="C78" s="141" t="str">
-        <x:v>냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
+        <x:v>설비 대응에서 익힌 패턴을 정비·구매에 적용하고 교대 인수인계의 검토·확인까지 마친다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
       </x:c>
       <x:c r="D78" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="79" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5713,7 +5709,7 @@
         <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
       </x:c>
       <x:c r="D79" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="80" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5727,10 +5723,10 @@
         <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
       </x:c>
       <x:c r="D80" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" s="1" customFormat="1" ht="145" customHeight="1">
       <x:c r="A81" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5738,10 +5734,10 @@
         <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
       </x:c>
       <x:c r="C81" s="143" t="str">
-        <x:v>교대 인수인계 흐름에 설비·교대 정보를 입력하고 정상·기록 불일치·정보 누락 사례를 실행한다. 인계자 검토, 인수자의 보완 요청과 확인을 거쳐 인계 내용·근거·완료 기록을 대조한다(30분). ProcessGPT 시연을 보며 자신이 만든 지식·에이전트·업무 흐름이 제품의 작업함과 실행 기록에 어떻게 연결되는지 비교한다(20분).</x:v>
+        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(50분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 관계 모델·판단 근거·실행 기록을 연결하여 전체 과정을 설명한다.</x:v>
       </x:c>
       <x:c r="D81" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6384,15 +6380,15 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="38" customHeight="1">
       <x:c r="A1" s="137" t="str">
-        <x:v>HYD 제조 AI | 실전반 오프라인 정규 9회 | 50분 수업 단위</x:v>
+        <x:v>HYD 제조 AI | 실전반 오프라인 정규 9회 | 수업 계획</x:v>
       </x:c>
       <x:c r="B1" s="137"/>
       <x:c r="C1" s="137"/>
       <x:c r="D1" s="137"/>
     </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="38" customHeight="1">
+    <x:row r="2" s="1" customFormat="1" ht="48" customHeight="1">
       <x:c r="A2" s="135" t="str">
-        <x:v>온라인 실습에서 주요 활동을 선별해 직접 수행합니다. 기본 편성은 수업200분·휴식40분이며, 강사가 학생 진행에 따라 시간을 조절합니다. 이론이 있는 회차는50분, 마지막 두 회차는 실습 중심입니다.</x:v>
+        <x:v>온라인 선행학습 후 목적·핵심 개념을 연결하고 주요 실습을 직접 수행합니다. 수업200분·휴식40분의 기본 배정이며 실제 진행은 강사가 조절합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</x:v>
       </x:c>
       <x:c r="B2" s="135"/>
       <x:c r="C2" s="135"/>
@@ -6406,7 +6402,7 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="38" customHeight="1">
       <x:c r="A4" s="138" t="str">
-        <x:v>01회차 | 설비 정보를 관계와 모델로 표현하기</x:v>
+        <x:v>01회차 | HYD 전체 흐름을 확인하고 설비 관계 표현하기</x:v>
       </x:c>
       <x:c r="B4" s="138"/>
       <x:c r="C4" s="138"/>
@@ -6426,32 +6422,32 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="6" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A6" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
       <x:c r="B6" s="141" t="str">
-        <x:v>설비 정보와 관계 모델 이해하기</x:v>
+        <x:v>HYD 시스템과 이번 과정의 학습 목표 이해하기</x:v>
       </x:c>
       <x:c r="C6" s="141" t="str">
-        <x:v>설비·센서·부품이 각각 어떤 정보를 나타내는지 구분한다. 쿨러의 온도 변화가 센서 값, 이상 징후, 원인 후보, 조치 판단으로 이어지는 경로를 살펴본다. 같은 종류와 개별 대상을 클래스·인스턴스로 나누고, 식별자·속성·관계 방향을 설비 사례에 적용한다.</x:v>
+        <x:v>HYD의 완성 흐름을 먼저 확인하고, 판단 근거를 표현하는 관계도와 그래프를 직접 다룬다. HYD가 유압 설비와 업무 시스템을 연결한 수업용 시스템임을 이해한다. 설비·센서 데이터 수집→상태 관찰→지식에 근거한 판단→사람 승인→조치→결과 확인의 전체 구조를 살펴본다. 포털에서 확인할 설비 화면·지식 지도·에이전트·작업함의 역할을 구분한다. 이번 과정에서 관계 모델을 만들고, 근거를 조회하는 에이전트와 업무 흐름으로 연결할 학습 목표를 확인한다.</x:v>
       </x:c>
       <x:c r="D6" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="125" customHeight="1">
       <x:c r="A7" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B7" s="143" t="str">
-        <x:v>관계도를 그리고 최소 모델 만들기</x:v>
+        <x:v>포털 시연으로 완성 흐름을 확인하고 관계도 그리기</x:v>
       </x:c>
       <x:c r="C7" s="143" t="str">
-        <x:v>arrows.app에서 쿨러·센서·부품·고장·조치를 노드로 만들고 관계를 연결한다. 각 화살표를 문장으로 읽어 방향을 확인한다. 제공 목록과 관계도를 대조해 클래스·고유 ID·속성을 갖춘 schema.json과 예시 인스턴스를 작성한다.</x:v>
+        <x:v>강사가 실제 HYD 포털을 열어 보여 주는 설비 상태·센서 값과 쿨러 열화 시나리오를 따라간다. 경보 발생→에이전트의 원인·조치 추천→운전원 승인→설비 명령→센서 값 재확인과 완료 기록을 보고, 추천·승인·실행의 차이를 구분한다. 지식 지도에서 판단에 사용된 설비·센서·고장·조치 연결을 확인한다. 이어 arrows.app에서 방금 본 대상을 노드와 관계로 그려 각 화살표를 문장으로 읽는다.</x:v>
       </x:c>
       <x:c r="D7" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6468,15 +6464,15 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="9" s="1" customFormat="1" ht="118" customHeight="1">
       <x:c r="A9" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B9" s="143" t="str">
-        <x:v>설비 모델을 적재하고 질문별 결과 확인하기</x:v>
+        <x:v>관계도를 설비 모델로 옮기고 적재·조회 결과 확인하기</x:v>
       </x:c>
       <x:c r="C9" s="143" t="str">
-        <x:v>작성한 설비 모델을 제공 절차로 별도 랩 DB에 적재한다. 설비의 센서·부품을 조회해 원자료와 비교하고 빠진 관계·식별자를 수정한다. 포털 기준 지도를 열어 자신의 모델과 연결 방향을 비교한다. 관계도·모델·조회 결과를 저장한다.</x:v>
+        <x:v>앞서 그린 관계도와 제공 자료를 대조해 클래스와 개별 설비를 구분한다. 제공 파일 형식에 맞춰 고유 ID·속성·관계 방향을 갖춘 작은 schema.json과 예시 인스턴스를 작성한다. 제공 절차로 별도 랩 DB에 적재한 뒤 설비의 센서·부품을 조회하고 원자료와 비교한다. 빠진 관계나 잘못된 식별자를 수정하고 관계도·모델·조회 결과를 저장한다. 다음 회차에는 부품의 사용 설비·공급 정보를 찾고 SOP 조건을 조치 판단에 적용한다. Notion 학습노트의 해당 주제에 관계도와 확인 결과를 연결한다.</x:v>
       </x:c>
       <x:c r="D9" s="144" t="n">
         <x:v>50</x:v>
@@ -6521,7 +6517,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="14" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A14" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -6529,10 +6525,10 @@
         <x:v>설비 모델·조건표·판정과 승인 이해하기</x:v>
       </x:c>
       <x:c r="C14" s="141" t="str">
-        <x:v>설비·부품·공급 정보를 연결해 답할 질문을 정한다. SOP의 작업 조건을 결정표로 표현하는 방법을 살펴보고, 조치 후보의 허용·제외 판정과 사람의 실행 승인이 서로 다른 단계임을 이해한다.</x:v>
+        <x:v>설비·부품 연결 조회와 작업 조건표를 조합해 선택 근거가 보이는 조치 검토 결과를 만든다. 설비·부품·공급 정보를 연결해 답할 질문을 정한다. SOP의 작업 조건을 결정표로 표현하는 방법을 살펴보고, 조치 후보의 허용·제외 판정과 사람의 실행 승인이 서로 다른 단계임을 이해한다.</x:v>
       </x:c>
       <x:c r="D14" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6560,10 +6556,10 @@
         <x:v>제공 SOP에서 입력·단위·연산자·경계·출처를 뽑아 조치 조건표를 만든다. 조건에 따라 허용·제외와 사유를 반환하는 기능을 구현하고, 허용 후보의 비용·생산·품질·에너지 성과를 비교한다.</x:v>
       </x:c>
       <x:c r="D16" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A17" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6571,7 +6567,7 @@
         <x:v>선택 근거와 확인 사항을 검증해 결과 완성하기</x:v>
       </x:c>
       <x:c r="C17" s="143" t="str">
-        <x:v>정상·경계·금지·누락 입력을 바꾸며 조치 검토 결과를 확인한다. 선택 이유·원문 근거·추가 확인 사항을 하나의 결과로 구성하고, 정보가 빠져도 이미 확인된 제외 근거가 유지되는지 검증한다.</x:v>
+        <x:v>정상·경계·금지·누락 입력을 바꾸며 조치 검토 결과를 확인한다. 선택 이유·원문 근거·추가 확인 사항을 하나의 결과로 구성하고, 정보가 빠져도 이미 확인된 제외 근거가 유지되는지 검증한다. 다음 회차에는 조건의 문서 출처를 연결하여 작업 확인 카드로 활용한다.</x:v>
       </x:c>
       <x:c r="D17" s="144" t="n">
         <x:v>50</x:v>
@@ -6616,7 +6612,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="22" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A22" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -6624,10 +6620,10 @@
         <x:v>문서 추출·검토·출처 재사용 이해하기</x:v>
       </x:c>
       <x:c r="C22" s="141" t="str">
-        <x:v>매뉴얼의 작업 조건을 추출 후보·검토 지식·작업 확인 자료로 전환하는 과정을 살펴본다. 문서 ID·페이지·인용 구간과 개정 정보를 보존하는 이유를 이해하고, 원문에 없는 내용을 판별한다.</x:v>
+        <x:v>매뉴얼의 조건을 추출·검토하고 특정 작업에서 바로 확인할 수 있는 카드로 바꾼다. 매뉴얼의 작업 조건을 추출 후보·검토 지식·작업 확인 자료로 전환하는 과정을 살펴본다. 문서 ID·페이지·인용 구간과 개정 정보를 보존하는 이유를 이해하고, 원문에 없는 내용을 판별한다.</x:v>
       </x:c>
       <x:c r="D22" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6641,7 +6637,7 @@
         <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 작업의 조건·순서·단위·금지 조건과 출처를 추출하고, 잘못 해석한 항목을 원문과 대조해 수정한다.</x:v>
       </x:c>
       <x:c r="D23" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6658,7 +6654,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="25" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A25" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6666,10 +6662,10 @@
         <x:v>작업 확인 카드를 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C25" s="143" t="str">
-        <x:v>선택한 작업의 준비·금지·완료 조건을 담은 확인 카드를 생성하는 기능을 만든다. 카드의 각 조건을 원문과 대조해 문서 밖 절차를 제거하고, 다른 제공 작업에도 적용해 결과를 검증한다.</x:v>
+        <x:v>선택한 작업의 준비·금지·완료 조건을 담은 확인 카드를 생성하는 기능을 만든다. 카드의 각 조건을 원문과 대조해 문서 밖 절차를 제거하고, 다른 제공 작업에도 적용해 결과를 검증한다. 다음 회차에는 검토한 설비·문서 근거를 점검 요청 초안에 연결한다.</x:v>
       </x:c>
       <x:c r="D25" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6711,7 +6707,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="30" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A30" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -6719,10 +6715,10 @@
         <x:v>원인 근거와 점검 요청 구조 이해하기</x:v>
       </x:c>
       <x:c r="C30" s="141" t="str">
-        <x:v>원인 후보를 뒷받침하는 설비·센서·문서 근거를 구분한다. 원인 분석 결과를 점검 대상·근거·확인 항목으로 바꾸는 방법을 살펴보고, 미확정 원인과 실제 확인된 사실을 구분한다.</x:v>
+        <x:v>원인 후보를 나열하는 데서 나아가 점검 대상·근거·확인 항목을 한 요청으로 만든다. 원인 후보를 뒷받침하는 설비·센서·문서 근거를 구분한다. 원인 분석 결과를 점검 대상·근거·확인 항목으로 바꾸는 방법을 살펴보고, 미확정 원인과 실제 확인된 사실을 구분한다.</x:v>
       </x:c>
       <x:c r="D30" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
@@ -6736,7 +6732,7 @@
         <x:v>포털 에이전트의 도구와 근거를 확인한다. VS Code에서 설비 증거를 읽어 원인 후보와 점검 순서를 제안하는 기능을 만들고, 제안의 각 항목에 사용한 근거가 표시되는지 확인한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6753,7 +6749,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="33" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A33" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6761,10 +6757,10 @@
         <x:v>점검 요청 초안을 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C33" s="143" t="str">
-        <x:v>점검 대상·근거·확인 항목을 담은 요청 초안을 만든다. 자료가 누락되거나 원인이 확정되지 않은 입력을 넣어 확인 질문이나 가설 표시가 남는지 검증한다. 근거 없는 단정을 수정해 요청 결과를 완성한다.</x:v>
+        <x:v>점검 대상·근거·확인 항목을 담은 요청 초안을 만든다. 자료가 누락되거나 원인이 확정되지 않은 입력을 넣어 확인 질문이나 가설 표시가 남는지 검증한다. 근거 없는 단정을 수정해 요청 결과를 완성한다. 다음 회차에는 반복하는 후속 업무를 스킬로 만들고 변경 자료를 확인해 협의 안건을 정리한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6806,7 +6802,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="38" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A38" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -6814,10 +6810,10 @@
         <x:v>스킬·도구 조합·변경 근거 이해하기</x:v>
       </x:c>
       <x:c r="C38" s="141" t="str">
-        <x:v>재사용할 업무 지침과 실행 도구의 역할을 구분한다. 회의록의 결정·담당·기한과 Git 변경 기록·시각 정보를 연결해 완료·미결·변경 내용을 판단하는 기준을 이해한다.</x:v>
+        <x:v>회의에서 정한 업무와 변경 기록을 비교하여 다음에 확인할 안건을 근거와 함께 만든다. 재사용할 업무 지침과 실행 도구의 역할을 구분한다. 회의록의 결정·담당·기한과 Git 변경 기록·시각 정보를 연결해 완료·미결·변경 내용을 판단하는 기준을 이해한다.</x:v>
       </x:c>
       <x:c r="D38" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6831,7 +6827,7 @@
         <x:v>공통 읽기 도구와 파일·Git·시간 MCP를 연결해 호출 결과를 확인한다. 제공 회의록 두 건과 점검 메모에서 결정·담당·기한·근거를 추출하는 스킬을 만들고, 없는 정보는 미정으로 남기는지 확인한다.</x:v>
       </x:c>
       <x:c r="D39" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="92" customHeight="1">
@@ -6848,7 +6844,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="41" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A41" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6856,10 +6852,10 @@
         <x:v>다음 협의 안건을 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C41" s="143" t="str">
-        <x:v>회의 업무 목록과 변경 기록을 합쳐 완료·미결·변경 사항 및 다음 협의에서 확인할 안건을 생성한다. 안건의 근거를 원문과 대조하고 같은 입력을 다시 실행해 필수 정보가 유지되는지 확인한다.</x:v>
+        <x:v>회의 업무 목록과 변경 기록을 합쳐 완료·미결·변경 사항 및 다음 협의에서 확인할 안건을 생성한다. 안건의 근거를 원문과 대조하고 같은 입력을 다시 실행해 필수 정보가 유지되는지 확인한다. 다음 회차에는 점검 요청 기능의 누락 입력과 변경 요구를 명세하고 검증한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6901,7 +6897,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="46" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A46" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -6909,10 +6905,10 @@
         <x:v>질문·승인·명세와 기대 결과 이해하기</x:v>
       </x:c>
       <x:c r="C46" s="141" t="str">
-        <x:v>필수 입력이 없을 때의 질문·보류와 사람 승인을 구분한다. 기능의 입력·출력·제약·완료 기준을 명세하고, 정상·누락·변경·기존 기능을 검증할 기대 결과로 바꾸는 방법을 익힌다.</x:v>
+        <x:v>점검 요청의 정보 누락·추가 답변·기능 변경을 처리하면서 기존 승인 조건을 보존한다. 필수 입력이 없을 때의 질문·보류와 사람 승인을 구분한다. 기능의 입력·출력·제약·완료 기준을 명세하고, 정상·누락·변경·기존 기능을 검증할 기대 결과로 바꾸는 방법을 익힌다.</x:v>
       </x:c>
       <x:c r="D46" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6926,7 +6922,7 @@
         <x:v>포털의 승인·보류 상태를 확인한다. 점검 요청 초안의 필수 정보가 빠졌을 때 질문하고, 추가 답변을 반영해 다시 판단하는 흐름을 구현한다. 사람이 승인할 결과가 자동 확정되지 않는지 확인한다.</x:v>
       </x:c>
       <x:c r="D47" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6940,10 +6936,10 @@
         <x:v>기존 점검 요청 기능에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기능을 구현한다. 변경 전부터 유지해야 할 출력 형식과 승인 조건을 함께 대조한다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="92" customHeight="1">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="108" customHeight="1">
       <x:c r="A49" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6951,10 +6947,10 @@
         <x:v>정상·누락·회귀 시나리오 검증하기</x:v>
       </x:c>
       <x:c r="C49" s="143" t="str">
-        <x:v>직접 정한 정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성한다. 실제 출력을 비교해 어긋난 조건을 수정하고, 기존 점검 요청과 승인 조건도 다시 실행해 회귀 오류가 없는지 확인한다.</x:v>
+        <x:v>직접 정한 정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성한다. 실제 출력을 비교해 어긋난 조건을 수정하고, 기존 점검 요청과 승인 조건도 다시 실행해 회귀 오류가 없는지 확인한다. 다음 회차에는 검증한 작업을 승인·반려 경로가 있는 BPMN으로 표현한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6996,7 +6992,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="54" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A54" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -7004,10 +7000,10 @@
         <x:v>BPMN 역할·분기·지연·실행 연결 이해하기</x:v>
       </x:c>
       <x:c r="C54" s="141" t="str">
-        <x:v>시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
+        <x:v>작업 순서·승인 역할·실행 연결을 구분하여 같은 BPMN을 그림과 실행 관점에서 읽는다. 시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
       </x:c>
       <x:c r="D54" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7021,7 +7017,7 @@
         <x:v>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</x:v>
       </x:c>
       <x:c r="D55" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7038,7 +7034,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="57" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A57" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7046,10 +7042,10 @@
         <x:v>BPMN과 등록된 실행 연결 비교하기</x:v>
       </x:c>
       <x:c r="C57" s="143" t="str">
-        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</x:v>
+        <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다. 다음 회차에는 등록된 흐름의 실행 이력을 대조하고 교대 인수인계 흐름을 구성한다.</x:v>
       </x:c>
       <x:c r="D57" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="1" customFormat="1" ht="28" customHeight="1">
@@ -7091,7 +7087,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="62" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A62" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7099,10 +7095,10 @@
         <x:v>실행 상태를 이해하고 정상·예외 경로 확인하기</x:v>
       </x:c>
       <x:c r="C62" s="141" t="str">
-        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+        <x:v>설비 대응의 실행 이력에서 조건과 결과를 확인하고 교대의 검토·보완 흐름을 구성한다. 포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D62" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7116,7 +7112,7 @@
         <x:v>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</x:v>
       </x:c>
       <x:c r="D63" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1" ht="98" customHeight="1">
@@ -7130,10 +7126,10 @@
         <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
       </x:c>
       <x:c r="D64" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A65" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7141,7 +7137,7 @@
         <x:v>제공 인수인계 BPMN의 에이전트 배정·등록하기</x:v>
       </x:c>
       <x:c r="C65" s="143" t="str">
-        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
+        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 시작 폼의 설비·교대 입력과 각 단계 배정을 확인한다. 다음 회차에는 정비·구매 기록을 확인하고 교대 흐름의 인수 확인까지 완료한다.</x:v>
       </x:c>
       <x:c r="D65" s="144" t="n">
         <x:v>50</x:v>
@@ -7186,7 +7182,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="70" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A70" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7194,10 +7190,10 @@
         <x:v>업무별 시작 조건을 비교하고 정비 흐름 설계하기</x:v>
       </x:c>
       <x:c r="C70" s="141" t="str">
-        <x:v>냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
+        <x:v>정비·구매의 완료 의미를 비교하고 교대 인계 내용과 검토·확인 기록을 연결한다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
       </x:c>
       <x:c r="D70" s="142" t="n">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7211,7 +7207,7 @@
         <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
       </x:c>
       <x:c r="D71" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7225,10 +7221,10 @@
         <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
       </x:c>
       <x:c r="D72" s="142" t="n">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="92" customHeight="1">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" s="1" customFormat="1" ht="145" customHeight="1">
       <x:c r="A73" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7236,10 +7232,10 @@
         <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
       </x:c>
       <x:c r="C73" s="143" t="str">
-        <x:v>교대 인수인계 흐름에 설비·교대 정보를 입력하고 정상·기록 불일치·정보 누락 사례를 실행한다. 인계자 검토, 인수자의 보완 요청과 확인을 거쳐 인계 내용·근거·완료 기록을 대조한다(30분). ProcessGPT 시연을 보며 자신이 만든 지식·에이전트·업무 흐름이 제품의 작업함과 실행 기록에 어떻게 연결되는지 비교한다(20분).</x:v>
+        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(50분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 각자 인계 결과의 근거와 추가 확인할 사항을 설명한다.</x:v>
       </x:c>
       <x:c r="D73" s="144" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="1" customFormat="1" ht="28" customHeight="1">

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R8bf50ea5b26f4890"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R604ce3e088134b2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="Rf4d11f162fb44998"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rbb8e2240d91e468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Re93bdb10729e45f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R47caf9fe29b5499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R680531491d234437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="R3521eeae494949c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4795,7 +4795,7 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="48" customHeight="1">
       <x:c r="A2" s="135" t="str">
-        <x:v>온라인 선행학습 후 목적·핵심 개념을 연결하고 주요 실습을 직접 수행합니다. 수업200분·휴식40분의 기본 배정이며 실제 진행은 강사가 조절합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</x:v>
+        <x:v>매회 50분 수업·10분 휴식 × 4교시입니다(수업200분·휴식40분). 온라인 선행학습을 바탕으로 목적·핵심 개념을 연결하고 실습합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</x:v>
       </x:c>
       <x:c r="B2" s="135"/>
       <x:c r="C2" s="135"/>
@@ -4840,7 +4840,7 @@
         <x:v>HYD의 완성 흐름을 먼저 확인하고, 판단 근거를 표현하는 관계도와 그래프를 직접 다룬다. HYD가 유압 설비와 업무 시스템을 연결한 수업용 시스템임을 이해한다. 설비·센서 데이터 수집→상태 관찰→지식에 근거한 판단→사람 승인→조치→결과 확인의 전체 구조를 살펴본다. 포털에서 확인할 설비 화면·지식 지도·에이전트·작업함의 역할을 구분한다. 이번 과정에서 관계 모델을 만들고, 근거를 조회하는 에이전트와 업무 흐름으로 연결할 학습 목표를 확인한다.</x:v>
       </x:c>
       <x:c r="D6" s="142" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="125" customHeight="1">
@@ -4854,7 +4854,7 @@
         <x:v>강사가 실제 HYD 포털을 열어 보여 주는 설비 상태·센서 값과 쿨러 열화 시나리오를 따라간다. 경보 발생→에이전트의 원인·조치 추천→운전원 승인→설비 명령→센서 값 재확인과 완료 기록을 보고, 추천·승인·실행의 차이를 구분한다. 지식 지도에서 판단에 사용된 설비·센서·고장·조치 연결을 확인한다. 이어 arrows.app에서 방금 본 대상을 노드와 관계로 그려 각 화살표를 문장으로 읽는다.</x:v>
       </x:c>
       <x:c r="D7" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="92" customHeight="1">
@@ -4935,7 +4935,7 @@
         <x:v>앞서 만든 작은 모델을 다시 적재해도 중복되지 않게 하고 작업 절차를 연결한다. 고유 식별자로 같은 대상을 구분하는 방법과 반복 적재 시 중복을 막는 원리를 살펴본다. 필수값·자료형·관계 끝점 제약을 설비 모델에 대어 확인하고, 고장·조치와 SOP의 전제·금지·완료 조건이 연결되는 구조를 이해한다.</x:v>
       </x:c>
       <x:c r="D14" s="142" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
@@ -4949,7 +4949,7 @@
         <x:v>설비 모델의 고유 ID·자료형·필수값·관계 끝점을 원자료와 대조해 보완한다. 모델을 적재하고 설비별 센서·부품을 조회한다. 같은 자료를 다시 적재한 뒤 노드와 관계가 불필요하게 늘어나지 않았는지 확인한다.</x:v>
       </x:c>
       <x:c r="D15" s="144" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1" ht="92" customHeight="1">
@@ -4977,7 +4977,7 @@
         <x:v>제공 SOP에서 작업의 전제·금지·수행 단계·완료 조건을 구분한다. 고장 유형과 조치 방법을 기존 설비 모델의 식별자에 연결하고, 선택한 고장에 적용할 절차와 금지 조건을 조회해 원문과 비교한다. 다음 회차에는 연결한 SOP 조건으로 조치의 허용·제외와 성과를 판정한다.</x:v>
       </x:c>
       <x:c r="D17" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5030,7 +5030,7 @@
         <x:v>관계와 절차를 읽는 데서 나아가 입력 조건에 따라 가능한 조치와 그 이유를 반환한다. SOP의 작업 순서와 DMN의 판단 조건을 구분한다. 입력값·단위·연산자·경계값으로 조치 허용·제외를 표현하고, 허용된 후보끼리 비용·생산·품질·에너지 성과를 비교하는 이유를 사례로 확인한다.</x:v>
       </x:c>
       <x:c r="D22" s="142" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5044,7 +5044,7 @@
         <x:v>포털 What-if에서 운전 조건을 바꿔 조치 허용·제외와 순위 변화를 비교한다. 제공 SOP에서 입력·단위·경계·출처를 뽑아 결정표를 작성하고, 각 조건이 어떤 조치를 허용하거나 제외하는지 표시한다.</x:v>
       </x:c>
       <x:c r="D23" s="144" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5058,7 +5058,7 @@
         <x:v>VS Code에서 결정표를 입력으로 사용해 조치의 허용·제외와 사유를 반환하는 기능을 만든다. 정상 조건, 경계값, 여러 규칙이 동시에 맞는 경우, 금지 조건을 입력해 실제 결과를 조건표와 대조한다.</x:v>
       </x:c>
       <x:c r="D24" s="142" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5072,7 +5072,7 @@
         <x:v>허용된 조치 후보만 비용·생산 영향·품질·에너지 기준으로 비교한다. 경계값이나 필수 정보 누락에 따라 결과가 달라지는지 확인하고, 선택 이유와 추가 확인 사항을 출력한다. 추천 결과와 사람의 실행 승인을 구분한다. 다음 회차에는 사용한 조건의 원문을 추출·검토하여 근거 지식을 보강한다.</x:v>
       </x:c>
       <x:c r="D25" s="144" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5125,7 +5125,7 @@
         <x:v>판단에 쓰는 조건을 원문까지 확인할 수 있도록 문서 추출·검토·적재를 연결한다. 매뉴얼 원문, AI가 추출한 후보, 검토를 거친 지식을 구분한다. 부정 조건·단위·작업 순서가 잘못 추출된 사례를 원문과 대조하고, 문서 ID·페이지·인용 구간을 지식과 함께 보존하는 이유를 이해한다.</x:v>
       </x:c>
       <x:c r="D30" s="142" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5139,7 +5139,7 @@
         <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 문서의 표·작업 절차·수치·단위·금지 조건을 구조화하는 기능을 만들고 문서 ID·페이지 또는 구간·인용을 함께 출력한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5153,7 +5153,7 @@
         <x:v>추출 후보의 조건·단위·순서를 원문과 비교해 채택·수정·제외한다. 채택한 항목을 기존 랩 그래프의 클래스와 식별자에 맞춰 적재하고, 고장→원인→조치→근거 문서 관계를 조회한다.</x:v>
       </x:c>
       <x:c r="D32" s="142" t="n">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="33" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5167,7 +5167,7 @@
         <x:v>제공된 다른 매뉴얼에 같은 추출 기능을 적용한다. 빠진 조건이나 잘못 연결된 대상이 있는지 원문과 대조하고 수정한다. 그래프에 반영한 지식에서 문서 출처를 다시 찾아 검토 결과와 일치하는지 확인한다. 이 검토 지식과 센서 자료를 다음 회차 에이전트의 근거로 사용한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5220,7 +5220,7 @@
         <x:v>검토한 지식과 현재 입력을 이용해 원인 후보·후속 업무·이상 구간을 확인한다. LLM의 답변, RAG의 근거 검색, 에이전트의 목표·도구·반복 실행을 구분한다. 설비 지식과 현재 센서 값을 각각 어디서 얻는지 살펴보고, 근거 부족이나 도구 오류가 생겼을 때 멈추거나 확인을 요청할 조건을 정한다.</x:v>
       </x:c>
       <x:c r="D38" s="142" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5234,7 +5234,7 @@
         <x:v>포털 에이전트의 목표·도구·근거를 확인한다. VS Code에서 설비·센서·고장·SOP 관계와 센서 입력을 읽어 원인 후보·증거·다음 점검 순서를 제안하는 에이전트를 만든다. 확인되지 않은 원인이 가설로 표시되는지 검토한다.</x:v>
       </x:c>
       <x:c r="D39" s="144" t="n">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="92" customHeight="1">
@@ -5248,7 +5248,7 @@
         <x:v>제공 불량 접수 메시지와 분류 기준으로 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 에이전트를 만든다. 원인이 확정되지 않은 사례를 입력해 단정 대신 조사 요청을 남기는지 확인한다.</x:v>
       </x:c>
       <x:c r="D40" s="142" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="41" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5262,7 +5262,7 @@
         <x:v>센서 CSV의 시간·온도·압력 변화를 읽어 이상 구간을 시각화한다. 관련 태그와 조회 기간을 함께 표시하고 원자료와 비교한다. 원인 점검·품질 대응·시각화 결과에서 근거와 미확인 사항이 구분되는지 검토한다. 다음 회차에는 반복 작업의 지침을 스킬로 만들고 파일·Git·시간 도구를 조합한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5315,7 +5315,7 @@
         <x:v>에이전트의 반복 작업을 재사용 지침과 도구 호출로 나누어 구성한다. SKILL.md에 담는 목적·입력·출력·절차와 MCP 도구의 역할을 구분한다. 파일·Git·시간 도구의 입력과 반환값을 살펴보고, 읽기·쓰기 권한과 접근 가능한 경로가 작업에 미치는 영향을 확인한다.</x:v>
       </x:c>
       <x:c r="D46" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5329,7 +5329,7 @@
         <x:v>준비된 MCP의 연결과 호출 결과를 확인한다. 회의록에서 결정사항·담당자·기한·출처를 추출하는 SKILL.md를 작성하고, 담당자나 기한이 없는 항목은 미정으로 남기는지 원문과 비교한다.</x:v>
       </x:c>
       <x:c r="D47" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5343,7 +5343,7 @@
         <x:v>파일 내용 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청으로 연결한다. 각 도구의 반환값이 결과에 어떻게 사용됐는지 확인하고, 업무 목록의 변경 내용과 시점을 원자료에 대어 검증한다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="108" customHeight="1">
@@ -5357,7 +5357,7 @@
         <x:v>제공 학습 자료를 바탕으로 문항 생성→답변 입력→정답·원문 근거 피드백으로 이어지는 대화형 학습 코치를 만든다. 답변을 달리 입력해 피드백이 바뀌는지 확인하고, 피드백의 출처가 학습 자료에 있는지 대조한다. 다음 회차에는 정보 누락과 요구 변경에도 결과를 확인할 수 있도록 질문·명세·검증을 연결한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5410,7 +5410,7 @@
         <x:v>앞서 만든 업무 요청 기능의 누락 입력과 변경 요구를 다루고 기존 동작이 유지되는지 확인한다. 정보 확인 질문과 사람의 승인을 구분한다. 입력·출력·금지 조건·수용 기준을 명세로 표현하고, Given/When/Then으로 기대 행동을 정하는 방법을 익힌다. 새 기능의 동작과 기존 기능 보존을 함께 확인하는 이유를 이해한다.</x:v>
       </x:c>
       <x:c r="D54" s="142" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5438,7 +5438,7 @@
         <x:v>같은 업무 요청 프로젝트에서 변경할 기능을 정하고 입력·출력·금지 조건·완료 기준을 spec.md로 작성한다. AI 코딩 도구로 변경을 구현한 뒤 기존 일반 요청과 변경 요청의 출력을 비교한다.</x:v>
       </x:c>
       <x:c r="D56" s="142" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="57" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5452,7 +5452,7 @@
         <x:v>정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성해 실제 출력과 비교한다. 제공 센서·정비·부품 자료를 연결해 완료·미완료·다음 조치·근거 시각을 담은 인수인계 결과를 만들고 원자료와 대조한다. 다음 회차에는 검증한 작업을 사람의 승인과 함께 BPMN으로 표현한다.</x:v>
       </x:c>
       <x:c r="D57" s="144" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
@@ -5505,7 +5505,7 @@
         <x:v>개별 작업의 결과가 다음 작업으로 넘어가는 조건과 담당 역할을 그림으로 명확히 한다. 시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
       </x:c>
       <x:c r="D62" s="142" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5519,7 +5519,7 @@
         <x:v>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</x:v>
       </x:c>
       <x:c r="D63" s="144" t="n">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5533,7 +5533,7 @@
         <x:v>승인·거절 분기와 각각의 종료 경로를 연결한다. 거절 경로에서 설비 명령으로 진행되지 않는지 확인하고, 승인 작업을 취소하지 않는 지연 알림 Timer를 추가한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검한다.</x:v>
       </x:c>
       <x:c r="D64" s="142" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5547,7 +5547,7 @@
         <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다. 다음 회차에는 등록된 흐름을 실행해 이 그림과 실제 처리 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D65" s="144" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="1" customFormat="1" ht="28" customHeight="1">
@@ -5600,7 +5600,7 @@
         <x:v>앞서 그린 BPMN과 실제 실행을 비교하고 같은 구조를 교대 검토·확인 흐름에 연결한다. 포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D70" s="142" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5614,7 +5614,7 @@
         <x:v>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</x:v>
       </x:c>
       <x:c r="D71" s="144" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1" ht="98" customHeight="1">
@@ -5628,7 +5628,7 @@
         <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
       </x:c>
       <x:c r="D72" s="142" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="1" customFormat="1" ht="108" customHeight="1">
@@ -5695,7 +5695,7 @@
         <x:v>설비 대응에서 익힌 패턴을 정비·구매에 적용하고 교대 인수인계의 검토·확인까지 마친다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
       </x:c>
       <x:c r="D78" s="142" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="79" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5709,7 +5709,7 @@
         <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
       </x:c>
       <x:c r="D79" s="144" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="80" s="1" customFormat="1" ht="92" customHeight="1">
@@ -5723,7 +5723,7 @@
         <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
       </x:c>
       <x:c r="D80" s="142" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="81" s="1" customFormat="1" ht="145" customHeight="1">
@@ -5734,10 +5734,10 @@
         <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
       </x:c>
       <x:c r="C81" s="143" t="str">
-        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(50분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 관계 모델·판단 근거·실행 기록을 연결하여 전체 과정을 설명한다.</x:v>
+        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(30분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 관계 모델·판단 근거·실행 기록을 연결하여 전체 과정을 설명한다.</x:v>
       </x:c>
       <x:c r="D81" s="144" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6388,7 +6388,7 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="48" customHeight="1">
       <x:c r="A2" s="135" t="str">
-        <x:v>온라인 선행학습 후 목적·핵심 개념을 연결하고 주요 실습을 직접 수행합니다. 수업200분·휴식40분의 기본 배정이며 실제 진행은 강사가 조절합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</x:v>
+        <x:v>매회 50분 수업·10분 휴식 × 4교시입니다(수업200분·휴식40분). 온라인 선행학습을 바탕으로 목적·핵심 개념을 연결하고 실습합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</x:v>
       </x:c>
       <x:c r="B2" s="135"/>
       <x:c r="C2" s="135"/>
@@ -6433,7 +6433,7 @@
         <x:v>HYD의 완성 흐름을 먼저 확인하고, 판단 근거를 표현하는 관계도와 그래프를 직접 다룬다. HYD가 유압 설비와 업무 시스템을 연결한 수업용 시스템임을 이해한다. 설비·센서 데이터 수집→상태 관찰→지식에 근거한 판단→사람 승인→조치→결과 확인의 전체 구조를 살펴본다. 포털에서 확인할 설비 화면·지식 지도·에이전트·작업함의 역할을 구분한다. 이번 과정에서 관계 모델을 만들고, 근거를 조회하는 에이전트와 업무 흐름으로 연결할 학습 목표를 확인한다.</x:v>
       </x:c>
       <x:c r="D6" s="142" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="125" customHeight="1">
@@ -6447,7 +6447,7 @@
         <x:v>강사가 실제 HYD 포털을 열어 보여 주는 설비 상태·센서 값과 쿨러 열화 시나리오를 따라간다. 경보 발생→에이전트의 원인·조치 추천→운전원 승인→설비 명령→센서 값 재확인과 완료 기록을 보고, 추천·승인·실행의 차이를 구분한다. 지식 지도에서 판단에 사용된 설비·센서·고장·조치 연결을 확인한다. 이어 arrows.app에서 방금 본 대상을 노드와 관계로 그려 각 화살표를 문장으로 읽는다.</x:v>
       </x:c>
       <x:c r="D7" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6528,7 +6528,7 @@
         <x:v>설비·부품 연결 조회와 작업 조건표를 조합해 선택 근거가 보이는 조치 검토 결과를 만든다. 설비·부품·공급 정보를 연결해 답할 질문을 정한다. SOP의 작업 조건을 결정표로 표현하는 방법을 살펴보고, 조치 후보의 허용·제외 판정과 사람의 실행 승인이 서로 다른 단계임을 이해한다.</x:v>
       </x:c>
       <x:c r="D14" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6556,7 +6556,7 @@
         <x:v>제공 SOP에서 입력·단위·연산자·경계·출처를 뽑아 조치 조건표를 만든다. 조건에 따라 허용·제외와 사유를 반환하는 기능을 구현하고, 허용 후보의 비용·생산·품질·에너지 성과를 비교한다.</x:v>
       </x:c>
       <x:c r="D16" s="142" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1" ht="108" customHeight="1">
@@ -6623,7 +6623,7 @@
         <x:v>매뉴얼의 조건을 추출·검토하고 특정 작업에서 바로 확인할 수 있는 카드로 바꾼다. 매뉴얼의 작업 조건을 추출 후보·검토 지식·작업 확인 자료로 전환하는 과정을 살펴본다. 문서 ID·페이지·인용 구간과 개정 정보를 보존하는 이유를 이해하고, 원문에 없는 내용을 판별한다.</x:v>
       </x:c>
       <x:c r="D22" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6637,7 +6637,7 @@
         <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 작업의 조건·순서·단위·금지 조건과 출처를 추출하고, 잘못 해석한 항목을 원문과 대조해 수정한다.</x:v>
       </x:c>
       <x:c r="D23" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6665,7 +6665,7 @@
         <x:v>선택한 작업의 준비·금지·완료 조건을 담은 확인 카드를 생성하는 기능을 만든다. 카드의 각 조건을 원문과 대조해 문서 밖 절차를 제거하고, 다른 제공 작업에도 적용해 결과를 검증한다. 다음 회차에는 검토한 설비·문서 근거를 점검 요청 초안에 연결한다.</x:v>
       </x:c>
       <x:c r="D25" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6718,7 +6718,7 @@
         <x:v>원인 후보를 나열하는 데서 나아가 점검 대상·근거·확인 항목을 한 요청으로 만든다. 원인 후보를 뒷받침하는 설비·센서·문서 근거를 구분한다. 원인 분석 결과를 점검 대상·근거·확인 항목으로 바꾸는 방법을 살펴보고, 미확정 원인과 실제 확인된 사실을 구분한다.</x:v>
       </x:c>
       <x:c r="D30" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="92" customHeight="1">
@@ -6732,7 +6732,7 @@
         <x:v>포털 에이전트의 도구와 근거를 확인한다. VS Code에서 설비 증거를 읽어 원인 후보와 점검 순서를 제안하는 기능을 만들고, 제안의 각 항목에 사용한 근거가 표시되는지 확인한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6760,7 +6760,7 @@
         <x:v>점검 대상·근거·확인 항목을 담은 요청 초안을 만든다. 자료가 누락되거나 원인이 확정되지 않은 입력을 넣어 확인 질문이나 가설 표시가 남는지 검증한다. 근거 없는 단정을 수정해 요청 결과를 완성한다. 다음 회차에는 반복하는 후속 업무를 스킬로 만들고 변경 자료를 확인해 협의 안건을 정리한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6813,7 +6813,7 @@
         <x:v>회의에서 정한 업무와 변경 기록을 비교하여 다음에 확인할 안건을 근거와 함께 만든다. 재사용할 업무 지침과 실행 도구의 역할을 구분한다. 회의록의 결정·담당·기한과 Git 변경 기록·시각 정보를 연결해 완료·미결·변경 내용을 판단하는 기준을 이해한다.</x:v>
       </x:c>
       <x:c r="D38" s="142" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6827,7 +6827,7 @@
         <x:v>공통 읽기 도구와 파일·Git·시간 MCP를 연결해 호출 결과를 확인한다. 제공 회의록 두 건과 점검 메모에서 결정·담당·기한·근거를 추출하는 스킬을 만들고, 없는 정보는 미정으로 남기는지 확인한다.</x:v>
       </x:c>
       <x:c r="D39" s="144" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="92" customHeight="1">
@@ -6855,7 +6855,7 @@
         <x:v>회의 업무 목록과 변경 기록을 합쳐 완료·미결·변경 사항 및 다음 협의에서 확인할 안건을 생성한다. 안건의 근거를 원문과 대조하고 같은 입력을 다시 실행해 필수 정보가 유지되는지 확인한다. 다음 회차에는 점검 요청 기능의 누락 입력과 변경 요구를 명세하고 검증한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="1" customFormat="1" ht="28" customHeight="1">
@@ -6908,7 +6908,7 @@
         <x:v>점검 요청의 정보 누락·추가 답변·기능 변경을 처리하면서 기존 승인 조건을 보존한다. 필수 입력이 없을 때의 질문·보류와 사람 승인을 구분한다. 기능의 입력·출력·제약·완료 기준을 명세하고, 정상·누락·변경·기존 기능을 검증할 기대 결과로 바꾸는 방법을 익힌다.</x:v>
       </x:c>
       <x:c r="D46" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6922,7 +6922,7 @@
         <x:v>포털의 승인·보류 상태를 확인한다. 점검 요청 초안의 필수 정보가 빠졌을 때 질문하고, 추가 답변을 반영해 다시 판단하는 흐름을 구현한다. 사람이 승인할 결과가 자동 확정되지 않는지 확인한다.</x:v>
       </x:c>
       <x:c r="D47" s="144" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
@@ -6936,7 +6936,7 @@
         <x:v>기존 점검 요청 기능에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기능을 구현한다. 변경 전부터 유지해야 할 출력 형식과 승인 조건을 함께 대조한다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="108" customHeight="1">
@@ -6950,7 +6950,7 @@
         <x:v>직접 정한 정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성한다. 실제 출력을 비교해 어긋난 조건을 수정하고, 기존 점검 요청과 승인 조건도 다시 실행해 회귀 오류가 없는지 확인한다. 다음 회차에는 검증한 작업을 승인·반려 경로가 있는 BPMN으로 표현한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1" ht="28" customHeight="1">
@@ -7003,7 +7003,7 @@
         <x:v>작업 순서·승인 역할·실행 연결을 구분하여 같은 BPMN을 그림과 실행 관점에서 읽는다. 시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</x:v>
       </x:c>
       <x:c r="D54" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7017,7 +7017,7 @@
         <x:v>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</x:v>
       </x:c>
       <x:c r="D55" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7045,7 +7045,7 @@
         <x:v>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다. 다음 회차에는 등록된 흐름의 실행 이력을 대조하고 교대 인수인계 흐름을 구성한다.</x:v>
       </x:c>
       <x:c r="D57" s="144" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="1" customFormat="1" ht="28" customHeight="1">
@@ -7098,7 +7098,7 @@
         <x:v>설비 대응의 실행 이력에서 조건과 결과를 확인하고 교대의 검토·보완 흐름을 구성한다. 포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
       </x:c>
       <x:c r="D62" s="142" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7112,7 +7112,7 @@
         <x:v>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</x:v>
       </x:c>
       <x:c r="D63" s="144" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1" ht="98" customHeight="1">
@@ -7126,7 +7126,7 @@
         <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
       </x:c>
       <x:c r="D64" s="142" t="n">
-        <x:v>75</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="1" customFormat="1" ht="108" customHeight="1">
@@ -7193,7 +7193,7 @@
         <x:v>정비·구매의 완료 의미를 비교하고 교대 인계 내용과 검토·확인 기록을 연결한다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</x:v>
       </x:c>
       <x:c r="D70" s="142" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7207,7 +7207,7 @@
         <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
       </x:c>
       <x:c r="D71" s="144" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1" ht="92" customHeight="1">
@@ -7221,7 +7221,7 @@
         <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
       </x:c>
       <x:c r="D72" s="142" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="1" customFormat="1" ht="145" customHeight="1">
@@ -7232,10 +7232,10 @@
         <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
       </x:c>
       <x:c r="C73" s="143" t="str">
-        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(50분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 각자 인계 결과의 근거와 추가 확인할 사항을 설명한다.</x:v>
+        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(30분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 각자 인계 결과의 근거와 추가 확인할 사항을 설명한다.</x:v>
       </x:c>
       <x:c r="D73" s="144" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="1" customFormat="1" ht="28" customHeight="1">

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Re93bdb10729e45f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R47caf9fe29b5499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R680531491d234437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="R3521eeae494949c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R559f3fb091c54d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="Rff09c0b331164257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R9b6354414a0d4c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="R0cd24173d5634523"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1028,19 +1028,17 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="9" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A9" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시스템 실행 환경을 구성하고 주요 서비스 동작 확인하기</x:t>
-        </x:is>
+      <x:c r="B9" s="31" t="str">
+        <x:v>준비된 수업 환경을 시작하고 실습 자료 열기</x:v>
       </x:c>
       <x:c r="C9" s="27" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex·Python·Docker Desktop·Docker Compose가 개발·AI 코딩·서비스 실행에서 맡는 역할을 구분한다. 준비된 학교 PC에서 필요한 도구와 접속 조건을 확인한다. 제공된 실행 절차로 HYD 서비스를 시작하고 컨테이너 상태·주요 서비스·포털 접속 결과를 확인한다.</x:v>
+        <x:v>준비된 학교 PC에서 VS Code·AI 코딩 도구·Python·Docker의 역할과 실행 상태를 확인한다. 제공 시작 절차로 HYD 포털을 열어 설비 화면·지식 지도·작업함을 찾는다. 재부팅하면 실습 파일이 사라지는 환경임을 확인하고, 실습 시작 도구로 필요한 자료를 새 폴더에 받아 가이드와 작업 폴더를 여는 방법을 익힌다. 보관할 결과는 USB 또는 개인 클라우드로 내보낸다.</x:v>
       </x:c>
       <x:c r="D9" s="33" t="n">
         <x:v>30</x:v>
@@ -1205,7 +1203,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" s="1" customFormat="1" ht="114" customHeight="1">
+    <x:row r="20" s="1" customFormat="1" ht="123" customHeight="1">
       <x:c r="A20" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1239,7 +1237,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" s="1" customFormat="1" ht="77.80000305175781" customHeight="1">
+    <x:row r="22" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A22" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1251,7 +1249,7 @@
         </x:is>
       </x:c>
       <x:c r="C22" s="19" t="str">
-        <x:v>VS Code에서 GitHub Copilot·Codex를 활용해 제공된 랩 전용 설비·센서·부품 자료를 분석한다. 어떤 질문에 답할 수 있는 지식 구조가 필요한지 정한 뒤, 대상별 클래스와 예시 인스턴스를 구분한다. 클래스별 속성·자료형·식별자·필수값, 클래스 사이의 관계 유형·방향·연결 제약을 정의한다. 이를 바탕으로 온톨로지 스키마 파일과 예시 인스턴스 데이터를 작성하고 생성 결과가 원래 자료의 의미와 일치하는지 확인한다.</x:v>
+        <x:v>제공 설비·센서·부품 원자료를 읽고 설비별 센서와 공용 부품을 찾을 질문을 정한다. VS Code에서 목표·자료·제약·확인 사례를 자기 말로 정리하고 AI와 모델을 설계한다. 같은 센서 이름이 다른 설비에 쓰인 경우, 별칭·중복·누락을 구분하여 고유 ID·단위·관계 방향을 정한다. schema.json과 graph.json을 작성하고 구조 검사와 질문별 원자료 대조를 따로 수행한다.</x:v>
       </x:c>
       <x:c r="D22" s="25" t="n">
         <x:v>40</x:v>
@@ -1267,7 +1265,7 @@
         <x:v>설계한 온톨로지를 그래프 DB에 구현하고 검증하기</x:v>
       </x:c>
       <x:c r="C23" s="27" t="str">
-        <x:v>앞 실습의 스키마·인스턴스·요구사항·원자료 검토 기록을 이어 쓴다. VS Code의 GitHub Copilot·Codex로 Cypher를 작성하고 별도 랩 DB에 적재한다. 식별자·관계 끝점·방향과 원자료 질문의 답, 반복 적재 시 중복 여부를 확인한다. 오류가 있으면 근거에 따라 수정하고 질의·결과를 저장한다. 확인한 설비 식별자와 관계는 다음 회차에서 작업 절차와 조치 조건을 연결하는 기준이 된다.</x:v>
+        <x:v>제공된 이전 단계 완성 모델을 출발점으로 적재·조회문을 직접 작성한다. 별도 랩 DB에서 설비별 센서·부품과 공용 부품의 사용 설비를 조회해 원자료와 대조한다. 같은 자료를 다시 적재해도 중복되지 않고 이름이 바뀌어도 같은 ID가 유지되는지 확인한다. 전체 데이터를 지우지 않고 필요한 부분을 수정하며 코드·질의·확인 결과를 저장한다. 개인 모델은 선택하여 가져올 수 있다.</x:v>
       </x:c>
       <x:c r="D23" s="33" t="n">
         <x:v>40</x:v>
@@ -1414,7 +1412,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="118" customHeight="1">
+    <x:row r="33" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A33" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1426,7 +1424,7 @@
         </x:is>
       </x:c>
       <x:c r="C33" s="27" t="str">
-        <x:v>VS Code에서 앞서 작성한 결정표를 활용해 GitHub Copilot·Codex로 간단한 조치 판정 기능을 제작한다. 설비 상태·운전 조건·금지 조건 등 입력값에 따라 가능한 조치와 제외해야 하는 조치를 구분하도록 구현한다. 제공된 효과·비용·성과 지표 값을 이용해 허용된 조치 후보를 비교하고 선택 이유를 표시한다. 정상 조건·경계값·복수 규칙 일치·조치 불가 상황을 실행해 결과를 확인하고, 조건을 변경했을 때 판단이 어떻게 달라지는지 살펴본다. 다음 회차에는 이 조건의 근거가 된 매뉴얼에서 지식을 추출하고 원문과 대조한다.</x:v>
+        <x:v>제공된 이전 단계 완성 조건표를 읽는 조치 판정 기능을 작성한다. 적용 대상과 복합 조건을 구분하고 경고·감점·제외·정보 부족을 이유와 함께 반환한다. 허용 후보의 비용·생산·품질·에너지 손실을 제공 교육용 산식으로 비교한다. 정상·경계·복수 조건·모두 제외·필수값 누락 사례를 대조한다. 실제 HYD의 성과 점수와 이 교육용 비교값을 구분한다. 다음 회차에는 조건의 원문 근거를 검토한다.</x:v>
       </x:c>
       <x:c r="D33" s="33" t="n">
         <x:v>50</x:v>
@@ -1517,25 +1515,23 @@
         <x:v>70</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" s="1" customFormat="1" ht="93.5" customHeight="1">
+    <x:row r="40" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A40" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B40" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">다양한 현장 문서에서 필요한 지식 자동 추출하기</x:t>
-        </x:is>
+      <x:c r="B40" s="23" t="str">
+        <x:v>제공 문서의 추출 후보를 검토하는 기능 만들기</x:v>
       </x:c>
       <x:c r="C40" s="19" t="str">
-        <x:v>VS Code에서 GitHub Copilot·Codex를 활용해 랩 전용 기술 매뉴얼과 작업 절차 자료를 분석한다. 문서에 포함된 표·절차 번호·예외 조건·수치·부품 정보·개정 사항을 확인하고, 기존 온톨로지 스키마에 필요한 증상·원인·조치·수행 조건·원문 출처를 구조화하도록 지시한다. 추출 결과에 문서 ID·페이지 또는 구간·원문 인용·지식 후보별 속성값이 포함되도록 구현한다. 원문과 결과를 대조하면서 빠진 조건이나 부정확한 추출을 수정하고, 이후 적재에 활용할 검토용 구조화 데이터를 완성한다.</x:v>
+        <x:v>강사가 제공한 HM-8·PM-02·PR-07 원문과 같은 판본의 추출 후보를 읽는다. VS Code에서 후보의 문서 ID·절·인용·수치·단위·대상 ID를 검사하고 검토 결과를 저장하는 기능을 작성한다. 원문과 대조해 채택·수정·제외·보류를 구분하고, 근거가 없거나 확인하지 못한 항목은 승인하지 않는다. 준비된 추출 결과를 사용하며 학생이 새 문서나 재추출 서비스를 추가하지 않는다.</x:v>
       </x:c>
       <x:c r="D40" s="25" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="118" customHeight="1">
+    <x:row r="41" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A41" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1547,7 +1543,7 @@
         </x:is>
       </x:c>
       <x:c r="C41" s="27" t="str">
-        <x:v>VS Code에서 앞서 추출한 지식 후보를 원문과 대조해 채택·수정·제외한다. 제공된 이전 단계의 모델과 3일차에 학습한 조치·규칙의 구조를 재사용하여 후보를 해당 클래스·인스턴스·관계에 매핑한다. GitHub Copilot·Codex로 기존 식별자를 활용한 그래프 DB 적재 코드를 구현하고, 검토한 항목만 랩 전용 그래프 DB에 반영한다. 이후 고장 유형에서 원인·조치·판단 규칙·원문 출처로 이어지는 관계를 조회하고, 문서에서 추출한 지식이 앞서 만든 그래프에 보강된 결과를 확인한다.</x:v>
+        <x:v>제공된 이전 단계 검토 결과와 랩 모델에서 시작한다. 승인한 후보만 별도 랩 DB의 기존 ID에 연결하는 적재·조회 기능을 작성한다. 조치의 조건·단계·근거 문서로 이어지는 경로를 조회하고 원문과 대조한다. 보류 후보가 들어가지 않는지, 같은 입력을 다시 적재해도 중복되지 않는지 확인한다. 포털 기준 지식과 별도 랩 결과를 구분하여 저장한다.</x:v>
       </x:c>
       <x:c r="D41" s="33" t="n">
         <x:v>50</x:v>
@@ -1653,17 +1649,17 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="49" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A49" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="55" t="str">
-        <x:v>업무 에이전트에 질문하고 도구와 근거 확인하기</x:v>
+        <x:v>업무 에이전트를 구성하고 질문의 도구·근거 확인하기</x:v>
       </x:c>
       <x:c r="C49" s="53" t="str">
-        <x:v>포털에서 준비된 에이전트의 역할과 사용 도구를 확인하고 수업용 설비 질문을 입력한다. 답변의 근거와 도구 호출 결과를 대조하여 확인된 사실과 추가 확인이 필요한 내용을 구분한다. 에이전트 구현은 이어지는 VS Code 랩에서 수행한다.</x:v>
+        <x:v>포털의 제공 에이전트에서 목표·지침·조회 도구를 읽고 수업용 에이전트를 구성한다. 지정 모델과 준비된 조회 서버 안에서 원인 근거와 추가 확인을 정리하도록 목표·지침을 작성한다. 같은 대상의 질문을 실행하고 실제 호출 입력·결과·관측 시각을 대조한다. 답이 길어진 것보다 근거가 확인되고 모르는 항목이 구분되는지 확인하며 설정과 결과를 저장한다.</x:v>
       </x:c>
       <x:c r="D49" s="54" t="n">
         <x:v>30</x:v>
@@ -1887,7 +1883,7 @@
         </x:is>
       </x:c>
       <x:c r="C63" s="53" t="str">
-        <x:v>Notion에서 내보낸 Markdown 학습노트나 제공 매뉴얼로 문항 생성→학생 답변 입력→정답·출처 기반 피드백→다음 문항 제공의 대화를 구성한다. 텍스트 파일 기반으로 우선 완주하며 실서비스 Notion API 연동은 필수로 가정하지 않는다. 다음 회차에는 정보가 부족한 요청을 질문으로 보완하고 기능 변경의 조건을 명세한다.</x:v>
+        <x:v>제공된 학습 자료를 읽고 설명·확인 질문·근거를 제시하는 학습 코치를 만든다. 질문의 주제와 참고한 구간을 연결하고 자료에 없는 질문에는 확인할 수 없음을 표시한다. 같은 자료의 다른 질문으로 답과 근거를 대조하고, 스킬·입력·검증 기록을 저장한다. 개인 노트나 외부 서비스를 연결하는 작업은 필수로 두지 않는다.</x:v>
       </x:c>
       <x:c r="D63" s="54" t="n">
         <x:v>45</x:v>
@@ -2381,7 +2377,7 @@
         </x:is>
       </x:c>
       <x:c r="C95" s="53" t="str">
-        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다. 이 승인·반려 패턴을 다음 회차의 정기 점검과 재고 보충 흐름에 적용한다.</x:v>
+        <x:v>포털의 준비된 냉각 대응 시나리오 A를 실행하고 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 따라간다. 승인 대기·거절·보류는 실제 기록이나 제공 사례와 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의·판본·처리 건과 결과를 기록한다.</x:v>
       </x:c>
       <x:c r="D95" s="54" t="n">
         <x:v>35</x:v>
@@ -2469,7 +2465,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="102" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A102" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2481,7 +2477,7 @@
         </x:is>
       </x:c>
       <x:c r="C102" s="53" t="str">
-        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
+        <x:v>포털의 준비된 정기 점검 시나리오 B에서 점검 시점 제안과 근거를 읽고 담당자의 결정을 거친다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조한다. 오더 등록은 실제 정비 완료와 구분한다. 거절·보류 사례는 확인한 기록 범위에서 비교하고, 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</x:v>
       </x:c>
       <x:c r="D102" s="54" t="n">
         <x:v>45</x:v>
@@ -2505,7 +2501,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="104" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A104" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2517,7 +2513,7 @@
         </x:is>
       </x:c>
       <x:c r="C104" s="53" t="str">
-        <x:v>포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
+        <x:v>포털의 준비된 재고 보충 시나리오 C에서 공급사·수량의 제안 근거와 승인 조건을 확인한다. 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교한다. 수업 시스템의 즉시 입고를 실제 배송으로 설명하지 않는다. 반려 사례는 제공 기록과 구분해 비교하고 BPMN의 해당 작업과 실제 결과를 연결한다.</x:v>
       </x:c>
       <x:c r="D104" s="54" t="n">
         <x:v>40</x:v>
@@ -2637,17 +2633,17 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="113" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A113" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="62" t="str">
-        <x:v>보충 매뉴얼을 추출·검토하여 기존 지식에 추가하기</x:v>
+        <x:v>제공 보충 매뉴얼의 추출 결과를 검토하고 지식에 추가하기</x:v>
       </x:c>
       <x:c r="C113" s="60" t="str">
-        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다.</x:v>
+        <x:v>강사 코드로 열린 교대 실습에서 제공 HI-01 보충 매뉴얼을 선택한다. 준비된 추출 후보를 원문과 대조하여 절차·조건·근거를 검토하고 승인한 지식을 추가한다. 추출 결과 재사용과 사람의 검토·적재를 구분한다. 지식 지도에서 새 항목의 식별자와 문서·판본·절 연결을 확인하고 이후 인계안의 확인 기준으로 사용한다.</x:v>
       </x:c>
       <x:c r="D113" s="61" t="n">
         <x:v>30</x:v>
@@ -2912,15 +2908,15 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="9" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A9" s="65" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B9" s="62" t="str">
-        <x:v>시스템 실행 환경을 구성하고 주요 서비스 동작 확인하기</x:v>
+        <x:v>준비된 수업 환경을 시작하고 실습 자료 열기</x:v>
       </x:c>
       <x:c r="C9" s="60" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex·Python·Docker Desktop·Docker Compose가 개발·AI 코딩·서비스 실행에서 맡는 역할을 구분한다. 준비된 학교 PC에서 필요한 도구와 접속 조건을 확인한다. 제공된 실행 절차로 HYD 서비스를 시작하고 컨테이너 상태·주요 서비스·포털 접속 결과를 확인한다.</x:v>
+        <x:v>준비된 학교 PC에서 VS Code·AI 코딩 도구·Python·Docker의 역할과 실행 상태를 확인한다. 제공 시작 절차로 HYD 포털을 열어 설비 화면·지식 지도·작업함을 찾는다. 재부팅하면 실습 파일이 사라지는 환경임을 확인하고, 실습 시작 도구로 필요한 자료를 새 폴더에 받아 가이드와 작업 폴더를 여는 방법을 익힌다. 보관할 결과는 USB 또는 개인 클라우드로 내보낸다.</x:v>
       </x:c>
       <x:c r="D9" s="61" t="n">
         <x:v>30</x:v>
@@ -3073,7 +3069,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" s="1" customFormat="1" ht="114" customHeight="1">
+    <x:row r="20" s="1" customFormat="1" ht="123" customHeight="1">
       <x:c r="A20" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3089,7 +3085,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="21" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A21" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3101,13 +3097,13 @@
         </x:is>
       </x:c>
       <x:c r="C21" s="53" t="str">
-        <x:v>포털 지식 지도에서 설비를 선택하고 연결된 센서·부품을 펼친다. 노드를 눌러 식별자와 속성을 확인하고 관계의 방향을 읽는다. 같은 센서 이름과 서로 다른 식별자를 구분하며, 별도 랩 DB에서 만든 모델과 포털의 기준 지도를 비교한다. 선택한 부품이 어느 설비와 연결되는지 찾아 조회 결과의 사용 범위를 확인한다.</x:v>
+        <x:v>포털 지식 지도에서 설비·구성 요소·부품·문서의 연결을 펼치고 노드의 ID·속성과 관계 방향을 확인한다. 한 부품을 사용하는 설비를 찾고, 연결이 있다는 사실과 실제 재고·공급 조건이 확보됐다는 판단을 구분한다. 이어지는 로컬 랩에서는 제공 공급 자료로 답할 질문을 정한다.</x:v>
       </x:c>
       <x:c r="D21" s="54" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="22" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A22" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3117,13 +3113,13 @@
         <x:v>설비·부품·공급 정보를 연결하는 온톨로지 설계하기</x:v>
       </x:c>
       <x:c r="C22" s="60" t="str">
-        <x:v>VS Code의 GitHub Copilot·Codex로 제공 설비·센서·부품 자료와 공급_조건.csv를 읽는다. 부품이 쓰이는 설비와 공급 정보를 찾을 수 있도록 기존 모델에 관계를 연결하고 schema.json과 인스턴스를 작성한다. 고유 ID·필수값·관계 방향을 원자료와 대조한다.</x:v>
+        <x:v>제공된 이전 단계 설비·부품 모델에 공급 조건 자료를 연결하도록 모델을 확장한다. 부품별 사용 설비와 공급사별 승인 여부·단가·불량률·납기를 찾을 질문을 정한다. 공용 부품을 설비별로 중복 생성하지 않고 단위와 출처를 보존한다. AI와 작성한 모델을 원자료의 품번·공급사·조건에 대조한다. 공급사를 자동 선정하는 기능은 이번 요구에 포함하지 않는다.</x:v>
       </x:c>
       <x:c r="D22" s="61" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="23" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A23" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3133,7 +3129,7 @@
         <x:v>부품의 사용 설비와 공급 정보를 조회하는 그래프 구현하기</x:v>
       </x:c>
       <x:c r="C23" s="53" t="str">
-        <x:v>앞 스키마·인스턴스를 별도 랩 Neo4j에 적재한다. 부품별 사용 설비와 제공된 공급 선택지를 조회하고 원자료와 비교한다. 반복 적재의 중복 여부를 확인해 질의와 결과를 저장한다. 공급사 선정 규칙을 새로 만들지 않으며 문서 인제스천은 3회차에서 수행한다.</x:v>
+        <x:v>앞 단계 완성 모델로 시작해 부품별 사용 설비와 공급 조건을 반환하는 적재·조회문을 작성한다. P-PMP-SEAL의 사용 설비 HYD-01·02·03과 공급 조건 3행을 원자료와 대조한다. 다른 품번과 없는 품번도 확인하고, 비승인 공급사를 승인 상태와 함께 구별한다. 반복 적재의 중복 여부를 검사하고 질의·결과·남은 확인 사항을 저장한다.</x:v>
       </x:c>
       <x:c r="D23" s="54" t="n">
         <x:v>40</x:v>
@@ -3260,7 +3256,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="32" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A32" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3270,7 +3266,7 @@
         <x:v>판정·성과 비교를 조치 검토 결과로 완성하기</x:v>
       </x:c>
       <x:c r="C32" s="53" t="str">
-        <x:v>앞 회차 조건표로 허용·제외와 사유를 반환하는 기능을 구현한다. 허용 후보의 비용·성과를 비교하고 선택 이유·원문 근거·추가 확인 사항을 한 결과로 저장한다. 경계·금지·누락을 확인하며 추천과 사람의 실행 승인을 구별한다.</x:v>
+        <x:v>제공된 완성 조건표에서 출발해 후보별 판정과 조치 검토 결과를 만드는 기능을 작성한다. 경고·감점·제외·정보 부족을 구분하고, 허용 후보만 제공 교육용 비용·생산·품질·에너지 산식으로 비교한다. 검토 결과에 후보별 이유·원문 출처·추가로 확인할 값을 함께 표시한다. 경계값, 제외 사유와 누락이 겹친 입력, 모두 제외된 입력으로 확인한다. 비교 순위와 실제 실행 승인은 구분한다.</x:v>
       </x:c>
       <x:c r="D32" s="54" t="n">
         <x:v>35</x:v>
@@ -3294,7 +3290,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="34" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A34" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3304,29 +3300,29 @@
         <x:v>매뉴얼 근거를 대조하고 작업 확인 항목 정리하기</x:v>
       </x:c>
       <x:c r="C34" s="53" t="str">
-        <x:v>제공 매뉴얼의 원문과 포털에 등록된 추출·검토 결과를 나란히 확인한다. 작업 순서·단위·금지 조건·대상 설비를 비교하고 수정하거나 제외할 후보를 표시한다. 지식 지도에서 채택된 항목의 설비·조치·출처 연결을 찾는다. 직접 추가 적재는 마지막 교대 실습에서 제공 보충 매뉴얼로 수행한다. 선택한 작업에 필요한 준비·금지·완료 조건을 원문 근거와 함께 정리한다.</x:v>
+        <x:v>제공 매뉴얼의 원문과 포털에 등록된 지식을 대조한다. 팬 운전과 핀 세척의 적용 조건·금지 사항·완료 기준에서 어떤 항목을 작업 전에 확인해야 하는지 찾고 원문 절에 연결한다. 현재 값은 문서의 기준값과 구분해 읽는다. 직접 추가 적재는 마지막 교대 실습에서 제공 보충 매뉴얼로 수행한다.</x:v>
       </x:c>
       <x:c r="D34" s="54" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="35" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A35" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="62" t="str">
-        <x:v>작업 조건과 출처를 보존해 문서 지식 추출하기</x:v>
+        <x:v>제공 문서의 추출 후보를 검토하는 기능 만들기</x:v>
       </x:c>
       <x:c r="C35" s="60" t="str">
-        <x:v>제공 매뉴얼의 표·작업 순서·단위·금지 조건을 구조화해 추출한다. 문서 ID·페이지 또는 구간·원문 인용을 보존하고 후보를 원문과 대조해 수정·채택한다. 작업별 조건과 해당 조건의 원문 근거를 연결한다.</x:v>
+        <x:v>강사가 제공한 HM-8·PM-02·PR-07 원문과 같은 판본의 추출 후보를 읽는다. VS Code에서 후보의 문서 ID·절·인용·수치·단위·대상 ID를 검사하고 검토 결과를 저장하는 기능을 작성한다. 원문과 대조해 채택·수정·제외·보류를 구분하고, 근거가 없거나 확인하지 못한 항목은 승인하지 않는다. 준비된 추출 결과를 사용하며 학생이 새 문서나 재추출 서비스를 추가하지 않는다.</x:v>
       </x:c>
       <x:c r="D35" s="61" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="36" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A36" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3336,7 +3332,7 @@
         <x:v>검토 지식으로 작업 확인 카드 만들기</x:v>
       </x:c>
       <x:c r="C36" s="53" t="str">
-        <x:v>채택한 후보만 기존 랩 그래프의 ID에 맞춰 반영하고 출처를 조회한다. 선택한 작업의 준비·금지·완료 조건을 담은 카드를 생성하는 로컬 기능을 만들고 원문과 대조한다. 문서 밖 절차는 추가하지 않고 카드 파일을 저장한다.</x:v>
+        <x:v>제공된 검토 결과와 랩 모델에서 시작해 승인 지식을 별도 랩 DB에 연결한다. 선택한 작업의 준비·금지·완료 조건과 원문 출처를 모아 작업 확인 카드를 생성하는 기능을 만든다. 팬 운전·핀 세척 등 제공 문서의 작업으로 대조하고, 미제공 절이나 해결하지 못한 조건은 확인 사항으로 남긴다. 카드 작성이 작업 승인이나 실행이 아님을 구분한다.</x:v>
       </x:c>
       <x:c r="D36" s="54" t="n">
         <x:v>35</x:v>
@@ -3429,23 +3425,23 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="43" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A43" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="62" t="str">
-        <x:v>에이전트 답변에서 점검에 필요한 근거 확인하기</x:v>
+        <x:v>업무 에이전트를 구성하고 질문의 도구·근거 확인하기</x:v>
       </x:c>
       <x:c r="C43" s="60" t="str">
-        <x:v>포털에서 준비된 에이전트의 역할과 사용 도구를 확인하고 수업용 설비 질문을 입력한다. 답변의 근거와 도구 호출 결과를 대조하여 확인된 사실과 추가 확인이 필요한 내용을 구분한다. 에이전트 구현은 이어지는 VS Code 랩에서 수행한다. 답변에서 점검 대상·근거·확인할 항목을 찾아 점검 요청에 사용할 정보를 구분한다.</x:v>
+        <x:v>포털의 제공 에이전트에서 목표·지침·조회 도구를 읽고 수업용 에이전트를 구성한다. 지정 모델과 준비된 조회 서버 안에서 원인 근거와 추가 확인을 정리하도록 목표·지침을 작성한다. 같은 대상의 질문을 실행하고 실제 호출 입력·결과·관측 시각을 대조한다. 답이 길어진 것보다 근거가 확인되고 모르는 항목이 구분되는지 확인하며 설정과 결과를 저장한다.</x:v>
       </x:c>
       <x:c r="D43" s="61" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="44" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A44" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3455,7 +3451,7 @@
         <x:v>원인 분석을 점검 요청 초안으로 연결하기</x:v>
       </x:c>
       <x:c r="C44" s="53" t="str">
-        <x:v>설비·문서·부품·센서 자료로 원인 후보와 점검 순서를 제안하는 로컬 에이전트를 만든다. 점검 대상·근거·확인 항목을 담은 요청 초안까지 한 과제로 완성한다. 확인되지 않은 원인은 가설로 표시하고 점검 요청 초안에 근거와 미확인 항목을 함께 남긴다. 포털 작업지시 연동은 하지 않는다.</x:v>
+        <x:v>제공 설비 그래프와 사례 입력을 읽어 원인 후보·근거·추가 확인을 반환하는 기능을 만들고 점검 요청 초안으로 연결한다. 요청에는 대상 설비·부품, 관측 시각, 확인할 항목과 그 이유를 남긴다. 오래된 값·표본 부족·복수 원인 후보와 문서 기준의 차이를 대조하고, 모르는 항목은 확인 필요로 표시한다. 원인 후보를 확정 원인으로 쓰거나 작업지시를 실제 발행하지 않는다.</x:v>
       </x:c>
       <x:c r="D44" s="54" t="n">
         <x:v>45</x:v>
@@ -3479,7 +3475,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="46" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A46" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3489,7 +3485,7 @@
         <x:v>회의 결정과 후속 업무를 추출하는 스킬 만들기</x:v>
       </x:c>
       <x:c r="C46" s="53" t="str">
-        <x:v>제공 회의록 두 건과 점검 메모에서 결정·담당·기한·근거를 뽑는 SKILL.md를 작성한다. 완료·미결 항목을 구분하고 담당이나 기한이 없는 항목은 미정으로 남긴다. 다음 협의 준비에 재사용할 업무 목록을 저장한다.</x:v>
+        <x:v>제공된 두 회의록에서 결정·제안·조건부 작업·담당 미정을 구분하는 스킬을 작성한다. 이전 결정과 후속 확인을 연결하여 전달 완료와 발주 완료, 설비별 점검 상태를 구별한다. 각 미결 항목에 다음 협의에서 확인할 질문과 원문 근거를 남기도록 지침을 보완한다. 두 원문에 다시 적용해 특정 이름·날짜에만 맞춘 결과가 아닌지 확인한다.</x:v>
       </x:c>
       <x:c r="D46" s="54" t="n">
         <x:v>45</x:v>
@@ -3523,7 +3519,7 @@
         <x:v>파일·Git·시간 도구로 다음 협의 안건 만들기</x:v>
       </x:c>
       <x:c r="C48" s="53" t="str">
-        <x:v>공통 HYD 읽기 도구 연결을 확인하고 준비된 파일·Git·시간 MCP를 VS Code에서 호출한다. 앞 업무 목록과 변경 이력을 연결해 완료·미결·변경 내용 및 다음 확인 안건을 생성한다. 원자료와 대조해 로컬 파일로 저장한다. 새 서버나 외부 계정 연동은 만들지 않는다. 다음 회차에는 점검 요청의 정보 누락을 질문으로 보완하고 기능 변경 전후의 동작을 검증한다.</x:v>
+        <x:v>제공된 읽기 전용 파일·Git·시간 MCP를 로컬에서 연결한다. 회의록과 점검 메모, 변경 이력·작업 중 변경을 대조해 다음 협의 안건을 만드는 기능을 구성한다. 안건마다 결정할 질문·현재 확인된 사실·남은 확인·파일과 판본 근거를 남긴다. 과거 회의의 기한을 현재 시각으로 바꾸지 않고, 접근 실패를 업무 없음으로 처리하지 않는지 확인한다. 포털의 도구 서버는 새로 등록하지 않는다.</x:v>
       </x:c>
       <x:c r="D48" s="54" t="n">
         <x:v>45</x:v>
@@ -3626,7 +3622,7 @@
         <x:v>점검 요청의 부족한 정보를 질문하고 재개하기</x:v>
       </x:c>
       <x:c r="C55" s="53" t="str">
-        <x:v>제공된 4회차 점검 요청 시작본의 필수 입력과 완료 기준을 정한다. 누락 시 보류·질문·추가 답변 반영·재판단을 구현하고 근거와 처리 상태를 보존한다. 사람 승인이 필요한 결과를 자동 확정하지 않는다.</x:v>
+        <x:v>제공된 이전 단계 점검 요청 기능에서 시작한다. 요청의 설비·경보·사례를 기존 자료로 먼저 확인하고 부족하거나 충돌한 정보만 질문하도록 확장한다. 답변을 같은 요청 번호에 연결해 다시 판단하며, 다른 요청의 답이 섞이지 않는지 대조한다. 초안의 확인 항목이 답변 전후에 어떻게 바뀌었는지 기록하고 정보 답변과 실제 승인을 구분한다.</x:v>
       </x:c>
       <x:c r="D55" s="54" t="n">
         <x:v>35</x:v>
@@ -3650,7 +3646,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="57" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A57" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3660,7 +3656,7 @@
         <x:v>내 활용 기능의 요구 변경을 명세하고 구현하기</x:v>
       </x:c>
       <x:c r="C57" s="53" t="str">
-        <x:v>같은 점검 요청 프로젝트에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기존 기능을 보존하며 변경한다.</x:v>
+        <x:v>점검 요청에 긴급 확인 표시를 추가하는 요구를 명세한다. 제공 교육용 조건인 쿨러 경보·유효한 TS1 120초 평균 60도 이상을 적용하고, 값 누락·신선도 실패·표본 부족은 미판정으로 남긴다. 기존 요청의 출력과 질문·승인 조건을 보존하면서 구현한다. 요청 초안에서 긴급 표시의 이유와 확인할 항목을 읽을 수 있는지 대조한다. 실제 설비 기준이나 승인 권한은 바꾸지 않는다.</x:v>
       </x:c>
       <x:c r="D57" s="54" t="n">
         <x:v>50</x:v>
@@ -3684,7 +3680,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="59" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A59" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3694,7 +3690,7 @@
         <x:v>직접 정한 기대 결과로 활용 기능 검증하기</x:v>
       </x:c>
       <x:c r="C59" s="53" t="str">
-        <x:v>같은 프로젝트와 spec.md를 기준으로 정상·정보 누락·변경 요구·기존 기능의 기대 결과를 Given/When/Then으로 작성한다. 실제 결과와 비교하고 발견된 오류를 수정해 회귀 확인한다.</x:v>
+        <x:v>일반·긴급·경계값·정보 누락·거절 사례의 기대 결과를 명세에서 먼저 작성한다. 변경한 요청 기능을 실행하여 긴급 표시·근거·미확인 항목과 기존 출력 계약을 대조한다. 실제 오류를 수정한 뒤 같은 사례와 기존 사례를 다시 확인한다. 로컬 상태 검사와 포털의 실제 권한 검증을 구분하여 결과를 저장한다.</x:v>
       </x:c>
       <x:c r="D59" s="54" t="n">
         <x:v>40</x:v>
@@ -3939,7 +3935,7 @@
         </x:is>
       </x:c>
       <x:c r="C74" s="60" t="str">
-        <x:v>포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다. 명령이 실행된 시점과 그 전에 필요한 승인·근거를 실행 기록에서 짚는다. 같은 패턴을 다음 회차 정비·구매에 적용하고 업무별 완료 결과를 비교한다.</x:v>
+        <x:v>포털의 준비된 냉각 대응 시나리오 A를 실행하고 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 따라간다. 승인 대기·거절·보류는 실제 기록이나 제공 사례와 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 다음 담당자가 계속 확인할 일이 무엇인지 근거와 함께 설명한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의·판본·처리 건과 결과를 기록한다.</x:v>
       </x:c>
       <x:c r="D74" s="61" t="n">
         <x:v>20</x:v>
@@ -4032,7 +4028,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="81" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A81" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4044,7 +4040,7 @@
         </x:is>
       </x:c>
       <x:c r="C81" s="53" t="str">
-        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다. 작업지시가 발행된 상태와 실제 정비가 끝난 상태를 구분한다.</x:v>
+        <x:v>포털의 준비된 정기 점검 시나리오 B에서 점검 시점 제안과 근거를 읽고 담당자의 결정을 거친다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조한다. 오더 등록은 실제 정비 완료와 구분한다. 예약 뒤 실제 정비와 다음 교대에 남는 확인을 정리한다. 거절·보류 사례는 확인한 기록 범위에서 비교하고, 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</x:v>
       </x:c>
       <x:c r="D81" s="54" t="n">
         <x:v>45</x:v>
@@ -4068,7 +4064,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="83" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A83" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4080,7 +4076,7 @@
         </x:is>
       </x:c>
       <x:c r="C83" s="53" t="str">
-        <x:v>포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다. 발주 수량과 입고 후 재고를 대조하고, 실제 거래가 아닌 수업용 시뮬레이션 결과임을 구분한다.</x:v>
+        <x:v>포털의 준비된 재고 보충 시나리오 C에서 공급사·수량의 제안 근거와 승인 조건을 확인한다. 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교한다. 수업 시스템의 즉시 입고를 실제 배송으로 설명하지 않는다. 발주 중과 입고 완료를 구분하여 다음 교대에 전달할 수량·남은 확인을 정리한다. 반려 사례는 제공 기록과 구분해 비교하고 BPMN의 해당 작업과 실제 결과를 연결한다.</x:v>
       </x:c>
       <x:c r="D83" s="54" t="n">
         <x:v>45</x:v>
@@ -4189,7 +4185,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="91" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A91" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4199,29 +4195,29 @@
         <x:v>교대 인수인계의 입력과 완료 조건 정의하기</x:v>
       </x:c>
       <x:c r="C91" s="53" t="str">
-        <x:v>대상 설비·교대·기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. ABC의 조치·정비·구매를 다시 실행하지 않고 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</x:v>
+        <x:v>ABC에서 확인한 업무 기록과 별개로, 다음 담당자가 설비 상태·열린 작업·부품·작업 메모를 이어 확인할 교대 인수인계 문제를 정한다. 제공 HI-01의 기준에 맞춰 대상·교대·기준 시각·메모를 정리한다. 인계안의 각 주장에 근거가 있고, 불일치와 확인할 일이 남으며, 인계자 검토와 인수자 확인이 기록되는 것을 완료 조건으로 정한다.</x:v>
       </x:c>
       <x:c r="D91" s="54" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="92" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A92" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="62" t="str">
-        <x:v>보충 매뉴얼을 추출·검토하여 기존 지식에 추가하기</x:v>
+        <x:v>제공 보충 매뉴얼의 추출 결과를 검토하고 지식에 추가하기</x:v>
       </x:c>
       <x:c r="C92" s="60" t="str">
-        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다.</x:v>
+        <x:v>강사 코드로 열린 교대 실습에서 제공 HI-01 보충 매뉴얼을 선택한다. 준비된 추출 후보를 원문과 대조하여 절차·조건·근거를 검토하고 승인한 지식을 추가한다. 추출 결과 재사용과 사람의 검토·적재를 구분한다. 지식 지도에서 새 항목의 식별자와 문서·판본·절 연결을 확인하고 이후 인계안의 확인 기준으로 사용한다.</x:v>
       </x:c>
       <x:c r="D92" s="61" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="93" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A93" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4231,13 +4227,13 @@
         <x:v>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</x:v>
       </x:c>
       <x:c r="C93" s="53" t="str">
-        <x:v>교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
+        <x:v>허용된 설비·정비·ERP 읽기 도구로 인계안을 작성하는 에이전트와 스킬을 구성한다. 설비 관측 시각, 열린 작업지시, 재고·예약·발주 중 수량, 작업 메모를 대조하도록 요구한다. 완료 주장과 원천 상태가 다르면 두 근거와 확인할 질문을 남기게 한다. 결과의 각 문장을 원천 기록과 비교하고 지침을 보완한다. 로컬 랩에서 익힌 출처·질문·검증 방법을 활용하되 코드를 포털에 자동 연결하지 않는다.</x:v>
       </x:c>
       <x:c r="D93" s="54" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="94" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A94" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -4247,7 +4243,7 @@
         <x:v>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</x:v>
       </x:c>
       <x:c r="C94" s="60" t="str">
-        <x:v>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고 근거와 완료 기록을 확인한다.</x:v>
+        <x:v>제공 교대 BPMN의 시작 입력·검토·보완 흐름을 유지하고 표시 이름·배치를 정리한다. 세 초안 단계에 작성한 에이전트를 배정해 판본을 등록한다. 인계안을 원천과 대조하고 인수자에게 근거와 남은 일을 설명한다. 실제 보완 요청이 있으면 같은 처리 건에서 반영해 재검토·인수 확인한다. 인수 확인을 정비·발주 완료로 바꾸지 않고 최종 인계안·근거·확인 기록을 저장한다.</x:v>
       </x:c>
       <x:c r="D94" s="61" t="n">
         <x:v>30</x:v>
@@ -4871,7 +4867,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="150" customHeight="1">
+    <x:row r="9" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A9" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -4879,7 +4875,7 @@
         <x:v>관계도를 설비 모델로 옮기고 적재·조회 결과 확인하기</x:v>
       </x:c>
       <x:c r="C9" s="143" t="str">
-        <x:v>VS Code에서 탐색기의 자료 위치와 터미널 실행 방법을 확인한다. 앞서 그린 관계도와 제공 자료를 대조해 클래스와 개별 설비를 구분한다. 제공 파일 형식에 맞춰 고유 ID·속성·관계 방향을 갖춘 작은 schema.json과 예시 인스턴스를 작성한다. 제공 절차로 별도 랩 DB에 적재한 뒤 설비의 센서·부품을 조회하고 원자료와 비교한다. 빠진 관계나 잘못된 식별자를 수정하고 관계도·모델·조회 결과를 저장한다. 다음 회차에는 이 작은 모델을 여러 설비와 공용 부품으로 확장하고 SOP를 연결한다. Notion 학습노트의 해당 주제에 관계도와 확인 결과를 연결한다.</x:v>
+        <x:v>제공 설비·센서·부품 자료에서 같은 대상의 ID와 관계를 확인하고 작은 모델을 작성한다. 앞 단계가 완성된 시작본과 제공 적재 도구를 활용해 별도 랩 DB에서 설비별 센서·부품을 조회한다. 구조 검사와 원자료의 의미 대조를 구분한다. 관계도·모델·조회 결과를 저장한다. 다음 회차에는 직접 적재·조회 기능을 만들고 SOP를 연결한다.</x:v>
       </x:c>
       <x:c r="D9" s="144" t="n">
         <x:v>50</x:v>
@@ -4952,15 +4948,15 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="16" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A16" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B16" s="141" t="str">
-        <x:v>새 설비와 공용 부품으로 모델 확장하기</x:v>
+        <x:v>제공된 다른 설비와 공용 부품으로 모델 확인하기</x:v>
       </x:c>
       <x:c r="C16" s="141" t="str">
-        <x:v>제공된 새 설비와 공용 부품을 기존 모델에 추가한다. 공용 부품이 여러 설비와 올바르게 연결되는지 조회하고, 기존 설비의 센서·부품 관계가 유지되는지 비교한다.</x:v>
+        <x:v>제공 원자료에 있는 다른 설비를 같은 스키마로 표현한다. 공용 부품의 ID를 재사용하고 설비별로 같은 이름을 쓰는 센서는 구분한다. 새로 연결한 설비와 기존 설비를 함께 조회해 누락·중복·잘못된 끝점을 확인한다. 제공 자료 밖의 설비나 상태를 만들지 않는다.</x:v>
       </x:c>
       <x:c r="D16" s="142" t="n">
         <x:v>50</x:v>
@@ -5128,21 +5124,21 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="31" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A31" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B31" s="143" t="str">
-        <x:v>등록된 문서 지식을 검토하고 로컬 추출 기능 만들기</x:v>
+        <x:v>제공 문서의 추출 후보를 검토하는 기능 만들기</x:v>
       </x:c>
       <x:c r="C31" s="143" t="str">
-        <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 문서의 표·작업 절차·수치·단위·금지 조건을 구조화하는 기능을 만들고 문서 ID·페이지 또는 구간·인용을 함께 출력한다.</x:v>
+        <x:v>포털의 제공 매뉴얼 원문과 등록 지식을 대조한다. 같은 판본의 원문과 추출 후보를 읽어 문서 ID·절·인용·수치·단위·대상 ID를 검사하는 로컬 기능을 작성한다. 추출 재사용과 검토를 구분하고 채택·수정·제외·보류를 기록한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="32" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A32" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5150,7 +5146,7 @@
         <x:v>원문을 대조하고 승인 지식 그래프에 반영하기</x:v>
       </x:c>
       <x:c r="C32" s="141" t="str">
-        <x:v>추출 후보의 조건·단위·순서를 원문과 비교해 채택·수정·제외한다. 채택한 항목을 기존 랩 그래프의 클래스와 식별자에 맞춰 적재하고, 고장→원인→조치→근거 문서 관계를 조회한다.</x:v>
+        <x:v>제공된 검토 결과와 랩 모델에서 시작해 승인한 후보만 별도 랩 DB에 연결한다. 작업 조건·단계·근거 문서의 경로를 조회하고 원문과 대조한다. 미승인 후보 제외와 반복 적재의 중복 방지를 확인한다.</x:v>
       </x:c>
       <x:c r="D32" s="142" t="n">
         <x:v>50</x:v>
@@ -5164,7 +5160,7 @@
         <x:v>다른 문서에 적용하고 결과 검증하기</x:v>
       </x:c>
       <x:c r="C33" s="143" t="str">
-        <x:v>제공된 다른 매뉴얼에 같은 추출 기능을 적용한다. 빠진 조건이나 잘못 연결된 대상이 있는지 원문과 대조하고 수정한다. 그래프에 반영한 지식에서 문서 출처를 다시 찾아 검토 결과와 일치하는지 확인한다. 이 검토 지식과 센서 자료를 다음 회차 에이전트의 근거로 사용한다.</x:v>
+        <x:v>HM-8에서 확인한 검토·적재 기능을 제공 PM-02·PR-07 자료에 적용한다. 단위·부정 조건·작업 순서·출처를 대조하고 빠진 항목을 고친다. 같은 입력으로 재확인하여 코드·검토 기록·질의를 저장한다. 다음 회차에는 이러한 근거를 원인 후보와 점검 제안에 사용한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
         <x:v>50</x:v>
@@ -5597,7 +5593,7 @@
         <x:v>실행 상태를 이해하고 정상·예외 경로 확인하기</x:v>
       </x:c>
       <x:c r="C70" s="141" t="str">
-        <x:v>앞서 그린 BPMN과 실제 실행을 비교하고 같은 구조를 교대 검토·확인 흐름에 연결한다. 포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+        <x:v>포털의 준비된 냉각 대응 시나리오 A를 실행하고 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 따라간다. 승인 대기·거절·보류는 실제 기록이나 제공 사례와 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의·판본·처리 건과 결과를 기록한다.</x:v>
       </x:c>
       <x:c r="D70" s="142" t="n">
         <x:v>50</x:v>
@@ -5617,7 +5613,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" s="1" customFormat="1" ht="98" customHeight="1">
+    <x:row r="72" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A72" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5625,7 +5621,7 @@
         <x:v>보충 지식과 인수인계 에이전트 구성하기</x:v>
       </x:c>
       <x:c r="C72" s="141" t="str">
-        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
+        <x:v>강사 코드로 열린 교대 실습에서 제공 HI-01 원문과 준비된 추출 후보를 대조해 검토한 지식을 추가한다. 문서·판본·절 연결을 확인하고, 허용된 설비·정비·ERP 읽기 도구로 인계안을 작성할 에이전트와 스킬을 구성한다. 관측 시각·작업지시·재고·메모의 불일치와 확인할 일을 남기는지 원천 기록과 대조한다.</x:v>
       </x:c>
       <x:c r="D72" s="142" t="n">
         <x:v>50</x:v>
@@ -5698,7 +5694,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="79" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A79" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5706,13 +5702,13 @@
         <x:v>등록된 정비 흐름을 실행하고 결과 검증하기</x:v>
       </x:c>
       <x:c r="C79" s="143" t="str">
-        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
+        <x:v>포털의 준비된 정기 점검 시나리오 B에서 점검 시점 제안과 근거를 읽고 담당자의 결정을 거친다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조한다. 오더 등록은 실제 정비 완료와 구분한다. 거절·보류 사례는 확인한 기록 범위에서 비교하고, 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</x:v>
       </x:c>
       <x:c r="D79" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="80" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A80" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5720,13 +5716,13 @@
         <x:v>구매 흐름을 설계하고 실행 검증하기</x:v>
       </x:c>
       <x:c r="C80" s="141" t="str">
-        <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
+        <x:v>제공 구매 업무를 bpmn.io에서 시작·제안·승인·발주·입고·보고로 표현한다. 포털의 준비된 재고 보충 시나리오 C에서 공급사·수량의 제안 근거와 승인 조건을 확인한다. 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교한다. 수업 시스템의 즉시 입고를 실제 배송으로 설명하지 않는다. 반려 사례는 제공 기록과 구분해 비교하고 BPMN의 해당 작업과 실제 결과를 연결한다.</x:v>
       </x:c>
       <x:c r="D80" s="142" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="145" customHeight="1">
+    <x:row r="81" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A81" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5734,7 +5730,7 @@
         <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
       </x:c>
       <x:c r="C81" s="143" t="str">
-        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(30분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 관계 모델·판단 근거·실행 기록을 연결하여 전체 과정을 설명한다.</x:v>
+        <x:v>교대 인계안을 원천 기록과 대조하고 근거와 남은 일을 상대에게 설명한다. 인계자 검토→인수자의 확인 또는 실제 보완 요청→같은 처리 건의 재검토·인수 확인을 수행한다. 최종 인계안과 확인 기록을 저장하며 인수 확인과 정비·발주 완료를 구분한다. 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록의 연결을 자신이 수행한 과정과 비교한다.</x:v>
       </x:c>
       <x:c r="D81" s="144" t="n">
         <x:v>50</x:v>
@@ -6464,7 +6460,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="118" customHeight="1">
+    <x:row r="9" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A9" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6472,7 +6468,7 @@
         <x:v>관계도를 설비 모델로 옮기고 적재·조회 결과 확인하기</x:v>
       </x:c>
       <x:c r="C9" s="143" t="str">
-        <x:v>앞서 그린 관계도와 제공 자료를 대조해 클래스와 개별 설비를 구분한다. 제공 파일 형식에 맞춰 고유 ID·속성·관계 방향을 갖춘 작은 schema.json과 예시 인스턴스를 작성한다. 제공 절차로 별도 랩 DB에 적재한 뒤 설비의 센서·부품을 조회하고 원자료와 비교한다. 빠진 관계나 잘못된 식별자를 수정하고 관계도·모델·조회 결과를 저장한다. 다음 회차에는 부품의 사용 설비·공급 정보를 찾고 SOP 조건을 조치 판단에 적용한다. Notion 학습노트의 해당 주제에 관계도와 확인 결과를 연결한다.</x:v>
+        <x:v>제공 설비·부품 모델을 읽고 공용 부품과 설비별 센서를 구분한다. 별도 랩 DB에서 부품을 사용하는 설비를 조회하고 원자료와 대조한다. 공급 조건 자료를 연결할 질문과 필요한 속성을 정리한다. 관계도·질의·확인 결과를 저장한다. 다음 회차에는 공급 정보 조회와 조치 검토 기능으로 확장한다.</x:v>
       </x:c>
       <x:c r="D9" s="144" t="n">
         <x:v>50</x:v>
@@ -6531,7 +6527,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="15" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A15" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6539,13 +6535,13 @@
         <x:v>설비·부품·공급 정보를 연결하고 조회하기</x:v>
       </x:c>
       <x:c r="C15" s="143" t="str">
-        <x:v>기존 설비·부품 모델에 제공 공급 조건을 연결한다. 부품별 사용 설비와 공급 정보를 조회하는 기능을 만들고, 조회 결과의 식별자·관계·공급 조건이 원자료와 일치하는지 확인한다.</x:v>
+        <x:v>앞 단계 완성 모델로 시작해 부품별 사용 설비와 공급 조건을 반환하는 적재·조회문을 작성한다. P-PMP-SEAL의 사용 설비 HYD-01·02·03과 공급 조건 3행을 원자료와 대조한다. 다른 품번과 없는 품번도 확인하고, 비승인 공급사를 승인 상태와 함께 구별한다. 반복 적재의 중복 여부를 검사하고 질의·결과·남은 확인 사항을 저장한다.</x:v>
       </x:c>
       <x:c r="D15" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="16" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A16" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6553,7 +6549,7 @@
         <x:v>조치 조건표와 판정·성과 비교 기능 만들기</x:v>
       </x:c>
       <x:c r="C16" s="141" t="str">
-        <x:v>제공 SOP에서 입력·단위·연산자·경계·출처를 뽑아 조치 조건표를 만든다. 조건에 따라 허용·제외와 사유를 반환하는 기능을 구현하고, 허용 후보의 비용·생산·품질·에너지 성과를 비교한다.</x:v>
+        <x:v>제공된 이전 단계 완성 조건표와 교육용 성과 자료에서 시작한다. 적용 대상과 복합 조건을 읽어 경고·감점·제외·정보 부족을 구분하는 기능을 작성한다. 허용 후보만 비용·생산·품질·에너지 산식으로 비교하고 원문 근거를 남긴다.</x:v>
       </x:c>
       <x:c r="D16" s="142" t="n">
         <x:v>50</x:v>
@@ -6567,7 +6563,7 @@
         <x:v>선택 근거와 확인 사항을 검증해 결과 완성하기</x:v>
       </x:c>
       <x:c r="C17" s="143" t="str">
-        <x:v>정상·경계·금지·누락 입력을 바꾸며 조치 검토 결과를 확인한다. 선택 이유·원문 근거·추가 확인 사항을 하나의 결과로 구성하고, 정보가 빠져도 이미 확인된 제외 근거가 유지되는지 검증한다. 다음 회차에는 조건의 문서 출처를 연결하여 작업 확인 카드로 활용한다.</x:v>
+        <x:v>조치 검토 결과에 후보별 이유·출처·추가 확인할 값을 표시한다. 경계값, 제외 사유와 누락이 겹친 입력, 모두 제외된 입력으로 검증한다. 점수의 높고 낮음과 실행 승인을 구분해 설명하고 결과를 저장한다. 다음 회차에는 작업 조건의 문서 근거를 확인 카드에 연결한다.</x:v>
       </x:c>
       <x:c r="D17" s="144" t="n">
         <x:v>50</x:v>
@@ -6620,27 +6616,27 @@
         <x:v>문서 추출·검토·출처 재사용 이해하기</x:v>
       </x:c>
       <x:c r="C22" s="141" t="str">
-        <x:v>매뉴얼의 조건을 추출·검토하고 특정 작업에서 바로 확인할 수 있는 카드로 바꾼다. 매뉴얼의 작업 조건을 추출 후보·검토 지식·작업 확인 자료로 전환하는 과정을 살펴본다. 문서 ID·페이지·인용 구간과 개정 정보를 보존하는 이유를 이해하고, 원문에 없는 내용을 판별한다.</x:v>
+        <x:v>문서의 추출 후보가 검토·승인 지식·작업 확인 카드로 이어지는 과정을 이해한다. 원문 ID·절·인용·판본을 보존하는 이유를 살펴보고, 준비된 추출 결과를 재사용해도 사람이 조건의 뜻과 누락을 확인해야 함을 구분한다.</x:v>
       </x:c>
       <x:c r="D22" s="142" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="23" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A23" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B23" s="143" t="str">
-        <x:v>문서를 추출하고 원문과 대조하기</x:v>
+        <x:v>제공 추출 후보를 검사하고 원문과 대조하기</x:v>
       </x:c>
       <x:c r="C23" s="143" t="str">
-        <x:v>포털의 제공 매뉴얼 원문과 등록된 추출 결과를 비교한다. VS Code에서 제공 작업의 조건·순서·단위·금지 조건과 출처를 추출하고, 잘못 해석한 항목을 원문과 대조해 수정한다.</x:v>
+        <x:v>포털의 제공 매뉴얼 원문과 등록 지식을 대조한다. 같은 판본의 원문과 추출 후보를 읽어 문서 ID·절·인용·수치·단위·대상 ID를 검사하는 로컬 기능을 작성한다. 추출 재사용과 검토를 구분하고 채택·수정·제외·보류를 기록한다.</x:v>
       </x:c>
       <x:c r="D23" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="24" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A24" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6648,7 +6644,7 @@
         <x:v>검토한 지식을 적재하고 출처 확인하기</x:v>
       </x:c>
       <x:c r="C24" s="141" t="str">
-        <x:v>채택한 지식만 기존 랩 그래프의 식별자에 맞춰 적재한다. 작업·조건·근거 문서의 관계를 조회하고, 각 지식에서 원문 페이지나 인용 구간을 찾아 검토한 내용과 일치하는지 확인한다.</x:v>
+        <x:v>제공된 검토 결과와 랩 모델에서 시작해 승인한 후보만 별도 랩 DB에 연결한다. 작업 조건·단계·근거 문서의 경로를 조회하고 원문과 대조한다. 미승인 후보 제외와 반복 적재의 중복 방지를 확인한다.</x:v>
       </x:c>
       <x:c r="D24" s="142" t="n">
         <x:v>50</x:v>
@@ -6662,7 +6658,7 @@
         <x:v>작업 확인 카드를 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C25" s="143" t="str">
-        <x:v>선택한 작업의 준비·금지·완료 조건을 담은 확인 카드를 생성하는 기능을 만든다. 카드의 각 조건을 원문과 대조해 문서 밖 절차를 제거하고, 다른 제공 작업에도 적용해 결과를 검증한다. 다음 회차에는 검토한 설비·문서 근거를 점검 요청 초안에 연결한다.</x:v>
+        <x:v>선택한 작업의 준비·금지·완료 조건과 근거 절을 모아 확인 카드를 만드는 기능을 작성한다. 제공 문서의 다른 작업에도 적용해 빠진 조건·미제공 절·잘못된 연결을 확인한다. 카드는 확인 자료이며 작업 승인과 다름을 설명한다. 다음 회차에는 같은 근거 확인 방식을 점검 요청에 적용한다.</x:v>
       </x:c>
       <x:c r="D25" s="144" t="n">
         <x:v>50</x:v>
@@ -6721,7 +6717,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="92" customHeight="1">
+    <x:row r="31" ht="108" customHeight="1">
       <x:c r="A31" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6729,13 +6725,13 @@
         <x:v>설비 원인과 점검 순서 기능 만들기</x:v>
       </x:c>
       <x:c r="C31" s="143" t="str">
-        <x:v>포털 에이전트의 도구와 근거를 확인한다. VS Code에서 설비 증거를 읽어 원인 후보와 점검 순서를 제안하는 기능을 만들고, 제안의 각 항목에 사용한 근거가 표시되는지 확인한다.</x:v>
+        <x:v>포털의 준비된 에이전트에서 실제 조회 도구와 근거를 확인한다. 로컬 제공 그래프·사례로 원인 후보와 근거를 읽는 기능을 만들고, 오래된 값·표본 부족을 미확인으로 남기는지 대조한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="32" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A32" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6743,7 +6739,7 @@
         <x:v>설비·문서·부품 근거 연결하기</x:v>
       </x:c>
       <x:c r="C32" s="141" t="str">
-        <x:v>기존 설비·문서·부품 자료의 식별자와 출처를 점검 대상에 연결한다. 제안된 점검 항목에서 관련 설비·부품·문서 근거를 찾아가고, 잘못 연결되거나 빠진 자료를 수정한다.</x:v>
+        <x:v>제공 그래프의 설비·부품·증거와 매뉴얼 절을 점검 대상에 연결한다. 그래프와 문서의 집계 구간이 다르거나 원문 절이 제공되지 않은 경우를 확인하고, 해결된 사실과 추가로 확인할 조건을 분리한다.</x:v>
       </x:c>
       <x:c r="D32" s="142" t="n">
         <x:v>50</x:v>
@@ -6757,7 +6753,7 @@
         <x:v>점검 요청 초안을 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C33" s="143" t="str">
-        <x:v>점검 대상·근거·확인 항목을 담은 요청 초안을 만든다. 자료가 누락되거나 원인이 확정되지 않은 입력을 넣어 확인 질문이나 가설 표시가 남는지 검증한다. 근거 없는 단정을 수정해 요청 결과를 완성한다. 다음 회차에는 반복하는 후속 업무를 스킬로 만들고 변경 자료를 확인해 협의 안건을 정리한다.</x:v>
+        <x:v>대상 설비·부품, 관측 시각, 근거, 확인할 항목과 이유를 담은 점검 요청 초안을 만드는 기능을 완성한다. 누락과 복수 원인 사례를 넣어 가설을 확정으로 쓰지 않는지 대조한다. 초안과 실제 작업지시를 구분해 저장한다. 다음 회차에는 같은 근거 정리 방법으로 협의 안건을 만든다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
         <x:v>50</x:v>
@@ -6852,7 +6848,7 @@
         <x:v>다음 협의 안건을 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C41" s="143" t="str">
-        <x:v>회의 업무 목록과 변경 기록을 합쳐 완료·미결·변경 사항 및 다음 협의에서 확인할 안건을 생성한다. 안건의 근거를 원문과 대조하고 같은 입력을 다시 실행해 필수 정보가 유지되는지 확인한다. 다음 회차에는 점검 요청 기능의 누락 입력과 변경 요구를 명세하고 검증한다.</x:v>
+        <x:v>회의별 결정과 점검 메모의 변경을 연결해 다음 협의 안건을 생성한다. 안건마다 결정할 질문·확인된 사실·남은 확인·파일과 판본 근거를 표시한다. 전달 완료와 발주 완료를 구분하고 후속 자료를 반영해 기존 결정이 사라지거나 중복되지 않는지 대조한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
         <x:v>50</x:v>
@@ -6925,7 +6921,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="48" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A48" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6933,7 +6929,7 @@
         <x:v>변경을 명세하고 기존 기능을 보존해 구현하기</x:v>
       </x:c>
       <x:c r="C48" s="141" t="str">
-        <x:v>기존 점검 요청 기능에서 필요한 변경 한 건을 정한다. 입력·출력·사람 확인·완료 기준을 spec.md에 적고 기능을 구현한다. 변경 전부터 유지해야 할 출력 형식과 승인 조건을 함께 대조한다.</x:v>
+        <x:v>점검 요청에 긴급 확인 표시를 추가하는 요구를 명세한다. 제공 교육용 조건인 쿨러 경보·유효한 TS1 120초 평균 60도 이상을 적용하고, 값 누락·신선도 실패·표본 부족은 미판정으로 남긴다. 기존 요청의 출력과 질문·승인 조건을 보존하면서 구현한다. 요청 초안에서 긴급 표시의 이유와 확인할 항목을 읽을 수 있는지 대조한다. 실제 설비 기준이나 승인 권한은 바꾸지 않는다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
         <x:v>50</x:v>
@@ -6947,7 +6943,7 @@
         <x:v>정상·누락·회귀 시나리오 검증하기</x:v>
       </x:c>
       <x:c r="C49" s="143" t="str">
-        <x:v>직접 정한 정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성한다. 실제 출력을 비교해 어긋난 조건을 수정하고, 기존 점검 요청과 승인 조건도 다시 실행해 회귀 오류가 없는지 확인한다. 다음 회차에는 검증한 작업을 승인·반려 경로가 있는 BPMN으로 표현한다.</x:v>
+        <x:v>일반·긴급·경계값·정보 누락·거절 사례의 기대 결과를 명세에서 먼저 작성한다. 변경한 요청 기능을 실행하여 긴급 표시·근거·미확인 항목과 기존 출력 계약을 대조한다. 실제 오류를 수정한 뒤 같은 사례와 기존 사례를 다시 확인한다. 로컬 상태 검사와 포털의 실제 권한 검증을 구분하여 결과를 저장한다. 다음 회차에는 사람의 판단과 실행 경계를 BPMN으로 표현한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
         <x:v>50</x:v>
@@ -7095,7 +7091,7 @@
         <x:v>실행 상태를 이해하고 정상·예외 경로 확인하기</x:v>
       </x:c>
       <x:c r="C62" s="141" t="str">
-        <x:v>설비 대응의 실행 이력에서 조건과 결과를 확인하고 교대의 검토·보완 흐름을 구성한다. 포털에 이미 등록된 설비 대응 흐름을 쿨러 열화 시나리오로 실행한다. 에이전트 판단→운전원 승인→설비 명령→재관측→완료 기록을 따라간다. 승인 대기와 반려 결과를 비교하고, 자신이 그린 BPMN의 작업·분기와 실행 이력을 대조한다.</x:v>
+        <x:v>포털의 준비된 냉각 대응 시나리오 A를 실행하고 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 따라간다. 승인 대기·거절·보류는 실제 기록이나 제공 사례와 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 다음 담당자가 계속 확인할 일이 무엇인지 근거와 함께 설명한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의·판본·처리 건과 결과를 기록한다.</x:v>
       </x:c>
       <x:c r="D62" s="142" t="n">
         <x:v>50</x:v>
@@ -7115,7 +7111,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" s="1" customFormat="1" ht="98" customHeight="1">
+    <x:row r="64" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A64" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7123,7 +7119,7 @@
         <x:v>보충 지식과 인수인계 에이전트 구성하기</x:v>
       </x:c>
       <x:c r="C64" s="141" t="str">
-        <x:v>강사 코드로 열린 교대 실습에서 제공 보충 매뉴얼을 선택한다. 준비된 추출 결과의 절차·조건·근거를 원문과 비교하고 검토한 항목을 기존 제조 지식에 추가한다. 추가된 지식의 식별자와 원문 연결을 확인한다. 교대 실습에서 허용된 설비·정비·ERP 조회 도구로 인계안을 작성하는 에이전트·스킬을 구성한다. 이름·설명·스킬에 확인할 항목을 적고, 완료 메모와 열린 작업지시 또는 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과와 원천을 대조한다.</x:v>
+        <x:v>강사 코드로 열린 교대 실습에서 제공 HI-01 원문과 준비된 추출 후보를 대조해 검토한 지식을 추가한다. 문서·판본·절 연결을 확인하고, 허용된 설비·정비·ERP 읽기 도구로 인계안을 작성할 에이전트와 스킬을 구성한다. 관측 시각·작업지시·재고·메모의 불일치와 확인할 일을 남기는지 원천 기록과 대조한다.</x:v>
       </x:c>
       <x:c r="D64" s="142" t="n">
         <x:v>50</x:v>
@@ -7196,7 +7192,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="71" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A71" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7204,13 +7200,13 @@
         <x:v>등록된 정비 흐름을 실행하고 결과 검증하기</x:v>
       </x:c>
       <x:c r="C71" s="143" t="str">
-        <x:v>포털의 정기 점검 시나리오로 등록된 정비 흐름을 실행한다. 정비 계획·승인·작업지시·예약 또는 출고·생산 공지의 처리 기록을 확인한다. 승인과 반려 사례를 비교하여 정비 오더가 만들어지는 조건을 자신의 BPMN과 대조한다.</x:v>
+        <x:v>포털의 준비된 정기 점검 시나리오 B에서 점검 시점 제안과 근거를 읽고 담당자의 결정을 거친다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조한다. 오더 등록은 실제 정비 완료와 구분한다. 예약 뒤 실제 정비와 다음 교대에 남는 확인을 정리한다. 거절·보류 사례는 확인한 기록 범위에서 비교하고, 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</x:v>
       </x:c>
       <x:c r="D71" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="72" s="1" customFormat="1" ht="123" customHeight="1">
       <x:c r="A72" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7218,13 +7214,13 @@
         <x:v>구매 흐름을 설계하고 실행 검증하기</x:v>
       </x:c>
       <x:c r="C72" s="141" t="str">
-        <x:v>bpmn.io에서 재고 부족→구매 제안→승인 또는 반려→발주→통지→입고 반영 흐름을 그린다. 포털의 재고 보충 시나리오로 등록된 구매 흐름을 실행한다. 수업용 업무 시스템에서 발주·공급사 통지·입고·재고 반영 기록을 확인하고, 반려 사례의 처리 결과와 비교한다. 자신의 BPMN에서 각 결과에 대응하는 작업을 찾는다.</x:v>
+        <x:v>제공 구매 업무를 bpmn.io에서 시작·제안·승인·발주·입고·보고로 표현한다. 포털의 준비된 재고 보충 시나리오 C에서 공급사·수량의 제안 근거와 승인 조건을 확인한다. 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교한다. 수업 시스템의 즉시 입고를 실제 배송으로 설명하지 않는다. 발주 중과 입고 완료를 구분하여 다음 교대에 전달할 수량·남은 확인을 정리한다. 반려 사례는 제공 기록과 구분해 비교하고 BPMN의 해당 작업과 실제 결과를 연결한다.</x:v>
       </x:c>
       <x:c r="D72" s="142" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="145" customHeight="1">
+    <x:row r="73" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A73" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -7232,7 +7228,7 @@
         <x:v>교대 인수인계를 완성하고 ProcessGPT 연결 보기</x:v>
       </x:c>
       <x:c r="C73" s="143" t="str">
-        <x:v>교대 흐름에 설비·교대 정보를 입력하고 인계안의 근거와 원천 기록을 대조한다. 인계자 검토→인수자 보완 요청→재검토→인수 확인을 거쳐 완료 기록을 확인한다. 실제 결과에서 빠진 정보나 불일치가 있으면 확인 사항으로 남긴다(30분). 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록이 어떻게 연결되는지 자신이 수행한 흐름과 비교한다(20분). 각자 인계 결과의 근거와 추가 확인할 사항을 설명한다.</x:v>
+        <x:v>교대 인계안을 원천 기록과 대조하고 근거와 남은 일을 상대에게 설명한다. 인계자 검토→인수자의 확인 또는 실제 보완 요청→같은 처리 건의 재검토·인수 확인을 수행한다. 최종 인계안과 확인 기록을 저장하며 인수 확인과 정비·발주 완료를 구분한다. 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록의 연결을 자신이 수행한 과정과 비교한다.</x:v>
       </x:c>
       <x:c r="D73" s="144" t="n">
         <x:v>50</x:v>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R559f3fb091c54d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="Rff09c0b331164257"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R9b6354414a0d4c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="R0cd24173d5634523"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Re157ed3d7b4545bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R2cec44d418884d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R692b4b35da064d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rd7ec40999a0a4631"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1515,17 +1515,17 @@
         <x:v>70</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="40" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A40" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="23" t="str">
-        <x:v>제공 문서의 추출 후보를 검토하는 기능 만들기</x:v>
+        <x:v>문서에서 근거 있는 지식을 추출하는 기능 만들기</x:v>
       </x:c>
       <x:c r="C40" s="19" t="str">
-        <x:v>강사가 제공한 HM-8·PM-02·PR-07 원문과 같은 판본의 추출 후보를 읽는다. VS Code에서 후보의 문서 ID·절·인용·수치·단위·대상 ID를 검사하고 검토 결과를 저장하는 기능을 작성한다. 원문과 대조해 채택·수정·제외·보류를 구분하고, 근거가 없거나 확인하지 못한 항목은 승인하지 않는다. 준비된 추출 결과를 사용하며 학생이 새 문서나 재추출 서비스를 추가하지 않는다.</x:v>
+        <x:v>포털에서 본 문서 지식화 과정을 VS Code의 독립 랩으로 구현한다. 원문에서 작업 순서·조건·단위·금지 사항을 추출하고 문서 ID·절·인용을 함께 반환하는 기능을 만든다. 생성된 후보를 원문과 대조하여 채택·수정·제외·보류를 기록한다. 다른 문서에도 적용해 누락과 근거 없는 생성을 확인한다. 제공 추출 결과는 비교·연결 장애 시 대안으로 사용하며, 실제 추출 실행과 구분한다.</x:v>
       </x:c>
       <x:c r="D40" s="25" t="n">
         <x:v>50</x:v>
@@ -1665,7 +1665,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="50" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A50" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1677,13 +1677,13 @@
         </x:is>
       </x:c>
       <x:c r="C50" s="60" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex에서 공용 HYD 온톨로지의 설비→센서→고장 유형→SOP 관계와 제공 센서 입력을 읽어 후보 원인·증거·다음 점검 순서를 산출하는 에이전트를 구성한다. 확인되지 않은 원인은 가설로 표시하고, 생성한 점검 계획과 사용 근거를 저장한다. 단순 Cypher 질의 실습을 반복하지 않는다.</x:v>
+        <x:v>포털에서 확인한 도구 호출과 근거 제시를 독립 에이전트로 구현한다. 설비 그래프 조회와 센서 입력을 읽는 함수를 연결하고 요청 해석·도구 선택·결과 확인·답변의 실행 기록을 살펴본다. 원인 후보·증거·다음 점검 순서를 출력하며 오래된 값·표본 부족·도구 오류를 확인 필요로 구분한다. 다른 설비 사례에도 적용해 근거와 가설이 구별되는지 검증한다.</x:v>
       </x:c>
       <x:c r="D50" s="61" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="51" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A51" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1695,7 +1695,7 @@
         </x:is>
       </x:c>
       <x:c r="C51" s="53" t="str">
-        <x:v>별도 제공된 불량 접수 메시지와 분류 기준을 사용해 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 작은 에이전트를 구현한다. 불량 원인 미확정 시 단정하지 않고 조사 요청으로 넘기는 분기를 두고, 결과를 구조화된 품질 대응 카드로 저장한다.</x:v>
+        <x:v>앞 에이전트의 실행 구조를 재사용하여 품질 접수 업무에 적용한다. 불량 접수 메시지와 분류 기준으로 품질 유형·추가 확인 항목·담당 부서·대응 초안을 구조화한다. 표현이 다른 접수와 정보가 빠진 접수를 비교하고, 미확정 원인을 단정하거나 담당자를 지어내지 않는지 원자료로 확인한다. 품질 대응 카드와 근거를 저장하고 설비 점검과 달라진 입력·판정 기준을 설명한다.</x:v>
       </x:c>
       <x:c r="D51" s="54" t="n">
         <x:v>45</x:v>
@@ -1835,19 +1835,17 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="61" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A61" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B61" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">서로 다른 MCP를 연결하고 조합해 사용하기</x:t>
-        </x:is>
+      <x:c r="B61" s="55" t="str">
+        <x:v>외부 MCP를 연결하고 내 조회 도구를 만들어 조합하기</x:v>
       </x:c>
       <x:c r="C61" s="53" t="str">
-        <x:v>VS Code·GitHub Copilot·Codex에서 사전 준비된 파일시스템·Git·시간 MCP 서버 3종 이상의 실행·접근 권한을 각각 설정하고 도구 목록과 호출 결과를 비교한다. 파일 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청에 조합한다. HYD 포털과 로컬 개발 도구의 연결 방식 차이를 살펴본다.</x:v>
+        <x:v>파일·Git·시간 MCP의 연결과 접근 범위를 설정하고 각 도구의 입력·반환값을 확인한다. 제공 서버 골격에 점검 자료 조회 함수를 구현하여 MCP 도구로 노출하고 기존 에이전트에서 호출한다. 파일 내용·변경 이력·기준 시각을 조합한 결과에서 출처와 조회 실패를 확인한다. 직접 만든 서버와 외부 서버를 로컬에서 연결하며 포털 등록을 전제하지 않는다. 다음 실습에서는 같은 연결 원리로 자기 Notion 자료를 읽는다.</x:v>
       </x:c>
       <x:c r="D61" s="54" t="n">
         <x:v>45</x:v>
@@ -1871,19 +1869,17 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="63" s="1" customFormat="1" ht="168" customHeight="1">
       <x:c r="A63" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
-      <x:c r="B63" s="55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">나만의 대화형 AI 학습 코치 만들기</x:t>
-        </x:is>
+      <x:c r="B63" s="55" t="str">
+        <x:v>내 Notion 학습노트로 출제·채점하는 퀴즈 에이전트 만들기</x:v>
       </x:c>
       <x:c r="C63" s="53" t="str">
-        <x:v>제공된 학습 자료를 읽고 설명·확인 질문·근거를 제시하는 학습 코치를 만든다. 질문의 주제와 참고한 구간을 연결하고 자료에 없는 질문에는 확인할 수 없음을 표시한다. 같은 자료의 다른 질문으로 답과 근거를 대조하고, 스킬·입력·검증 기록을 저장한다. 개인 노트나 외부 서비스를 연결하는 작업은 필수로 두지 않는다.</x:v>
+        <x:v>1회차부터 자기 Notion에 정리한 학습노트의 페이지를 선택하고 MCP 읽기 연결을 설정한다. 노트에서 문항·정답 기준·해설·원문 근거를 구성하는 퀴즈 에이전트를 만들되, 답하기 전에는 정답과 해설을 숨긴다. 학생 답변을 받아 정답·부분 정답·오답과 이유를 알려주고 원문을 다시 열어 확인한다. 다음 문항과 틀린 개념 재도전으로 이어가며 풀이 기록을 저장한다. 표현만 다른 정답·불완전한 답·노트에 없는 질문으로 검증하고, 근거가 부족하면 출제나 채점을 보류한다. Notion 연결이 안 되면 같은 노트의 Markdown 내보내기로 진행하고 실제 MCP 연결 여부를 따로 기록한다.</x:v>
       </x:c>
       <x:c r="D63" s="54" t="n">
         <x:v>45</x:v>
@@ -1971,7 +1967,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="70" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A70" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1983,13 +1979,13 @@
         </x:is>
       </x:c>
       <x:c r="C70" s="53" t="str">
-        <x:v>제공된 5회차 완성 시작본의 후속 업무 요청 결과와 처리 프로젝트를 재사용한다. 해당 업무의 필수 정보가 빠지면 확정하지 않고 확인 질문을 생성하며, 추가 입력 후 다시 판단해 상태 변화를 기록한다.</x:v>
+        <x:v>5회차 원인·점검 계획을 바탕으로 제공된 점검 요청 처리 시작본을 연다. 도구로 확인할 수 있는 정보는 먼저 조회하고 부족하거나 충돌하는 정보만 질문하도록 구현한다. 답변을 같은 요청 번호에 연결해 판단을 재개하고, 답변 전후의 근거·미확인·상태 변화를 비교한다. 다른 요청의 답이 섞이지 않는지 확인하고 정보 답변과 실제 승인을 구분한다. 이 프로젝트를 이후 역할 분담·명세 변경·검증에 이어 쓴다.</x:v>
       </x:c>
       <x:c r="D70" s="54" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="71" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A71" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2001,7 +1997,7 @@
         </x:is>
       </x:c>
       <x:c r="C71" s="60" t="str">
-        <x:v>작성 역할은 업무 요청 초안을 만들고 검토 역할은 근거·수량·승인 정보 누락을 독립적으로 검토한다. 검토 의견에 따라 작성 결과를 수정하고, AI 간 상호 검토와 사람의 최종 승인 여부를 서로 다른 필드로 남긴다.</x:v>
+        <x:v>같은 점검 요청 프로젝트에 작성자와 검토자 역할을 구현한다. 작성자는 점검 초안을 만들고 검토자는 원자료와 대조해 근거 누락·불일치·추정을 지적한다. 지적에 따라 수정한 내용과 남은 확인을 기록하고, 수정이 끝날 조건을 정한다. 두 AI가 동의한 것과 사람의 최종 승인을 구분한다. 실제 지적이 없을 때 억지 반려를 만들지 않는다.</x:v>
       </x:c>
       <x:c r="D71" s="61" t="n">
         <x:v>45</x:v>
@@ -2025,7 +2021,7 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="73" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A73" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2035,7 +2031,7 @@
         <x:v>모호한 기능 변경이 기존 계약에 미치는 영향 확인하기</x:v>
       </x:c>
       <x:c r="C73" s="60" t="str">
-        <x:v>앞 실습과 같은 업무 요청 프로젝트에 긴급 조건을 추가한다. 모호한 요청으로 변경한 결과와 기존 일반 요청의 출력·승인 계약을 비교한다. 제공된 사례를 실행하고 실제로 달라진 입력·출력·승인 조건을 기록한다.</x:v>
+        <x:v>같은 점검 요청 프로젝트에 긴급 표시를 추가하는 요구를 AI에 전달하고 변경된 코드와 실행 결과를 확인한다. 일반 요청·정보 누락·승인 경계가 유지되는지 기존 계약과 비교하고 실제 차이를 기록한다. 실패가 반드시 난다고 가정하지 않는다. 다음 단계에서는 모호했던 입력·판정·출력 조건을 명세로 고정한다.</x:v>
       </x:c>
       <x:c r="D73" s="61" t="n">
         <x:v>50</x:v>
@@ -2053,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c r="C74" s="53" t="str">
-        <x:v>같은 프로젝트의 spec.md에 일반·긴급 요청, 필수 정보 누락 시 보류, 승인 없이 확정 금지, 결과 형식·수용 기준을 명시한다. 구현 후 두 요청을 재실행하고 실제 출력과 명세의 기대 결과를 비교한다. 이 명세와 출력 사례를 다음 회차에서 실행 가능한 검증 시나리오로 바꾼다.</x:v>
+        <x:v>같은 점검 요청의 spec.md에 일반·긴급 조건, 필수 정보 누락 시 보류, 승인 없이 확정 금지, 출력 형식과 수용 기준을 작성한다. 제공 교육용 센서 조건의 시간 구간·단위·경계값을 명시하고 구현한다. 일반·긴급·누락 입력의 실제 결과를 명세와 대조해 바뀐 기능과 보존된 기능을 설명한다. 이 명세와 사례를 다음 회차의 실행 가능한 검증에 사용한다.</x:v>
       </x:c>
       <x:c r="D74" s="54" t="n">
         <x:v>25</x:v>
@@ -2135,13 +2131,13 @@
         </x:is>
       </x:c>
       <x:c r="C80" s="60" t="str">
-        <x:v>제공된 7일차 시작본의 spec.md와 동일 에이전트를 활용한다. 일반 정비, 긴급 정비, 필수 정보 누락, 승인 거절, 도구 오류에 대해 Given·When·Then과 입력값·기대 상태·출력 계약을 작성한다.</x:v>
+        <x:v>이전 단계 기능이 완성된 동일 점검 요청 시작본과 spec.md를 연다. 일반·긴급·정보 누락·승인 거절·도구 오류의 Given·When·Then을 쓰고 입력·기대 상태·필수 출력 근거를 정한다. 구현이 낸 답을 그대로 기대값으로 복사하지 않고 요구와 원자료에서 판정 기준을 도출한다.</x:v>
       </x:c>
       <x:c r="D80" s="61" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" s="1" customFormat="1" ht="60" customHeight="1">
+    <x:row r="81" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A81" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2153,7 +2149,7 @@
         </x:is>
       </x:c>
       <x:c r="C81" s="53" t="str">
-        <x:v>준비한 자동 테스트 또는 반복 실행 스크립트에 BDD 시나리오를 연결한다. 실제 출력과 기대값을 비교하고 어떤 조건에서 규칙을 어겼는지 로그·결과 파일로 확인한다. 모델 출력의 표현 차이와 필수 계약 위반을 구별한다.</x:v>
+        <x:v>실행 환경과 제공 테스트 골격에 자신이 정한 입력·기대 결과·판정 코드를 연결한다. 실제 에이전트 결과를 비교하여 필수 근거·상태·승인 조건의 위반을 찾는다. 모델의 표현 차이와 내용 오류를 구분하고, 반복 실행 결과와 실패 원인을 기록한다. 제공 결과 재생과 실제 도구·모델 호출을 구분한다.</x:v>
       </x:c>
       <x:c r="D81" s="54" t="n">
         <x:v>50</x:v>
@@ -2177,7 +2173,7 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" s="1" customFormat="1" ht="69" customHeight="1">
+    <x:row r="83" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A83" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -2189,7 +2185,7 @@
         </x:is>
       </x:c>
       <x:c r="C83" s="53" t="str">
-        <x:v>기존 설비 이벤트·정비 이력·부품 DB의 실제 연결 가능한 조회 결과 또는 동일 스키마의 수업 준비 자료를 조합한다. 완료 작업·미완료 요청·주의 사항·근거 시각을 포함한 인수인계서를 생성한다. 데이터 패브릭 관점의 다중 출처 통합이지 새 데이터 플랫폼 구축이 아니다.</x:v>
+        <x:v>앞에서 만든 조회 도구·출력 계약·검증 방식을 재사용해 설비 이벤트·정비 이력·부품 자료를 연결하는 인수인계 기능을 구현한다. 같은 대상·시점의 자료인지 대조하고 완료·미완료·주의·근거 시각을 출력한다. 자료 없음·조회 실패·서로 다른 기록을 구분하는 사례로 검증한다. 저장한 결과에서 원자료를 다시 찾을 수 있게 한다. 실제 연결 자료와 준비된 파일을 표시하며 포털 교대 실행은 마지막 회차에 별도로 수행한다.</x:v>
       </x:c>
       <x:c r="D83" s="54" t="n">
         <x:v>45</x:v>
@@ -3306,17 +3302,17 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="35" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A35" s="65" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="62" t="str">
-        <x:v>제공 문서의 추출 후보를 검토하는 기능 만들기</x:v>
+        <x:v>문서에서 작업 조건과 근거를 추출하는 기능 만들기</x:v>
       </x:c>
       <x:c r="C35" s="60" t="str">
-        <x:v>강사가 제공한 HM-8·PM-02·PR-07 원문과 같은 판본의 추출 후보를 읽는다. VS Code에서 후보의 문서 ID·절·인용·수치·단위·대상 ID를 검사하고 검토 결과를 저장하는 기능을 작성한다. 원문과 대조해 채택·수정·제외·보류를 구분하고, 근거가 없거나 확인하지 못한 항목은 승인하지 않는다. 준비된 추출 결과를 사용하며 학생이 새 문서나 재추출 서비스를 추가하지 않는다.</x:v>
+        <x:v>포털에서 본 문서 지식화 과정을 VS Code의 독립 랩으로 구현한다. 원문에서 작업 순서·조건·단위·금지 사항을 추출하고 문서 ID·절·인용을 함께 반환하는 기능을 만든다. 생성된 후보를 원문과 대조하여 채택·수정·제외·보류를 기록한다. 다른 문서에도 적용해 누락과 근거 없는 생성을 확인한다. 제공 추출 결과는 비교·연결 장애 시 대안으로 사용하며, 실제 추출 실행과 구분한다. 실전반은 선택한 작업의 준비·금지·완료 조건을 추출하여 다음 실습의 작업 확인 카드에 연결한다.</x:v>
       </x:c>
       <x:c r="D35" s="61" t="n">
         <x:v>40</x:v>
@@ -3441,7 +3437,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="44" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A44" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3451,7 +3447,7 @@
         <x:v>원인 분석을 점검 요청 초안으로 연결하기</x:v>
       </x:c>
       <x:c r="C44" s="53" t="str">
-        <x:v>제공 설비 그래프와 사례 입력을 읽어 원인 후보·근거·추가 확인을 반환하는 기능을 만들고 점검 요청 초안으로 연결한다. 요청에는 대상 설비·부품, 관측 시각, 확인할 항목과 그 이유를 남긴다. 오래된 값·표본 부족·복수 원인 후보와 문서 기준의 차이를 대조하고, 모르는 항목은 확인 필요로 표시한다. 원인 후보를 확정 원인으로 쓰거나 작업지시를 실제 발행하지 않는다.</x:v>
+        <x:v>포털에서 본 조회·판단을 독립 에이전트로 구현한다. 설비 그래프와 사례 입력을 읽는 도구를 연결하고 호출 기록에서 선택한 도구·입력·결과를 확인한다. 원인 후보·근거·추가 확인을 대상 설비·부품·관측 시각·확인 항목이 있는 점검 요청 초안으로 바꾼다. 오래된 값·표본 부족·복수 원인과 문서 기준의 차이를 대조한다. 다른 대상에도 적용하고 가설을 확정 원인으로 쓰거나 작업지시를 발행한 것처럼 표시하지 않는지 검증한다.</x:v>
       </x:c>
       <x:c r="D44" s="54" t="n">
         <x:v>45</x:v>
@@ -3509,17 +3505,17 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="48" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A48" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="55" t="str">
-        <x:v>파일·Git·시간 도구로 다음 협의 안건 만들기</x:v>
+        <x:v>외부 MCP와 내 도구로 다음 협의 안건 만들기</x:v>
       </x:c>
       <x:c r="C48" s="53" t="str">
-        <x:v>제공된 읽기 전용 파일·Git·시간 MCP를 로컬에서 연결한다. 회의록과 점검 메모, 변경 이력·작업 중 변경을 대조해 다음 협의 안건을 만드는 기능을 구성한다. 안건마다 결정할 질문·현재 확인된 사실·남은 확인·파일과 판본 근거를 남긴다. 과거 회의의 기한을 현재 시각으로 바꾸지 않고, 접근 실패를 업무 없음으로 처리하지 않는지 확인한다. 포털의 도구 서버는 새로 등록하지 않는다.</x:v>
+        <x:v>자기가 정리한 Notion 회의·학습 기록의 읽기 연결과 파일·Git·시간 MCP를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 외부 도구와 조합한다. 앞 회의 스킬을 재사용해 결정할 질문·확인된 사실·남은 확인·페이지나 파일 근거를 담은 다음 협의 안건을 만든다. 서로 다른 회의와 후속 변경을 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 접근 실패를 업무 없음으로 처리하지 않는다. Notion 미연결 시 같은 자료의 내보내기로 이어가되 연결 성공으로 기록하지 않는다.</x:v>
       </x:c>
       <x:c r="D48" s="54" t="n">
         <x:v>45</x:v>
@@ -3690,7 +3686,7 @@
         <x:v>직접 정한 기대 결과로 활용 기능 검증하기</x:v>
       </x:c>
       <x:c r="C59" s="53" t="str">
-        <x:v>일반·긴급·경계값·정보 누락·거절 사례의 기대 결과를 명세에서 먼저 작성한다. 변경한 요청 기능을 실행하여 긴급 표시·근거·미확인 항목과 기존 출력 계약을 대조한다. 실제 오류를 수정한 뒤 같은 사례와 기존 사례를 다시 확인한다. 로컬 상태 검사와 포털의 실제 권한 검증을 구분하여 결과를 저장한다.</x:v>
+        <x:v>일반·긴급·경계값·정보 누락·거절·도구 오류의 기대 결과를 명세와 원자료에서 먼저 작성한다. 테스트 골격에 판정 코드를 구현하여 점검 요청의 긴급 표시·근거·미확인·기존 출력 계약을 검사한다. 실제 오류의 원인을 고친 뒤 기존 사례도 재실행한다. 모델 표현 차이와 계약 위반을 구분하고, 새 대상에 적용한 결과와 재사용할 명세·검증 기록을 저장한다.</x:v>
       </x:c>
       <x:c r="D59" s="54" t="n">
         <x:v>40</x:v>
@@ -5129,10 +5125,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B31" s="143" t="str">
-        <x:v>제공 문서의 추출 후보를 검토하는 기능 만들기</x:v>
+        <x:v>문서 지식 추출 기능을 만들고 원문과 대조하기</x:v>
       </x:c>
       <x:c r="C31" s="143" t="str">
-        <x:v>포털의 제공 매뉴얼 원문과 등록 지식을 대조한다. 같은 판본의 원문과 추출 후보를 읽어 문서 ID·절·인용·수치·단위·대상 ID를 검사하는 로컬 기능을 작성한다. 추출 재사용과 검토를 구분하고 채택·수정·제외·보류를 기록한다.</x:v>
+        <x:v>포털의 제공 원문과 등록 지식을 비교한 뒤, 독립 랩에서 원문을 읽어 조건·단위·금지 사항·근거 절을 추출하는 기능을 작성한다. 생성한 후보를 원문과 대조해 채택·수정·제외·보류를 기록한다. 제공 후보만 검사한 경우와 실제 추출한 경우를 구분한다.</x:v>
       </x:c>
       <x:c r="D31" s="144" t="n">
         <x:v>50</x:v>
@@ -5160,7 +5156,7 @@
         <x:v>다른 문서에 적용하고 결과 검증하기</x:v>
       </x:c>
       <x:c r="C33" s="143" t="str">
-        <x:v>HM-8에서 확인한 검토·적재 기능을 제공 PM-02·PR-07 자료에 적용한다. 단위·부정 조건·작업 순서·출처를 대조하고 빠진 항목을 고친다. 같은 입력으로 재확인하여 코드·검토 기록·질의를 저장한다. 다음 회차에는 이러한 근거를 원인 후보와 점검 제안에 사용한다.</x:v>
+        <x:v>앞에서 만든 추출·검토·적재 기능을 다른 문서에 적용한다. 제공 PM-02·PR-07 또는 학습자가 사용할 수 있는 문서에서 조건·단위·작업 순서·출처를 대조하고 누락을 고친다. 같은 입력의 재실행과 다른 문서의 결과를 확인하고 코드·검토 기록·질의를 저장한다. 다음 회차 에이전트가 이 근거를 사용한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
         <x:v>50</x:v>
@@ -5233,7 +5229,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="92" customHeight="1">
+    <x:row r="40" ht="108" customHeight="1">
       <x:c r="A40" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5241,7 +5237,7 @@
         <x:v>품질 접수 후속 업무 에이전트 만들기</x:v>
       </x:c>
       <x:c r="C40" s="141" t="str">
-        <x:v>제공 불량 접수 메시지와 분류 기준으로 품질 유형·추가 확인 항목·담당 부서·대응 초안을 출력하는 에이전트를 만든다. 원인이 확정되지 않은 사례를 입력해 단정 대신 조사 요청을 남기는지 확인한다.</x:v>
+        <x:v>앞 에이전트의 실행 구조를 재사용하여 품질 접수 메시지와 분류 기준으로 유형·추가 확인·담당 부서·대응 초안을 만든다. 표현이 다른 접수와 정보가 빠진 접수를 비교해 단정 대신 조사 요청을 남기는지 확인한다. 품질 대응 카드와 근거를 저장하고 설비 점검과 달라진 입력·판정 기준을 설명한다.</x:v>
       </x:c>
       <x:c r="D40" s="142" t="n">
         <x:v>50</x:v>
@@ -5328,29 +5324,29 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="48" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A48" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B48" s="141" t="str">
-        <x:v>파일·Git·시간 도구를 조합해 작업하기</x:v>
+        <x:v>외부 MCP와 직접 만든 조회 도구 조합하기</x:v>
       </x:c>
       <x:c r="C48" s="141" t="str">
-        <x:v>파일 내용 읽기→Git 변경 기록 확인→시간 정보 확인을 하나의 요청으로 연결한다. 각 도구의 반환값이 결과에 어떻게 사용됐는지 확인하고, 업무 목록의 변경 내용과 시점을 원자료에 대어 검증한다.</x:v>
+        <x:v>파일·Git·시간 MCP를 연결하고 제공 서버 골격의 점검 자료 조회 함수를 구현한다. 도구 목록·입력·반환값을 확인한 뒤 기존 에이전트에서 외부 도구와 함께 호출한다. 자료 내용·변경 이력·기준 시각이 결과의 어느 근거에 쓰였는지 대조하고, 조회 실패와 자료 없음을 구분한다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="108" customHeight="1">
+    <x:row r="49" ht="188" customHeight="1">
       <x:c r="A49" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B49" s="143" t="str">
-        <x:v>대화형 학습 코치를 만들고 검증하기</x:v>
+        <x:v>내 Notion 노트로 퀴즈를 풀고 피드백 확인하기</x:v>
       </x:c>
       <x:c r="C49" s="143" t="str">
-        <x:v>제공 학습 자료를 바탕으로 문항 생성→답변 입력→정답·원문 근거 피드백으로 이어지는 대화형 학습 코치를 만든다. 답변을 달리 입력해 피드백이 바뀌는지 확인하고, 피드백의 출처가 학습 자료에 있는지 대조한다. 다음 회차에는 정보 누락과 요구 변경에도 결과를 확인할 수 있도록 질문·명세·검증을 연결한다.</x:v>
+        <x:v>1회차부터 자기 Notion에 정리한 학습노트의 페이지를 선택하고 MCP 읽기 연결을 설정한다. 노트에서 문항·정답 기준·해설·원문 근거를 구성하는 퀴즈 에이전트를 만들되, 답하기 전에는 정답과 해설을 숨긴다. 학생 답변을 받아 정답·부분 정답·오답과 이유를 알려주고 원문을 다시 열어 확인한다. 다음 문항과 틀린 개념 재도전으로 이어가며 풀이 기록을 저장한다. 표현만 다른 정답·불완전한 답·노트에 없는 질문으로 검증하고, 근거가 부족하면 출제나 채점을 보류한다. Notion 연결이 안 되면 같은 노트의 Markdown 내보내기로 진행하고 실제 MCP 연결 여부를 따로 기록한다. 다음 회차에는 업무 에이전트의 정보 누락·변경 요구를 질문·명세·검증으로 다룬다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
         <x:v>50</x:v>
@@ -5417,13 +5413,13 @@
         <x:v>질문·답변·재개를 구현하고 작성·검토 결과 비교하기</x:v>
       </x:c>
       <x:c r="C55" s="143" t="str">
-        <x:v>포털의 승인 대기·승인·반려 상태를 확인한다. 제공된 품질 후속 업무 시작본에서 필수 정보가 빠지면 질문하고 답변 뒤 다시 판단하도록 구현한다. 제공 작성·검토 결과를 대조해 AI 검토와 사람의 최종 승인을 구분한다.</x:v>
+        <x:v>포털의 승인·반려 상태를 확인한 뒤 원인·점검 계획에서 이어진 점검 요청 시작본을 연다. 도구로 확인 가능한 정보는 먼저 읽고 부족한 정보만 질문하며 같은 요청의 답변으로 재개하도록 구현한다. 제공 작성·검토 시작본에 원자료 대조 기준을 적용하고 AI 검토와 사람 승인을 구분한다. 이후 명세 변경과 검증도 같은 점검 요청 프로젝트에서 진행한다.</x:v>
       </x:c>
       <x:c r="D55" s="144" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" s="1" customFormat="1" ht="92" customHeight="1">
+    <x:row r="56" s="1" customFormat="1" ht="108" customHeight="1">
       <x:c r="A56" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5431,7 +5427,7 @@
         <x:v>변경 요구를 명세하고 기능 구현하기</x:v>
       </x:c>
       <x:c r="C56" s="141" t="str">
-        <x:v>같은 업무 요청 프로젝트에서 변경할 기능을 정하고 입력·출력·금지 조건·완료 기준을 spec.md로 작성한다. AI 코딩 도구로 변경을 구현한 뒤 기존 일반 요청과 변경 요청의 출력을 비교한다.</x:v>
+        <x:v>같은 점검 요청 프로젝트에 긴급 표시를 추가할 입력·조건·출력·금지 사항을 spec.md로 작성한다. 시간 구간·단위·경계값과 누락 처리 기준을 정하고 AI와 구현한다. 기존 일반 요청과 변경 요청을 비교해 근거·미확인·사람 승인 조건이 유지되는지 확인한다.</x:v>
       </x:c>
       <x:c r="D56" s="142" t="n">
         <x:v>50</x:v>
@@ -6627,10 +6623,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B23" s="143" t="str">
-        <x:v>제공 추출 후보를 검사하고 원문과 대조하기</x:v>
+        <x:v>작업 조건을 추출하고 원문과 대조하기</x:v>
       </x:c>
       <x:c r="C23" s="143" t="str">
-        <x:v>포털의 제공 매뉴얼 원문과 등록 지식을 대조한다. 같은 판본의 원문과 추출 후보를 읽어 문서 ID·절·인용·수치·단위·대상 ID를 검사하는 로컬 기능을 작성한다. 추출 재사용과 검토를 구분하고 채택·수정·제외·보류를 기록한다.</x:v>
+        <x:v>포털의 제공 매뉴얼과 등록 지식을 비교한 뒤 독립 랩에서 선택한 작업의 준비·금지·완료 조건과 근거 절을 추출하는 기능을 작성한다. 원문과 대조해 채택·수정·제외·보류를 기록한다. 다른 작업에도 적용하며 실제 추출 결과와 제공 비교 결과를 구분한다.</x:v>
       </x:c>
       <x:c r="D23" s="144" t="n">
         <x:v>50</x:v>
@@ -6826,21 +6822,21 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="92" customHeight="1">
+    <x:row r="40" ht="108" customHeight="1">
       <x:c r="A40" s="141" t="str">
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B40" s="141" t="str">
-        <x:v>파일·Git·시간으로 변경 자료 확인하기</x:v>
+        <x:v>Notion·외부 MCP와 내 조회 도구 연결하기</x:v>
       </x:c>
       <x:c r="C40" s="141" t="str">
-        <x:v>파일 내용과 Git 변경 이력, 시간 정보를 대조한다. 이전 회의에서 정한 업무 중 무엇이 바뀌었는지 찾고, 변경된 내용·근거 파일·변경 시각을 연결해 기록한다.</x:v>
+        <x:v>자기 Notion 기록과 파일·Git·시간 MCP의 접근 범위를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 기존 에이전트에서 호출한다. 이전 회의와 후속 자료에서 바뀐 내용·근거 페이지 또는 파일·시각을 연결한다. Notion 미연결 시 같은 자료의 내보내기로 진행하되 실제 연결 성공과 구분한다.</x:v>
       </x:c>
       <x:c r="D40" s="142" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="41" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A41" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6848,7 +6844,7 @@
         <x:v>다음 협의 안건을 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C41" s="143" t="str">
-        <x:v>회의별 결정과 점검 메모의 변경을 연결해 다음 협의 안건을 생성한다. 안건마다 결정할 질문·확인된 사실·남은 확인·파일과 판본 근거를 표시한다. 전달 완료와 발주 완료를 구분하고 후속 자료를 반영해 기존 결정이 사라지거나 중복되지 않는지 대조한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</x:v>
+        <x:v>앞서 연결한 Notion 기록·회의록·점검 메모와 회의 스킬을 조합해 다음 협의 안건을 만든다. 안건마다 결정할 질문·확인된 사실·남은 확인·페이지 또는 파일 근거를 표시한다. 후속 자료를 반영한 결과를 이전 결과와 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 직접 쓴 기록이 부족하면 제공 회의 자료를 사용한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
         <x:v>50</x:v>
@@ -6935,7 +6931,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="108" customHeight="1">
+    <x:row r="49" ht="128" customHeight="1">
       <x:c r="A49" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6943,7 +6939,7 @@
         <x:v>정상·누락·회귀 시나리오 검증하기</x:v>
       </x:c>
       <x:c r="C49" s="143" t="str">
-        <x:v>일반·긴급·경계값·정보 누락·거절 사례의 기대 결과를 명세에서 먼저 작성한다. 변경한 요청 기능을 실행하여 긴급 표시·근거·미확인 항목과 기존 출력 계약을 대조한다. 실제 오류를 수정한 뒤 같은 사례와 기존 사례를 다시 확인한다. 로컬 상태 검사와 포털의 실제 권한 검증을 구분하여 결과를 저장한다. 다음 회차에는 사람의 판단과 실행 경계를 BPMN으로 표현한다.</x:v>
+        <x:v>일반·긴급·경계값·정보 누락·거절·도구 오류의 기대 결과를 명세와 원자료에서 먼저 작성한다. 테스트 골격에 판정 코드를 구현하여 점검 요청의 긴급 표시·근거·미확인·기존 출력 계약을 검사한다. 실제 오류의 원인을 고친 뒤 기존 사례도 재실행한다. 모델 표현 차이와 계약 위반을 구분하고, 새 대상에 적용한 결과와 재사용할 명세·검증 기록을 저장한다. 다음 회차에는 사람의 판단과 실행 경계를 BPMN으로 표현한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
         <x:v>50</x:v>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Re157ed3d7b4545bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R2cec44d418884d74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R692b4b35da064d32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rd7ec40999a0a4631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Rc10916e20a7c4c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R8c64c90e0aba4c4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R4bd41221b5ac405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rea900fb1e68f4ad8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1531,7 +1531,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="41" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A41" s="30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -1543,13 +1543,13 @@
         </x:is>
       </x:c>
       <x:c r="C41" s="27" t="str">
-        <x:v>제공된 이전 단계 검토 결과와 랩 모델에서 시작한다. 승인한 후보만 별도 랩 DB의 기존 ID에 연결하는 적재·조회 기능을 작성한다. 조치의 조건·단계·근거 문서로 이어지는 경로를 조회하고 원문과 대조한다. 보류 후보가 들어가지 않는지, 같은 입력을 다시 적재해도 중복되지 않는지 확인한다. 포털 기준 지식과 별도 랩 결과를 구분하여 저장한다.</x:v>
+        <x:v>앞 단계의 검토 결과와 랩 모델에서 시작해 승인한 후보를 기존 ID와 관계에 연결하는 적재·조회 기능을 작성한다. 처음 정한 질문으로 설비·조치·작업 조건·문서 근거를 조회하고 원문과 대조한다. 보류 후보 제외·반복 적재·다른 문서의 추가 반영을 확인한다. 질문·스키마·원문·추출/검토 기록·적재 코드·조회 결과를 연결해 하나의 온톨로지 구축 결과로 저장한다. 어떤 질문에 답할 수 있고 현재값이나 추가 자료가 필요한 질문은 무엇인지 설명한다. 다음 에이전트 실습이 이 지식과 조회 기능을 활용한다.</x:v>
       </x:c>
       <x:c r="D41" s="33" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" s="1" customFormat="1" ht="118" customHeight="1">
+    <x:row r="42" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A42" s="22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1561,7 +1561,7 @@
         </x:is>
       </x:c>
       <x:c r="C42" s="19" t="str">
-        <x:v>1일차 온톨로지의 필요성에서 시작해 2일차 클래스·인스턴스·속성·관계·스키마와 그래프 DB, 3일차 SOP·DMN·BSC/KPI의 조치·판단·성과 체계, 4일차 원천 자료 추출·검토·인제스천·출처 관리를 하나의 흐름으로 복습한다. 각 단계의 입력과 결과물, 지식 구조와 실제 데이터의 차이, 판단 규칙과 근거 문서의 관계를 되짚는다. 이렇게 구축된 지식과 규칙이 이후 에이전트의 업무 판단과 도구 활용에 어떤 역할을 하는지 연결해 살펴본다. 새로운 실습은 진행하지 않는다. 검토한 지식은 다음 회차 에이전트가 원인 후보와 점검 순서를 제안할 때 사용하는 근거가 된다.</x:v>
+        <x:v>필요한 질문 정의→클래스·관계·식별자 설계→그래프 구현→SOP·판단 조건 연결→문서 인제스천→원문 검토·적재→근거 조회를 하나의 구축 과정으로 정리한다. 각 단계에서 직접 만든 결과와 설계 이유, 다른 문서를 추가할 때 바꿀 곳을 설명한다. 그래프 DB에 넣었다는 사실만으로 온톨로지의 의미가 옳거나 자동 추론이 완성되는 것은 아님을 구분한다. 온톨로지가 답할 관계·조건·출처 질문과 현재값 조회·판단 규칙·사람 확인이 필요한 질문의 경계를 살펴본다. 새 과제를 추가하지 않고 구축한 지식을 다음 에이전트의 근거로 연결한다.</x:v>
       </x:c>
       <x:c r="D42" s="25" t="n">
         <x:v>30</x:v>
@@ -1613,7 +1613,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="47" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="47" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A47" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -1625,7 +1625,7 @@
         </x:is>
       </x:c>
       <x:c r="C47" s="53" t="str">
-        <x:v>지식 조회 결과를 실제 요청의 답과 점검 제안으로 바꾸고, 근거 없는 단정을 찾아낸다. LLM의 응답 생성, RAG의 근거 검색, Agent의 목표 지향 작업 수행을 구분한다. 요청 해석→계획→도구 선택·호출→결과 관찰→필요 시 재시도→종료의 실행 고리를 살펴보고, 단순 답변과 점검·요청 등 업무 산출물 생성의 차이를 쿨러 사례로 연결한다.</x:v>
+        <x:v>구축한 온톨로지를 활용하는 원인·점검 에이전트에서 출발해 품질 접수, 데이터 분석·시각화, 회의 후속 업무, 자기 자료 퀴즈, 작성·검토 협업의 서로 다른 목적과 결과를 비교한다. LLM 응답·RAG 근거 검색·Agent의 목표·도구·반복 실행을 구분하고 요청 해석→계획→도구 호출→관찰→종료를 살펴본다. 어떤 작업은 정해진 코드로 충분하고 어떤 작업은 자료 해석과 도구 선택이 필요한지 판단한다. 연결된 도구·자료·권한과 검증 기준이 실제 수행 범위를 결정함을 이해하고 각 활용을 이후 실습에 연결한다.</x:v>
       </x:c>
       <x:c r="D47" s="54" t="n">
         <x:v>40</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="84" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A84" s="63" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -2203,7 +2203,7 @@
         </x:is>
       </x:c>
       <x:c r="C84" s="60" t="str">
-        <x:v>에이전트의 목표와 도구, Skill·MCP의 구분, HITL, SDD·BDD와 회귀 검증, 응용별 산출물의 차이를 복습한다. 신규 실습·과제 없이 배운 내용을 정리한다. 다음 회차에는 검증한 작업을 사람의 승인과 함께 하나의 BPMN 흐름으로 표현한다.</x:v>
+        <x:v>원인 점검·품질 접수·분석 시각화·회의 스킬·자기 자료 퀴즈·협업 검토·자료 통합에서 달랐던 목표·입력·도구·결과 판정을 비교한다. 같은 실행 구조를 재사용한 곳과 새로 구현한 능력을 구분한다. 새 업무를 맡길 때 필요한 자료·도구·완료 조건·사람 확인을 어떻게 정할지 설명한다. Skill·MCP·HITL·SDD·BDD가 각각 해결한 문제를 결과와 연결하며, 다음 회차에는 검증한 작업을 사람 승인과 함께 BPMN 흐름으로 표현한다. 새로운 실습을 추가하지 않는다.</x:v>
       </x:c>
       <x:c r="D84" s="61" t="n">
         <x:v>30</x:v>
@@ -3318,7 +3318,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="36" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A36" s="64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">실습</x:t>
@@ -3328,7 +3328,7 @@
         <x:v>검토 지식으로 작업 확인 카드 만들기</x:v>
       </x:c>
       <x:c r="C36" s="53" t="str">
-        <x:v>제공된 검토 결과와 랩 모델에서 시작해 승인 지식을 별도 랩 DB에 연결한다. 선택한 작업의 준비·금지·완료 조건과 원문 출처를 모아 작업 확인 카드를 생성하는 기능을 만든다. 팬 운전·핀 세척 등 제공 문서의 작업으로 대조하고, 미제공 절이나 해결하지 못한 조건은 확인 사항으로 남긴다. 카드 작성이 작업 승인이나 실행이 아님을 구분한다.</x:v>
+        <x:v>앞 단계의 검토 결과와 랩 모델에서 시작해 승인 지식을 별도 랩 DB의 기존 ID·관계에 연결한다. 선택한 작업의 준비·금지·완료 조건과 원문 출처를 모아 작업 확인 카드를 생성한다. 다른 작업·미제공 절·반복 적재를 확인하고 남은 질문을 표시한다. 질문·모델·문서·추출/검토·적재·조회 결과를 연결해 온톨로지 구축 결과로 저장한다. 공급 정보와 작업 조건을 어디까지 답할 수 있는지, 현재값·승인 없이 결정할 수 없는 것은 무엇인지 설명한다. 다음 회차에는 이 지식으로 점검 요청을 만든다.</x:v>
       </x:c>
       <x:c r="D36" s="54" t="n">
         <x:v>35</x:v>
@@ -3403,7 +3403,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="42" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="42" s="1" customFormat="1" ht="148" customHeight="1">
       <x:c r="A42" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">이론</x:t>
@@ -3415,7 +3415,7 @@
         </x:is>
       </x:c>
       <x:c r="C42" s="53" t="str">
-        <x:v>설비·문서 근거를 점검 요청으로 연결하고 반복하는 후속 업무를 스킬과 도구로 처리한다. LLM·RAG·Agent의 목표·도구·반복 실행 차이, 온톨로지·업무 DB·SOP를 근거로 선택하는 과정과 실패 시 확인해야 할 실행 기록을 사례로 살펴본다.</x:v>
+        <x:v>온톨로지 구축 결과를 점검 요청에 활용하는 사례에서 출발해 분석·시각화, 회의 후속 업무, 자기 자료 학습, 작성·검토 협업으로 에이전트의 활용 범위를 살펴본다. LLM·RAG·Agent의 목표·근거·도구·반복 실행 차이를 비교하고, 작업마다 필요한 입력·결과·검증이 달라짐을 이해한다. 로컬 실습은 근거 있는 점검 요청과 외부 자료를 연결한 다음 협의 안건으로 완성한다. 무엇이든 자동 수행한다고 가정하지 않고 연결된 기능·권한·종료 조건과 사람의 판단을 구분한다.</x:v>
       </x:c>
       <x:c r="D42" s="54" t="n">
         <x:v>30</x:v>
@@ -5148,7 +5148,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="33" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A33" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -5156,7 +5156,7 @@
         <x:v>다른 문서에 적용하고 결과 검증하기</x:v>
       </x:c>
       <x:c r="C33" s="143" t="str">
-        <x:v>앞에서 만든 추출·검토·적재 기능을 다른 문서에 적용한다. 제공 PM-02·PR-07 또는 학습자가 사용할 수 있는 문서에서 조건·단위·작업 순서·출처를 대조하고 누락을 고친다. 같은 입력의 재실행과 다른 문서의 결과를 확인하고 코드·검토 기록·질의를 저장한다. 다음 회차 에이전트가 이 근거를 사용한다.</x:v>
+        <x:v>앞에서 만든 추출·검토·적재 기능을 다른 문서에 적용한다. 제공 PM-02·PR-07 또는 사용할 수 있는 문서의 단위·부정 조건·작업 순서·출처를 대조한다. 처음 정한 질문으로 그래프와 원문 근거를 다시 조회하고 반복 적재를 확인한다. 질문·모델·문서·인제스천 코드·검토·조회 결과를 묶어 구축 결과를 완성한다. 답할 수 있는 질문과 현재값·추가 자료가 필요한 질문을 설명한 뒤 다음 회차 에이전트의 근거로 연결한다.</x:v>
       </x:c>
       <x:c r="D33" s="144" t="n">
         <x:v>50</x:v>
@@ -5201,7 +5201,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="38" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A38" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -5209,7 +5209,7 @@
         <x:v>에이전트의 근거·도구·종료 조건 이해하기</x:v>
       </x:c>
       <x:c r="C38" s="141" t="str">
-        <x:v>검토한 지식과 현재 입력을 이용해 원인 후보·후속 업무·이상 구간을 확인한다. LLM의 답변, RAG의 근거 검색, 에이전트의 목표·도구·반복 실행을 구분한다. 설비 지식과 현재 센서 값을 각각 어디서 얻는지 살펴보고, 근거 부족이나 도구 오류가 생겼을 때 멈추거나 확인을 요청할 조건을 정한다.</x:v>
+        <x:v>앞에서 구축한 온톨로지를 원인·점검 에이전트의 근거로 사용한다. 품질 접수·데이터 시각화·회의 후속 업무·학습 퀴즈 등 활용에 따라 입력·도구·결과가 어떻게 달라지는지 비교한다. LLM·RAG·에이전트의 역할과 관찰·도구 선택·실행·종료를 이해한다. 설비 지식과 현재값을 구분하고 근거 부족·도구 오류에서 멈추거나 물을 조건을 정한다. 이후 직접 구현과 다른 입력 검증으로 연결한다.</x:v>
       </x:c>
       <x:c r="D38" s="142" t="n">
         <x:v>50</x:v>
@@ -6646,7 +6646,7 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="25" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A25" s="143" t="str">
         <x:v>실습</x:v>
       </x:c>
@@ -6654,7 +6654,7 @@
         <x:v>작업 확인 카드를 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C25" s="143" t="str">
-        <x:v>선택한 작업의 준비·금지·완료 조건과 근거 절을 모아 확인 카드를 만드는 기능을 작성한다. 제공 문서의 다른 작업에도 적용해 빠진 조건·미제공 절·잘못된 연결을 확인한다. 카드는 확인 자료이며 작업 승인과 다름을 설명한다. 다음 회차에는 같은 근거 확인 방식을 점검 요청에 적용한다.</x:v>
+        <x:v>승인 지식에서 선택한 작업의 준비·금지·완료 조건과 근거 절을 모아 작업 확인 카드를 구현한다. 다른 작업에도 적용해 누락·미제공 절·잘못된 연결을 확인한다. 질문·설계·문서 추출·검토·적재·조회까지 이어지는 구축 결과를 저장하고, 공급 정보와 작업 조건을 어디까지 확인할 수 있는지 설명한다. 카드가 실제 승인이나 현재 상태 확인을 대신하지 않음을 구분한다. 다음 회차 에이전트가 이 근거를 점검 요청에 사용한다.</x:v>
       </x:c>
       <x:c r="D25" s="144" t="n">
         <x:v>50</x:v>
@@ -6699,7 +6699,7 @@
         <x:v>시간(분)</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" s="1" customFormat="1" ht="108" customHeight="1">
+    <x:row r="30" s="1" customFormat="1" ht="128" customHeight="1">
       <x:c r="A30" s="141" t="str">
         <x:v>이론</x:v>
       </x:c>
@@ -6707,7 +6707,7 @@
         <x:v>원인 근거와 점검 요청 구조 이해하기</x:v>
       </x:c>
       <x:c r="C30" s="141" t="str">
-        <x:v>원인 후보를 나열하는 데서 나아가 점검 대상·근거·확인 항목을 한 요청으로 만든다. 원인 후보를 뒷받침하는 설비·센서·문서 근거를 구분한다. 원인 분석 결과를 점검 대상·근거·확인 항목으로 바꾸는 방법을 살펴보고, 미확정 원인과 실제 확인된 사실을 구분한다.</x:v>
+        <x:v>구축한 온톨로지의 설비·문서 근거를 점검 요청에 활용한다. 같은 에이전트 구조가 분석·회의 후속 업무·자기 자료 학습에도 쓰이되 입력·도구·결과 판정이 달라짐을 비교한다. 이번 실습에서는 원인 후보를 대상·관측 시각·근거·확인할 항목이 있는 요청으로 바꾼다. 실제 도구가 확인한 사실과 가설, 요청 초안과 실제 실행을 구분하고 다른 사례에도 적용할 검증 기준을 정한다.</x:v>
       </x:c>
       <x:c r="D30" s="142" t="n">
         <x:v>50</x:v>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="Rc10916e20a7c4c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="R8c64c90e0aba4c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="R4bd41221b5ac405f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Rea900fb1e68f4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 온라인 44H" sheetId="1" r:id="R21568ba90def4a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 온라인 32H" sheetId="2" r:id="Rbfc15289e32e4af4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통합반 오프라인 정규 10회" sheetId="3" r:id="Ra8ec69ab4946483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실전반 오프라인 정규 9회" sheetId="4" r:id="Ra430b6b3422a4a78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5329,10 +5329,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B48" s="141" t="str">
-        <x:v>외부 MCP와 직접 만든 조회 도구 조합하기</x:v>
+        <x:v>파일·Git·시간 MCP를 연결하고 반환값 확인하기</x:v>
       </x:c>
       <x:c r="C48" s="141" t="str">
-        <x:v>파일·Git·시간 MCP를 연결하고 제공 서버 골격의 점검 자료 조회 함수를 구현한다. 도구 목록·입력·반환값을 확인한 뒤 기존 에이전트에서 외부 도구와 함께 호출한다. 자료 내용·변경 이력·기준 시각이 결과의 어느 근거에 쓰였는지 대조하고, 조회 실패와 자료 없음을 구분한다.</x:v>
+        <x:v>파일·Git·시간 MCP의 실행과 접근 범위를 설정하고 도구 목록·입력·반환값을 확인한다. 같은 자료의 내용·변경 이력·기준 시각을 대조하여 각 도구가 어떤 정보를 제공하는지 구분한다. 접근 실패와 자료 없음을 구분하고 연결 설정과 확인 결과를 저장한다.</x:v>
       </x:c>
       <x:c r="D48" s="142" t="n">
         <x:v>50</x:v>
@@ -5343,10 +5343,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B49" s="143" t="str">
-        <x:v>내 Notion 노트로 퀴즈를 풀고 피드백 확인하기</x:v>
+        <x:v>내 조회 도구를 구현하고 외부 MCP와 조합해 검증하기</x:v>
       </x:c>
       <x:c r="C49" s="143" t="str">
-        <x:v>1회차부터 자기 Notion에 정리한 학습노트의 페이지를 선택하고 MCP 읽기 연결을 설정한다. 노트에서 문항·정답 기준·해설·원문 근거를 구성하는 퀴즈 에이전트를 만들되, 답하기 전에는 정답과 해설을 숨긴다. 학생 답변을 받아 정답·부분 정답·오답과 이유를 알려주고 원문을 다시 열어 확인한다. 다음 문항과 틀린 개념 재도전으로 이어가며 풀이 기록을 저장한다. 표현만 다른 정답·불완전한 답·노트에 없는 질문으로 검증하고, 근거가 부족하면 출제나 채점을 보류한다. Notion 연결이 안 되면 같은 노트의 Markdown 내보내기로 진행하고 실제 MCP 연결 여부를 따로 기록한다. 다음 회차에는 업무 에이전트의 정보 누락·변경 요구를 질문·명세·검증으로 다룬다.</x:v>
+        <x:v>제공 서버 골격에 점검 자료 조회 함수를 구현하고 MCP 도구로 노출한다. 앞에서 연결한 파일·Git·시간 도구와 함께 호출해 자료 내용·변경 이력·시각을 근거로 확인 결과를 만든다. 다른 대상·없는 자료·조회 실패 사례로 결과를 검증하고 코드·설정·출처를 저장한다. 다음 회차에는 점검 요청의 정보 누락과 요구 변경을 질문·명세·검증으로 다룬다. 기본 진행은 Notion 없이 한다. 현장에서 Notion 설치·접속·MCP 연결과 자기 노트 준비가 가능하면, 이 교시의 조회 도구 실습 대신 자기 노트로 문항을 만들고 답변·채점·해설·원문 근거를 확인하는 퀴즈 에이전트 실습을 선택한다. 연결이 안 되면 기본 실습을 계속한다.</x:v>
       </x:c>
       <x:c r="D49" s="144" t="n">
         <x:v>50</x:v>
@@ -6827,10 +6827,10 @@
         <x:v>실습</x:v>
       </x:c>
       <x:c r="B40" s="141" t="str">
-        <x:v>Notion·외부 MCP와 내 조회 도구 연결하기</x:v>
+        <x:v>파일·Git·시간 MCP와 내 조회 도구 연결하기</x:v>
       </x:c>
       <x:c r="C40" s="141" t="str">
-        <x:v>자기 Notion 기록과 파일·Git·시간 MCP의 접근 범위를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 기존 에이전트에서 호출한다. 이전 회의와 후속 자료에서 바뀐 내용·근거 페이지 또는 파일·시각을 연결한다. Notion 미연결 시 같은 자료의 내보내기로 진행하되 실제 연결 성공과 구분한다.</x:v>
+        <x:v>제공 회의록·점검 메모를 읽도록 파일·Git·시간 MCP의 접근 범위를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 기존 에이전트에서 호출한다. 이전 회의와 후속 자료에서 바뀐 내용·근거 파일·시각을 연결하고 조회 실패와 자료 없음을 구분한다. 기본 진행은 Notion 없이 한다. 현장에서 Notion 설치·접속·MCP 연결이 가능하고 자기 기록이 준비되어 있으면, 제공 파일 대신 자기 Notion 기록을 읽어 후속 협의 안건에 활용한다. 연결이 안 되면 제공 파일로 계속한다.</x:v>
       </x:c>
       <x:c r="D40" s="142" t="n">
         <x:v>50</x:v>
@@ -6844,7 +6844,7 @@
         <x:v>다음 협의 안건을 만들고 검증하기</x:v>
       </x:c>
       <x:c r="C41" s="143" t="str">
-        <x:v>앞서 연결한 Notion 기록·회의록·점검 메모와 회의 스킬을 조합해 다음 협의 안건을 만든다. 안건마다 결정할 질문·확인된 사실·남은 확인·페이지 또는 파일 근거를 표시한다. 후속 자료를 반영한 결과를 이전 결과와 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 직접 쓴 기록이 부족하면 제공 회의 자료를 사용한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</x:v>
+        <x:v>앞서 연결한 회의록·점검 메모·변경 이력과 회의 스킬을 조합해 다음 협의 안건을 만든다. 안건마다 결정할 질문·확인된 사실·남은 확인·파일 근거를 표시한다. 후속 자료를 반영한 결과를 이전 결과와 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</x:v>
       </x:c>
       <x:c r="D41" s="144" t="n">
         <x:v>50</x:v>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -5149,7 +5149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="1" max="1"/>
@@ -5608,17 +5608,17 @@
     <row r="31" ht="108" customHeight="1" s="1">
       <c r="A31" s="143" t="inlineStr">
         <is>
-          <t>실습</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B31" s="143" t="inlineStr">
         <is>
-          <t>문서 지식 추출 기능을 만들고 원문과 대조하기</t>
+          <t>포털에서 매뉴얼을 지식으로 올리고 원문과 대조하기</t>
         </is>
       </c>
       <c r="C31" s="143" t="inlineStr">
         <is>
-          <t>포털의 제공 원문과 등록 지식을 비교한 뒤, 독립 랩에서 원문을 읽어 조건·단위·금지 사항·근거 절을 추출하는 기능을 작성한다. 생성한 후보를 원문과 대조해 채택·수정·제외·보류를 기록한다. 제공 후보만 검사한 경우와 실제 추출한 경우를 구분한다.</t>
+          <t>포털 지식 관리에서 제공 쿨러 팬 매뉴얼을 올려 미리 보기로 원문을 확인하고, 에이전트에게 추출을 요청한다. 나온 후보의 단계와 조건을 원문과 한 줄씩 대조해 단위·부정 조건·작업 순서가 틀린 곳은 원문 문장으로 고치고, 원문에 없는 절차는 실행 후보에서 빼며, 고장 유형 같은 필수 선택을 채운다. 검토 표시를 한 뒤 적재하고, 지식 지도에서 새로 연결된 절차·조건과 출처를 확인하며 기존 지식이 줄지 않았는지 본다. 검토 표시 없이는 적재되지 않고 단계를 고치면 다시 검토해야 하는 까닭을 단계마다 결과와 함께 확인한다.</t>
         </is>
       </c>
       <c r="D31" s="144" t="n">
@@ -5628,17 +5628,17 @@
     <row r="32" ht="108" customHeight="1" s="1">
       <c r="A32" s="141" t="inlineStr">
         <is>
-          <t>실습</t>
+          <t>실습(VS Code)</t>
         </is>
       </c>
       <c r="B32" s="141" t="inlineStr">
         <is>
-          <t>원문을 대조하고 승인 지식 그래프에 반영하기</t>
+          <t>문서 지식 추출 기능을 만들고 승인 지식을 그래프에 반영하기</t>
         </is>
       </c>
       <c r="C32" s="141" t="inlineStr">
         <is>
-          <t>제공된 검토 결과와 랩 모델에서 시작해 승인한 후보만 별도 랩 DB에 연결한다. 작업 조건·단계·근거 문서의 경로를 조회하고 원문과 대조한다. 미승인 후보 제외와 반복 적재의 중복 방지를 확인한다.</t>
+          <t>포털에서 거친 과정을 독립 랩에서 직접 만든다. 원문을 읽어 조건·단위·금지 사항·근거 절을 추출하는 기능을 작성하고, 생성한 후보를 원문과 대조해 채택·수정·제외·보류를 기록한다. 승인한 후보만 별도 랩 DB의 설비 모델에 연결하고, 작업 조건·단계·근거 문서의 경로를 조회해 원문과 대조한다. 승인하지 않은 후보가 들어가지 않았는지, 같은 자료를 다시 적재해도 중복되지 않는지 확인한다.</t>
         </is>
       </c>
       <c r="D32" s="142" t="n">
@@ -6855,33 +6855,6 @@
       <c r="C150" s="135" t="n"/>
       <c r="D150" s="135" t="n"/>
     </row>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A66:C66"/>
@@ -6920,7 +6893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="1" max="1"/>
@@ -7147,7 +7120,7 @@
     <row r="16" ht="108" customHeight="1" s="1">
       <c r="A16" s="141" t="inlineStr">
         <is>
-          <t>실습</t>
+          <t>실습(VS Code)</t>
         </is>
       </c>
       <c r="B16" s="141" t="inlineStr">
@@ -7157,7 +7130,7 @@
       </c>
       <c r="C16" s="141" t="inlineStr">
         <is>
-          <t>제공된 이전 단계 완성 조건표와 교육용 성과 자료에서 시작한다. 적용 대상과 복합 조건을 읽어 경고·감점·제외·정보 부족을 구분하는 기능을 작성한다. 허용 후보만 비용·생산·품질·에너지 산식으로 비교하고 원문 근거를 남긴다.</t>
+          <t>포털 What-if에서 운전 조건을 바꿔 조치의 허용·제외와 순위, 성과 지표가 달라지는 것을 먼저 확인한다. 이어 SOP 작업 조건을 옮긴 조건표와 조치별 성과 자료를 읽어, 적용 대상과 복합 조건에 따라 경고·감점·제외·정보 부족을 구분하는 기능을 작성한다. 허용 후보만 비용·생산·품질·에너지 산식으로 비교하고 원문 근거를 남긴다.</t>
         </is>
       </c>
       <c r="D16" s="142" t="n">
@@ -7253,17 +7226,17 @@
     <row r="23" ht="108" customHeight="1" s="1">
       <c r="A23" s="143" t="inlineStr">
         <is>
-          <t>실습</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B23" s="143" t="inlineStr">
         <is>
-          <t>작업 조건을 추출하고 원문과 대조하기</t>
+          <t>포털에서 매뉴얼을 지식으로 올리고 원문과 대조하기</t>
         </is>
       </c>
       <c r="C23" s="143" t="inlineStr">
         <is>
-          <t>포털의 제공 매뉴얼과 등록 지식을 비교한 뒤 독립 랩에서 선택한 작업의 준비·금지·완료 조건과 근거 절을 추출하는 기능을 작성한다. 원문과 대조해 채택·수정·제외·보류를 기록한다. 다른 작업에도 적용하며 실제 추출 결과와 제공 비교 결과를 구분한다.</t>
+          <t>포털 지식 관리에서 제공 쿨러 팬 매뉴얼을 올려 미리 보기로 원문을 확인하고, 에이전트에게 추출을 요청한다. 나온 후보에서 작업의 준비·금지·완료 조건과 단계를 원문과 한 줄씩 대조해 틀린 곳은 원문 문장으로 고치고, 원문에 없는 절차는 실행 후보에서 빼며, 고장 유형 같은 필수 선택을 채운다. 검토 표시를 한 뒤 적재하고, 지식 지도에서 새로 연결된 작업 조건과 출처를 확인하며 기존 지식이 줄지 않았는지 본다. 검토 표시 없이는 적재되지 않고 단계를 고치면 다시 검토해야 하는 까닭을 결과와 함께 확인한다.</t>
         </is>
       </c>
       <c r="D23" s="144" t="n">
@@ -7273,17 +7246,17 @@
     <row r="24" ht="108" customHeight="1" s="1">
       <c r="A24" s="141" t="inlineStr">
         <is>
-          <t>실습</t>
+          <t>실습(VS Code)</t>
         </is>
       </c>
       <c r="B24" s="141" t="inlineStr">
         <is>
-          <t>검토한 지식을 적재하고 출처 확인하기</t>
+          <t>작업 조건 추출 기능을 만들고 검토한 지식을 적재하기</t>
         </is>
       </c>
       <c r="C24" s="141" t="inlineStr">
         <is>
-          <t>제공된 검토 결과와 랩 모델에서 시작해 승인한 후보만 별도 랩 DB에 연결한다. 작업 조건·단계·근거 문서의 경로를 조회하고 원문과 대조한다. 미승인 후보 제외와 반복 적재의 중복 방지를 확인한다.</t>
+          <t>포털에서 거친 과정을 독립 랩에서 직접 만든다. 선택한 작업의 준비·금지·완료 조건과 근거 절을 추출하는 기능을 작성하고, 원문과 대조해 채택·수정·제외·보류를 기록한 뒤 다른 작업에도 적용한다. 승인한 후보만 별도 랩 DB에 연결하고, 작업 조건·단계·근거 문서의 경로를 조회해 원문과 대조한다. 승인하지 않은 후보가 들어가지 않았는지, 같은 자료를 다시 적재해도 중복되지 않는지 확인한다.</t>
         </is>
       </c>
       <c r="D24" s="142" t="n">
@@ -8548,33 +8521,6 @@
       <c r="C150" s="135" t="n"/>
       <c r="D150" s="135" t="n"/>
     </row>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="A66:C66"/>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -932,7 +932,7 @@
     <row r="2" ht="36" customHeight="1" s="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2026-10-26 개편 | 11회×240분 | 온라인 설명·시연 및 Wrap-up 유지 | 시간은 편성값이며 녹화 실측과 구별</t>
+          <t>11회 × 240분 | 회차마다 이론으로 배우고, 포털에서 써 보고, VS Code에서 직접 만들어 본다</t>
         </is>
       </c>
       <c r="D2" s="10">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B83" s="55" t="inlineStr">
         <is>
-          <t>서로 다른 업무 데이터를 연결해 교대 업무 인수인계 완성하기</t>
+          <t>서로 다른 업무 데이터를 연결해 인수인계 자료 만들기</t>
         </is>
       </c>
       <c r="C83" s="53" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B94" s="130" t="inlineStr">
         <is>
-          <t>작성한 흐름을 기존 에이전트와 실제 시스템에 연결하기</t>
+          <t>작성한 BPMN과 등록된 실행 흐름의 연결 비교하기</t>
         </is>
       </c>
       <c r="C94" s="131" t="inlineStr">
         <is>
-          <t>강사를 따라 bpmn.io에서 작성한 설비 대응 흐름을 포털의 흐름 가져오기로 불러온다. 쿨러 경보를 시작 조건으로 정하고, 진단 · 조치 제안 작업에 기존 에이전트를, 승인 작업에 운전원 역할을, 설비 명령 · 재관측 · 결과 보고 작업에 시스템 기능을 연결하며 승인 · 거절 분기 조건을 정한다. 검사를 실행해 빠진 연결을 찾아 고치고 판본으로 등록한 뒤, 포털에 등록된 기준 흐름과 비교해 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지와 그림 파일 · 실행 정의의 차이를 확인한다.</t>
+          <t>강사를 따라 포털 흐름 화면에서 등록된 냉각 대응 흐름을 열어, 쿨러 경보 시작 조건과 진단 · 조치 제안 작업의 에이전트, 승인 작업의 운전원 역할, 설비 명령 · 재관측 · 결과 보고 작업의 시스템 기능, 승인 · 거절 분기 조건이 어떻게 연결돼 있는지 확인한다. bpmn.io에서 그린 자신의 흐름과 나란히 놓고 각 작업이 어떤 실행 기능에 대응하는지 표시해, 빠진 연결이 있으면 그림을 고치고 그림 파일과 실행 정의가 어떻게 다른지 확인한다.</t>
         </is>
       </c>
       <c r="D94" s="132" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C102" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 작성한 정기 점검 BPMN을 흐름 가져오기로 불러와 정기 점검 도래를 시작 조건으로, 정비 계획 에이전트 · 설비보전팀장 승인 · CMMS 정비 오더 · 생산 공지 작업을 연결하고 검사해 판본으로 등록한다. 정기 점검을 일으켜 처리 건을 시작하고, 점검 시점 제안과 근거를 읽은 뒤 담당자로서 결정한다. 승인했을 때 같은 처리 건의 작업지시 · 부품 예약 · 생산 공지 · 보고를 대조하고, 거절했을 때 오더가 만들어지지 않는 것과 비교한다. 오더 등록은 실제 정비 완료와 구분하고, 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</t>
+          <t>강사를 따라 정기 점검 도래를 일으켜 등록된 정비 흐름으로 처리 건을 시작하고, 점검 시점 제안과 근거를 읽은 뒤 설비보전팀장으로 결정한다. 승인했을 때 같은 처리 건의 작업지시 · 부품 예약 · 생산 공지 · 보고를 대조하고, 거절했을 때 오더가 만들어지지 않는 것과 비교한다. 오더 등록과 실제 정비 완료를 구분하고, 실행 결과를 앞에서 그린 정비 BPMN의 작업과 연결해 저장한다.</t>
         </is>
       </c>
       <c r="D102" s="54" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C104" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 작성한 구매 BPMN을 같은 방식으로 불러와 재고 부족을 시작 조건으로, 구매 에이전트 · 구매 담당자 승인 · ERP 발주 · 공급사 통지 · 입고 반영 작업을 연결하고 검사해 등록한다. 재고 보충을 일으켜 처리 건을 시작하고 공급사 · 수량의 제안 근거와 승인 조건을 확인한 뒤 결정한다. 승인했을 때 발주 · 통지 · 입고 · 재고 반영을 각각 찾아 시작 재고 · 예약 · 발주 중 수량과 비교하고, 거절했을 때 발주가 막히는 것과 비교한다. 시스템에서 즉시 반영되는 입고와 실제 배송 · 도착을 구분하고, BPMN의 해당 작업과 실제 결과를 연결한다.</t>
+          <t>강사를 따라 재고 보충을 일으켜 등록된 구매 흐름으로 처리 건을 시작하고, 공급사 · 수량의 제안 근거와 승인 조건을 확인한 뒤 구매 담당자로 결정한다. 승인했을 때 발주 · 통지 · 입고 · 재고 반영을 각각 찾아 시작 재고 · 예약 · 발주 중 수량과 비교하고, 거절했을 때 발주가 막히는 것과 비교한다. 시스템에서 바로 반영되는 입고와 실제 배송 · 도착을 구분하고, 앞에서 그린 구매 BPMN의 작업과 실제 결과를 연결한다.</t>
         </is>
       </c>
       <c r="D104" s="54" t="n">
@@ -2992,7 +2992,7 @@
     <row r="2" ht="36" customHeight="1" s="1">
       <c r="A2" s="66" t="inlineStr">
         <is>
-          <t>2026-10-26 개편 | 8회×240분 | 온라인 설명·시연 및 Wrap-up 유지 | 시간은 편성값이며 녹화 실측과 구별</t>
+          <t>8회 × 240분 | 회차마다 이론으로 배우고, 포털에서 써 보고, VS Code에서 직접 만들어 본다</t>
         </is>
       </c>
       <c r="D2" s="49">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="B72" s="130" t="inlineStr">
         <is>
-          <t>작성한 흐름에 에이전트와 실행 기능 연결하기</t>
+          <t>작성한 BPMN과 등록된 작업의 실행 연결 비교하기</t>
         </is>
       </c>
       <c r="C72" s="131" t="inlineStr">
         <is>
-          <t>강사를 따라 bpmn.io에서 작성한 설비 대응 흐름을 포털의 흐름 가져오기로 불러와, 쿨러 경보 시작 조건 · 진단 · 조치 제안 에이전트 · 운전원 승인 역할 · 설비 명령 · 재관측 · 결과 보고 작업과 승인 · 거절 분기 조건을 연결한다. 포털에 등록된 기준 흐름과 비교해 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다.</t>
+          <t>강사를 따라 포털 흐름 화면에서 등록된 냉각 대응 흐름을 열어, 쿨러 경보 시작 조건 · 진단 · 조치 제안 에이전트 · 운전원 승인 역할 · 설비 명령 · 재관측 · 결과 보고 작업과 승인 · 거절 분기 조건이 어떻게 연결돼 있는지 확인한다. bpmn.io에서 그린 자신의 흐름과 나란히 놓고 각 작업이 어떤 실행 기능에 대응하는지 표시해 빠진 연결을 찾는다.</t>
         </is>
       </c>
       <c r="D72" s="132" t="n">
@@ -4238,17 +4238,17 @@
     <row r="73" ht="92" customHeight="1" s="1">
       <c r="A73" s="64" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(bpmn.io)</t>
         </is>
       </c>
       <c r="B73" s="55" t="inlineStr">
         <is>
-          <t>연결 오류를 검사하고 실행할 흐름으로 등록하기</t>
+          <t>BPMN의 역할·분기·종료 연결 검사하고 수정하기</t>
         </is>
       </c>
       <c r="C73" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 흐름 화면의 검사를 실행해 작업 부품 누락 · 분기 조건 누락 같은 연결 오류를 찾고, 자신의 BPMN에서 승인 · 반려 경로와 종료 연결을 따라가며 고친다. 작업별 담당 역할과 실행 기능이 빠지지 않았는지 기준 흐름과 비교하고, 검사를 통과한 정의를 판본으로 등록한다.</t>
+          <t>등록된 기준 흐름의 승인 · 반려 경로와 종료 연결을 따라가며, 자신의 BPMN에서 작업 담당 역할 · 실행 기능 · 분기 조건 · 종료가 빠지거나 어긋난 곳을 찾아 고친다. 고친 그림을 다시 기준 흐름과 대조해 모든 경로가 끝까지 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="D73" s="54" t="n">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C81" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 작성한 정비 BPMN을 흐름 가져오기로 불러와 정기 점검 도래 시작 조건 · 정비 계획 에이전트 · 설비보전팀장 승인 · CMMS 오더 · 생산 공지 작업을 연결하고 검사해 등록한다. 정기 점검을 일으켜 처리 건을 시작하고 점검 시점 제안과 근거를 읽은 뒤 담당자로서 결정한다. 승인했을 때 같은 처리 건의 작업지시 · 부품 예약 · 생산 공지 · 보고를 대조하고, 거절했을 때 오더가 만들어지지 않는 것과 비교한다. 오더 등록은 실제 정비 완료와 구분하고, 예약 뒤 실제 정비와 다음 교대에 남는 확인을 정리하며, 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</t>
+          <t>강사를 따라 정기 점검 도래를 일으켜 등록된 정비 흐름으로 처리 건을 시작하고, 점검 시점 제안과 근거를 읽은 뒤 설비보전팀장으로 결정한다. 승인했을 때 작업지시 · 부품 예약 · 생산 공지 · 보고를, 거절했을 때 오더가 만들어지지 않는 것을 비교하고, 오더 등록과 실제 정비 완료를 구분해 결과를 자신의 BPMN 작업과 연결한다.</t>
         </is>
       </c>
       <c r="D81" s="54" t="n">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C83" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 작성한 구매 BPMN을 같은 방식으로 불러와 재고 부족 시작 조건 · 구매 에이전트 · 구매 담당자 승인 · ERP 발주 · 공급사 통지 · 입고 반영 작업을 연결하고 검사해 등록한다. 재고 보충을 일으켜 처리 건을 시작하고 공급사 · 수량의 제안 근거와 승인 조건을 확인한 뒤 결정한다. 승인했을 때 발주 · 통지 · 입고 · 재고 반영을 각각 찾아 시작 재고 · 예약 · 발주 중 수량과 비교하고, 거절했을 때 발주가 막히는 것과 비교한다. 시스템에서 즉시 반영되는 입고와 실제 배송 · 도착을 구분하고, 발주 중과 입고 완료를 구분하여 다음 교대에 전달할 수량 · 남은 확인을 정리한다. BPMN의 해당 작업과 실제 결과를 연결한다.</t>
+          <t>강사를 따라 재고 보충을 일으켜 등록된 구매 흐름으로 처리 건을 시작하고, 공급사 · 수량의 제안 근거와 승인 조건을 확인한 뒤 구매 담당자로 결정한다. 승인했을 때 발주 · 통지 · 입고 · 재고 반영을, 거절했을 때 발주가 막히는 것을 비교하고, 바로 반영되는 입고와 실제 배송 · 도착을 구분해 결과를 자신의 BPMN 작업과 연결한다.</t>
         </is>
       </c>
       <c r="D83" s="54" t="n">
@@ -5168,7 +5168,7 @@
     <row r="2" ht="48" customHeight="1" s="1">
       <c r="A2" s="135" t="inlineStr">
         <is>
-          <t>매회 50분 수업·10분 휴식 × 4교시입니다(수업200분·휴식40분). 온라인 선행학습을 바탕으로 목적·핵심 개념을 연결하고 실습합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</t>
+          <t>매회 50분 수업 · 10분 휴식 × 4교시(수업 200분 · 휴식 40분). 온라인 한 회차의 내용을 한 회에 담아, 핵심 이론을 짚은 뒤 포털에서 써 보고 VS Code에서 직접 만들어 본다.</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
     <row r="4" ht="38" customHeight="1" s="1">
       <c r="A4" s="138" t="inlineStr">
         <is>
-          <t>01회차 | HYD 전체 흐름을 확인하고 설비 관계 표현하기</t>
+          <t>01회차  |  설비 데이터가 판단과 조치로 이어지는 전체 흐름 이해하기</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="B6" s="141" t="inlineStr">
         <is>
-          <t>HYD 시스템과 이번 과정의 학습 목표 이해하기</t>
+          <t>설비 데이터가 판단으로 이어지는 구조와 온톨로지가 필요한 이유 이해하기</t>
         </is>
       </c>
       <c r="C6" s="141" t="inlineStr">
         <is>
-          <t>설비 데이터가 실제 조치로 이어지려면 무엇이 필요한지, 과정 전체의 줄기를 먼저 잡는다. 유압 설비와 업무 시스템을 하나로 연결한 HYD를 예로, 설비·센서 데이터 수집→상태 관찰→지식에 근거한 판단→사람 승인→조치→결과 확인이 한 흐름으로 이어지는 구조를 살펴본다. 포털의 설비 화면·지식 지도·에이전트·작업함이 이 흐름에서 각각 어떤 역할을 맡는지 구분한다. 이번 과정에서 관계 모델을 만들고, 그 근거를 조회하는 에이전트를 만들고, 업무 흐름으로 연결하는 학습 목표를 확인한다. 이어지는 실습에서 이 흐름을 포털에서 직접 돌려 보고 판단 근거를 관계도와 그래프로 표현한다.</t>
+          <t>설비 데이터가 실제 조치로 이어지려면 무엇이 필요한지, 과정 전체의 줄기를 잡는다. 기록을 쌓는 것과 다시 찾아 쓸 수 있는 지식 자산으로 남기는 것의 차이를 보고, 개념·원리·출처·실습 결과를 연결해 기록하는 이유를 이해한다. 설비·센서·PLC·관제 화면의 역할을 짧게 되짚은 뒤, HYD의 OT·DMZ·IT 영역과 층 구조에서 센서 데이터가 메시지 처리·시계열 DB·분석 서비스를 거쳐 화면과 판단 기능에 쓰이는 경로를 데이터 리니지로 따라가고, 분석 결과가 실제 조치로 이어질 때 명령 게이트웨이와 설비 제어 영역이 필요한 이유를 살펴본다. 이어 온도가 올랐다는 사실만으로는 원인과 조치를 알 수 없는 까닭에서 출발해 데이터·정보·지식의 차이와, 대상의 종류·속성·관계·제약을 명시하는 지식 모델인 온톨로지를 배우고, 관계 그림이나 그래프 DB 자체가 곧 온톨로지는 아님을 구분한다.</t>
         </is>
       </c>
       <c r="D6" s="142" t="n">
@@ -5230,17 +5230,17 @@
     <row r="7" ht="125" customHeight="1" s="1">
       <c r="A7" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(Notion)</t>
         </is>
       </c>
       <c r="B7" s="143" t="inlineStr">
         <is>
-          <t>포털에서 완성 흐름을 직접 돌려 보고 관계도 그리기</t>
+          <t>Notion으로 지식 자산화를 위한 학습노트 만들기</t>
         </is>
       </c>
       <c r="C7" s="143" t="inlineStr">
         <is>
-          <t>포털에 접속해 홈과 설비 화면에서 설비 상태와 센서 값을 확인하고, 쿨러 열화를 직접 일으켜 경보가 뜨는 것을 본다. 에이전트가 낸 원인·조치 추천을 읽고 작업함에서 운전원으로 승인해, 설비 명령→센서 값 재확인→완료 기록까지 따라간다. 승인 권한이 없는 역할로는 처리되지 않고, 거절하면 설비 명령이 나가지 않으며, 승인을 미루면 지연 알림이 뜨는 것도 직접 해 보며 추천·승인·실행의 차이를 구분한다. 지식 지도에서 설비를 골라 판단에 쓰인 설비·센서·고장·조치 연결과 속성·방향을 눌러 확인한다. 이어 arrows.app에서 방금 본 대상을 노드와 관계로 그리고 각 화살표를 문장으로 읽는다.</t>
+          <t>Notion에서 학습노트 홈과 주제별 카드·페이지를 구성한다. 샘플 개념·출처·실습 결과를 연결해 저장하고, 다시 열어 검색·보완·재사용할 수 있는지 확인한다. 이 노트에 이번 과정에서 배우는 개념과 실습 결과를 이어서 쌓는다. 6회에는 이 노트로 자기 노트 퀴즈 에이전트를 만든다.</t>
         </is>
       </c>
       <c r="D7" s="144" t="n">
@@ -5250,17 +5250,17 @@
     <row r="8" ht="92" customHeight="1" s="1">
       <c r="A8" s="141" t="inlineStr">
         <is>
-          <t>실습(Neo4j)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B8" s="141" t="inlineStr">
         <is>
-          <t>Cypher로 그래프 생성·조회·수정·삭제하기</t>
+          <t>실습 환경을 열고 설비 이상부터 승인·조치까지 직접 돌려 보기</t>
         </is>
       </c>
       <c r="C8" s="141" t="inlineStr">
         <is>
-          <t>별도 Neo4j 랩 DB에서 작은 예제를 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 생성·조회·수정한다. 그래프의 노드와 관계를 눌러 속성을 확인하고 표 결과와 비교한다. DELETE·DETACH DELETE로 연습 데이터만 정리하고 재조회한다.</t>
+          <t>학교 PC의 VS Code·AI 코딩 도구(GitHub Copilot·Codex)·Python·Docker가 각각 무슨 일을 하는지 알고 실행 상태를 확인한 뒤 HYD 포털을 연다. 홈의 상태 표시와 시스템 구성 화면에서 설비·데이터·판단·업무 시스템이 어떻게 이어지는지 보고, 실시간 모니터링·지식 지도·지식 관리·에이전트·내 작업함·처리 건 메뉴를 눌러 각 화면에서 할 일을 확인한다. 오늘 쓸 자료를 작업 폴더에 받아 가이드를 열고, 남길 결과를 USB나 개인 클라우드로 내보내는 방법을 익힌다. 이어 결함 시뮬레이션에서 쿨러 열화를 직접 일으켜 센서 값이 변하고 경보가 뜨는 것을 보고, AI의 원인·조치 추천과 근거를 내 작업함에서 읽고 승인한 뒤 설비 명령→온도 재관측→결과 보고까지 처리 건에서 따라간다. 단계마다 쓰인 정보와 다음 단계로 넘어간 것을 비교하며 AI의 추천·사람의 승인·실제 조치가 서로 다른 단계임을 확인한다.</t>
         </is>
       </c>
       <c r="D8" s="142" t="n">
@@ -5270,17 +5270,17 @@
     <row r="9" ht="108" customHeight="1" s="1">
       <c r="A9" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(ARROWS)</t>
         </is>
       </c>
       <c r="B9" s="143" t="inlineStr">
         <is>
-          <t>관계도를 설비 모델로 옮기고 적재·조회 결과 확인하기</t>
+          <t>설비 이상과 원인·조치의 관계를 관계도로 그리기</t>
         </is>
       </c>
       <c r="C9" s="143" t="inlineStr">
         <is>
-          <t>제공 설비·센서·부품 자료에서 같은 대상의 ID와 관계를 찾아 작은 설비 모델을 작성한다. 제공 적재 도구로 이 모델을 별도 랩 DB에 올리고 설비별 센서·부품을 조회해, 그림으로 그린 관계가 실제 질문에 답하는지 확인한다. 형식이 맞는지 보는 구조 검사와 원자료와 뜻이 맞는지 보는 대조가 서로 다른 확인임을 구분한다. 관계도·모델·조회 결과를 저장한다. 다음 회차에는 적재·조회 기능을 직접 만들고 작업 절차(SOP)를 연결한다.</t>
+          <t>arrows.app에서 노드·관계·레이블을 만드는 법을 익히고, 방금 따라간 쿨러 이상을 바탕으로 설비·센서·증상·원인·조치를 배치해 연결 관계와 방향을 직접 그린다. 각 화살표를 문장으로 읽어 보며 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 이 관계도를 다음 회차에 식별자와 속성을 갖춘 모델로 옮겨 그래프로 조회한다.</t>
         </is>
       </c>
       <c r="D9" s="144" t="n">
@@ -5307,7 +5307,7 @@
     <row r="12" ht="38" customHeight="1" s="1">
       <c r="A12" s="138" t="inlineStr">
         <is>
-          <t>02회차 | 설비 모델을 완성하고 작업 절차 연결하기</t>
+          <t>02회차  |  설비와 데이터의 관계를 체계화해 필요한 정보 찾기</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5341,12 @@
       </c>
       <c r="B14" s="141" t="inlineStr">
         <is>
-          <t>식별자·적재·SOP 연결 원리 이해하기</t>
+          <t>클래스·스키마·그래프 DB로 설비 지식의 구조 이해하기</t>
         </is>
       </c>
       <c r="C14" s="141" t="inlineStr">
         <is>
-          <t>앞서 만든 작은 모델을 다시 적재해도 중복되지 않게 하고 작업 절차를 연결한다. 고유 식별자로 같은 대상을 구분하는 방법과 반복 적재 시 중복을 막는 원리를 살펴본다. 필수값·자료형·관계 끝점 제약을 설비 모델에 대어 확인하고, 고장·조치와 SOP의 전제·금지·완료 조건이 연결되는 구조를 이해한다.</t>
+          <t>1회에 그린 관계도에 같은 대상의 식별 기준을 정하고, 질문에 답할 수 있는 그래프로 만든다. 클래스·인스턴스·속성·관계를 설비·센서·부품 같은 유형과 실제 설비 한 대·센서 하나의 비교로 구분하고, 데이터 속성과 객체 사이 관계, 관계 방향과 카디널리티, 새 클래스로 둘지 속성이나 관계로 둘지를 설비 사례로 판단한다. 스키마가 클래스·속성·관계·제약을 일관되게 정의하는 구조임을 배우고 식별자·자료형·필수 여부·관계의 시작과 끝 클래스, 스키마와 인스턴스 데이터의 차이, 스키마 없이 연결할 때 생기는 의미 불일치를 살펴본다. 그래프 DB의 노드·관계·속성 구조를 관계형 DB의 테이블·행·조인과 비교하고, Cypher의 MATCH·WHERE·RETURN·CREATE·MERGE가 각각 무엇을 하는지 예제로 익힌다.</t>
         </is>
       </c>
       <c r="D14" s="142" t="n">
@@ -5356,17 +5356,17 @@
     <row r="15" ht="92" customHeight="1" s="1">
       <c r="A15" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(Neo4j)</t>
         </is>
       </c>
       <c r="B15" s="143" t="inlineStr">
         <is>
-          <t>모델을 보완하고 적재·조회 검증하기</t>
+          <t>Cypher로 그래프를 다루고 포털 지식 지도와 비교하기</t>
         </is>
       </c>
       <c r="C15" s="143" t="inlineStr">
         <is>
-          <t>설비 모델의 고유 ID·자료형·필수값·관계 끝점을 원자료와 대조해 보완한다. 모델을 적재하고 설비별 센서·부품을 조회한다. 같은 자료를 다시 적재한 뒤 노드와 관계가 불필요하게 늘어나지 않았는지 확인한다.</t>
+          <t>별도 Neo4j 랩 DB에서 작은 예제를 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 생성·조회·수정하고, 그래프를 눌러 속성을 확인하며 RETURN 대상에 따른 그래프·표 결과를 비교한다. DELETE·DETACH DELETE로 연습 데이터만 정리하고 재조회한 뒤, 제공 설비 예제에서 구성 요소·센서·부품의 연결을 한 단계·여러 단계 경로로 조회하고 조건·집계 결과를 원래 행과 대조한다. 이어 포털 지식 지도에서 설비를 골라 연결된 센서·부품을 펼치고, 노드를 눌러 식별자와 속성을 확인하며 관계의 방향을 읽는다. 같은 센서 이름이라도 설비마다 식별자가 다른 것을 구분하고, 랩 DB의 연습 그래프와 포털의 기준 지도를 비교한다.</t>
         </is>
       </c>
       <c r="D15" s="144" t="n">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="B16" s="141" t="inlineStr">
         <is>
-          <t>제공된 다른 설비와 공용 부품으로 모델 확인하기</t>
+          <t>관계도를 설비 모델로 설계하기</t>
         </is>
       </c>
       <c r="C16" s="141" t="inlineStr">
         <is>
-          <t>제공 원자료에 있는 다른 설비를 같은 스키마로 표현한다. 공용 부품의 ID를 재사용하고 설비별로 같은 이름을 쓰는 센서는 구분한다. 새로 연결한 설비와 기존 설비를 함께 조회해 누락·중복·잘못된 끝점을 확인한다. 모델에는 원자료에 있는 설비와 상태만 담는다.</t>
+          <t>제공 설비·센서·부품 원자료를 읽고 설비별 센서와 공용 부품을 찾을 질문을 정한다. VS Code에서 목표·자료·제약·확인 사례를 자기 말로 정리하고 AI와 함께 모델을 설계한다. 같은 센서 이름이 다른 설비에 쓰인 경우와 별칭·중복·누락을 구분해 고유 ID·단위·관계 방향을 정하고 스키마와 그래프 자료를 작성한다. 형식이 맞는지 보는 구조 검사와 질문마다 원자료와 뜻이 맞는지 보는 대조를 따로 해 본다.</t>
         </is>
       </c>
       <c r="D16" s="142" t="n">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B17" s="143" t="inlineStr">
         <is>
-          <t>SOP를 모델에 연결하고 결과 완성하기</t>
+          <t>설계한 모델을 그래프 DB에 적재하고 조회로 검증하기</t>
         </is>
       </c>
       <c r="C17" s="143" t="inlineStr">
         <is>
-          <t>제공 SOP에서 작업의 전제·금지·수행 단계·완료 조건을 구분한다. 고장 유형과 조치 방법을 기존 설비 모델의 식별자에 연결하고, 선택한 고장에 적용할 절차와 금지 조건을 조회해 원문과 비교한다. 다음 회차에는 연결한 SOP 조건으로 조치의 허용·제외와 성과를 판정한다.</t>
+          <t>앞에서 설계한 설비·센서·부품 모델을 그래프 DB에 적재하는 코드와 조회문을 직접 작성하고, 스키마의 식별자와 관계 방향이 노드·관계로 어떻게 옮겨지는지 확인한다. 별도 랩 DB에서 설비별 센서·부품과 공용 부품을 쓰는 설비를 조회해 원자료와 대조한다. 같은 자료를 다시 적재해도 노드와 관계가 늘어나지 않는지, 이름이 바뀌어도 같은 ID가 유지되는지 확인하고, 전체를 지우지 않고 필요한 부분만 고친다. 코드·질의·확인 결과를 저장한다. 다음 회차에는 이 모델에 작업 절차를 연결하고 조치 판단 조건으로 만든다.</t>
         </is>
       </c>
       <c r="D17" s="144" t="n">
@@ -5433,7 +5433,7 @@
     <row r="20" ht="38" customHeight="1" s="1">
       <c r="A20" s="138" t="inlineStr">
         <is>
-          <t>03회차 | 안전한 조치와 성과 비교 기능 만들기</t>
+          <t>03회차  |  설비 상황에 맞는 안전하고 효과적인 조치 선택하기</t>
         </is>
       </c>
     </row>
@@ -5467,12 +5467,12 @@
       </c>
       <c r="B22" s="141" t="inlineStr">
         <is>
-          <t>안전한 판단 규칙과 성과 비교 기준 이해하기</t>
+          <t>안전한 조치 절차·판단 규칙·성과 기준 이해하기</t>
         </is>
       </c>
       <c r="C22" s="141" t="inlineStr">
         <is>
-          <t>관계와 절차를 읽는 데서 나아가 입력 조건에 따라 가능한 조치와 그 이유를 반환한다. SOP의 작업 순서와 DMN의 판단 조건을 구분한다. 입력값·단위·연산자·경계값으로 조치 허용·제외를 표현하고, 허용된 후보끼리 비용·생산·품질·에너지 성과를 비교하는 이유를 사례로 확인한다.</t>
+          <t>설비 관계를 안다는 것만으로 조치를 실행할 수 없으므로 허용 조건과 선택 근거를 구분한다. 원인을 진단하는 것과 조치 방법을 정하는 것이 다른 단계임을 이해하고, SOP의 적용 대상·전제 조건·안전 조건·수행 단계·금지 사항·담당 역할·완료 확인 기준과 같은 조치도 운전 상태에 따라 수행 여부가 달라지는 이유를 살펴본다. 고장 유형·원인·조치 방법·작업 단계·근거 매뉴얼이 지식 모델에서 연결되는 구조와 즉시 완화·근본 조치·예방 조치의 차이도 본다. DMN의 입력·결정·결정표·규칙과 비교 연산자·임계값·범위·복수 조건, 규칙의 중복·누락·상충과 여러 규칙이 맞을 때 결과를 고르는 방식을 배운다. 끝으로 BSC 네 관점과 전략 목표·KPI, 서로 부딪칠 수 있는 복구 시간·생산 차질·전력비·품질·안전 성과를 비교하고, 조치 가능 여부를 정하는 규칙과 허용된 조치의 효과·비용을 견주는 기준, What-if 분석의 목적과 한계를 구분한다.</t>
         </is>
       </c>
       <c r="D22" s="142" t="n">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="B23" s="143" t="inlineStr">
         <is>
-          <t>SOP 조건표를 만들고 조치 차이 확인하기</t>
+          <t>운전 조건과 성과 기준에 따라 조치 결과 비교하기</t>
         </is>
       </c>
       <c r="C23" s="143" t="inlineStr">
         <is>
-          <t>포털의 판단 화면에서 현재 값으로 판단을 실행해 입력·규칙·조치 후보를 확인하고, What-if에서 운전 조건을 바꿔 조치의 허용·제외와 순위, 성과 지표가 어떻게 달라지는지 비교한다. 이어 제공 SOP에서 입력·단위·경계·출처를 뽑아 결정표를 작성하고, 각 조건이 어떤 조치를 허용하거나 제외하는지 표시한다.</t>
+          <t>포털 조치 판단 규칙 화면에서 설비와 이상 상황을 골라 판단을 실행하고 입력값·적용 규칙·조치 후보를 확인한다. 설비 상태나 운전 모드를 바꿔 다시 실행하며 어떤 규칙이 적용되어 어떤 조치가 허용·제외되는지 비교한다. 조건별 손익 화면에서 값 하나를 바꿔 허용된 조치의 예상 손익과 순위가 달라지는 것을 보고, 성과 지표 화면에서 KPI 목표를 바꿔 판정을 시험한다. 결과마다 근거와 입력 단위를 확인하고, 시험값을 되돌린 뒤 원본 업무 데이터와 지식이 그대로인지 확인해 시험값 변경과 실제 설비 조치를 구분한다.</t>
         </is>
       </c>
       <c r="D23" s="144" t="n">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="B24" s="141" t="inlineStr">
         <is>
-          <t>조건별 판정 기능 구현하기</t>
+          <t>작업 절차와 판단 조건을 연결해 조치 기준 만들기</t>
         </is>
       </c>
       <c r="C24" s="141" t="inlineStr">
         <is>
-          <t>VS Code에서 결정표를 입력으로 사용해 조치의 허용·제외와 사유를 반환하는 기능을 만든다. 정상 조건, 경계값, 여러 규칙이 동시에 맞는 경우, 금지 조건을 입력해 실제 결과를 조건표와 대조한다.</t>
+          <t>VS Code에서 AI 코딩 도구와 함께 작업 조건이 정리된 제공 SOP를 쓴다. 2회에 만든 설비 모델의 식별자를 재사용해 제공된 고장 유형과 조치 방법을 연결하고, 작업의 적용 조건·금지 조건·수행 단계·완료 기준을 구분해 구조화한다. 이를 입력·단위·연산자·경계값과 판단 결과로 된 결정표로 옮기고, 각 조건이 어떤 조치를 허용하거나 제외하는지와 원문 출처를 표시한다.</t>
         </is>
       </c>
       <c r="D24" s="142" t="n">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="B25" s="143" t="inlineStr">
         <is>
-          <t>성과를 비교하고 경계·누락 입력 검증하기</t>
+          <t>설비 조건별 조치를 판정하고 성과를 비교하는 기능 만들기</t>
         </is>
       </c>
       <c r="C25" s="143" t="inlineStr">
         <is>
-          <t>허용된 조치 후보만 비용·생산 영향·품질·에너지 기준으로 비교한다. 경계값이나 필수 정보 누락에 따라 결과가 달라지는지 확인하고, 선택 이유와 추가 확인 사항을 출력한다. 추천 결과와 사람의 실행 승인을 구분한다. 다음 회차에는 사용한 조건의 원문을 추출·검토하여 근거 지식을 보강한다.</t>
+          <t>앞의 결정표를 읽어 조치를 판정하는 기능을 만든다. 적용 대상과 복합 조건을 구분해 경고·감점·제외·정보 부족을 이유와 함께 돌려주고, 허용된 후보만 비용·생산·품질·에너지 손실을 주어진 비교 산식으로 견준다. 정상·경계값·여러 조건이 겹친 경우·모두 제외·필수값 누락 사례로 결과를 결정표와 대조하고 선택 이유와 추가 확인 사항을 출력한다. 이 비교값은 후보를 견주는 계산으로 포털 성과 지표의 점수와 다르고, 추천 결과는 사람의 실행 승인과 다른 단계임을 구분한다. 다음 회차에는 사용한 조건의 원문을 추출·검토해 근거 지식을 보강한다.</t>
         </is>
       </c>
       <c r="D25" s="144" t="n">
@@ -5559,7 +5559,7 @@
     <row r="28" ht="38" customHeight="1" s="1">
       <c r="A28" s="138" t="inlineStr">
         <is>
-          <t>04회차 | 문서를 지식으로 추출하고 검토하기</t>
+          <t>04회차  |  현장 자료를 검증해 신뢰할 수 있는 판단 근거 만들기</t>
         </is>
       </c>
     </row>
@@ -5593,12 +5593,12 @@
       </c>
       <c r="B30" s="141" t="inlineStr">
         <is>
-          <t>문서 추출·검토·출처 관리 원리 이해하기</t>
+          <t>현장 자료를 검증된 지식으로 바꾸는 과정과 온톨로지 구축 정리하기</t>
         </is>
       </c>
       <c r="C30" s="141" t="inlineStr">
         <is>
-          <t>판단에 쓰는 조건을 원문까지 확인할 수 있도록 문서 추출·검토·적재를 연결한다. 매뉴얼 원문, AI가 추출한 후보, 검토를 거친 지식을 구분한다. 부정 조건·단위·작업 순서가 잘못 추출된 사례를 원문과 대조하고, 문서 ID·페이지·인용 구간을 지식과 함께 보존하는 이유를 이해한다.</t>
+          <t>판단에 쓰는 조건을 문서에서 찾아 검토하고 출처를 다시 확인할 수 있는 지식으로 만든다. 원천 확보→내용 분석→지식 후보 추출→기존 스키마·식별자에 매핑→원문 대조와 사람 검토→승인 지식 적재→관계·출처 조회의 단계별 역할을 이해하고, LLM이 문서를 구조화할 때 생기는 부정 조건 누락·수치와 단위 오류·잘못된 관계 추론·근거 없는 생성을 사례로 본다. 원문 페이지·인용 구간·문서 식별자·개정 이력을 지식과 함께 남기는 이유, 문서를 검색해 참고하는 방식과 구조화된 지식으로 등록하는 방식의 차이, 원인·절차 같은 안정적 지식과 센서·재고처럼 계속 변하는 값은 원천에서 조회해야 하는 까닭을 살펴본다. 끝으로 질문 정의부터 근거 조회까지를 하나의 구축 과정으로 정리하고, 그래프에 넣었다는 사실만으로 의미가 옳은 것은 아님과 온톨로지가 답할 질문과 현재값·사람 확인이 필요한 질문의 경계를 구분한다.</t>
         </is>
       </c>
       <c r="D30" s="142" t="n">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="C31" s="143" t="inlineStr">
         <is>
-          <t>포털 지식 관리에서 제공 쿨러 팬 매뉴얼을 올려 미리 보기로 원문을 확인하고, 에이전트에게 추출을 요청한다. 나온 후보의 단계와 조건을 원문과 한 줄씩 대조해 단위·부정 조건·작업 순서가 틀린 곳은 원문 문장으로 고치고, 원문에 없는 절차는 실행 후보에서 빼며, 고장 유형 같은 필수 선택을 채운다. 검토 표시를 한 뒤 적재하고, 지식 지도에서 새로 연결된 절차·조건과 출처를 확인하며 기존 지식이 줄지 않았는지 본다. 검토 표시 없이는 적재되지 않고 단계를 고치면 다시 검토해야 하는 까닭을 단계마다 결과와 함께 확인한다.</t>
+          <t>포털 지식 관리에서 제공 쿨러 팬 매뉴얼을 올려 미리 보기로 원문을 확인하고, 에이전트에게 추출을 요청한다. 나온 후보의 단계와 조건을 원문과 한 줄씩 대조해 단위·부정 조건·작업 순서가 틀린 곳은 원문 문장으로 고치고, 원문에 없는 절차는 실행 후보에서 빼며, 고장 유형 같은 필수 선택을 채운다. 검토 표시를 한 뒤 적재하고, 지식 지도에서 새로 연결된 절차·조건과 출처를 확인하며 기존 지식이 줄지 않았는지 본다. 검토 표시 없이는 적재되지 않고 단계를 고치면 다시 검토해야 하는 까닭을 단계마다 결과와 함께 확인한다. 데이터 연결 화면에서는 문서에서 온 판단 기준과 업무 DB·시계열 DB에서 조회되는 현재값이 어떻게 다른지 살펴본다.</t>
         </is>
       </c>
       <c r="D31" s="144" t="n">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="B32" s="141" t="inlineStr">
         <is>
-          <t>문서 지식 추출 기능을 만들고 승인 지식을 그래프에 반영하기</t>
+          <t>문서에서 근거 있는 지식을 추출하는 기능 만들기</t>
         </is>
       </c>
       <c r="C32" s="141" t="inlineStr">
         <is>
-          <t>포털에서 거친 과정을 독립 랩에서 직접 만든다. 원문을 읽어 조건·단위·금지 사항·근거 절을 추출하는 기능을 작성하고, 생성한 후보를 원문과 대조해 채택·수정·제외·보류를 기록한다. 승인한 후보만 별도 랩 DB의 설비 모델에 연결하고, 작업 조건·단계·근거 문서의 경로를 조회해 원문과 대조한다. 승인하지 않은 후보가 들어가지 않았는지, 같은 자료를 다시 적재해도 중복되지 않는지 확인한다.</t>
+          <t>포털에서 거친 문서 지식화 과정을 VS Code의 독립 랩으로 만든다. 원문에서 작업 순서·조건·단위·금지 사항을 추출하고 문서 ID·절·인용을 함께 돌려주는 기능을 작성한다. 생성한 후보를 원문과 대조해 채택·수정·제외·보류를 기록하고, 제공 정기 점검표·예비품 기준 같은 다른 문서에도 적용해 누락과 근거 없는 생성을 확인한다.</t>
         </is>
       </c>
       <c r="D32" s="142" t="n">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="B33" s="143" t="inlineStr">
         <is>
-          <t>다른 문서에 적용하고 결과 검증하기</t>
+          <t>검토한 문서 지식을 그래프 DB에 반영하고 온톨로지 구축 결과 완성하기</t>
         </is>
       </c>
       <c r="C33" s="143" t="inlineStr">
         <is>
-          <t>앞에서 만든 추출·검토·적재 기능을 다른 문서에 적용한다. 제공 정기 점검표·예비품 기준이나 직접 고른 문서에서 단위·부정 조건·작업 순서·출처를 원문과 대조한다. 처음 정한 질문으로 그래프와 원문 근거를 다시 조회하고 반복 적재를 확인한다. 질문·모델·문서·추출 코드·검토·조회 결과를 묶어 온톨로지 구축 결과를 완성한다. 지금 지식으로 답할 수 있는 질문과 현재값·추가 자료가 필요한 질문을 설명하고, 이를 다음 회차 에이전트의 근거로 잇는다.</t>
+          <t>검토 결과에서 승인한 후보만 별도 랩 DB의 기존 ID와 관계에 연결하는 적재·조회 기능을 작성한다. 처음 정한 질문으로 설비·조치·작업 조건·문서 근거를 조회해 원문과 대조하고, 보류한 후보가 들어가지 않았는지, 같은 자료를 다시 적재해도 중복되지 않는지, 다른 문서를 더 반영해도 기존 연결이 유지되는지 확인한다. 질문·스키마·원문·추출과 검토 기록·적재 코드·조회 결과를 묶어 하나의 온톨로지 구축 결과로 저장하고, 지금 지식으로 답할 수 있는 질문과 현재값이나 추가 자료가 필요한 질문을 설명한다. 다음 회차 에이전트가 이 지식과 조회 기능을 근거로 쓴다.</t>
         </is>
       </c>
       <c r="D33" s="144" t="n">
@@ -5685,7 +5685,7 @@
     <row r="36" ht="38" customHeight="1" s="1">
       <c r="A36" s="138" t="inlineStr">
         <is>
-          <t>05회차 | 서로 다른 일을 하는 에이전트 만들기</t>
+          <t>05회차  |  현장 지식을 활용해 실제 문제를 해결하는 AI 에이전트 만들기</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="B38" s="141" t="inlineStr">
         <is>
-          <t>에이전트의 근거·도구·종료 조건 이해하기</t>
+          <t>일하는 AI의 구조와 정보·도구를 쓰는 원리 이해하기</t>
         </is>
       </c>
       <c r="C38" s="141" t="inlineStr">
         <is>
-          <t>앞에서 구축한 온톨로지를 원인·점검 에이전트의 근거로 사용한다. 품질 접수·데이터 시각화·회의 후속 업무·학습 퀴즈 등 활용에 따라 입력·도구·결과가 어떻게 달라지는지 비교한다. LLM·RAG·에이전트의 역할과 관찰·도구 선택·실행·종료를 이해한다. 설비 지식과 현재값을 구분하고 근거 부족·도구 오류에서 멈추거나 물을 조건을 정한다. 이후 직접 구현과 다른 입력 검증으로 연결한다.</t>
+          <t>구축한 온톨로지를 근거로 쓰는 원인·점검 에이전트에서 출발해 품질 접수·데이터 분석과 시각화·회의 후속 업무·자기 자료 퀴즈·작성과 검토 협업이 목적과 결과에서 어떻게 다른지 비교한다. LLM 응답·근거 검색(RAG)·에이전트를 목표·도구·반복 실행으로 구분하고, 요청 해석→계획→도구 호출→관찰→종료의 흐름과 정해진 코드로 충분한 작업·자료 해석과 도구 선택이 필요한 작업을 가른다. 온톨로지(설비·증상·원인 관계)·시계열 DB(측정값)·업무 DB(정비·재고)·SOP(작업 방법)의 역할을 나누어 지식과 현재값을 혼동하지 않는 법을 익히고, 근거 부족·도구 실패·권한 제한에서 멈추거나 묻는 조건과 구조화 출력·실행 기록을 살펴본다.</t>
         </is>
       </c>
       <c r="D38" s="142" t="n">
@@ -5734,17 +5734,17 @@
     <row r="39" ht="92" customHeight="1" s="1">
       <c r="A39" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B39" s="143" t="inlineStr">
         <is>
-          <t>설비 원인과 점검 순서 에이전트 만들기</t>
+          <t>업무 에이전트를 만들고 질문의 도구·근거 확인하기</t>
         </is>
       </c>
       <c r="C39" s="143" t="inlineStr">
         <is>
-          <t>포털에서 에이전트를 직접 만들어 역할·목표·지침을 적고, 지식 그래프·업무 DB 같은 도구를 골라 연결한 뒤 설비 이상을 질문해, 답이 어떤 도구 조회와 근거에서 나왔는지 확인한다. 이어 VS Code에서 설비·센서·고장·SOP 관계와 센서 입력을 읽어 원인 후보·증거·다음 점검 순서를 제안하는 에이전트를 만든다. 확인되지 않은 원인이 가설로 표시되는지 검토한다.</t>
+          <t>포털 에이전트 화면에서 기준 에이전트의 목표·지침·사용 도구를 읽은 뒤 나의 에이전트를 새로 만든다. 이름·역할·목표·성격을 쓰고, 지식 그래프·업무 DB·판단 도구 가운데 원인 근거를 찾는 데 필요한 도구를 고른다. 에이전트에게 질문 화면에서 이론에서 다룬 쿨러 이상을 직접 물어 답과 근거, 처리 과정에 남은 도구 호출의 입력·결과·관측 시각을 대조한다. 같은 질문을 기준 에이전트에게도 물어 설정에 따라 답과 근거가 어떻게 달라지는지 비교하고, 지식에 없는 질문을 던져 지어내지 않고 답할 수 없다고 하는지 확인한다. 답이 길어진 것보다 근거가 확인되고 모르는 항목이 구분되는지를 기준으로 본다.</t>
         </is>
       </c>
       <c r="D39" s="144" t="n">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B40" s="141" t="inlineStr">
         <is>
-          <t>품질 접수 후속 업무 에이전트 만들기</t>
+          <t>설비 이상 원인을 추론하고 다음 점검 작업을 정하는 에이전트 만들기</t>
         </is>
       </c>
       <c r="C40" s="141" t="inlineStr">
         <is>
-          <t>앞 에이전트의 실행 구조를 재사용하여 품질 접수 메시지와 분류 기준으로 유형·추가 확인·담당 부서·대응 초안을 만든다. 표현이 다른 접수와 정보가 빠진 접수를 비교해 단정 대신 조사 요청을 남기는지 확인한다. 품질 대응 카드와 근거를 저장하고 설비 점검과 달라진 입력·판정 기준을 설명한다.</t>
+          <t>포털에서 확인한 도구 호출과 근거 제시를 VS Code의 독립 에이전트로 만든다. 설비 그래프 조회와 센서 입력을 읽는 함수를 연결하고 요청 해석·도구 선택·결과 확인·답변의 실행 기록을 살펴본다. 원인 후보·증거·다음 점검 순서를 출력하되 오래된 값·표본 부족·도구 오류는 확인 필요로 구분하고, 확인되지 않은 원인이 가설로 표시되는지 본다. 다른 설비 사례에도 적용해 근거와 가설이 구별되는지 검증한다.</t>
         </is>
       </c>
       <c r="D40" s="142" t="n">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="B41" s="143" t="inlineStr">
         <is>
-          <t>센서 시각화와 에이전트 결과 검증하기</t>
+          <t>품질 접수 에이전트로 재사용하고 센서 이상 징후 시각화하기</t>
         </is>
       </c>
       <c r="C41" s="143" t="inlineStr">
         <is>
-          <t>센서 CSV의 시간·온도·압력 변화를 읽어 이상 구간을 시각화한다. 관련 태그와 조회 기간을 함께 표시하고 원자료와 비교한다. 원인 점검·품질 대응·시각화 결과에서 근거와 미확인 사항이 구분되는지 검토한다. 다음 회차에는 반복 작업의 지침을 스킬로 만들고 파일·Git·시간 도구를 조합한다.</t>
+          <t>앞 에이전트의 실행 구조를 재사용해 품질 불량 접수 메시지와 분류 기준으로 품질 유형·추가 확인 항목·담당 부서·대응 초안을 만든다. 표현이 다른 접수와 정보가 빠진 접수를 비교해 미확정 원인을 단정하거나 담당자를 지어내지 않고 조사 요청을 남기는지 원자료로 확인하고, 설비 점검과 달라진 입력·판정 기준을 설명한다. 이어 센서 CSV나 시계열 조회 결과에서 온도·압력·시간 변화와 상승 구간을 도표로 만들고, 이상 구간·관련 태그·조회 기간을 근거와 함께 요약하되 상관관계로 고장 원인을 단정하지 않는지 점검한다. 다음 회차에는 반복하는 작업 방법을 스킬로 정리하고 필요한 도구를 연결한다.</t>
         </is>
       </c>
       <c r="D41" s="144" t="n">
@@ -5811,7 +5811,7 @@
     <row r="44" ht="38" customHeight="1" s="1">
       <c r="A44" s="138" t="inlineStr">
         <is>
-          <t>06회차 | 스킬과 MCP로 반복 작업 처리하기</t>
+          <t>06회차  |  업무 능력을 재사용하고 여러 외부 시스템을 연결하기</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="B46" s="141" t="inlineStr">
         <is>
-          <t>스킬·MCP·접근 범위 이해하기</t>
+          <t>스킬·MCP와 도구 연결의 안전 기준 이해하기</t>
         </is>
       </c>
       <c r="C46" s="141" t="inlineStr">
         <is>
-          <t>에이전트의 반복 작업을 재사용 지침과 도구 호출로 나누어 구성한다. SKILL.md에 담는 목적·입력·출력·절차와 MCP 도구의 역할을 구분한다. 파일·Git·시간 도구의 입력과 반환값을 살펴보고, 읽기·쓰기 권한과 접근 가능한 경로가 작업에 미치는 영향을 확인한다.</t>
+          <t>에이전트가 같은 작업을 반복할 수 있도록 지침과 도구의 역할을 나눈다. 스킬의 목적과 SKILL.md에 담는 작업 목적·호출 조건·입력·출력·순서·예외 지침을 배우고, 현장 SOP와 에이전트 실행 지침, 재사용 지침과 한 번의 프롬프트를 구분한다. MCP의 Host·Client·Server·Tool 구성, 도구 목록 발견, 입력 스키마와 응답, stdio·HTTP 연결 방식을 살펴보고 스킬은 수행 방법, MCP는 연결된 실행 도구임을 구분한다. 도구별 읽기·쓰기 권한, 파일 접근 범위, 인증 정보, 실패·시간 초과와 근거 표시를 살펴보고, 정해진 업무 도구만 고르는 포털과 MCP 서버를 직접 연결하는 로컬 VS Code가 권한·범위에서 어떻게 다른지 비교한다.</t>
         </is>
       </c>
       <c r="D46" s="142" t="n">
@@ -5860,17 +5860,17 @@
     <row r="47" ht="92" customHeight="1" s="1">
       <c r="A47" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B47" s="143" t="inlineStr">
         <is>
-          <t>도구를 연결하고 회의록 스킬 만들기</t>
+          <t>포털 도구를 직접 호출하고 외부 MCP·내 조회 도구 조합하기</t>
         </is>
       </c>
       <c r="C47" s="143" t="inlineStr">
         <is>
-          <t>포털의 도구 화면에서 지식 그래프·업무 DB 서버의 도구 하나를 직접 호출해 입력과 반환값을 보고, 그 도구를 에이전트에 연결해 질문에서 실제로 쓰이는지 확인한다. 포털에서 스킬을 만들어 에이전트에 붙여 보며 지침이 결과를 어떻게 바꾸는지 본다. 이어 VS Code에서 회의록의 결정사항·담당자·기한·출처를 추출하는 SKILL.md를 작성하고, 담당자나 기한이 없는 항목은 미정으로 남기는지 원문과 비교한다.</t>
+          <t>포털 도구 연결 화면에서 지식 그래프·업무 DB·판단 도구 서버의 연결 상태와 도구 목록(이름·입력 형식)을 열어 보고, 도구를 직접 시험 호출해 반환값을 확인한다. 이 도구를 쓰는 에이전트에게 질문한 뒤 호출 기록에서 도구 이름·입력·반환값을 찾아 설비 지식에서 온 내용과 현재 업무 조회 결과를 구분하고, 각 반환값이 답의 어느 근거에 쓰였는지 대조한다. 이어 VS Code에서 파일·Git·시간 MCP의 연결과 접근 범위를 설정해 입력·반환값을 확인하고, 제공 서버 골격에 점검 자료 조회 함수를 구현해 MCP 도구로 노출한 뒤 에이전트에서 함께 호출한다. 파일 내용·변경 이력·기준 시각을 조합한 결과에서 출처와 조회 실패를 확인한다.</t>
         </is>
       </c>
       <c r="D47" s="144" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="B48" s="141" t="inlineStr">
         <is>
-          <t>파일·Git·시간 MCP를 연결하고 반환값 확인하기</t>
+          <t>회의 내용을 후속 업무로 바꾸는 스킬 만들기</t>
         </is>
       </c>
       <c r="C48" s="141" t="inlineStr">
         <is>
-          <t>파일·Git·시간 MCP의 실행과 접근 범위를 설정하고 도구 목록·입력·반환값을 확인한다. 같은 자료의 내용·변경 이력·기준 시각을 대조하여 각 도구가 어떤 정보를 제공하는지 구분한다. 접근 실패와 자료 없음을 구분하고 연결 설정과 확인 결과를 저장한다.</t>
+          <t>예제 회의록을 입력받아 결정사항·담당자·완료 시점을 추출하는 SKILL.md를 작성한다. 담당자와 기한이 없는 항목은 미정으로 표시하고, 작업 목록을 Markdown·JSON으로 만들어 원문과 비교한다. 회의록 요약에서 끝내지 않고 다음 행동이 분명한지 확인한다.</t>
         </is>
       </c>
       <c r="D48" s="142" t="n">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="B49" s="143" t="inlineStr">
         <is>
-          <t>내 조회 도구를 구현하고 외부 MCP와 조합해 검증하기</t>
+          <t>내 Notion 학습노트로 출제·채점하는 퀴즈 에이전트 만들기</t>
         </is>
       </c>
       <c r="C49" s="143" t="inlineStr">
         <is>
-          <t>제공 서버 골격에 점검 자료 조회 함수를 구현하고 MCP 도구로 노출한다. 앞에서 연결한 파일·Git·시간 도구와 함께 호출해 자료 내용·변경 이력·시각을 근거로 확인 결과를 만든다. 다른 대상·없는 자료·조회 실패 사례로 결과를 검증하고 코드·설정·출처를 저장한다. 선택 실습: 자기 Notion 노트를 MCP로 연결할 수 있으면, 조회 도구 대신 자기 노트로 문항을 만들고 답변·채점·해설·원문 근거를 확인하는 퀴즈 에이전트를 만든다. 다음 회차에는 점검 요청의 정보 누락과 요구 변경을 질문·명세·검증으로 다룬다.</t>
+          <t>1회에 만든 자기 Notion 학습노트에서 페이지를 골라 MCP 읽기 연결을 설정한다. 노트에서 문항·정답 기준·해설·원문 근거를 구성하는 퀴즈 에이전트를 만들되 답하기 전에는 정답과 해설을 숨긴다. 답변을 받아 정답·부분 정답·오답과 이유를 알려 주고 원문을 다시 열어 확인하며, 틀린 개념의 재도전으로 이어 가고 풀이 기록을 저장한다. 표현만 다른 정답·불완전한 답·노트에 없는 질문으로 검증해 근거가 부족하면 출제나 채점을 보류하는지 본다. 다음 회차에는 점검 요청의 정보 누락과 요구 변경을 질문·명세·검증으로 다룬다.</t>
         </is>
       </c>
       <c r="D49" s="144" t="n">
@@ -5937,7 +5937,7 @@
     <row r="52" ht="38" customHeight="1" s="1">
       <c r="A52" s="138" t="inlineStr">
         <is>
-          <t>07회차 | 사람 확인·명세·검증으로 결과 완성하기</t>
+          <t>07회차  |  사람의 판단과 명확한 요구사항으로 믿고 쓸 수 있는 에이전트 완성하기</t>
         </is>
       </c>
     </row>
@@ -5971,12 +5971,12 @@
       </c>
       <c r="B54" s="141" t="inlineStr">
         <is>
-          <t>질문·승인·명세·행동 검증 이해하기</t>
+          <t>사람 확인·명세·행동 검증으로 에이전트의 신뢰성 높이기</t>
         </is>
       </c>
       <c r="C54" s="141" t="inlineStr">
         <is>
-          <t>앞서 만든 업무 요청 기능의 누락 입력과 변경 요구를 다루고 기존 동작이 유지되는지 확인한다. 정보 확인 질문과 사람의 승인을 구분한다. 입력·출력·금지 조건·수용 기준을 명세로 표현하고, Given/When/Then으로 기대 행동을 정하는 방법을 익힌다. 새 기능의 동작과 기존 기능 보존을 함께 확인하는 이유를 이해한다.</t>
+          <t>앞서 만든 업무 요청 기능이 정보 누락이나 새 요구를 만났을 때 지킬 동작을 정하고, 그 동작을 실제 출력으로 확인한다. HITL의 자동 처리·승인·보류·거절, 승인권자와 권한의 경계, 결정 기록을 살펴보고 AI의 자기 검토와 사람의 승인을 구분한다. 명세 중심 개발(SDD)로 요구·입력/출력 계약·금지 조건·수용 기준을 구현 전에 정하는 방식과, 모호한 기능 추가가 기존 출력이나 승인 규칙을 흔들 수 있는 까닭을 이해한다. Given/When/Then으로 기대 행동을 정하고 정상·경계·예외·회귀 검증으로 새 기능과 기존 기능을 함께 확인하는 방법을 익힌다. 끝으로 지금까지 만든 에이전트들의 목표·입력·도구·결과 판정과 스킬·MCP·HITL·SDD·BDD가 각각 해결한 문제를 정리한다.</t>
         </is>
       </c>
       <c r="D54" s="142" t="n">
@@ -5986,17 +5986,17 @@
     <row r="55" ht="108" customHeight="1" s="1">
       <c r="A55" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B55" s="143" t="inlineStr">
         <is>
-          <t>질문·답변·재개를 구현하고 작성·검토 결과 비교하기</t>
+          <t>사람의 확인이 실제 업무 결과를 바꾸는 과정 확인하기</t>
         </is>
       </c>
       <c r="C55" s="143" t="inlineStr">
         <is>
-          <t>포털 작업함에서 승인 요청을 직접 처리해 본다. 권한이 없는 사람으로는 처리할 수 없고, 권한 있는 사람이 승인하거나 반려하면 같은 처리 건의 상태와 다음 단계가 어떻게 달라지는지 확인한다. 이어 앞 회차의 원인·점검 계획에서 이어지는 점검 요청 프로젝트에서, 도구로 확인할 수 있는 정보는 먼저 읽고 부족한 정보만 질문하며 같은 요청에 온 답변으로 재개하도록 구현한다. 작성 역할과 검토 역할을 나눈 구성에 원자료 대조 기준을 적용하고 AI 검토와 사람 승인을 구분한다. 이후 명세 변경과 검증도 같은 점검 요청 프로젝트에서 이어 간다.</t>
+          <t>결함 시뮬레이션에서 쿨러 열화를 일으켜 승인 대기 건을 만든다. 내 작업함에서 「나」를 바꿔 가며 승인 권한이 있는 담당자에게는 이 작업이 보이고 관계없는 담당자에게는 보이지 않는지, 권한 없는 사람이 승인하려 하면 막히는지 확인한다. 권한 있는 담당자로 추천 근거를 읽고 거절한 뒤 처리 건 기록에서 설비 명령 없이 결과 보고로 끝났는지 보고, 1회에 승인했던 처리 건과 비교해 대기·완료 상태와 사람의 결정이 실제 업무 결과를 어떻게 바꾸는지 확인한다.</t>
         </is>
       </c>
       <c r="D55" s="144" t="n">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="B56" s="141" t="inlineStr">
         <is>
-          <t>변경 요구를 명세하고 기능 구현하기</t>
+          <t>부족한 정보를 질문해 재개하고 변경 요구를 명세로 구현하기</t>
         </is>
       </c>
       <c r="C56" s="141" t="inlineStr">
         <is>
-          <t>같은 점검 요청 프로젝트에 긴급 표시를 추가할 입력·조건·출력·금지 사항을 spec.md로 작성한다. 시간 구간·단위·경계값과 누락 처리 기준을 정하고 AI와 구현한다. 기존 일반 요청과 변경 요청을 비교해 근거·미확인·사람 승인 조건이 유지되는지 확인한다.</t>
+          <t>앞 회차의 원인·점검 계획을 점검 요청 프로젝트로 이어 간다. 도구로 확인할 수 있는 정보는 먼저 조회하고 부족하거나 충돌하는 정보만 질문하도록 구현하고, 답변을 같은 요청 번호에 연결해 판단을 재개한다. 답변 전후의 근거·미확인·상태 변화를 비교하고, 다른 요청의 답이 섞이지 않는지와 정보 답변과 실제 승인이 구분되는지 확인한다. 이어 같은 프로젝트의 spec.md에 일반·긴급 조건, 필수 정보 누락 때 보류, 승인 없이 확정하지 않음, 출력 형식과 수용 기준을 쓰고, 긴급 판정에 쓰는 센서 조건의 시간 구간·단위·경계값을 정해 구현한다. 일반·긴급·누락 입력의 실제 결과를 명세와 대조해 바뀐 기능과 보존된 기능을 설명한다. 빨리 끝나면 해 볼 것: 같은 프로젝트에 작성자와 검토자 역할을 나눠 검토자가 원자료와 대조해 근거 누락·불일치·추정을 지적하고 작성자가 고치게 한 뒤, 두 AI가 동의한 것과 사람의 최종 승인을 구분한다. 또 명세 없이 긴급 표시 요구만 AI에 전달해 바뀐 코드와 결과가 기존 계약의 어디를 흔드는지 비교한다.</t>
         </is>
       </c>
       <c r="D56" s="142" t="n">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="B57" s="143" t="inlineStr">
         <is>
-          <t>행동을 검증하고 인수인계 결과 만들기</t>
+          <t>기대 행동을 정하고 에이전트 동작 검증하기</t>
         </is>
       </c>
       <c r="C57" s="143" t="inlineStr">
         <is>
-          <t>정상·정보 누락·변경 요구의 기대 결과를 Given/When/Then으로 작성해 실제 출력과 비교한다. 제공 센서·정비·부품 자료를 연결해 완료·미완료·다음 조치·근거 시각을 담은 인수인계 결과를 만들고 원자료와 대조한다. 다음 회차에는 검증한 작업을 사람의 승인과 함께 BPMN으로 표현한다.</t>
+          <t>같은 점검 요청 프로젝트에서 일반·긴급·정보 누락·승인 거절·도구 오류의 Given/When/Then을 쓰고 입력·기대 상태·필수 출력 근거를 정한다. 구현이 낸 답을 그대로 기대값으로 옮기지 않고 요구와 원자료에서 판정 기준을 끌어낸다. 제공 테스트 골격에 자신이 정한 입력·기대 결과·판정 코드를 연결해 실제 에이전트 결과를 비교하고, 필수 근거·상태·승인 조건 위반을 찾아 모델의 표현 차이와 내용 오류를 구분해 기록한다. 다음 회차에는 검증한 작업을 사람의 승인과 함께 BPMN으로 표현한다. 빨리 끝나면 해 볼 것: 실제로 실패한 시나리오만 원인을 추적해 프롬프트·명세·코드 가운데 고칠 곳을 정해 고치고, 긴급 조건과 함께 기존 일반 요청·보류·거절 조건이 유지되는지 전체를 다시 돌려 확인한다. 또 조회 도구·출력 계약·검증 방식을 재사용해 설비 이벤트·정비 이력·부품 자료를 연결한 교대 인수인계 기능을 만들고 완료·미완료·주의·근거 시각을 원자료와 대조한다.</t>
         </is>
       </c>
       <c r="D57" s="144" t="n">
@@ -6063,7 +6063,7 @@
     <row r="60" ht="38" customHeight="1" s="1">
       <c r="A60" s="138" t="inlineStr">
         <is>
-          <t>08회차 | 설비 대응 프로세스를 설계하고 연결하기</t>
+          <t>08회차  |  AI와 사람이 함께 일하는 업무 프로세스를 직접 설계하고 실행하기</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="B62" s="141" t="inlineStr">
         <is>
-          <t>BPMN 역할·분기·지연·실행 연결 이해하기</t>
+          <t>비즈니스 프로세스·BPMN·실행 연결 이해하기</t>
         </is>
       </c>
       <c r="C62" s="141" t="inlineStr">
         <is>
-          <t>개별 작업의 결과가 다음 작업으로 넘어가는 조건과 담당 역할을 그림으로 명확히 한다. 시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</t>
+          <t>개별 에이전트의 답을 넘어 작업 순서·담당자·승인·완료를 하나의 흐름으로 표현한다. 비즈니스 프로세스의 시작 조건·입력·출력·책임자·완료 조건과 BPM의 분석→설계→실행→모니터링→개선을 살펴보고, 에이전트만으로 전체 업무 순서와 책임이 보장되지 않는 이유를 이해한다. BPMN의 시작·종료 이벤트, 작업, 게이트웨이, 순서 흐름, Pool·Lane, 메시지 흐름, Timer·경계 이벤트를 설비 대응 사례로 구분하고 승인·거절 분기와 사람·에이전트·시스템의 책임 배치를 본다. 프로세스 정의와 인스턴스, 토큰의 진행, 변수와 결과 전달, 사람 작업·시스템 작업·에이전트 단계, 실행 상태·승인 대기·판본·감사 기록이 실제 실행에서 어떻게 이어지는지 살펴보고 승인 거절과 승인 대기의 차이를 확인한다.</t>
         </is>
       </c>
       <c r="D62" s="142" t="n">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B63" s="143" t="inlineStr">
         <is>
-          <t>기본 승인 흐름에서 설비 대응 흐름 만들기</t>
+          <t>bpmn.io로 간단한 승인 절차 그리기</t>
         </is>
       </c>
       <c r="C63" s="143" t="inlineStr">
         <is>
-          <t>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</t>
+          <t>bpmn.io의 팔레트·요소 배치·연결·속성·저장·열기를 익힌 뒤 정비 요청→담당자 확인→승인 여부→승인·반려 종료를 직접 그린다. 게이트웨이의 각 분기가 종료 이벤트까지 이어졌는지 확인하고 .bpmn 파일로 저장한다.</t>
         </is>
       </c>
       <c r="D63" s="144" t="n">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="B64" s="141" t="inlineStr">
         <is>
-          <t>승인·거절·지연 경로 완성하기</t>
+          <t>설비 이상 대응의 역할과 승인 조건을 갖춘 흐름 만들기</t>
         </is>
       </c>
       <c r="C64" s="141" t="inlineStr">
         <is>
-          <t>승인·거절 분기와 각각의 종료 경로를 연결한다. 거절 경로에서 설비 명령으로 진행되지 않는지 확인하고, 승인 작업을 취소하지 않는 지연 알림 Timer를 추가한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검한다.</t>
+          <t>쿨러 열화 시작→에이전트 진단·조치 제안→운전원 승인→설비 명령→효과 재확인→결과 보고를 담당 역할별 Lane에 배치해 그린다. 승인·거절 분기와 각각의 종료 경로를 연결하고, 거절 경로가 설비 명령으로 가지 않는지 확인한 뒤 승인 작업을 취소하지 않는 지연 알림 Timer를 더한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검하고 파일로 저장한다.</t>
         </is>
       </c>
       <c r="D64" s="142" t="n">
@@ -6152,17 +6152,17 @@
     <row r="65" ht="108" customHeight="1" s="1">
       <c r="A65" s="143" t="inlineStr">
         <is>
-          <t>실습(bpmn.io)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B65" s="143" t="inlineStr">
         <is>
-          <t>BPMN과 등록된 실행 연결 비교하기</t>
+          <t>그린 흐름을 등록된 실행 흐름과 대어 보고 실제 설비 이벤트로 실행하기</t>
         </is>
       </c>
       <c r="C65" s="143" t="inlineStr">
         <is>
-          <t>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다. 다음 회차에는 등록된 흐름을 실행해 이 그림과 실제 처리 이력을 대조한다.</t>
+          <t>포털 흐름 화면에서 등록된 냉각 대응 흐름을 열어, 쿨러 경보 시작 조건과 진단·조치 제안 작업의 에이전트, 승인 작업의 운전원 역할, 설비 명령·재관측·결과 보고 작업의 시스템 기능, 승인·거절 분기 조건이 어떻게 연결돼 있는지 확인한다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시해 빠진 연결이 있으면 그림을 고치고, 그림 파일과 실행 정의를 구분한다. 이어 결함 시뮬레이션에서 쿨러 열화를 일으켜 처리 건을 만들고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 건 화면에서 따라간다. 처리 건이 어느 흐름·판본으로 열렸는지 확인하고 승인 대기·정상 종료·거절로 끝난 처리 건을 구분해 비교하며, 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 작성한 BPMN에서 해당 작업을 찾아 실제 정의·판본·처리 건과 결과를 기록한다.</t>
         </is>
       </c>
       <c r="D65" s="144" t="n">
@@ -6189,7 +6189,7 @@
     <row r="68" ht="38" customHeight="1" s="1">
       <c r="A68" s="138" t="inlineStr">
         <is>
-          <t>09회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</t>
+          <t>09회차  |  설비 대응을 넘어 정비와 구매 업무까지 자동으로 연결하기</t>
         </is>
       </c>
     </row>
@@ -6218,17 +6218,17 @@
     <row r="70" ht="108" customHeight="1" s="1">
       <c r="A70" s="141" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(bpmn.io)</t>
         </is>
       </c>
       <c r="B70" s="141" t="inlineStr">
         <is>
-          <t>실행 상태를 이해하고 정상·예외 경로 확인하기</t>
+          <t>업무별 시작 조건을 비교하고 정비 흐름 설계하기</t>
         </is>
       </c>
       <c r="C70" s="141" t="inlineStr">
         <is>
-          <t>포털에서 쿨러 열화를 일으켜 냉각 대응 흐름을 실행하고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 기록에서 따라간다. 승인을 미루거나 거절한 처리 건과 비교해 승인 대기·거절·보류가 기록에 어떻게 남는지 확인한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의·판본·처리 건과 결과를 기록한다.</t>
+          <t>설비 대응에서 익힌 승인 흐름을 정비·구매에 적용한다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 에이전트·승인자·실행 시스템, 완료 결과가 어떻게 다른지 비교한다. bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지→결과 보고를 그리고, 설비 대응에서 쓴 작업·Lane·게이트웨이·Timer 패턴을 재사용해 승인·반려 경로를 나눈다.</t>
         </is>
       </c>
       <c r="D70" s="142" t="n">
@@ -6238,17 +6238,17 @@
     <row r="71" ht="92" customHeight="1" s="1">
       <c r="A71" s="143" t="inlineStr">
         <is>
-          <t>실습(bpmn.io)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B71" s="143" t="inlineStr">
         <is>
-          <t>BPMN을 보완하고 교대 인수인계 요구 정하기</t>
+          <t>등록된 정비 흐름을 실행하고 결과 검증하기</t>
         </is>
       </c>
       <c r="C71" s="143" t="inlineStr">
         <is>
-          <t>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</t>
+          <t>포털에서 정기 점검 도래를 일으켜 정비 흐름을 시작하고, 정비 계획 제안과 그 근거를 읽은 뒤 설비보전팀장으로 승인한다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조하고, 오더 등록과 실제 정비 완료를 구분한다. 다른 처리 건에서 반려하면 오더가 만들어지지 않는 것을 비교하고, 보류 기록이 있으면 함께 본다. 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</t>
         </is>
       </c>
       <c r="D71" s="144" t="n">
@@ -6258,17 +6258,17 @@
     <row r="72" ht="108" customHeight="1" s="1">
       <c r="A72" s="141" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(bpmn.io)</t>
         </is>
       </c>
       <c r="B72" s="141" t="inlineStr">
         <is>
-          <t>보충 지식과 인수인계 에이전트 구성하기</t>
+          <t>재고 부족부터 구매·입고까지 이어지는 흐름 설계하기</t>
         </is>
       </c>
       <c r="C72" s="141" t="inlineStr">
         <is>
-          <t>포털 지식 관리에 교대 점검 보충 매뉴얼을 올려 추출을 요청하고, 나온 후보를 원문과 대조해 고친 뒤 적재해 지식을 보충한다. 문서·판본·절이 지식에 연결됐는지, 기존 설비 지식이 그대로 남아 있는지 확인한다. 이어 포털에서 설비·정비·ERP를 읽는 도구로 인계안을 쓰는 스킬과 에이전트를 만들고, 관측 시각·작업지시·재고·메모가 서로 어긋날 때 불일치와 확인할 일을 남기는지 원천 기록과 대조한다.</t>
+          <t>bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인·거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 그린다. 정비 흐름에서 쓴 역할·승인 구조를 재사용해 승인·거절 경로를 나누고, HYD의 업무 시스템 시뮬레이션에서 발주·통지·입고가 어떻게 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="D72" s="142" t="n">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="B73" s="143" t="inlineStr">
         <is>
-          <t>제공 인수인계 BPMN의 에이전트 배정·등록하기</t>
+          <t>등록된 구매 흐름을 실행하고 결과 검증하기</t>
         </is>
       </c>
       <c r="C73" s="143" t="inlineStr">
         <is>
-          <t>제공 교대 BPMN을 bpmn.io에서 열어 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 시작 폼의 설비·교대 입력과 각 단계 배정을 확인한다. 다음 회차에는 정비·구매의 실행 결과를 확인하고 준비한 교대 흐름을 끝까지 수행한다.</t>
+          <t>포털에서 재고 보충 흐름을 시작해 공급사·수량 제안의 근거와 승인 조건을 확인하고 구매 담당으로 승인한다. 같은 처리 건의 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교하고, 기록에 남은 입고가 실제 배송 기간을 거친 입고와 같지 않음을 구분한다. 다른 처리 건에서 거절하면 발주가 막히는 것을 비교하고 BPMN의 해당 작업과 실제 결과를 연결한다. 끝으로 설비 조치·정기 점검·재고 보충의 시작 이벤트, 에이전트 판단, 사람 승인·반려, 시스템 처리와 종료 기록을 되짚고, 다음 회차에 이 기록을 교대 인계안으로 묶는다.</t>
         </is>
       </c>
       <c r="D73" s="144" t="n">
@@ -6315,7 +6315,7 @@
     <row r="76" ht="38" customHeight="1" s="1">
       <c r="A76" s="138" t="inlineStr">
         <is>
-          <t>10회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</t>
+          <t>10회차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</t>
         </is>
       </c>
     </row>
@@ -6344,17 +6344,17 @@
     <row r="78" ht="108" customHeight="1" s="1">
       <c r="A78" s="141" t="inlineStr">
         <is>
-          <t>실습(bpmn.io)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B78" s="141" t="inlineStr">
         <is>
-          <t>업무별 시작 조건을 비교하고 정비 흐름 설계하기</t>
+          <t>교대 인수인계의 입력·완료 조건을 정하고 보충 지식 적재하기</t>
         </is>
       </c>
       <c r="C78" s="141" t="inlineStr">
         <is>
-          <t>설비 대응에서 익힌 패턴을 정비·구매에 적용하고 교대 인수인계의 검토·확인까지 마친다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</t>
+          <t>그동안 만든 지식·에이전트·업무 흐름을 교대 인수인계 한 건에 연결한다. 교대 인수인계의 대상 설비·교대·기준 시각과 작업 메모를 입력으로 정하고, 설비 상태·미완료 작업지시·부품 대기 정보를 대조해 다음 근무자가 확인할 사항을 정한다. 인계는 조치·정비·구매를 새로 실행하는 일이 아니라 그 기록을 이어받아 확인하는 일이므로 인계자 검토와 인수자 확인을 완료 조건으로 적는다. 이어 포털 지식 관리에 제공 교대 보충 매뉴얼을 올려 원문을 미리 보고 추출을 요청한 뒤, 나온 절차·조건·근거를 원문과 대조해 고치거나 빼고 새 문서로 적재한다. 앞서 적재한 설비 지식이 그대로 남아 있는지 확인하고, 지식 지도에서 새 항목과 문서·판본·절의 연결을 찾아 인계안의 확인 기준으로 삼는다.</t>
         </is>
       </c>
       <c r="D78" s="142" t="n">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="B79" s="143" t="inlineStr">
         <is>
-          <t>등록된 정비 흐름을 실행하고 결과 검증하기</t>
+          <t>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</t>
         </is>
       </c>
       <c r="C79" s="143" t="inlineStr">
         <is>
-          <t>포털에서 정기 점검 도래를 일으켜 정비 흐름을 시작하고, 정비 계획 제안과 그 근거를 읽은 뒤 설비보전팀장으로 승인한다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조하고, 오더 등록과 실제 정비 완료를 구분한다. 다른 처리 건에서 반려하면 오더가 만들어지지 않는 것을 비교하고, 보류 기록이 있으면 함께 본다. 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</t>
+          <t>포털 에이전트 화면에서 교대 인수인계 스킬을 새로 만들어 확인할 항목과 대조 규칙을 적는다. 작업 메모는 주장이므로 실제 설비 상태·열린 작업지시·재고와 입고 예정을 각각 조회하고, 자료가 없으면 확인 필요로 남기게 한다. 이 스킬을 쓰고 지식 그래프·업무 DB·판단 도구를 고른 인수인계 에이전트를 만든 뒤, 완료 메모와 열린 작업지시, 입고 예정과 실제 재고가 다를 때 확인 사항으로 남기는지 결과를 원천 기록과 대조한다.</t>
         </is>
       </c>
       <c r="D79" s="144" t="n">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B80" s="141" t="inlineStr">
         <is>
-          <t>구매 흐름을 설계하고 실행 검증하기</t>
+          <t>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</t>
         </is>
       </c>
       <c r="C80" s="141" t="inlineStr">
         <is>
-          <t>제공 구매 업무를 bpmn.io에서 시작·제안·승인·발주·입고·보고로 표현한다. 포털에서 재고 보충 흐름을 시작해 공급사·수량 제안의 근거와 승인 조건을 확인하고 구매 담당으로 승인한다. 같은 처리 건의 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교하고, 기록에 남은 입고가 실제 배송 기간을 거친 입고와 같지 않음을 구분한다. 다른 처리 건에서 거절하면 발주가 막히는 것을 비교하고, BPMN의 해당 작업과 실제 결과를 연결한다.</t>
+          <t>제공 교대 BPMN을 bpmn.io에서 열어 작업 이름과 배치를 정리하고, 시작 입력·검토·보완 분기를 유지한 채 포털로 가져와 세 초안 단계에 앞에서 만든 인수인계 에이전트를 배정하고 검사해 별도 판본으로 등록한다. 설비·교대 정보를 입력해 인계안 작성→인계자 검토→인수자 보완 요청→재검토→인수 확인을 수행하고, 인계안을 원천 기록과 대조해 상대에게 근거와 남은 일을 설명한다. 인수 확인과 정비·발주 완료를 구분하고 최종 인계안과 확인 기록을 저장한다.</t>
         </is>
       </c>
       <c r="D80" s="142" t="n">
@@ -6404,17 +6404,17 @@
     <row r="81" ht="108" customHeight="1" s="1">
       <c r="A81" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(Notion)</t>
         </is>
       </c>
       <c r="B81" s="143" t="inlineStr">
         <is>
-          <t>교대 인수인계를 완성하고 ProcessGPT 연결 보기</t>
+          <t>ProcessGPT 시연과 비교하고 학습 결과를 지식 자산으로 정리하기</t>
         </is>
       </c>
       <c r="C81" s="143" t="inlineStr">
         <is>
-          <t>교대 인계안을 원천 기록과 대조하고 근거와 남은 일을 상대에게 설명한다. 인계자 검토→인수자의 확인 또는 실제 보완 요청→같은 처리 건의 재검토·인수 확인을 수행한다. 최종 인계안과 확인 기록을 저장하며 인수 확인과 정비·발주 완료를 구분한다. 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록의 연결을 자신이 수행한 과정과 비교한다.</t>
+          <t>ProcessGPT 시연을 보며 지금까지 만든 지식·에이전트·업무 흐름이 실제 제품의 업무 흐름에 어떻게 연결되는지 살펴보고, 프로세스 정의·실행 인스턴스·작업함·에이전트 활동을 포털에서 직접 해 본 것과 비교하며 기업 업무에 적용할 때 필요한 권한·승인·실행 기록을 확인한다. 이어 1회에 만든 Notion 학습노트에 개념·참고 자료·실습 산출물·검증 결과를 연결해 기록하고, MCP로 Notion에 기록을 남기는 방법을 살펴본 뒤 정리한 Markdown을 노트에 옮긴다. 관계 모델·판단 근거·명세·검증 결과·인계 기록을 함께 찾아볼 수 있게 정리하며 과정을 마친다.</t>
         </is>
       </c>
       <c r="D81" s="144" t="n">
@@ -6912,7 +6912,7 @@
     <row r="2" ht="48" customHeight="1" s="1">
       <c r="A2" s="135" t="inlineStr">
         <is>
-          <t>매회 50분 수업·10분 휴식 × 4교시입니다(수업200분·휴식40분). 온라인 선행학습을 바탕으로 목적·핵심 개념을 연결하고 실습합니다. 이전 개인 결과 없이 제공 시작본으로 시작할 수 있습니다.</t>
+          <t>매회 50분 수업 · 10분 휴식 × 4교시(수업 200분 · 휴식 40분). 온라인 한 회차의 내용을 한 회에 담아(온라인 4회차는 두 회에 나눔), 핵심 이론을 짚은 뒤 포털에서 써 보고 VS Code에서 직접 만들어 본다.</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
     <row r="4" ht="38" customHeight="1" s="1">
       <c r="A4" s="138" t="inlineStr">
         <is>
-          <t>01회차 | HYD 전체 흐름을 확인하고 설비 관계 표현하기</t>
+          <t>01회차  |  설비 데이터가 판단과 조치로 이어지는 전체 흐름 이해하기</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B6" s="141" t="inlineStr">
         <is>
-          <t>HYD 시스템과 이번 과정의 학습 목표 이해하기</t>
+          <t>설비 데이터가 판단으로 이어지는 구조와 온톨로지가 필요한 이유 이해하기</t>
         </is>
       </c>
       <c r="C6" s="141" t="inlineStr">
         <is>
-          <t>통합반 6행 「상세 후」와 같은 문장</t>
+          <t>설비 데이터가 실제 조치로 이어지려면 무엇이 필요한지, 과정 전체의 줄기를 잡는다. 기록을 쌓는 것과 다시 찾아 쓸 수 있는 지식 자산으로 남기는 것의 차이를 보고, 개념·원리·출처·실습 결과를 연결해 기록하는 이유를 이해한다. 설비·센서·PLC·관제 화면의 역할을 짧게 되짚은 뒤, HYD의 OT·DMZ·IT 영역과 층 구조에서 센서 데이터가 메시지 처리·시계열 DB·분석 서비스를 거쳐 화면과 판단 기능에 쓰이는 경로를 데이터 리니지로 따라가고, 분석 결과가 실제 조치로 이어질 때 명령 게이트웨이와 설비 제어 영역이 필요한 이유를 살펴본다. 이어 온도가 올랐다는 사실만으로는 원인과 조치를 알 수 없는 까닭에서 출발해 데이터·정보·지식의 차이와, 대상의 종류·속성·관계·제약을 명시하는 지식 모델인 온톨로지를 배우고, 관계 그림이나 그래프 DB 자체가 곧 온톨로지는 아님을 구분한다.</t>
         </is>
       </c>
       <c r="D6" s="142" t="n">
@@ -6974,17 +6974,17 @@
     <row r="7" ht="125" customHeight="1" s="1">
       <c r="A7" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(Notion)</t>
         </is>
       </c>
       <c r="B7" s="143" t="inlineStr">
         <is>
-          <t>포털에서 완성 흐름을 직접 돌려 보고 관계도 그리기</t>
+          <t>Notion으로 지식 자산화를 위한 학습노트 만들기</t>
         </is>
       </c>
       <c r="C7" s="143" t="inlineStr">
         <is>
-          <t>통합반 7행 「상세 후」와 같은 문장</t>
+          <t>Notion에서 학습노트 홈과 주제별 카드·페이지를 구성한다. 샘플 개념·출처·실습 결과를 연결해 저장하고, 다시 열어 검색·보완·재사용할 수 있는지 확인한다. 이 노트에 이번 과정에서 배우는 개념과 실습 결과를 이어서 쌓는다. 5회에는 이 노트의 기록을 읽어 다음 협의 안건에 쓴다.</t>
         </is>
       </c>
       <c r="D7" s="144" t="n">
@@ -6994,17 +6994,17 @@
     <row r="8" ht="92" customHeight="1" s="1">
       <c r="A8" s="141" t="inlineStr">
         <is>
-          <t>실습(Neo4j)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B8" s="141" t="inlineStr">
         <is>
-          <t>Cypher로 그래프 생성·조회·수정·삭제하기</t>
+          <t>실습 환경을 열고 설비 이상부터 승인·조치까지 직접 돌려 보기</t>
         </is>
       </c>
       <c r="C8" s="141" t="inlineStr">
         <is>
-          <t>별도 Neo4j 랩 DB에서 작은 예제를 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 생성·조회·수정한다. 그래프의 노드와 관계를 눌러 속성을 확인하고 표 결과와 비교한다. DELETE·DETACH DELETE로 연습 데이터만 정리하고 재조회한다.</t>
+          <t>학교 PC의 VS Code·AI 코딩 도구(GitHub Copilot·Codex)·Python·Docker가 각각 무슨 일을 하는지 알고 실행 상태를 확인한 뒤 HYD 포털을 연다. 홈의 상태 표시와 시스템 구성 화면에서 설비·데이터·판단·업무 시스템이 어떻게 이어지는지 보고, 실시간 모니터링·지식 지도·지식 관리·에이전트·내 작업함·처리 건 메뉴를 눌러 각 화면에서 할 일을 확인한다. 오늘 쓸 자료를 작업 폴더에 받아 가이드를 열고, 남길 결과를 USB나 개인 클라우드로 내보내는 방법을 익힌다. 이어 결함 시뮬레이션에서 쿨러 열화를 직접 일으켜 센서 값이 변하고 경보가 뜨는 것을 보고, AI의 원인·조치 추천과 근거를 내 작업함에서 읽고 승인한 뒤 설비 명령→온도 재관측→결과 보고까지 처리 건에서 따라간다. 단계마다 쓰인 정보와 다음 단계로 넘어간 것을 비교하며 AI의 추천·사람의 승인·실제 조치가 서로 다른 단계임을 확인한다.</t>
         </is>
       </c>
       <c r="D8" s="142" t="n">
@@ -7014,17 +7014,17 @@
     <row r="9" ht="108" customHeight="1" s="1">
       <c r="A9" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(ARROWS)</t>
         </is>
       </c>
       <c r="B9" s="143" t="inlineStr">
         <is>
-          <t>관계도를 설비 모델로 옮기고 적재·조회 결과 확인하기</t>
+          <t>설비 이상과 원인·조치의 관계를 관계도로 그리기</t>
         </is>
       </c>
       <c r="C9" s="143" t="inlineStr">
         <is>
-          <t>제공 설비·부품 모델을 읽고 공용 부품과 설비별 센서를 구분한다. 별도 랩 DB에서 부품을 사용하는 설비를 조회하고 원자료와 대조한다. 공급 조건 자료를 연결할 질문과 필요한 속성을 정리한다. 관계도·질의·확인 결과를 저장한다. 다음 회차에는 공급 정보 조회와 조치 검토 기능으로 확장한다.</t>
+          <t>arrows.app에서 노드·관계·레이블을 만드는 법을 익히고, 방금 따라간 쿨러 이상을 바탕으로 설비·센서·증상·원인·조치를 배치해 연결 관계와 방향을 직접 그린다. 각 화살표를 문장으로 읽어 보며 정보를 나열하는 방식과 관계를 중심으로 표현하는 방식의 차이를 확인한다. 이 관계도를 다음 회차에 식별자와 속성을 갖춘 모델로 옮겨 그래프로 조회한다.</t>
         </is>
       </c>
       <c r="D9" s="144" t="n">
@@ -7051,7 +7051,7 @@
     <row r="12" ht="38" customHeight="1" s="1">
       <c r="A12" s="138" t="inlineStr">
         <is>
-          <t>02회차 | 설비 지식과 조건을 조치 검토에 활용하기</t>
+          <t>02회차  |  설비의 지식 구조를 만들고 안전한 조치 기준 마련하기</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="B14" s="141" t="inlineStr">
         <is>
-          <t>설비 모델·조건표·판정과 승인 이해하기</t>
+          <t>클래스·스키마·그래프 조회와 절차·판단 조건의 차이 이해하기</t>
         </is>
       </c>
       <c r="C14" s="141" t="inlineStr">
         <is>
-          <t>설비·부품 연결 조회와 작업 조건표를 조합해 선택 근거가 보이는 조치 검토 결과를 만든다. 설비·부품·공급 정보를 연결해 답할 질문을 정한다. SOP의 작업 조건을 결정표로 표현하는 방법을 살펴보고, 조치 후보의 허용·제외 판정과 사람의 실행 승인이 서로 다른 단계임을 이해한다.</t>
+          <t>관계도에서 부품이 쓰이는 설비와 공급 정보를 찾고, 작업 조건을 판단에 쓸 수 있는 형태로 바꾼다. 클래스·인스턴스·속성·관계, 관계 방향과 카디널리티를 설비·센서 실례로 살펴보고 같은 종류의 설비와 실제 설비 한 대를 구별한다. 고유 식별자·자료형·필수값·레이블·관계 제약과 스키마·인스턴스의 역할을 배우고, 중복된 부품 이름과 고유 식별자로 구분한 결과를 비교한다. Neo4j의 노드·관계·속성과 Cypher의 MATCH·WHERE·RETURN·CREATE·MERGE의 목적, 구조 조회와 실제 데이터 적재의 차이를 살펴본다. 끝으로 SOP의 단계·안전 전제·금지 조건과 DMN의 입력 조건·결정표·출력 판단을 비교하고, 절차를 모두 규칙으로 바꿀 수는 없는 까닭을 이해한다.</t>
         </is>
       </c>
       <c r="D14" s="142" t="n">
@@ -7100,17 +7100,17 @@
     <row r="15" ht="108" customHeight="1" s="1">
       <c r="A15" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(Neo4j)</t>
         </is>
       </c>
       <c r="B15" s="143" t="inlineStr">
         <is>
-          <t>설비·부품·공급 정보를 연결하고 조회하기</t>
+          <t>Cypher로 그래프를 다루고 기준 설비 지식의 연결 확인하기</t>
         </is>
       </c>
       <c r="C15" s="143" t="inlineStr">
         <is>
-          <t>설비·부품 모델에 공급 정보를 더해, 부품별 사용 설비와 공급 조건을 돌려주는 적재·조회문을 작성한다. 여러 설비가 함께 쓰는 펌프 씰 부품으로 사용 설비 세 대와 공급 조건 세 행을 원자료와 대조하고, 다른 품번과 없는 품번도 확인하며, 비승인 공급사를 승인 상태와 함께 구별한다. 반복 적재의 중복 여부를 검사하고 질의·결과·남은 확인 사항을 저장한다. 이렇게 연결하면 「이 부품이 떨어지면 어느 설비가 멈추고 어디서 받을 수 있는가」 같은 질문에 답할 수 있다.</t>
+          <t>별도 Neo4j 랩 DB에서 작은 예제를 CREATE·MATCH·WHERE·RETURN·MERGE·SET으로 생성·조회·수정하고, 그래프를 눌러 속성을 확인하며 RETURN 대상에 따른 그래프·표 결과를 비교한다. DELETE·DETACH DELETE로 연습 데이터만 정리하고 재조회한 뒤, 제공 설비 예제에서 구성 요소·센서·부품의 연결을 한 단계·여러 단계 경로로 조회하고 조건·집계 결과를 원래 행과 대조한다. 이어 포털 지식 지도에서 설비·구성 요소·부품·문서의 연결을 펼쳐 노드의 ID·속성과 관계 방향을 확인하고, 한 부품을 사용하는 설비를 찾아 연결이 있다는 사실과 실제 재고·공급 조건이 확보됐다는 판단을 구분한다. 랩 DB의 연습 그래프와 포털의 기준 지도를 구분하고, 다음 실습에서 제공 공급 자료로 답할 질문을 정한다.</t>
         </is>
       </c>
       <c r="D15" s="144" t="n">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="B16" s="141" t="inlineStr">
         <is>
-          <t>조치 조건표와 판정·성과 비교 기능 만들기</t>
+          <t>설비·부품·공급 정보를 연결하는 모델을 설계하고 조회 그래프 구현하기</t>
         </is>
       </c>
       <c r="C16" s="141" t="inlineStr">
         <is>
-          <t>포털 What-if에서 운전 조건을 바꿔 조치의 허용·제외와 순위, 성과 지표가 달라지는 것을 먼저 확인한다. 이어 SOP 작업 조건을 옮긴 조건표와 조치별 성과 자료를 읽어, 적용 대상과 복합 조건에 따라 경고·감점·제외·정보 부족을 구분하는 기능을 작성한다. 허용 후보만 비용·생산·품질·에너지 산식으로 비교하고 원문 근거를 남긴다.</t>
+          <t>제공 설비·부품 모델에 공급 조건 자료를 연결하도록 모델을 확장하고, 부품별 사용 설비와 공급사별 승인 여부·단가·불량률·납기를 찾을 질문을 정한다. 공용 부품을 설비별로 중복 생성하지 않고 단위와 출처를 보존하며, AI와 함께 작성한 모델을 원자료의 품번·공급사·조건과 대조한다. 이어 확장한 모델로 부품별 사용 설비와 공급 조건을 돌려주는 적재·조회문을 작성하고, 여러 설비가 함께 쓰는 펌프 씰 부품으로 사용 설비 세 대와 공급 조건 세 행을 원자료와 대조한다. 다른 품번과 없는 품번도 확인하고 비승인 공급사를 승인 상태와 함께 구별하며, 반복 적재의 중복 여부를 검사하고 질의·결과·남은 확인 사항을 저장한다. 이 모델은 공급사를 골라 주는 판단이 아니라 고를 때 필요한 정보를 찾아 주는 구조임을 구분한다.</t>
         </is>
       </c>
       <c r="D16" s="142" t="n">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="B17" s="143" t="inlineStr">
         <is>
-          <t>선택 근거와 확인 사항을 검증해 결과 완성하기</t>
+          <t>작업 기준의 복합 조건과 예외를 조치 조건표로 표현하기</t>
         </is>
       </c>
       <c r="C17" s="143" t="inlineStr">
         <is>
-          <t>조치 검토 결과에 후보별 이유·출처·추가 확인할 값을 표시한다. 경계값, 제외 사유와 누락이 겹친 입력, 모두 제외된 입력으로 검증한다. 점수의 높고 낮음과 실행 승인을 구분해 설명하고 결과를 저장한다. 다음 회차에는 작업 조건의 문서 근거를 확인 카드에 연결한다.</t>
+          <t>제공 SOP에서 경고·감점·제외를 구분해 입력·단위·연산자·경계·출력·출처를 조건표로 작성한다. 복수 사유를 함께 남기고, 입력이 빠져도 이미 확인된 제외 근거는 보존하는지 사례로 확인한다. 조건표에 남은 후보와 실제 실행 승인을 구별한다. 다음 회차에는 이 조건표로 조치 검토 결과를 만들고 매뉴얼 근거를 연결한다.</t>
         </is>
       </c>
       <c r="D17" s="144" t="n">
@@ -7177,7 +7177,7 @@
     <row r="20" ht="38" customHeight="1" s="1">
       <c r="A20" s="138" t="inlineStr">
         <is>
-          <t>03회차 | 문서 지식을 작업 확인 자료로 활용하기</t>
+          <t>03회차  |  조치의 성과를 비교하고 현장 자료를 판단 근거로 전환하기</t>
         </is>
       </c>
     </row>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="B22" s="141" t="inlineStr">
         <is>
-          <t>문서 추출·검토·출처 재사용 이해하기</t>
+          <t>성과 비교 기준과 문서를 검토 가능한 지식으로 바꾸는 과정 이해하기</t>
         </is>
       </c>
       <c r="C22" s="141" t="inlineStr">
         <is>
-          <t>문서의 추출 후보가 검토·승인 지식·작업 확인 카드로 이어지는 과정을 이해한다. 원문 ID·절·인용·판본을 보존하는 이유를 살펴보고, 이미 있는 추출 결과를 다시 쓰더라도 사람이 조건의 뜻과 누락을 확인해야 하는 까닭을 이해한다.</t>
+          <t>조건표에 따른 조치 선택과 문서의 원문 근거를 연결해 검토 결과와 작업 확인 카드를 만든다. BSC 네 관점과 전략 목표·KPI, 안전을 만족한 후보 사이에서 비용·생산 영향·품질·에너지를 견주는 이유와 What-if 분석의 개념을 살펴본다. 원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회의 과정과 출처·개정 기록의 원리를 이해하고, 작은 예제 적재와 본격 문서 인제스천의 차이를 구분한다. 이미 있는 추출 결과를 다시 쓰더라도 사람이 조건의 뜻과 누락을 확인해야 하는 까닭을 보고, 끝으로 온톨로지 설계→그래프 DB→SOP·DMN→성과 지표→문서 인제스천으로 이어진 지식 자산이 다음 회차 점검 요청 에이전트의 입력이 되는 흐름을 정리한다.</t>
         </is>
       </c>
       <c r="D22" s="142" t="n">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="B23" s="143" t="inlineStr">
         <is>
-          <t>포털에서 매뉴얼을 지식으로 올리고 원문과 대조하기</t>
+          <t>운전 조건을 바꿔 조치 순위·성과를 비교하고 조치 검토 결과 완성하기</t>
         </is>
       </c>
       <c r="C23" s="143" t="inlineStr">
         <is>
-          <t>포털 지식 관리에서 제공 쿨러 팬 매뉴얼을 올려 미리 보기로 원문을 확인하고, 에이전트에게 추출을 요청한다. 나온 후보에서 작업의 준비·금지·완료 조건과 단계를 원문과 한 줄씩 대조해 틀린 곳은 원문 문장으로 고치고, 원문에 없는 절차는 실행 후보에서 빼며, 고장 유형 같은 필수 선택을 채운다. 검토 표시를 한 뒤 적재하고, 지식 지도에서 새로 연결된 작업 조건과 출처를 확인하며 기존 지식이 줄지 않았는지 본다. 검토 표시 없이는 적재되지 않고 단계를 고치면 다시 검토해야 하는 까닭을 결과와 함께 확인한다.</t>
+          <t>포털 조치 판단 규칙 화면에서 같은 설비의 설비 상태·운전 모드를 바꿔 판단을 다시 실행하며 적용 규칙·허용 또는 제외된 조치·순위를 비교하고, 조건별 손익과 성과 지표 화면에서 값과 KPI 목표를 바꿔 예상 성과와 판정이 어떻게 달라지는지 본다. 순위가 높은 후보라도 금지 조건에 해당하면 선택할 수 없는 이유를 결과에서 찾고, 시험값을 되돌려 원본이 그대로인지 확인한다. 이어 VS Code에서 앞 회차 조건표를 읽어 후보별 판정과 조치 검토 결과를 만드는 기능을 작성한다. 경고·감점·제외·정보 부족을 구분하고, 허용 후보만 주어진 비용·생산·품질·에너지 비교 산식으로 견주며, 후보별 이유·원문 출처·추가로 확인할 값을 함께 표시한다. 경계값, 제외 사유와 누락이 겹친 입력, 모두 제외된 입력으로 확인하고 비교 순위와 실제 실행 승인을 구분한다.</t>
         </is>
       </c>
       <c r="D23" s="144" t="n">
@@ -7246,17 +7246,17 @@
     <row r="24" ht="108" customHeight="1" s="1">
       <c r="A24" s="141" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B24" s="141" t="inlineStr">
         <is>
-          <t>작업 조건 추출 기능을 만들고 검토한 지식을 적재하기</t>
+          <t>포털에서 매뉴얼을 지식으로 올리고 원문과 대조하기</t>
         </is>
       </c>
       <c r="C24" s="141" t="inlineStr">
         <is>
-          <t>포털에서 거친 과정을 독립 랩에서 직접 만든다. 선택한 작업의 준비·금지·완료 조건과 근거 절을 추출하는 기능을 작성하고, 원문과 대조해 채택·수정·제외·보류를 기록한 뒤 다른 작업에도 적용한다. 승인한 후보만 별도 랩 DB에 연결하고, 작업 조건·단계·근거 문서의 경로를 조회해 원문과 대조한다. 승인하지 않은 후보가 들어가지 않았는지, 같은 자료를 다시 적재해도 중복되지 않는지 확인한다.</t>
+          <t>포털 지식 관리에서 제공 쿨러 팬 매뉴얼을 올려 미리 보기로 원문을 확인하고, 에이전트에게 추출을 요청한다. 나온 후보에서 작업의 준비·금지·완료 조건과 단계를 원문과 한 줄씩 대조해 틀린 곳은 원문 문장으로 고치고, 원문에 없는 절차는 실행 후보에서 빼며, 고장 유형 같은 필수 선택을 채운다. 검토 표시를 한 뒤 적재하고, 지식 지도에서 팬 운전과 핀 세척의 적용 조건·금지 사항·완료 기준이 어느 원문 절에 연결됐는지 찾아 작업 전에 확인할 항목을 정리하며 기존 지식이 줄지 않았는지 본다. 검토 표시 없이는 적재되지 않고 단계를 고치면 다시 검토해야 하는 까닭을 결과와 함께 확인한다. 데이터 연결 화면에서는 현재 값을 문서의 기준값과 구분해 읽는다.</t>
         </is>
       </c>
       <c r="D24" s="142" t="n">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B25" s="143" t="inlineStr">
         <is>
-          <t>작업 확인 카드를 만들고 검증하기</t>
+          <t>작업 조건 추출 기능을 만들고 작업 확인 카드로 완성하기</t>
         </is>
       </c>
       <c r="C25" s="143" t="inlineStr">
         <is>
-          <t>승인 지식에서 선택한 작업의 준비·금지·완료 조건과 근거 절을 모아 작업 확인 카드를 구현한다. 다른 작업에도 적용해 누락·미제공 절·잘못된 연결을 확인한다. 질문·설계·문서 추출·검토·적재·조회까지 이어지는 구축 결과를 저장하고, 공급 정보와 작업 조건을 어디까지 확인할 수 있는지 설명한다. 카드가 실제 승인이나 현재 상태 확인을 대신하지 않음을 구분한다. 다음 회차 에이전트가 이 근거를 점검 요청에 사용한다.</t>
+          <t>포털에서 거친 문서 지식화 과정을 VS Code의 독립 랩으로 만든다. 원문에서 작업 순서·조건·단위·금지 사항을 추출하고 문서 ID·절·인용을 함께 돌려주는 기능을 작성하고, 선택한 작업의 준비·금지·완료 조건을 뽑아 원문과 대조해 채택·수정·제외·보류를 기록한다. 이어 승인한 지식만 별도 랩 DB의 기존 ID·관계에 연결하고, 선택한 작업의 준비·금지·완료 조건과 원문 출처를 모아 작업 확인 카드를 만든다. 다른 작업·제공되지 않은 절·반복 적재로 누락과 잘못된 연결을 확인하고 남은 질문을 표시한다. 질문·모델·문서·추출과 검토·적재·조회 결과를 연결해 온톨로지 구축 결과로 저장하고, 공급 정보와 작업 조건으로 어디까지 답할 수 있는지와 카드가 실제 승인이나 현재 상태 확인을 대신하지 않음을 설명한다. 다음 회차 에이전트가 이 근거를 점검 요청에 쓴다.</t>
         </is>
       </c>
       <c r="D25" s="144" t="n">
@@ -7303,7 +7303,7 @@
     <row r="28" ht="38" customHeight="1" s="1">
       <c r="A28" s="138" t="inlineStr">
         <is>
-          <t>04회차 | 분석 결과를 점검 요청으로 연결하기</t>
+          <t>04회차  |  업무를 수행하는 AI를 만들어 점검 요청으로 연결하기</t>
         </is>
       </c>
     </row>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="B30" s="141" t="inlineStr">
         <is>
-          <t>원인 근거와 점검 요청 구조 이해하기</t>
+          <t>업무를 수행하는 AI의 구조와 점검 요청 이해하기</t>
         </is>
       </c>
       <c r="C30" s="141" t="inlineStr">
         <is>
-          <t>구축한 온톨로지의 설비·문서 근거를 점검 요청에 활용한다. 같은 에이전트 구조가 분석·회의 후속 업무·자기 자료 학습에도 쓰이되 입력·도구·결과 판정이 달라짐을 비교한다. 이번 실습에서는 원인 후보를 대상·관측 시각·근거·확인할 항목이 있는 요청으로 바꾼다. 실제 도구가 확인한 사실과 가설, 요청 초안과 실제 실행을 구분하고 다른 사례에도 적용할 검증 기준을 정한다.</t>
+          <t>온톨로지 구축 결과를 점검 요청에 활용하는 사례에서 출발해 분석·시각화, 회의 후속 업무, 자기 자료 학습, 작성·검토 협업으로 에이전트의 활용 범위를 살펴본다. LLM·RAG·에이전트의 목표·근거·도구·반복 실행 차이를 비교하고, 작업마다 필요한 입력·결과·검증이 달라짐을 이해한다. 원인 후보를 대상·관측 시각·근거·확인할 항목이 있는 점검 요청으로 바꾸는 구조를 보고, 실제 도구가 확인한 사실과 가설, 요청 초안과 실제 실행, 연결된 기능·권한·종료 조건과 사람의 판단을 구분한다.</t>
         </is>
       </c>
       <c r="D30" s="142" t="n">
@@ -7352,17 +7352,17 @@
     <row r="31" ht="108" customHeight="1" s="1">
       <c r="A31" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B31" s="143" t="inlineStr">
         <is>
-          <t>설비 원인과 점검 순서 기능 만들기</t>
+          <t>업무 에이전트를 만들고 질문의 도구·근거 확인하기</t>
         </is>
       </c>
       <c r="C31" s="143" t="inlineStr">
         <is>
-          <t>포털에서 에이전트를 직접 만들어 지식 그래프·업무 DB 도구를 연결하고 설비 이상을 질문해, 답이 어떤 도구 조회와 근거에서 나왔는지 확인한다. 이어 VS Code에서 제공 그래프·사례로 원인 후보와 근거를 읽는 기능을 만들고, 오래된 값·표본 부족을 확정하지 않고 미확인으로 남기는지 대조한다.</t>
+          <t>포털 에이전트 화면에서 기준 에이전트의 목표·지침·사용 도구를 읽고 나의 에이전트를 만든다. 원인 근거와 추가 확인을 정리하도록 역할·목표·성격을 쓰고 지식 그래프·업무 DB·판단 도구 가운데 필요한 것을 고른다. 이론에서 다룬 쿨러 이상 질문을 직접 물어 실제 호출의 입력·결과·관측 시각을 대조하고, 같은 질문에 대한 기준 에이전트의 답과 비교한다. 목표·지침을 한 가지씩 바꿔 같은 질문을 다시 물어 답의 범위와 근거가 어떻게 달라지는지 확인하고, 지식에 없는 질문에는 답할 수 없다고 하는지 본다. 답이 길어진 것보다 근거가 확인되고 모르는 항목이 구분되는지를 기준으로 본다.</t>
         </is>
       </c>
       <c r="D31" s="144" t="n">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="B32" s="141" t="inlineStr">
         <is>
-          <t>설비·문서·부품 근거 연결하기</t>
+          <t>원인 후보와 설비·문서·부품 근거를 읽는 에이전트 만들기</t>
         </is>
       </c>
       <c r="C32" s="141" t="inlineStr">
         <is>
-          <t>제공 그래프의 설비·부품·증거와 매뉴얼 절을 점검 대상에 연결한다. 그래프와 문서의 집계 구간이 다르거나 원문 절이 제공되지 않은 경우를 확인하고, 해결된 사실과 추가로 확인할 조건을 분리한다.</t>
+          <t>포털에서 본 조회·판단을 VS Code의 독립 에이전트로 만든다. 설비 그래프와 사례 입력을 읽는 도구를 연결하고 호출 기록에서 선택한 도구·입력·결과를 확인한다. 원인 후보와 근거를 읽되 오래된 값·표본 부족은 확정하지 않고 미확인으로 남기는지 대조한다. 이어 제공 그래프의 설비·부품·증거와 매뉴얼 절을 점검 대상에 연결하고, 그래프와 문서의 집계 구간이 다르거나 원문 절이 제공되지 않은 경우를 찾아 해결된 사실과 추가로 확인할 조건을 나눈다. 다른 설비 사례로 다시 돌려 근거와 미확인이 어떻게 바뀌는지 비교한다.</t>
         </is>
       </c>
       <c r="D32" s="142" t="n">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="B33" s="143" t="inlineStr">
         <is>
-          <t>점검 요청 초안을 만들고 검증하기</t>
+          <t>점검 요청 초안을 만들고 다른 입력으로 검증하기</t>
         </is>
       </c>
       <c r="C33" s="143" t="inlineStr">
         <is>
-          <t>대상 설비·부품, 관측 시각, 근거, 확인할 항목과 이유를 담은 점검 요청 초안을 만드는 기능을 완성한다. 누락과 복수 원인 사례를 넣어 가설을 확정으로 쓰지 않는지 대조한다. 초안과 실제 작업지시를 구분해 저장한다. 다음 회차에는 같은 근거 정리 방법으로 협의 안건을 만든다.</t>
+          <t>대상 설비·부품, 관측 시각, 근거, 확인할 항목과 이유를 담은 점검 요청 초안을 만드는 기능을 완성한다. 누락과 복수 원인 사례, 문서 기준과 측정값이 다른 사례를 넣어 가설을 확정 원인으로 쓰지 않는지, 작업지시를 발행한 것처럼 표시하지 않는지 대조하고, 다른 대상에도 적용해 결과를 비교한다. 초안과 실제 작업지시를 구분해 저장한다. 다음 회차에는 같은 근거 정리 방법으로 협의 안건을 만든다.</t>
         </is>
       </c>
       <c r="D33" s="144" t="n">
@@ -7429,7 +7429,7 @@
     <row r="36" ht="38" customHeight="1" s="1">
       <c r="A36" s="138" t="inlineStr">
         <is>
-          <t>05회차 | 스킬과 도구로 다음 협의 준비하기</t>
+          <t>05회차  |  스킬과 다양한 도구를 연결해 다음 협의 준비하기</t>
         </is>
       </c>
     </row>
@@ -7463,12 +7463,12 @@
       </c>
       <c r="B38" s="141" t="inlineStr">
         <is>
-          <t>스킬·도구 조합·변경 근거 이해하기</t>
+          <t>재사용 스킬과 외부 시스템 연결의 원리 이해하기</t>
         </is>
       </c>
       <c r="C38" s="141" t="inlineStr">
         <is>
-          <t>회의에서 정한 업무와 변경 기록을 비교하여 다음에 확인할 안건을 근거와 함께 만든다. 재사용할 업무 지침과 실행 도구의 역할을 구분한다. 회의록의 결정·담당·기한과 Git 변경 기록·시각 정보를 연결해 완료·미결·변경 내용을 판단하는 기준을 이해한다.</t>
+          <t>반복 업무를 재사용 가능한 능력으로 만들고 외부 자료와 안전하게 연결한다. SKILL.md의 목표·호출 조건·입출력·절차와 현장 SOP와 스킬의 차이, 여러 업무에 같은 지침을 재사용하는 이유를 살펴본다. MCP의 Host·Client·Server·Tool, stdio·HTTP 연결, 입력 스키마와 출력, 읽기·쓰기 권한과 호출 실패를 배우고, 정해진 도구만 쓰는 포털과 MCP를 직접 설정하는 로컬 VS Code의 차이를 비교한다. 회의록의 결정·담당·기한과 Git 변경 기록·시각 정보를 연결해 완료·미결·변경을 판단하는 기준을 이해한다.</t>
         </is>
       </c>
       <c r="D38" s="142" t="n">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="B39" s="143" t="inlineStr">
         <is>
-          <t>도구를 연결하고 회의 후속 업무 스킬 만들기</t>
+          <t>회의 결정과 후속 업무를 추출하는 스킬 만들기</t>
         </is>
       </c>
       <c r="C39" s="143" t="inlineStr">
         <is>
-          <t>포털의 도구 화면에서 지식 그래프·업무 DB 서버의 읽기 도구를 직접 호출해 입력과 반환값을 보고, 포털에서 스킬을 만들어 에이전트에 붙여 지침이 결과를 어떻게 바꾸는지 확인한다. 이어 VS Code에서 포털 읽기 도구와 파일·Git·시간 MCP를 연결해 호출 결과를 확인하고, 제공 회의록 두 건과 점검 메모에서 결정·담당·기한·근거를 추출하는 스킬을 만들어 없는 정보는 미정으로 남기는지 확인한다.</t>
+          <t>제공된 회의록 두 건에서 결정·제안·조건부 작업·담당 미정을 구분하는 스킬을 작성한다. 이전 결정과 후속 확인을 연결해 전달 완료와 발주 완료, 설비별 점검 상태를 구별하고, 각 미결 항목에 다음 협의에서 확인할 질문과 원문 근거를 남기도록 지침을 보완한다. 결과를 원문과 한 줄씩 대조하고, 두 원문에 다시 적용해 특정 이름·날짜에만 맞춘 결과가 아닌지 확인한다.</t>
         </is>
       </c>
       <c r="D39" s="144" t="n">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B40" s="141" t="inlineStr">
         <is>
-          <t>파일·Git·시간 MCP와 내 조회 도구 연결하기</t>
+          <t>외부 MCP를 연결하고 내 점검 메모 조회 도구 만들기</t>
         </is>
       </c>
       <c r="C40" s="141" t="inlineStr">
         <is>
-          <t>제공 회의록·점검 메모를 읽도록 파일·Git·시간 MCP의 접근 범위를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 기존 에이전트에서 호출한다. 이전 회의와 후속 자료에서 바뀐 내용·근거 파일·시각을 연결하고 조회 실패와 자료 없음을 구분한다. 선택 실습: 자기 Notion 기록을 MCP로 연결할 수 있으면, 제공 파일 대신 자기 Notion 기록을 읽어 후속 협의 안건에 활용한다.</t>
+          <t>1회에 만든 Notion 학습노트의 회의·학습 기록 읽기 연결과 파일·Git·시간 MCP를 VS Code에 설정하고 접근 범위를 정한다. 각 도구의 입력과 반환값을 확인하고, 제공 서버 골격에 점검 메모 조회 함수를 구현해 기존 에이전트에서 호출한다. 이전 회의와 후속 자료에서 바뀐 내용·근거 파일·시각을 연결하고, 조회 실패와 자료 없음이 서로 다르게 표시되는지 일부러 없는 자료를 불러 확인한다.</t>
         </is>
       </c>
       <c r="D40" s="142" t="n">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="B41" s="143" t="inlineStr">
         <is>
-          <t>다음 협의 안건을 만들고 검증하기</t>
+          <t>다음 협의 안건을 만들고 다른 회의로 다시 검증하기</t>
         </is>
       </c>
       <c r="C41" s="143" t="inlineStr">
         <is>
-          <t>앞서 연결한 회의록·점검 메모·변경 이력과 회의 스킬을 조합해 다음 협의 안건을 만든다. 안건마다 결정할 질문·확인된 사실·남은 확인·파일 근거를 표시한다. 후속 자료를 반영한 결과를 이전 결과와 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</t>
+          <t>앞의 회의 스킬과 연결한 도구를 조합해 결정할 질문·확인된 사실·남은 확인·페이지나 파일 근거를 담은 다음 협의 안건을 만든다. 서로 다른 회의와 후속 변경을 대조해 결정이 사라지거나 중복되지 않는지 확인하고, 후속 자료를 더해 다시 만든 안건을 이전 결과와 비교한다. 다음 회차에는 점검 요청의 변경 요구를 명세하고 검증한다.</t>
         </is>
       </c>
       <c r="D41" s="144" t="n">
@@ -7555,7 +7555,7 @@
     <row r="44" ht="38" customHeight="1" s="1">
       <c r="A44" s="138" t="inlineStr">
         <is>
-          <t>06회차 | 활용 기능의 요구를 명세하고 검증하기</t>
+          <t>06회차  |  사람과 협업하고 변경된 기능까지 검증하기</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B46" s="141" t="inlineStr">
         <is>
-          <t>질문·승인·명세와 기대 결과 이해하기</t>
+          <t>사람 승인·명세·시나리오 검증 이해하기</t>
         </is>
       </c>
       <c r="C46" s="141" t="inlineStr">
         <is>
-          <t>점검 요청의 정보 누락·추가 답변·기능 변경을 처리하면서 기존 승인 조건을 보존한다. 필수 입력이 없을 때의 질문·보류와 사람 승인을 구분한다. 기능의 입력·출력·제약·완료 기준을 명세하고, 정상·누락·변경·기존 기능을 검증할 기대 결과로 바꾸는 방법을 익힌다.</t>
+          <t>점검 요청을 바로 확정할 수 없는 경우를 구분하고, 새 요구를 반영해도 기존 조건을 지키게 한다. HITL의 승인·보류·거절, 역할별 책임과 감사 기록, AI의 자체 검토와 사람 결정의 차이를 살펴본다. 명세 중심 개발(SDD)의 입력/출력 계약·제약·수용 기준과 모호한 변경의 위험을 보고, spec.md에 일반 기능과 긴급 요청의 차이를 적는 이유를 이해한다. Given/When/Then으로 정상·누락·거절·경계 조건과 회귀를 검증하는 방법을 익히고, 끝으로 에이전트·스킬·MCP·HITL·SDD·BDD가 각각 해결하는 문제를 정리한다.</t>
         </is>
       </c>
       <c r="D46" s="142" t="n">
@@ -7604,17 +7604,17 @@
     <row r="47" ht="92" customHeight="1" s="1">
       <c r="A47" s="143" t="inlineStr">
         <is>
-          <t>실습(VS Code)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B47" s="143" t="inlineStr">
         <is>
-          <t>점검 요청의 질문·답변·재개 구현하기</t>
+          <t>사람 승인에 따라 업무가 달라지는 것을 확인하고 질문·재개 구현하기</t>
         </is>
       </c>
       <c r="C47" s="143" t="inlineStr">
         <is>
-          <t>포털 작업함에서 승인 요청을 직접 처리해, 권한이 없는 사람은 처리할 수 없고 승인·반려·보류에 따라 같은 처리 건의 상태가 어떻게 달라지는지 확인한다. 이어 점검 요청 초안의 필수 정보가 빠졌을 때 질문하고, 추가 답변을 반영해 다시 판단하는 흐름을 구현한다. 사람이 승인할 결과가 자동으로 확정되지 않는지 확인한다.</t>
+          <t>쿨러 열화로 승인 대기 건을 만들고, 내 작업함에서 「나」를 바꿔 가며 권한 있는 담당자에게만 작업이 보이고 권한 없는 사람의 승인은 막히는지 확인한다. 권한 있는 담당자로 추천 근거를 읽고 거절해 설비 명령 없이 결과 보고로 끝나는 것을 처리 건 기록에서 보고, 승인했던 처리 건과 비교한다. 이어 VS Code에서 4회의 점검 요청 초안 기능을 이어, 요청의 설비·경보·사례를 기존 자료로 먼저 확인하고 부족하거나 충돌한 정보만 질문하도록 확장한다. 답변을 같은 요청 번호에 연결해 다시 판단하고, 다른 요청의 답이 섞이지 않는지와 초안의 확인 항목이 답변 전후에 어떻게 바뀌었는지 대조하며 정보 답변과 실제 승인을 구분한다.</t>
         </is>
       </c>
       <c r="D47" s="144" t="n">
@@ -7681,7 +7681,7 @@
     <row r="52" ht="38" customHeight="1" s="1">
       <c r="A52" s="138" t="inlineStr">
         <is>
-          <t>07회차 | 설비 대응 프로세스를 설계하고 연결하기</t>
+          <t>07회차  |  설비 이상 대응을 안전하게 실행하는 프로세스 완성하기</t>
         </is>
       </c>
     </row>
@@ -7715,12 +7715,12 @@
       </c>
       <c r="B54" s="141" t="inlineStr">
         <is>
-          <t>BPMN 역할·분기·지연·실행 연결 이해하기</t>
+          <t>업무 흐름의 표현 규칙과 실행·통제 구조 이해하기</t>
         </is>
       </c>
       <c r="C54" s="141" t="inlineStr">
         <is>
-          <t>작업 순서·승인 역할·실행 연결을 구분하여 같은 BPMN을 그림과 실행 관점에서 읽는다. 시작·종료 이벤트, 작업, 역할별 Lane, 승인 분기와 지연 알림의 의미를 설비 대응 사례로 구분한다. BPMN 그림의 각 작업이 에이전트·사람·시스템 중 누구에게 연결되는지 살펴보고, 승인 거절과 승인 대기 상태의 차이를 확인한다.</t>
+          <t>개별 판단이 실제 조치로 이어지려면 어떤 역할·승인·실행 연결이 필요한지 흐름과 기록을 대조한다. 끝에서 끝까지의 업무, 시작·입력·담당·완료와 BPM의 분석·설계·실행·모니터링·개선, 에이전트의 단일 작업과 전체 흐름을 책임지는 오케스트레이션을 살펴본다. BPMN의 이벤트·작업·게이트웨이·Lane·순서 흐름·메시지 흐름과 승인·거절·Timer·경계 이벤트를 설비 이상 대응으로 구분한다. 프로세스 정의·인스턴스·변수·토큰, 프로세스 엔진, 사람·시스템·에이전트 작업과 상태·권한·배포·감사 기록의 의미를 이해한다.</t>
         </is>
       </c>
       <c r="D54" s="142" t="n">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="B55" s="143" t="inlineStr">
         <is>
-          <t>기본 승인 흐름에서 설비 대응 흐름 만들기</t>
+          <t>bpmn.io 기본 사용법을 익히고 간단한 승인 흐름 그리기</t>
         </is>
       </c>
       <c r="C55" s="143" t="inlineStr">
         <is>
-          <t>bpmn.io에서 시작→요청 확인→승인 또는 반려→종료를 그린다. 이어 쿨러 경보→원인 분석·조치 제안→운전원 승인→설비 명령→효과 확인→보고로 흐름을 확장하고, 담당 역할에 맞게 작업을 Lane에 배치한다.</t>
+          <t>bpmn.io에서 요소 배치·연결·수정·속성 확인과 .bpmn 저장·불러오기를 직접 해 본다. 이어 시작→요청 확인→승인 여부→승인·반려 종료를 그려 이벤트·작업·게이트웨이와 각 경로의 연결을 확인한다.</t>
         </is>
       </c>
       <c r="D55" s="144" t="n">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="B56" s="141" t="inlineStr">
         <is>
-          <t>승인·거절·지연 경로 완성하기</t>
+          <t>설비 이상을 조치까지 잇고 승인 조건과 예외를 반영한 흐름 만들기</t>
         </is>
       </c>
       <c r="C56" s="141" t="inlineStr">
         <is>
-          <t>승인·거절 분기와 각각의 종료 경로를 연결한다. 거절 경로에서 설비 명령으로 진행되지 않는지 확인하고, 승인 작업을 취소하지 않는 지연 알림 Timer를 추가한다. 각 경로를 따라가며 분기 조건과 연결 누락을 점검한다.</t>
+          <t>쿨러 경보→진단·조치 제안 에이전트→운전원 승인→설비 명령→효과 재확인→보고를 bpmn.io에서 그리고 역할별 Lane을 구성한다. 승인·거절 분기와 반려 종료, 승인 지연 알림 Timer를 더해, 거절하면 명령이 실행되지 않고 알림이 사람 작업을 취소하지 않는 구조를 경로마다 따라가며 확인한다.</t>
         </is>
       </c>
       <c r="D56" s="142" t="n">
@@ -7770,17 +7770,17 @@
     <row r="57" ht="108" customHeight="1" s="1">
       <c r="A57" s="143" t="inlineStr">
         <is>
-          <t>실습(bpmn.io)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B57" s="143" t="inlineStr">
         <is>
-          <t>BPMN과 등록된 실행 연결 비교하기</t>
+          <t>그린 흐름을 등록된 실행 흐름과 대어 보고 실제 설비 이벤트로 실행하기</t>
         </is>
       </c>
       <c r="C57" s="143" t="inlineStr">
         <is>
-          <t>bpmn.io에서 작성한 설비 대응 흐름과 포털에 등록된 기준 흐름을 비교한다. 제공 매핑 자료에서 시작 이벤트·에이전트·운전원 승인·설비 명령·재관측 작업의 연결을 찾는다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 그림 파일과 실행 정의를 구분한다. 다음 회차에는 등록된 흐름의 실행 이력을 대조하고 교대 인수인계 흐름을 구성한다.</t>
+          <t>포털 흐름 화면에서 등록된 냉각 대응 흐름을 열어 쿨러 경보 시작 조건, 진단·조치 제안 에이전트, 운전원 승인 역할, 설비 명령·재관측·결과 보고 작업, 승인·거절 분기 조건이 어떻게 연결돼 있는지 확인한다. 자신이 그린 각 작업이 어떤 실행 기능에 대응하는지 표시하고, 기준 흐름과 비교해 담당 역할·실행 기능·승인과 반려 경로·종료 연결이 빠진 곳을 찾아 그림을 고친다. 이어 쿨러 열화를 일으켜 처리 건을 만들고 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 건 화면에서 따라간다. 처리 건이 어느 흐름·판본으로 열렸는지 확인하고 승인 대기·정상 종료·거절로 끝난 처리 건을 구분해 비교하며, 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 다음 담당자가 계속 확인할 일을 근거와 함께 설명하고, 작성한 BPMN에서 해당 작업을 찾아 실제 정의·판본·처리 건과 결과를 기록한다.</t>
         </is>
       </c>
       <c r="D57" s="144" t="n">
@@ -7807,7 +7807,7 @@
     <row r="60" ht="38" customHeight="1" s="1">
       <c r="A60" s="138" t="inlineStr">
         <is>
-          <t>08회차 | 프로세스를 실행·검증하고 교대 인수인계 제작 시작하기</t>
+          <t>08회차  |  정비와 구매 업무를 연결하고 프로세스의 실행 결과 검증하기</t>
         </is>
       </c>
     </row>
@@ -7836,17 +7836,17 @@
     <row r="62" ht="108" customHeight="1" s="1">
       <c r="A62" s="141" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(bpmn.io)</t>
         </is>
       </c>
       <c r="B62" s="141" t="inlineStr">
         <is>
-          <t>실행 상태를 이해하고 정상·예외 경로 확인하기</t>
+          <t>업무별 시작 조건을 비교하고 정비 흐름 설계하기</t>
         </is>
       </c>
       <c r="C62" s="141" t="inlineStr">
         <is>
-          <t>포털에서 쿨러 열화를 일으켜 냉각 대응 흐름을 실행하고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 기록에서 따라간다. 승인을 미루거나 거절한 처리 건과 비교해 승인 대기·거절·보류가 기록에 어떻게 남는지 확인한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인하고, 다음 담당자가 계속 확인할 일이 무엇인지 근거와 함께 설명한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의·판본·처리 건과 결과를 기록한다.</t>
+          <t>설비 제어와 정비·구매 처리가 끝나는 지점을 구분한다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 승인자·실행 시스템, 완료 결과가 어떻게 다른지 비교한다. bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지→종료를 그리고, 설비 대응의 역할·승인 구조를 재사용해 작업과 분기 조건을 완성한다.</t>
         </is>
       </c>
       <c r="D62" s="142" t="n">
@@ -7856,17 +7856,17 @@
     <row r="63" ht="92" customHeight="1" s="1">
       <c r="A63" s="143" t="inlineStr">
         <is>
-          <t>실습(bpmn.io)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B63" s="143" t="inlineStr">
         <is>
-          <t>BPMN을 보완하고 교대 인수인계 요구 정하기</t>
+          <t>등록된 정비 흐름을 실행하고 승인 조건 검증하기</t>
         </is>
       </c>
       <c r="C63" s="143" t="inlineStr">
         <is>
-          <t>자신의 BPMN 그림과 실행 이력의 작업·역할·분기 차이를 찾아 그림을 수정한다. 교대 인수인계에 필요한 설비·교대·기준 시각·작업 메모를 정하고, 인계자 검토와 인수자 확인을 완료 조건으로 작성한다.</t>
+          <t>포털에서 정기 점검 도래를 일으켜 정비 흐름을 시작하고, 정비 계획 제안과 그 근거를 읽은 뒤 설비보전팀장으로 승인한다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조하고, 오더 등록과 실제 정비 완료를 구분한다. 예약 뒤 실제 정비와 다음 교대에 남는 확인을 정리한다. 다른 처리 건에서 반려하면 오더가 만들어지지 않는 것을 비교하고, 보류 기록이 있으면 함께 본다. 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</t>
         </is>
       </c>
       <c r="D63" s="144" t="n">
@@ -7876,17 +7876,17 @@
     <row r="64" ht="108" customHeight="1" s="1">
       <c r="A64" s="141" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(bpmn.io)</t>
         </is>
       </c>
       <c r="B64" s="141" t="inlineStr">
         <is>
-          <t>보충 지식과 인수인계 에이전트 구성하기</t>
+          <t>재고 부족부터 발주·입고까지 이어지는 흐름 설계하기</t>
         </is>
       </c>
       <c r="C64" s="141" t="inlineStr">
         <is>
-          <t>포털 지식 관리에 교대 점검 보충 매뉴얼을 올려 추출을 요청하고, 나온 후보를 원문과 대조해 고친 뒤 적재해 지식을 보충한다. 문서·판본·절이 지식에 연결됐는지, 기존 설비 지식이 그대로 남아 있는지 확인한다. 이어 포털에서 설비·정비·ERP를 읽는 도구로 인계안을 쓰는 스킬과 에이전트를 만들고, 관측 시각·작업지시·재고·메모가 서로 어긋날 때 불일치와 확인할 일을 남기는지 원천 기록과 대조한다.</t>
+          <t>bpmn.io에서 재고 부족→구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→입고 반영→종료를 그린다. 정비 흐름의 역할·승인 구조를 재사용해 승인·거절 경로를 나누고, ERP와 재고 기능이 HYD의 업무 시스템 시뮬레이션에서 어떻게 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="D64" s="142" t="n">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="B65" s="143" t="inlineStr">
         <is>
-          <t>제공 인수인계 BPMN의 에이전트 배정·등록하기</t>
+          <t>등록된 구매 흐름을 실행하고 처리 결과 검증하기</t>
         </is>
       </c>
       <c r="C65" s="143" t="inlineStr">
         <is>
-          <t>제공 교대 BPMN을 bpmn.io에서 열어 이름과 배치를 정리한다. 시작 입력·검토·보완 분기를 유지하고 세 초안 단계에 교대 에이전트를 배정하여 별도 판본을 등록한다. 시작 폼의 설비·교대 입력과 각 단계 배정을 확인한다. 다음 회차에는 정비·구매 기록을 확인하고 교대 흐름의 인수 확인까지 완료한다.</t>
+          <t>포털에서 재고 보충 흐름을 시작해 공급사·수량 제안의 근거와 승인 조건을 확인하고 구매 담당으로 승인한다. 같은 처리 건의 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교하고, 기록에 남은 입고가 실제 배송 기간을 거친 입고와 같지 않음을 구분한다. 발주 중과 입고 완료를 구분해 다음 교대에 전달할 수량·남은 확인을 정리하고, 다른 처리 건에서 거절하면 발주가 막히는 것을 비교해 BPMN의 해당 작업과 실제 결과를 연결한다. 끝으로 이벤트·에이전트·사람·시스템의 역할을 되짚고, 다음 회차에 이 기록의 미완료·불일치를 인계안으로 모은다.</t>
         </is>
       </c>
       <c r="D65" s="144" t="n">
@@ -7933,7 +7933,7 @@
     <row r="68" ht="38" customHeight="1" s="1">
       <c r="A68" s="138" t="inlineStr">
         <is>
-          <t>09회차 | 정비·구매에 적용하고 교대 인수인계 완성하기</t>
+          <t>09회차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</t>
         </is>
       </c>
     </row>
@@ -7962,17 +7962,17 @@
     <row r="70" ht="108" customHeight="1" s="1">
       <c r="A70" s="141" t="inlineStr">
         <is>
-          <t>실습(bpmn.io)</t>
+          <t>실습(포털)</t>
         </is>
       </c>
       <c r="B70" s="141" t="inlineStr">
         <is>
-          <t>업무별 시작 조건을 비교하고 정비 흐름 설계하기</t>
+          <t>교대 인수인계의 입력·완료 조건을 정하고 보충 지식 적재하기</t>
         </is>
       </c>
       <c r="C70" s="141" t="inlineStr">
         <is>
-          <t>정비·구매의 완료 의미를 비교하고 교대 인계 내용과 검토·확인 기록을 연결한다. 냉각 경보·정기 점검 도래·재고 부족의 시작 조건과 완료 결과를 비교한다. 정기 점검→정비 계획→설비보전팀장 승인 또는 거절→정비 오더→생산팀 공지 흐름을 bpmn.io에서 작성하고 담당 역할과 분기 조건을 연결한다.</t>
+          <t>지식·도구·에이전트·승인 흐름을 교대 인수인계 한 건에 연결한다. 앞 회차까지 처리한 조치·정비·구매 기록을 이어받아, 다음 담당자가 설비 상태·열린 작업·부품·작업 메모를 이어 확인할 교대 인수인계 문제를 정한다. 대상·교대·기준 시각·메모를 정리하고, 인계안의 각 주장에 근거가 있고 불일치와 확인할 일이 남으며 인계자 검토와 인수자 확인이 기록되는 것을 완료 조건으로 정한다. 이어 포털 지식 관리에 제공 교대 보충 매뉴얼을 올려 원문을 미리 보고 추출을 요청한 뒤, 나온 절차·조건·근거를 원문과 대조해 고치거나 빼고 새 문서로 적재한다. 앞서 적재한 설비 지식이 그대로 남아 있는지 확인하고, 지식 지도에서 새 항목과 문서·판본·절의 연결을 찾아 인계안의 확인 기준으로 삼는다.</t>
         </is>
       </c>
       <c r="D70" s="142" t="n">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="B71" s="143" t="inlineStr">
         <is>
-          <t>등록된 정비 흐름을 실행하고 결과 검증하기</t>
+          <t>설비·정비·ERP를 대조하는 인수인계 에이전트 만들기</t>
         </is>
       </c>
       <c r="C71" s="143" t="inlineStr">
         <is>
-          <t>포털에서 정기 점검 도래를 일으켜 정비 흐름을 시작하고, 정비 계획 제안과 그 근거를 읽은 뒤 설비보전팀장으로 승인한다. 같은 처리 건의 작업지시·부품 예약·생산 공지·보고를 대조하고, 오더 등록과 실제 정비 완료를 구분한다. 예약 뒤 실제 정비와 다음 교대에 남는 확인을 정리한다. 다른 처리 건에서 반려하면 오더가 만들어지지 않는 것을 비교하고, 보류 기록이 있으면 함께 본다. 실행 결과를 자신의 BPMN 작업과 연결해 저장한다.</t>
+          <t>포털 에이전트 화면에서 교대 인수인계 스킬과 에이전트를 만들고 지식 그래프·업무 DB·판단 도구를 고른다. 설비 관측 시각, 열린 작업지시, 재고·예약·발주 중 수량, 작업 메모를 대조하도록 지침을 쓰고, 완료 주장과 원천 상태가 다르면 두 근거와 확인할 질문을 남기게 한다. 결과의 각 문장을 원천 기록과 비교해 지침을 보완하고, 로컬 랩에서 익힌 출처·질문·검증 방법을 지침에 반영한다.</t>
         </is>
       </c>
       <c r="D71" s="144" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="B72" s="141" t="inlineStr">
         <is>
-          <t>구매 흐름을 설계하고 실행 검증하기</t>
+          <t>교대 인수인계 BPMN을 등록하고 검토·확인 흐름 실행하기</t>
         </is>
       </c>
       <c r="C72" s="141" t="inlineStr">
         <is>
-          <t>제공 구매 업무를 bpmn.io에서 시작·제안·승인·발주·입고·보고로 표현한다. 포털에서 재고 보충 흐름을 시작해 공급사·수량 제안의 근거와 승인 조건을 확인하고 구매 담당으로 승인한다. 같은 처리 건의 발주·통지·입고·재고 반영을 각각 찾아 시작 재고·예약·발주 중 수량과 비교하고, 기록에 남은 입고가 실제 배송 기간을 거친 입고와 같지 않음을 구분한다. 발주 중과 입고 완료를 구분하여 다음 교대에 전달할 수량·남은 확인을 정리한다. 다른 처리 건에서 거절하면 발주가 막히는 것을 비교하고, BPMN의 해당 작업과 실제 결과를 연결한다.</t>
+          <t>제공 교대 BPMN의 시작 입력·검토·보완 흐름을 유지한 채 표시 이름·배치를 정리하고, 세 초안 단계에 앞에서 만든 인수인계 에이전트를 배정해 판본을 등록한다. 설비·교대 정보를 입력해 인계안을 받고, 원천과 대조해 인수자에게 근거와 남은 일을 설명한다. 실제 보완 요청이 있으면 같은 처리 건에서 반영해 재검토·인수 확인한다. 인수 확인을 정비·발주 완료로 바꾸지 않고 최종 인계안·근거·확인 기록을 저장한다.</t>
         </is>
       </c>
       <c r="D72" s="142" t="n">
@@ -8022,17 +8022,17 @@
     <row r="73" ht="108" customHeight="1" s="1">
       <c r="A73" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(Notion)</t>
         </is>
       </c>
       <c r="B73" s="143" t="inlineStr">
         <is>
-          <t>교대 인수인계를 완성하고 ProcessGPT 연결 보기</t>
+          <t>ProcessGPT 시연과 비교하고 제작 결과를 학습노트에 기록하기</t>
         </is>
       </c>
       <c r="C73" s="143" t="inlineStr">
         <is>
-          <t>교대 인계안을 원천 기록과 대조하고 근거와 남은 일을 상대에게 설명한다. 인계자 검토→인수자의 확인 또는 실제 보완 요청→같은 처리 건의 재검토·인수 확인을 수행한다. 최종 인계안과 확인 기록을 저장하며 인수 확인과 정비·발주 완료를 구분한다. 이어 ProcessGPT 시연에서 지식·에이전트·사람 작업·실행 기록의 연결을 자신이 수행한 과정과 비교한다.</t>
+          <t>ProcessGPT 시연을 보며 지식 조회·에이전트 판단·사람 작업·프로세스 실행이 연결되는 모습을 확인하고, 프로세스 정의·실행 인스턴스·작업함을 포털에서 직접 해 본 것과 비교해 실제 제품의 업무 통제와 실행 기록을 살펴본다. 이어 1회에 만든 Notion 학습노트에 핵심 개념·실습 결과·참고 출처를 연결하고, MCP로 Notion에 기록을 남기는 방법을 살펴본 뒤 작성한 Markdown을 노트에 옮긴다. 조회·판단·검토·실행 확인에 쓴 자료와 산출물을 연결해 다시 활용할 수 있게 학습노트를 완성한다.</t>
         </is>
       </c>
       <c r="D73" s="144" t="n">

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -2911,25 +2911,13 @@
       </c>
     </row>
     <row r="122" ht="50" customHeight="1" s="1">
-      <c r="A122" s="69" t="inlineStr">
-        <is>
-          <t>운영 유의: HYD BPMN은 포털의 일부 시스템 단계 설정 칸이 부족하여 제공 mapping.json·검증된 API 절차가 필요할 수 있음. 공용 서버에 여러 학생이 동시에 배포하면 마지막 배포 흐름이 경보를 수신하므로 학생별 환경 또는 순차 진행 필요.</t>
-        </is>
-      </c>
+      <c r="A122" s="69" t="n"/>
     </row>
     <row r="124" ht="50" customHeight="1" s="1">
-      <c r="A124" s="69" t="inlineStr">
-        <is>
-          <t>실습 사전검증: 외부 MCP(파일시스템·Git·시간) 설치·권한·접속, Notion 쓰기 권한, SDD 기능 변경 실패 재현 입력, 오프라인 수강생 실행 시간은 미실측이므로 강사 리허설 필요. 지원되지 않는 업무 기능은 실제 구현 완료로 표기하지 않음.</t>
-        </is>
-      </c>
+      <c r="A124" s="69" t="n"/>
     </row>
     <row r="126" ht="50" customHeight="1" s="1">
-      <c r="A126" s="69" t="inlineStr">
-        <is>
-          <t>HYD 근거: https://github.com/uengine-oss/hyd-iot-edu/tree/claude/hyd-handoff-work-xziutz/students/flows · https://github.com/uengine-oss/hyd-iot-edu/blob/claude/hyd-handoff-work-xziutz/docs/handoff/verification/2026-10-10/final-verify.md</t>
-        </is>
-      </c>
+      <c r="A126" s="69" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4692,11 +4680,7 @@
       <c r="D100" s="50" t="n"/>
     </row>
     <row r="101" ht="50" customHeight="1" s="1">
-      <c r="A101" s="69" t="inlineStr">
-        <is>
-          <t>운영 유의: HYD BPMN은 포털의 일부 시스템 단계 설정 칸이 부족하여 제공 mapping.json·검증된 API 절차가 필요할 수 있음. 공용 서버에 여러 학생이 동시에 배포하면 마지막 배포 흐름이 경보를 수신하므로 학생별 환경 또는 순차 진행 필요.</t>
-        </is>
-      </c>
+      <c r="A101" s="69" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="50" t="n"/>
@@ -4705,11 +4689,7 @@
       <c r="D102" s="50" t="n"/>
     </row>
     <row r="103" ht="50" customHeight="1" s="1">
-      <c r="A103" s="69" t="inlineStr">
-        <is>
-          <t>실습 사전검증: 외부 MCP(파일시스템·Git·시간) 설치·권한·접속, Notion 쓰기 권한, SDD 기능 변경 실패 재현 입력, 오프라인 수강생 실행 시간은 미실측이므로 강사 리허설 필요. 지원되지 않는 업무 기능은 실제 구현 완료로 표기하지 않음.</t>
-        </is>
-      </c>
+      <c r="A103" s="69" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="50" t="n"/>
@@ -4718,11 +4698,7 @@
       <c r="D104" s="50" t="n"/>
     </row>
     <row r="105" ht="50" customHeight="1" s="1">
-      <c r="A105" s="69" t="inlineStr">
-        <is>
-          <t>HYD 근거: https://github.com/uengine-oss/hyd-iot-edu/tree/claude/hyd-handoff-work-xziutz/students/flows · https://github.com/uengine-oss/hyd-iot-edu/blob/claude/hyd-handoff-work-xziutz/docs/handoff/verification/2026-10-10/final-verify.md</t>
-        </is>
-      </c>
+      <c r="A105" s="69" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="50" t="n"/>

--- a/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
+++ b/문서/교재/실라버스/피지컬AI_실라버스_최종본.xlsx
@@ -949,7 +949,7 @@
     <row r="4" ht="36" customHeight="1" s="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>01일차  |  설비 데이터가 판단과 조치로 이어지는 전체 흐름 이해하기</t>
+          <t>01회차  |  설비 데이터가 판단과 조치로 이어지는 전체 흐름 이해하기</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>학교 PC에서 VS Code · AI 코딩 도구(GitHub Copilot · Codex) · Python · Docker가 각각 무슨 일을 하는지 알아보고 실행 상태를 확인한다. 강사를 따라 시작 절차로 HYD 포털을 열고 홈의 상태 표시와 시스템 구성 화면에서 설비 · 데이터 · 판단 · 업무 시스템이 어떻게 이어지는지 본 뒤, 실시간 모니터링 · 지식 지도 · 지식 관리 · 에이전트 · 내 작업함 · 처리 건 메뉴를 차례로 눌러 앞으로 각 화면에서 무엇을 하게 되는지 확인한다. 실습 시작 도구로 오늘 쓸 자료를 새 폴더에 받아 가이드와 작업 폴더를 열고, 실습 PC는 다시 켜면 처음 상태로 돌아가므로 남길 결과를 USB나 개인 클라우드로 내보내는 방법을 익힌다.</t>
+          <t>GitHub의 프로젝트 소개(README)로 이 시스템이 무엇이고 어떻게 이루어졌는지 본 뒤, 실습에 필요한 도구 여섯 개(Python · Node.js · VS Code · Git · WSL · Docker)가 각각 무슨 일을 맡는지 알고 직접 설치한다. VS Code에는 AI 코딩 도구인 Codex를 연결한다. 강사를 따라 프로젝트 저장소를 내려받고 시작 명령 한 번으로 여러 서비스를 함께 띄워 실행 상태를 확인한 뒤 HYD 포털을 연다. 홈에서 전체 상태와 시스템이 이어진 모습을 보고, 왼쪽의 일곱 메뉴 묶음을 차례로 열어 앞으로 각 화면에서 무엇을 하게 되는지 확인한다.</t>
         </is>
       </c>
       <c r="D9" s="33" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>강사를 따라 결함 시뮬레이션에서 쿨러 열화를 직접 일으키고, 실시간 모니터링에서 센서 값이 변해 경보가 뜨는 것을 본다. AI가 원인을 분석해 조치를 추천하면 내 작업함에서 담당자로서 추천과 근거를 읽고 승인한 뒤, 시스템이 설비에 조치를 내리고 온도를 다시 관측해 결과를 보고하기까지 처리 건에서 따라간다. 단계마다 어떤 정보가 쓰였고 무엇이 다음 단계로 넘어갔는지 비교하며, AI의 추천과 사람의 승인 · 실제 조치가 서로 다른 단계임을 확인한다.</t>
+          <t>강사를 따라 먼저 지식 관리에 설비 매뉴얼을 넣고, 에이전트가 고장 · 원인 · 조치를 추출해 오면 원문과 맞춰 검토한 뒤 지식으로 적재한다. 이어 결함 시뮬레이션에서 쿨러 열화를 직접 일으켜 경보가 뜨고 처리 건이 생기는 것을 본다. AI가 원인을 가리고 조치를 추천하면 내 작업함에서 운전원으로서 추천과 근거를 읽고 승인한 뒤, 시스템이 설비에 명령을 내리고 다시 관측해 정상으로 돌아온 결과와 따로 남은 정비 요청까지 처리 건에서 따라간다. 단계마다 어떤 정보가 쓰였고 무엇이 다음 단계로 넘어갔는지 비교하며, AI의 추천과 사람의 승인 · 실제 조치가 서로 다른 단계임을 확인한다.</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
@@ -1123,7 +1123,7 @@
     <row r="13" ht="32" customHeight="1" s="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D13" s="37">
@@ -1140,7 +1140,7 @@
     <row r="15" ht="36" customHeight="1" s="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>02일차  |  설비와 데이터의 관계를 체계화해 필요한 정보 찾기</t>
+          <t>02회차  |  설비와 데이터의 관계를 체계화해 필요한 정보 찾기</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>강사를 따라 포털 지식 지도에서 설비를 선택하고 연결된 센서 · 부품을 펼친다. 노드를 눌러 식별자와 속성을 확인하고 관계의 방향을 읽는다. 같은 센서 이름과 서로 다른 식별자를 구분하며, 별도 랩 DB에서 만든 모델과 포털의 기준 지도를 비교한다.</t>
+          <t>강사를 따라 포털 지식 지도에서 설비를 선택하고 연결된 센서 · 부품을 펼친다. 노드를 눌러 식별자와 속성을 확인하고 관계의 방향을 읽는다. 같은 센서 이름과 서로 다른 식별자를 구분하며, 앞 실습의 Cypher 예제 그래프와 포털의 기준 지도를 비교한다.</t>
         </is>
       </c>
       <c r="D21" s="33" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>앞 실습에서 설계한 설비 · 센서 · 부품 모델을 그래프 DB에 적재하는 코드와 조회문을 직접 작성한다. 스키마의 식별자와 관계 방향이 그래프의 노드 · 관계로 어떻게 옮겨지는지 다시 짚는다. 별도 랩 DB에서 설비별 센서 · 부품과 공용 부품의 사용 설비를 조회해 원자료와 대조한다. 같은 자료를 다시 적재해도 중복되지 않고 이름이 바뀌어도 같은 ID가 유지되는지 확인한다. 전체 데이터를 지우지 않고 필요한 부분을 수정하며 코드 · 질의 · 확인 결과를 저장한다.</t>
+          <t>앞 실습에서 설계한 설비 · 센서 · 부품 모델을 그래프 DB에 적재하는 코드와 조회문을 직접 작성한다. 스키마의 식별자와 관계 방향이 그래프의 노드 · 관계로 어떻게 옮겨지는지 다시 짚는다. 별도 랩 DB에서 설비별 센서 · 부품과 공용 부품의 사용 설비를 조회해 원자료와 대조한다. 같은 자료를 다시 적재해도 중복되지 않고 이름이 바뀌어도 같은 ID가 유지되는지 확인한다. 전체 데이터를 지우지 않고 필요한 부분을 수정하며 코드 · 질의 · 확인 결과를 저장한다. 끝으로 직접 만든 모델을 포털의 기준 지도와 비교해 식별자와 관계 방향이 어디서 같고 다른지 확인한다. 다음 회차에는 이 모델에 작업 절차와 판단 조건을 연결한다.</t>
         </is>
       </c>
       <c r="D23" s="33" t="n">
@@ -1314,7 +1314,7 @@
     <row r="24" ht="32" customHeight="1" s="1">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D24" s="37">
@@ -1331,7 +1331,7 @@
     <row r="26" ht="36" customHeight="1" s="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>03일차  |  설비 상황에 맞는 안전하고 효과적인 조치 선택하기</t>
+          <t>03회차  |  설비 상황에 맞는 안전하고 효과적인 조치 선택하기</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>설비 관계를 안다는 것만으로 조치를 실행할 수 없으므로, 허용 조건과 선택 근거를 구분한다. 설비 고장 원인을 진단하는 것과 실제 조치 방법을 결정하는 것이 서로 다른 단계임을 이해한다. SOP(Standard Operating Procedure)의 목적과 역할을 배우고, 적용 대상·작업 전제 조건·안전 조건·준비사항·수행 단계·금지 사항·담당 역할·완료 확인 기준 등 SOP의 구성요소를 살펴본다. 작업 절차의 순서와 조건을 구분하고, 동일한 조치도 설비 운전 상태에 따라 수행 가능 여부가 달라지는 이유를 학습한다. HYD 온톨로지에서 고장 유형·원인·조치 방법(Skill)·작업 단계(Step)·근거 매뉴얼이 연결되는 구조와, 즉시 완화·근본 조치·예방 조치의 차이를 살펴본다.</t>
+          <t>설비 관계를 안다는 것만으로 조치를 실행할 수 없으므로, 허용 조건과 선택 근거를 구분한다. 설비 고장 원인을 진단하는 것과 실제 조치 방법을 결정하는 것이 서로 다른 단계임을 이해한다. SOP(Standard Operating Procedure)의 목적과 역할을 배우고, 적용 대상·작업 전제 조건·안전 조건·준비사항·수행 단계·금지 사항·담당 역할·완료 확인 기준 등 SOP의 구성요소를 살펴본다. 작업 절차의 순서와 조건을 구분하고, 동일한 조치도 설비 운전 상태에 따라 수행 가능 여부가 달라지는 이유를 학습한다. HYD 온톨로지에서 고장 유형·원인·조치 방법·작업 단계·근거 매뉴얼이 연결되는 구조와, 즉시 완화·근본 조치·예방 조치의 차이를 살펴본다.</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>DMN(Decision Model and Notation)이 업무 의사결정을 명확하게 정의하기 위한 표준이라는 점을 배우고, SOP와 DMN의 차이를 살펴본다. 판단에 필요한 입력 데이터(InputData), 결정(Decision), 결정표(DecisionTable), 규칙(Rule), 조건과 출력의 관계를 학습한다. 비교 연산자·임계값·범위·복수 조건을 이용해 결정표를 구성하는 원리를 살펴본다. 규칙의 중복·누락·상충이 어떤 문제를 일으키는지 알아보고, 여러 규칙이 일치했을 때 결과를 선택하는 Hit Policy의 기본 개념과 HYD에서 사용하는 판단 방식을 이해한다. 설비 상태에 따른 조치 허용·제외·감점과 해당 판단의 근거를 표현하는 방법까지 학습한다.</t>
+          <t>DMN(Decision Model and Notation)이 업무 의사결정을 명확하게 정의하기 위한 표준이라는 점을 배우고, SOP와 DMN의 차이를 살펴본다. 판단에 필요한 입력 데이터(InputData), 결정(Decision), 결정표(DecisionTable), 규칙(Rule), 조건과 출력의 관계를 학습한다. 비교 연산자·임계값·범위·복수 조건을 이용해 결정표를 구성하는 원리를 살펴본다. 규칙의 중복·누락·상충이 어떤 문제를 일으키는지 알아보고, 여러 규칙이 일치했을 때 결과를 선택하는 Hit Policy의 기본 개념을 배우고, 여러 규칙이 맞을 때 결과를 하나로 고르는 방식을 이 설비의 예로 이해한다. 설비 상태에 따른 조치 허용·제외·감점과 해당 판단의 근거를 표현하는 방법까지 학습한다.</t>
         </is>
       </c>
       <c r="D29" s="33" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>VS Code에서 GitHub Copilot · Codex를 활용해 작업 조건이 정리된 랩 전용 SOP 자료를 사용한다. 2일차에 만든 설비 모델과 식별자를 재사용하고, 제공된 고장 유형과 조치 방법을 연결한다. SOP와 결정표가 각각 무엇을 담는지 다시 짚은 뒤, 작업의 적용 조건 · 금지 조건 · 수행 단계 · 완료 기준을 구분해 구조화하고, 이를 DMN 형태의 입력 조건과 판단 결과로 구성한다. 조치 방법과 단계, 판단 규칙의 의미적 관계를 정리해 SOP 구조와 결정표 자료를 완성한다. 원문 문서에서 이런 조건을 자동으로 뽑아내는 인제스천은 4회차에 다룬다.</t>
+          <t>VS Code에서 AI와 함께, 작업 조건이 정리된 SOP 자료를 읽는다. 2회차에 만든 설비 모델과 식별자를 재사용하고, 제공된 고장 유형과 조치 방법을 연결한다. SOP와 결정표가 각각 무엇을 담는지 다시 짚은 뒤, 작업의 적용 조건 · 금지 조건 · 수행 단계 · 완료 기준을 구분해 구조화하고, 이를 DMN 형태의 입력 조건과 판단 결과로 구성한다. 조치 방법과 단계, 판단 규칙의 의미적 관계를 정리해 SOP 구조와 결정표 자료를 완성한다. 원문 문서에서 이런 조건을 자동으로 뽑아내는 인제스천은 4회차에 다룬다.</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
@@ -1485,7 +1485,7 @@
     <row r="34" ht="32" customHeight="1" s="1">
       <c r="A34" s="35" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D34" s="37">
@@ -1502,7 +1502,7 @@
     <row r="36" ht="36" customHeight="1" s="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>04일차  |  현장 자료를 검증해 신뢰할 수 있는 판단 근거 만들기</t>
+          <t>04회차  |  현장 자료를 검증해 신뢰할 수 있는 판단 근거 만들기</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>앞 단계의 검토 결과와 랩 모델에서 시작해 승인한 후보를 기존 ID와 관계에 연결하는 적재·조회 기능을 작성한다. 처음 정한 질문으로 설비·조치·작업 조건·문서 근거를 조회하고 원문과 대조한다. 보류 후보 제외·반복 적재·다른 문서의 추가 반영을 확인한다. 질문·스키마·원문·추출/검토 기록·적재 코드·조회 결과를 연결해 하나의 온톨로지 구축 결과로 저장한다. 어떤 질문에 답할 수 있고 현재값이나 추가 자료가 필요한 질문은 무엇인지 설명한다. 다음 에이전트 실습이 이 지식과 조회 기능을 활용한다.</t>
+          <t>앞 실습에서 검토해 승인한 후보를 기존 ID와 관계에 연결하는 적재·조회 기능을 작성한다. 처음 정한 질문으로 설비·조치·작업 조건·문서 근거를 조회하고 원문과 대조한다. 보류 후보 제외·반복 적재·다른 문서의 추가 반영을 확인한다. 질문·스키마·원문·추출/검토 기록·적재 코드·조회 결과를 연결해 하나의 온톨로지 구축 결과로 저장한다. 어떤 질문에 답할 수 있고 현재값이나 추가 자료가 필요한 질문은 무엇인지 설명한다. 다음 에이전트 실습이 이 지식과 조회 기능을 활용한다.</t>
         </is>
       </c>
       <c r="D41" s="33" t="n">
@@ -1636,7 +1636,7 @@
     <row r="43" ht="32" customHeight="1" s="1">
       <c r="A43" s="35" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D43" s="37">
@@ -1644,10 +1644,11 @@
         <v/>
       </c>
     </row>
+    <row r="44"/>
     <row r="45" ht="39" customHeight="1" s="1">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>05일차  |  현장 지식을 활용해 실제 문제를 해결하는 AI 에이전트 만들기</t>
+          <t>05회차  |  현장 지식을 활용해 실제 문제를 해결하는 AI 에이전트 만들기</t>
         </is>
       </c>
       <c r="D45" s="44" t="inlineStr">
@@ -1801,7 +1802,7 @@
     <row r="53" ht="29" customHeight="1" s="1">
       <c r="A53" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D53" s="49">
@@ -1809,10 +1810,11 @@
         <v/>
       </c>
     </row>
+    <row r="54"/>
     <row r="55" ht="39" customHeight="1" s="1">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t>06일차  |  업무 능력을 재사용하고 여러 외부 시스템을 연결하기</t>
+          <t>06회차  |  업무 능력을 재사용하고 여러 외부 시스템을 연결하기</t>
         </is>
       </c>
       <c r="D55" s="44" t="inlineStr">
@@ -1976,7 +1978,7 @@
       </c>
       <c r="C63" s="53" t="inlineStr">
         <is>
-          <t>1회차부터 자기 Notion에 정리한 학습노트의 페이지를 선택하고 MCP 읽기 연결을 설정한다. 노트에서 문항 · 정답 기준 · 해설 · 원문 근거를 구성하는 퀴즈 에이전트를 만들되, 답하기 전에는 정답과 해설을 숨긴다. 학생 답변을 받아 정답 · 부분 정답 · 오답과 이유를 알려주고 원문을 다시 열어 확인한다. 다음 문항과 틀린 개념 재도전으로 이어가며 풀이 기록을 저장한다. 표현만 다른 정답 · 불완전한 답 · 노트에 없는 질문으로 검증하고, 근거가 부족하면 출제나 채점을 보류한다.</t>
+          <t>1회차부터 자기 Notion에 정리한 학습노트의 페이지를 선택하고 MCP 읽기 연결을 설정한다. 노트에서 문항 · 정답 기준 · 해설 · 원문 근거를 구성하는 퀴즈 에이전트를 만들되, 답하기 전에는 정답과 해설을 숨긴다. 학생 답변을 받아 정답 · 부분 정답 · 오답과 이유를 알려주고 원문을 다시 열어 확인한다. 다음 문항과 틀린 개념 재도전으로 이어가며 풀이 기록을 저장한다. 표현만 다른 정답 · 불완전한 답 · 노트에 없는 질문으로 검증하고, 근거가 부족하면 출제나 채점을 보류한다. 다음 회차에는 이 에이전트들이 멈추고 사람에게 물어야 할 때를 다룬다.</t>
         </is>
       </c>
       <c r="D63" s="54" t="n">
@@ -1986,7 +1988,7 @@
     <row r="64" ht="29" customHeight="1" s="1">
       <c r="A64" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D64" s="49">
@@ -1994,10 +1996,11 @@
         <v/>
       </c>
     </row>
+    <row r="65"/>
     <row r="66" ht="39" customHeight="1" s="1">
       <c r="A66" s="43" t="inlineStr">
         <is>
-          <t>07일차  |  사람의 판단과 명확한 요구사항으로 AI 업무의 신뢰성 높이기</t>
+          <t>07회차  |  사람의 판단과 명확한 요구사항으로 AI 업무의 신뢰성 높이기</t>
         </is>
       </c>
       <c r="D66" s="44" t="inlineStr">
@@ -2041,7 +2044,7 @@
       </c>
       <c r="C68" s="53" t="inlineStr">
         <is>
-          <t>앞서 만든 업무 요청 기능이 정보 누락이나 새 요구를 만났을 때 지켜야 할 동작을 정한다. HITL의 정의, 자동 처리와 승인·보류·거절의 구분, 승인권자와 권한의 경계, 사람의 책임과 결정 기록을 살펴본다. AI의 자기 검토와 실제 사람 승인 절차는 다른 것임을 구분한다.</t>
+          <t>앞서 만든 점검 에이전트가 정보 누락이나 새 요구를 만났을 때 지켜야 할 동작을 정한다. HITL의 정의, 자동 처리와 승인·보류·거절의 구분, 승인권자와 권한의 경계, 사람의 책임과 결정 기록을 살펴본다. AI의 자기 검토와 실제 사람 승인 절차는 다른 것임을 구분한다.</t>
         </is>
       </c>
       <c r="D68" s="54" t="n">
@@ -2171,7 +2174,7 @@
     <row r="75" ht="29" customHeight="1" s="1">
       <c r="A75" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D75" s="49">
@@ -2179,10 +2182,11 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77" ht="39" customHeight="1" s="1">
       <c r="A77" s="43" t="inlineStr">
         <is>
-          <t>08일차  |  요구가 바뀌어도 믿고 사용할 수 있는 에이전트 완성하기</t>
+          <t>08회차  |  요구가 바뀌어도 믿고 사용할 수 있는 에이전트 완성하기</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
@@ -2336,7 +2340,7 @@
     <row r="85" ht="29" customHeight="1" s="1">
       <c r="A85" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D85" s="49">
@@ -2344,10 +2348,11 @@
         <v/>
       </c>
     </row>
+    <row r="86"/>
     <row r="87" ht="39" customHeight="1" s="1">
       <c r="A87" s="43" t="inlineStr">
         <is>
-          <t>09일차  |  AI와 사람이 함께 일하는 업무 프로세스를 직접 설계하고 실행하기</t>
+          <t>09회차  |  AI와 사람이 함께 일하는 업무 프로세스를 직접 설계하고 실행하기</t>
         </is>
       </c>
       <c r="D87" s="44" t="inlineStr">
@@ -2431,7 +2436,7 @@
       </c>
       <c r="C91" s="53" t="inlineStr">
         <is>
-          <t>프로세스 정의와 인스턴스, Token의 진행 개념, 변수와 결과 전달, User Task·Service Task와 HYD 에이전트 단계, 실행 상태·승인 대기·배포 버전·감사 기록을 살펴본다. 온톨로지·DB·SOP를 쓰는 에이전트의 결과가 BPMN에서 어떤 순서로 전달되는지 확인한다.</t>
+          <t>프로세스 정의와 인스턴스, Token의 진행 개념, 변수와 결과 전달, 사람 작업·시스템 작업과 에이전트 작업, 실행 상태·승인 대기·배포 버전·감사 기록을 살펴본다. 온톨로지·DB·SOP를 쓰는 에이전트의 결과가 BPMN에서 어떤 순서로 전달되는지 확인한다.</t>
         </is>
       </c>
       <c r="D91" s="54" t="n">
@@ -2511,7 +2516,7 @@
       </c>
       <c r="C95" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 결함 시뮬레이션에서 쿨러 열화를 일으켜 처리 건을 만들고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 건 화면에서 따라간다. 처리 건이 어느 흐름 · 판본으로 열렸는지 확인하고, 승인 대기 · 정상 종료 · 거절로 끝난 처리 건을 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의 · 판본 · 처리 건과 결과를 기록한다.</t>
+          <t>강사를 따라 결함 시뮬레이션에서 쿨러 열화를 일으켜 처리 건을 만들고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 건 화면에서 따라간다. 처리 건이 어느 흐름 · 판본으로 열렸는지 확인하고, 승인 대기 · 정상 종료 · 거절로 끝난 처리 건을 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의 · 판본 · 처리 건과 결과를 기록한다. 다음 회차에는 같은 설계 원리를 정비와 구매 업무에 적용한다.</t>
         </is>
       </c>
       <c r="D95" s="54" t="n">
@@ -2521,7 +2526,7 @@
     <row r="96" ht="29" customHeight="1" s="1">
       <c r="A96" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D96" s="49">
@@ -2529,10 +2534,11 @@
         <v/>
       </c>
     </row>
+    <row r="97"/>
     <row r="98" ht="39" customHeight="1" s="1">
       <c r="A98" s="43" t="inlineStr">
         <is>
-          <t>10일차  |  설비 대응을 넘어 정비와 구매 업무까지 자동으로 연결하기</t>
+          <t>10회차  |  설비 대응을 넘어 정비와 구매 업무까지 자동으로 연결하기</t>
         </is>
       </c>
       <c r="D98" s="44" t="inlineStr">
@@ -2596,7 +2602,7 @@
       </c>
       <c r="C101" s="131" t="inlineStr">
         <is>
-          <t>bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인/거절→CMMS 정비 오더→생산팀 공지→결과 보고를 작도한다. 9일차의 Task·Lane·Gateway·Timer 패턴을 재사용하고 승인·반려 경로를 구분한다.</t>
+          <t>bpmn.io에서 정기 점검 도래→정비 계획 에이전트→설비보전팀장 승인/거절→CMMS 정비 오더→생산팀 공지→결과 보고를 작도한다. 9회차의 Task·Lane·Gateway·Timer 패턴을 재사용하고 승인·반려 경로를 구분한다.</t>
         </is>
       </c>
       <c r="D101" s="132" t="n">
@@ -2636,7 +2642,7 @@
       </c>
       <c r="C103" s="131" t="inlineStr">
         <is>
-          <t>bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인/거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 작도한다. HYD의 기업 시스템 시뮬레이션에서 발주·통지·입고가 연결되는 구조를 확인한다.</t>
+          <t>bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인/거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 작도한다. 발주·통지·입고가 업무 시스템에서 이어지는 구조를 확인한다.</t>
         </is>
       </c>
       <c r="D103" s="132" t="n">
@@ -2686,7 +2692,7 @@
     <row r="106" ht="29" customHeight="1" s="1">
       <c r="A106" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D106" s="49">
@@ -2694,10 +2700,11 @@
         <v/>
       </c>
     </row>
+    <row r="107"/>
     <row r="108" ht="39" customHeight="1" s="1">
       <c r="A108" s="43" t="inlineStr">
         <is>
-          <t>11일차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</t>
+          <t>11회차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</t>
         </is>
       </c>
       <c r="D108" s="44" t="inlineStr">
@@ -2781,7 +2788,7 @@
       </c>
       <c r="C112" s="53" t="inlineStr">
         <is>
-          <t>대상 설비 · 교대 · 기준 시각과 작업 메모를 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. 인계는 조치 · 정비 · 구매를 새로 실행하는 일이 아니라 그 기록을 이어받아 확인하는 일이므로, 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</t>
+          <t>강사를 따라 포털 흐름 화면에서 교대 인수인계 흐름의 시작 입력 항목(설비 · 교대 · 기준 시각 · 작업 메모)을 열어 보고, 이 항목을 인계의 입력으로 정한다. 설비 상태, 미완료 작업지시, 부품 대기 정보를 대조하여 다음 근무자의 확인 사항을 인계한다. 인계는 조치 · 정비 · 구매를 새로 실행하는 일이 아니라 그 기록을 이어받아 확인하는 일이므로, 인계자 검토와 인수자 확인을 완료 조건으로 정한다.</t>
         </is>
       </c>
       <c r="D112" s="54" t="n">
@@ -2881,7 +2888,7 @@
       </c>
       <c r="C117" s="131" t="inlineStr">
         <is>
-          <t>첫날 준비한 Notion 학습노트에 개념 · 참고 자료 · 실습 산출물 · 검증 결과를 연결해 기록한다. MCP로 Notion에 기록을 남기는 방법을 살펴보고, 정리한 Markdown을 노트에 옮긴다. 관계 모델 · 판단 근거 · 명세 · 검증 결과 · 인계 기록을 함께 찾아볼 수 있게 정리하며 과정을 마친다.</t>
+          <t>1회차에 만든 Notion 학습노트에 개념 · 참고 자료 · 실습 산출물 · 검증 결과를 연결해 기록한다. MCP로 Notion에 기록을 남기는 방법을 살펴보고, 정리한 Markdown을 노트에 옮긴다. 관계 모델 · 판단 근거 · 명세 · 검증 결과 · 인계 기록을 함께 찾아볼 수 있게 정리하며 과정을 마친다.</t>
         </is>
       </c>
       <c r="D117" s="132" t="n">
@@ -2891,7 +2898,7 @@
     <row r="118" ht="29" customHeight="1" s="1">
       <c r="A118" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D118" s="49">
@@ -2899,6 +2906,7 @@
         <v/>
       </c>
     </row>
+    <row r="119"/>
     <row r="120" ht="36" customHeight="1" s="1">
       <c r="A120" s="43" t="inlineStr">
         <is>
@@ -2910,12 +2918,15 @@
         <v/>
       </c>
     </row>
+    <row r="121"/>
     <row r="122" ht="50" customHeight="1" s="1">
       <c r="A122" s="69" t="n"/>
     </row>
+    <row r="123"/>
     <row r="124" ht="50" customHeight="1" s="1">
       <c r="A124" s="69" t="n"/>
     </row>
+    <row r="125"/>
     <row r="126" ht="50" customHeight="1" s="1">
       <c r="A126" s="69" t="n"/>
     </row>
@@ -2997,7 +3008,7 @@
     <row r="4" ht="39" customHeight="1" s="1">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>01일차  |  설비 데이터가 판단과 조치로 이어지는 전체 흐름 이해하기</t>
+          <t>01회차  |  설비 데이터가 판단과 조치로 이어지는 전체 흐름 이해하기</t>
         </is>
       </c>
       <c r="D4" s="44" t="inlineStr">
@@ -3101,7 +3112,7 @@
       </c>
       <c r="C9" s="131" t="inlineStr">
         <is>
-          <t>학교 PC에서 VS Code · AI 코딩 도구(GitHub Copilot · Codex) · Python · Docker가 각각 무슨 일을 하는지 알아보고 실행 상태를 확인한다. 강사를 따라 시작 절차로 HYD 포털을 열고 홈의 상태 표시와 시스템 구성 화면에서 설비 · 데이터 · 판단 · 업무 시스템이 어떻게 이어지는지 본 뒤, 실시간 모니터링 · 지식 지도 · 지식 관리 · 에이전트 · 내 작업함 · 처리 건 메뉴를 차례로 눌러 앞으로 각 화면에서 무엇을 하게 되는지 확인한다. 실습 시작 도구로 오늘 쓸 자료를 새 폴더에 받아 가이드와 작업 폴더를 열고, 실습 PC는 다시 켜면 처음 상태로 돌아가므로 남길 결과를 USB나 개인 클라우드로 내보내는 방법을 익힌다.</t>
+          <t>GitHub의 프로젝트 소개(README)로 이 시스템이 무엇이고 어떻게 이루어졌는지 본 뒤, 실습에 필요한 도구 여섯 개(Python · Node.js · VS Code · Git · WSL · Docker)가 각각 무슨 일을 맡는지 알고 직접 설치한다. VS Code에는 AI 코딩 도구인 Codex를 연결한다. 강사를 따라 프로젝트 저장소를 내려받고 시작 명령 한 번으로 여러 서비스를 함께 띄워 실행 상태를 확인한 뒤 HYD 포털을 연다. 홈에서 전체 상태와 시스템이 이어진 모습을 보고, 왼쪽의 일곱 메뉴 묶음을 차례로 열어 앞으로 각 화면에서 무엇을 하게 되는지 확인한다.</t>
         </is>
       </c>
       <c r="D9" s="132" t="n">
@@ -3121,7 +3132,7 @@
       </c>
       <c r="C10" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 결함 시뮬레이션에서 쿨러 열화를 직접 일으키고, 실시간 모니터링에서 센서 값이 변해 경보가 뜨는 것을 본다. AI가 원인을 분석해 조치를 추천하면 내 작업함에서 담당자로서 추천과 근거를 읽고 승인한 뒤, 시스템이 설비에 조치를 내리고 온도를 다시 관측해 결과를 보고하기까지 처리 건에서 따라간다. 단계마다 어떤 정보가 쓰였고 무엇이 다음 단계로 넘어갔는지 비교하며, AI의 추천과 사람의 승인 · 실제 조치가 서로 다른 단계임을 확인한다.</t>
+          <t>강사를 따라 먼저 지식 관리에 설비 매뉴얼을 넣고, 에이전트가 고장 · 원인 · 조치를 추출해 오면 원문과 맞춰 검토한 뒤 지식으로 적재한다. 이어 결함 시뮬레이션에서 쿨러 열화를 직접 일으켜 경보가 뜨고 처리 건이 생기는 것을 본다. AI가 원인을 가리고 조치를 추천하면 내 작업함에서 운전원으로서 추천과 근거를 읽고 승인한 뒤, 시스템이 설비에 명령을 내리고 다시 관측해 정상으로 돌아온 결과와 따로 남은 정비 요청까지 처리 건에서 따라간다. 단계마다 어떤 정보가 쓰였고 무엇이 다음 단계로 넘어갔는지 비교하며, AI의 추천과 사람의 승인 · 실제 조치가 서로 다른 단계임을 확인한다.</t>
         </is>
       </c>
       <c r="D10" s="54" t="n">
@@ -3171,7 +3182,7 @@
     <row r="13" ht="29" customHeight="1" s="1">
       <c r="A13" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D13" s="49">
@@ -3188,7 +3199,7 @@
     <row r="15" ht="39" customHeight="1" s="1">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>02일차  |  설비의 지식 구조를 만들고 안전한 조치 기준 마련하기</t>
+          <t>02회차  |  설비의 지식 구조를 만들고 안전한 조치 기준 마련하기</t>
         </is>
       </c>
       <c r="D15" s="44" t="inlineStr">
@@ -3232,7 +3243,7 @@
       </c>
       <c r="C17" s="53" t="inlineStr">
         <is>
-          <t>관계도에서 부품이 쓰이는 설비와 공급 정보를 찾고, 작업 조건을 판단에 쓸 수 있는 형태로 바꾼다. 클래스·인스턴스·속성·관계, 관계 방향, 카디널리티를 HYD 설비와 센서 실례로 살펴본다. 같은 종류의 설비와 실제 설비 1대를 구별한다.</t>
+          <t>1회차에 그린 관계도를 식별자와 속성을 갖춘 구조로 옮기는 데 필요한 개념을 배운다. 클래스·인스턴스·속성·관계, 관계 방향, 카디널리티를 HYD 설비와 센서 실례로 살펴본다. 같은 종류의 설비와 실제 설비 1대를 구별한다.</t>
         </is>
       </c>
       <c r="D17" s="54" t="n">
@@ -3312,7 +3323,7 @@
       </c>
       <c r="C21" s="53" t="inlineStr">
         <is>
-          <t>강사를 따라 포털 지식 지도에서 설비 · 구성 요소 · 부품 · 문서의 연결을 펼치고 노드의 ID · 속성과 관계 방향을 확인한다. 한 부품을 사용하는 설비를 찾고, 연결이 있다는 사실과 실제 재고 · 공급 조건이 확보됐다는 판단을 구분한다. 이어지는 로컬 랩에서는 제공 공급 자료로 답할 질문을 정한다.</t>
+          <t>강사를 따라 포털 지식 지도에서 설비 · 구성 요소 · 부품 · 문서의 연결을 펼치고 노드의 ID · 속성과 관계 방향을 확인한다. 한 부품을 사용하는 설비를 찾고, 연결이 있다는 사실과 실제 재고 · 공급 조건이 확보됐다는 판단을 구분한다.</t>
         </is>
       </c>
       <c r="D21" s="54" t="n">
@@ -3332,7 +3343,7 @@
       </c>
       <c r="C22" s="131" t="inlineStr">
         <is>
-          <t>앞 실습의 설비 · 부품 모델에 공급 조건 자료를 연결하도록 모델을 확장한다. 부품별 사용 설비와 공급사별 승인 여부 · 단가 · 불량률 · 납기를 찾을 질문을 정한다. 공용 부품을 설비별로 중복 생성하지 않고 단위와 출처를 보존한다. AI와 작성한 모델을 원자료의 품번 · 공급사 · 조건에 대조한다. 이 모델은 공급사를 골라 주는 판단이 아니라 고를 때 필요한 정보를 찾아 주는 구조임을 구분한다.</t>
+          <t>포털에서 본 부품 · 설비 연결에 공급 조건을 더해, 제공된 설비 · 부품 모델을 확장한다. 부품별 사용 설비와 공급사별 승인 여부 · 단가 · 불량률 · 납기를 찾을 질문을 정한다. 공용 부품을 설비별로 중복 생성하지 않고 단위와 출처를 보존한다. AI와 작성한 모델을 원자료의 품번 · 공급사 · 조건에 대조한다. 이 모델은 공급사를 골라 주는 판단이 아니라 고를 때 필요한 정보를 찾아 주는 구조임을 구분한다.</t>
         </is>
       </c>
       <c r="D22" s="132" t="n">
@@ -3352,7 +3363,7 @@
       </c>
       <c r="C23" s="53" t="inlineStr">
         <is>
-          <t>앞 실습의 확장 모델로 부품별 사용 설비와 공급 조건을 반환하는 적재 · 조회문을 작성한다. 스키마의 식별자와 관계 방향이 그래프의 노드 · 관계로 어떻게 옮겨지는지 다시 짚는다. 세 설비가 함께 쓰는 공용 씰 부품(P-PMP-SEAL)의 사용 설비와 공급 조건 3행을 원자료와 대조한다. 다른 품번과 없는 품번도 확인하고, 비승인 공급사를 승인 상태와 함께 구별한다. 반복 적재의 중복 여부를 검사하고 질의 · 결과 · 남은 확인 사항을 저장한다.</t>
+          <t>앞 실습의 확장 모델로 부품별 사용 설비와 공급 조건을 반환하는 적재 · 조회문을 작성한다. 스키마의 식별자와 관계 방향이 그래프의 노드 · 관계로 어떻게 옮겨지는지 다시 짚는다. 세 설비가 함께 쓰는 펌프 씰 부품의 사용 설비와 공급 조건 3행을 원자료와 대조한다. 다른 품번과 없는 품번도 확인하고, 비승인 공급사를 승인 상태와 함께 구별한다. 반복 적재의 중복 여부를 검사하고 질의 · 결과 · 남은 확인 사항을 저장한다.</t>
         </is>
       </c>
       <c r="D23" s="54" t="n">
@@ -3402,7 +3413,7 @@
     <row r="26" ht="29" customHeight="1" s="1">
       <c r="A26" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D26" s="49">
@@ -3419,7 +3430,7 @@
     <row r="28" ht="39" customHeight="1" s="1">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>03일차  |  조치의 성과를 비교하고 현장 자료를 판단 근거로 전환하기</t>
+          <t>03회차  |  조치의 성과를 비교하고 현장 자료를 판단 근거로 전환하기</t>
         </is>
       </c>
       <c r="D28" s="44" t="inlineStr">
@@ -3463,7 +3474,7 @@
       </c>
       <c r="C30" s="53" t="inlineStr">
         <is>
-          <t>조건표에 따른 조치 선택과 문서의 원문 근거를 연결해 검토 결과와 작업 확인 카드를 만든다. BSC 4관점과 전략 목표·KPI의 역할, 안전을 만족한 후보 사이에서 예상 비용·생산 영향·품질·에너지 측면을 비교하는 이유, What-if 분석의 개념을 살펴본다.</t>
+          <t>조건표를 통과한 조치 후보를 무엇으로 견줄지, 성과 관점의 평가 기준을 배운다. BSC 4관점과 전략 목표·KPI의 역할, 안전을 만족한 후보 사이에서 예상 비용·생산 영향·품질·에너지 측면을 비교하는 이유, What-if 분석의 개념을 살펴본다.</t>
         </is>
       </c>
       <c r="D30" s="54" t="n">
@@ -3523,7 +3534,7 @@
       </c>
       <c r="C33" s="131" t="inlineStr">
         <is>
-          <t>원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회, 출처·개정 기록의 원리를 살펴본다. 2일차 샘플 인스턴스 적재와 본격 문서 인제스천의 차이를 구분한다.</t>
+          <t>원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회, 출처·개정 기록의 원리를 살펴본다. 2회차 샘플 인스턴스 적재와 본격 문서 인제스천의 차이를 구분한다.</t>
         </is>
       </c>
       <c r="D33" s="132" t="n">
@@ -3563,7 +3574,7 @@
       </c>
       <c r="C35" s="131" t="inlineStr">
         <is>
-          <t>포털에서 본 문서 지식화 과정을 VS Code의 독립 랩으로 구현한다. 원문에서 작업 순서 · 조건 · 단위 · 금지 사항을 추출하고 문서 ID · 절 · 인용을 함께 반환하는 기능을 만든다. 생성된 후보를 원문과 대조하여 채택 · 수정 · 제외 · 보류를 기록한다. 다른 문서에도 적용해 누락과 근거 없는 생성을 확인한다. 실전반은 선택한 작업의 준비 · 금지 · 완료 조건을 추출하여 다음 실습의 작업 확인 카드에 연결한다.</t>
+          <t>포털에서 본 문서 지식화 과정을 VS Code의 독립 랩으로 구현한다. 원문에서 작업 순서 · 조건 · 단위 · 금지 사항을 추출하고 문서 ID · 절 · 인용을 함께 반환하는 기능을 만든다. 생성된 후보를 원문과 대조하여 채택 · 수정 · 제외 · 보류를 기록한다. 다른 문서에도 적용해 누락과 근거 없는 생성을 확인한다. 선택한 작업의 준비 · 금지 · 완료 조건을 추출하여 다음 실습의 작업 확인 카드에 연결한다.</t>
         </is>
       </c>
       <c r="D35" s="132" t="n">
@@ -3583,7 +3594,7 @@
       </c>
       <c r="C36" s="53" t="inlineStr">
         <is>
-          <t>앞 단계의 검토 결과와 랩 모델에서 시작해 승인 지식을 별도 랩 DB의 기존 ID·관계에 연결한다. 선택한 작업의 준비·금지·완료 조건과 원문 출처를 모아 작업 확인 카드를 생성한다. 다른 작업·미제공 절·반복 적재를 확인하고 남은 질문을 표시한다. 질문·모델·문서·추출/검토·적재·조회 결과를 연결해 온톨로지 구축 결과로 저장한다. 공급 정보와 작업 조건을 어디까지 답할 수 있는지, 현재값·승인 없이 결정할 수 없는 것은 무엇인지 설명한다. 다음 회차에는 이 지식으로 점검 요청을 만든다.</t>
+          <t>앞 실습에서 검토해 승인한 지식을 별도 랩 DB의 기존 ID·관계에 연결한다. 선택한 작업의 준비·금지·완료 조건과 원문 출처를 모아 작업 확인 카드를 생성한다. 다른 작업·미제공 절·반복 적재를 확인하고 남은 질문을 표시한다. 질문·모델·문서·추출/검토·적재·조회 결과를 연결해 온톨로지 구축 결과로 저장한다. 공급 정보와 작업 조건을 어디까지 답할 수 있는지, 현재값·승인 없이 결정할 수 없는 것은 무엇인지 설명한다. 다음 회차에는 이 지식으로 점검 요청을 만든다.</t>
         </is>
       </c>
       <c r="D36" s="54" t="n">
@@ -3613,7 +3624,7 @@
     <row r="38" ht="29" customHeight="1" s="1">
       <c r="A38" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D38" s="49">
@@ -3630,7 +3641,7 @@
     <row r="40" ht="39" customHeight="1" s="1">
       <c r="A40" s="43" t="inlineStr">
         <is>
-          <t>04일차  |  업무를 수행하는 AI를 만들고 다양한 도구 연결하기</t>
+          <t>04회차  |  업무를 수행하는 AI를 만들고 다양한 도구 연결하기</t>
         </is>
       </c>
       <c r="D40" s="44" t="inlineStr">
@@ -3794,7 +3805,7 @@
       </c>
       <c r="C48" s="53" t="inlineStr">
         <is>
-          <t>자기가 정리한 Notion 회의 · 학습 기록의 읽기 연결과 파일 · Git · 시간 MCP를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 외부 도구와 조합한다. 앞 회의 스킬을 재사용해 결정할 질문 · 확인된 사실 · 남은 확인 · 페이지나 파일 근거를 담은 다음 협의 안건을 만든다. 서로 다른 회의와 후속 변경을 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 접근 실패를 업무 없음으로 처리하지 않는다.</t>
+          <t>자기가 정리한 Notion 회의 · 학습 기록의 읽기 연결과 파일 · Git · 시간 MCP를 설정한다. 제공 서버 골격에 점검 메모 조회 함수를 구현하고 외부 도구와 조합한다. 앞 회의 스킬을 재사용해 결정할 질문 · 확인된 사실 · 남은 확인 · 페이지나 파일 근거를 담은 다음 협의 안건을 만든다. 서로 다른 회의와 후속 변경을 대조하여 결정이 사라지거나 중복되지 않는지 확인한다. 접근 실패를 업무 없음으로 처리하지 않는다. 다음 회차에는 점검 요청을 사람이 판단해야 할 때와 새 요구를 명세 · 검증으로 반영하는 법을 다룬다.</t>
         </is>
       </c>
       <c r="D48" s="54" t="n">
@@ -3804,7 +3815,7 @@
     <row r="49" ht="29" customHeight="1" s="1">
       <c r="A49" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D49" s="49">
@@ -3821,7 +3832,7 @@
     <row r="51" ht="39" customHeight="1" s="1">
       <c r="A51" s="43" t="inlineStr">
         <is>
-          <t>05일차  |  사람과 협업하고 변경된 기능까지 검증하기</t>
+          <t>05회차  |  사람과 협업하고 변경된 기능까지 검증하기</t>
         </is>
       </c>
       <c r="D51" s="44" t="inlineStr">
@@ -4015,7 +4026,7 @@
     <row r="61" ht="29" customHeight="1" s="1">
       <c r="A61" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D61" s="49">
@@ -4032,7 +4043,7 @@
     <row r="63" ht="39" customHeight="1" s="1">
       <c r="A63" s="43" t="inlineStr">
         <is>
-          <t>06일차  |  설비 이상 대응을 안전하게 실행하는 프로세스 완성하기</t>
+          <t>06회차  |  설비 이상 대응을 안전하게 실행하는 프로세스 완성하기</t>
         </is>
       </c>
       <c r="D63" s="44" t="inlineStr">
@@ -4256,7 +4267,7 @@
       </c>
       <c r="C74" s="131" t="inlineStr">
         <is>
-          <t>강사를 따라 쿨러 열화를 일으켜 처리 건을 만들고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 건 화면에서 따라간다. 처리 건이 어느 흐름 · 판본으로 열렸는지 확인하고, 승인 대기 · 정상 종료 · 거절로 끝난 처리 건을 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 다음 담당자가 계속 확인할 일이 무엇인지 근거와 함께 설명한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의 · 판본 · 처리 건과 결과를 기록한다.</t>
+          <t>강사를 따라 쿨러 열화를 일으켜 처리 건을 만들고, 같은 처리 건의 판단→운전원 승인→명령→재관측→보고를 처리 건 화면에서 따라간다. 처리 건이 어느 흐름 · 판본으로 열렸는지 확인하고, 승인 대기 · 정상 종료 · 거절로 끝난 처리 건을 구분해 비교한다. 명령 처리와 온도 회복, 작업지시 등록과 정비 완료를 따로 확인한다. 다음 담당자가 계속 확인할 일이 무엇인지 근거와 함께 설명한다. 작성한 BPMN에서 해당 작업을 찾고 실제 정의 · 판본 · 처리 건과 결과를 기록한다. 다음 회차에는 같은 설계 원리를 정비와 구매 업무에 적용한다.</t>
         </is>
       </c>
       <c r="D74" s="132" t="n">
@@ -4266,7 +4277,7 @@
     <row r="75" ht="29" customHeight="1" s="1">
       <c r="A75" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D75" s="49">
@@ -4283,7 +4294,7 @@
     <row r="77" ht="39" customHeight="1" s="1">
       <c r="A77" s="43" t="inlineStr">
         <is>
-          <t>07일차  |  정비와 구매 업무를 연결하고 프로세스의 실행 결과 검증하기</t>
+          <t>07회차  |  정비와 구매 업무를 연결하고 프로세스의 실행 결과 검증하기</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
@@ -4387,7 +4398,7 @@
       </c>
       <c r="C82" s="131" t="inlineStr">
         <is>
-          <t>bpmn.io에서 재고 부족→기존 구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→즉시 입고 반영→종료를 작성한다. ERP와 재고 기능은 HYD 시뮬레이션으로 다룬다.</t>
+          <t>bpmn.io에서 재고 부족→기존 구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→즉시 입고 반영→종료를 작성한다.</t>
         </is>
       </c>
       <c r="D82" s="132" t="n">
@@ -4437,7 +4448,7 @@
     <row r="85" ht="29" customHeight="1" s="1">
       <c r="A85" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D85" s="49">
@@ -4454,7 +4465,7 @@
     <row r="87" ht="39" customHeight="1" s="1">
       <c r="A87" s="43" t="inlineStr">
         <is>
-          <t>08일차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</t>
+          <t>08회차  |  추가 지식과 에이전트로 교대 인수인계 완성하기</t>
         </is>
       </c>
       <c r="D87" s="44" t="inlineStr">
@@ -4538,7 +4549,7 @@
       </c>
       <c r="C91" s="53" t="inlineStr">
         <is>
-          <t>앞 회차에서 처리한 조치 · 정비 · 구매 기록을 이어받아, 다음 담당자가 설비 상태 · 열린 작업 · 부품 · 작업 메모를 이어 확인할 교대 인수인계 문제를 정한다. 교대 점검 보충 매뉴얼의 기준에 맞춰 대상 · 교대 · 기준 시각 · 메모를 정리한다. 인계안의 각 주장에 근거가 있고, 불일치와 확인할 일이 남으며, 인계자 검토와 인수자 확인이 기록되는 것을 완료 조건으로 정한다.</t>
+          <t>강사를 따라 포털 흐름 화면에서 교대 인수인계 흐름의 시작 입력 항목(설비 · 교대 · 기준 시각 · 작업 메모)을 열어 본다. 앞 회차에서 처리한 조치 · 정비 · 구매 기록을 이어받아, 다음 담당자가 설비 상태 · 열린 작업 · 부품 · 작업 메모를 이어 확인할 교대 인수인계 문제를 정한다. 교대 점검 보충 매뉴얼의 기준에 맞춰 대상 · 교대 · 기준 시각 · 메모를 정리한다. 인계안의 각 주장에 근거가 있고, 불일치와 확인할 일이 남으며, 인계자 검토와 인수자 확인이 기록되는 것을 완료 조건으로 정한다.</t>
         </is>
       </c>
       <c r="D91" s="54" t="n">
@@ -4648,7 +4659,7 @@
     <row r="97" ht="29" customHeight="1" s="1">
       <c r="A97" s="66" t="inlineStr">
         <is>
-          <t>일차 합계</t>
+          <t>회차 합계</t>
         </is>
       </c>
       <c r="D97" s="49">
@@ -5332,7 +5343,7 @@
     <row r="15" ht="92" customHeight="1" s="1">
       <c r="A15" s="143" t="inlineStr">
         <is>
-          <t>실습(Neo4j)</t>
+          <t>실습(Neo4j · 포털)</t>
         </is>
       </c>
       <c r="B15" s="143" t="inlineStr">
@@ -5836,7 +5847,7 @@
     <row r="47" ht="92" customHeight="1" s="1">
       <c r="A47" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(포털 · VS Code)</t>
         </is>
       </c>
       <c r="B47" s="143" t="inlineStr">
@@ -5952,7 +5963,7 @@
       </c>
       <c r="C54" s="141" t="inlineStr">
         <is>
-          <t>앞서 만든 업무 요청 기능이 정보 누락이나 새 요구를 만났을 때 지킬 동작을 정하고, 그 동작을 실제 출력으로 확인한다. HITL의 자동 처리·승인·보류·거절, 승인권자와 권한의 경계, 결정 기록을 살펴보고 AI의 자기 검토와 사람의 승인을 구분한다. 명세 중심 개발(SDD)로 요구·입력/출력 계약·금지 조건·수용 기준을 구현 전에 정하는 방식과, 모호한 기능 추가가 기존 출력이나 승인 규칙을 흔들 수 있는 까닭을 이해한다. Given/When/Then으로 기대 행동을 정하고 정상·경계·예외·회귀 검증으로 새 기능과 기존 기능을 함께 확인하는 방법을 익힌다. 끝으로 지금까지 만든 에이전트들의 목표·입력·도구·결과 판정과 스킬·MCP·HITL·SDD·BDD가 각각 해결한 문제를 정리한다.</t>
+          <t>앞서 만든 점검 에이전트가 정보 누락이나 새 요구를 만났을 때 지킬 동작을 정하고, 그 동작을 실제 출력으로 확인한다. HITL의 자동 처리·승인·보류·거절, 승인권자와 권한의 경계, 결정 기록을 살펴보고 AI의 자기 검토와 사람의 승인을 구분한다. 명세 중심 개발(SDD)로 요구·입력/출력 계약·금지 조건·수용 기준을 구현 전에 정하는 방식과, 모호한 기능 추가가 기존 출력이나 승인 규칙을 흔들 수 있는 까닭을 이해한다. Given/When/Then으로 기대 행동을 정하고 정상·경계·예외·회귀 검증으로 새 기능과 기존 기능을 함께 확인하는 방법을 익힌다. 끝으로 지금까지 만든 에이전트들의 목표·입력·도구·결과 판정과 스킬·MCP·HITL·SDD·BDD가 각각 해결한 문제를 정리한다.</t>
         </is>
       </c>
       <c r="D54" s="142" t="n">
@@ -6244,7 +6255,7 @@
       </c>
       <c r="C72" s="141" t="inlineStr">
         <is>
-          <t>bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인·거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 그린다. 정비 흐름에서 쓴 역할·승인 구조를 재사용해 승인·거절 경로를 나누고, HYD의 업무 시스템 시뮬레이션에서 발주·통지·입고가 어떻게 이어지는지 확인한다.</t>
+          <t>bpmn.io에서 재고 부족→구매 에이전트의 수량·공급사 제안→구매 담당자 승인·거절→ERP 발주→공급사 통지→입고·재고 반영→결과 보고를 그린다. 정비 흐름에서 쓴 역할·승인 구조를 재사용해 승인·거절 경로를 나누고, 업무 시스템에서 발주·통지·입고가 어떻게 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="D72" s="142" t="n">
@@ -6380,7 +6391,7 @@
     <row r="81" ht="108" customHeight="1" s="1">
       <c r="A81" s="143" t="inlineStr">
         <is>
-          <t>실습(Notion)</t>
+          <t>실습(ProcessGPT 시연 · Notion)</t>
         </is>
       </c>
       <c r="B81" s="143" t="inlineStr">
@@ -7066,7 +7077,7 @@
       </c>
       <c r="C14" s="141" t="inlineStr">
         <is>
-          <t>관계도에서 부품이 쓰이는 설비와 공급 정보를 찾고, 작업 조건을 판단에 쓸 수 있는 형태로 바꾼다. 클래스·인스턴스·속성·관계, 관계 방향과 카디널리티를 설비·센서 실례로 살펴보고 같은 종류의 설비와 실제 설비 한 대를 구별한다. 고유 식별자·자료형·필수값·레이블·관계 제약과 스키마·인스턴스의 역할을 배우고, 중복된 부품 이름과 고유 식별자로 구분한 결과를 비교한다. Neo4j의 노드·관계·속성과 Cypher의 MATCH·WHERE·RETURN·CREATE·MERGE의 목적, 구조 조회와 실제 데이터 적재의 차이를 살펴본다. 끝으로 SOP의 단계·안전 전제·금지 조건과 DMN의 입력 조건·결정표·출력 판단을 비교하고, 절차를 모두 규칙으로 바꿀 수는 없는 까닭을 이해한다.</t>
+          <t>1회에 그린 관계도를 식별자와 속성을 갖춘 구조로 옮기고, 작업 조건을 판단에 쓸 수 있는 형태로 바꾸는 데 필요한 개념을 배운다. 클래스·인스턴스·속성·관계, 관계 방향과 카디널리티를 설비·센서 실례로 살펴보고 같은 종류의 설비와 실제 설비 한 대를 구별한다. 고유 식별자·자료형·필수값·레이블·관계 제약과 스키마·인스턴스의 역할을 배우고, 중복된 부품 이름과 고유 식별자로 구분한 결과를 비교한다. Neo4j의 노드·관계·속성과 Cypher의 MATCH·WHERE·RETURN·CREATE·MERGE의 목적, 구조 조회와 실제 데이터 적재의 차이를 살펴본다. 끝으로 SOP의 단계·안전 전제·금지 조건과 DMN의 입력 조건·결정표·출력 판단을 비교하고, 절차를 모두 규칙으로 바꿀 수는 없는 까닭을 이해한다.</t>
         </is>
       </c>
       <c r="D14" s="142" t="n">
@@ -7076,7 +7087,7 @@
     <row r="15" ht="108" customHeight="1" s="1">
       <c r="A15" s="143" t="inlineStr">
         <is>
-          <t>실습(Neo4j)</t>
+          <t>실습(Neo4j · 포털)</t>
         </is>
       </c>
       <c r="B15" s="143" t="inlineStr">
@@ -7192,7 +7203,7 @@
       </c>
       <c r="C22" s="141" t="inlineStr">
         <is>
-          <t>조건표에 따른 조치 선택과 문서의 원문 근거를 연결해 검토 결과와 작업 확인 카드를 만든다. BSC 네 관점과 전략 목표·KPI, 안전을 만족한 후보 사이에서 비용·생산 영향·품질·에너지를 견주는 이유와 What-if 분석의 개념을 살펴본다. 원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회의 과정과 출처·개정 기록의 원리를 이해하고, 작은 예제 적재와 본격 문서 인제스천의 차이를 구분한다. 이미 있는 추출 결과를 다시 쓰더라도 사람이 조건의 뜻과 누락을 확인해야 하는 까닭을 보고, 끝으로 온톨로지 설계→그래프 DB→SOP·DMN→성과 지표→문서 인제스천으로 이어진 지식 자산이 다음 회차 점검 요청 에이전트의 입력이 되는 흐름을 정리한다.</t>
+          <t>조건표를 통과한 조치 후보를 견주는 성과 기준과, 문서를 근거로 쓸 수 있는 지식으로 바꾸는 과정을 배운다. BSC 네 관점과 전략 목표·KPI, 안전을 만족한 후보 사이에서 비용·생산 영향·품질·에너지를 견주는 이유와 What-if 분석의 개념을 살펴본다. 원본 문서 확보→추출→클래스·관계 매핑→원문 대조·검토→승인→그래프 적재→조회의 과정과 출처·개정 기록의 원리를 이해하고, 작은 예제 적재와 본격 문서 인제스천의 차이를 구분한다. 이미 있는 추출 결과를 다시 쓰더라도 사람이 조건의 뜻과 누락을 확인해야 하는 까닭을 보고, 끝으로 온톨로지 설계→그래프 DB→SOP·DMN→성과 지표→문서 인제스천으로 이어진 지식 자산이 다음 회차 점검 요청 에이전트의 입력이 되는 흐름을 정리한다.</t>
         </is>
       </c>
       <c r="D22" s="142" t="n">
@@ -7202,7 +7213,7 @@
     <row r="23" ht="108" customHeight="1" s="1">
       <c r="A23" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(포털 · VS Code)</t>
         </is>
       </c>
       <c r="B23" s="143" t="inlineStr">
@@ -7580,7 +7591,7 @@
     <row r="47" ht="92" customHeight="1" s="1">
       <c r="A47" s="143" t="inlineStr">
         <is>
-          <t>실습(포털)</t>
+          <t>실습(포털 · VS Code)</t>
         </is>
       </c>
       <c r="B47" s="143" t="inlineStr">
@@ -7862,7 +7873,7 @@
       </c>
       <c r="C64" s="141" t="inlineStr">
         <is>
-          <t>bpmn.io에서 재고 부족→구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→입고 반영→종료를 그린다. 정비 흐름의 역할·승인 구조를 재사용해 승인·거절 경로를 나누고, ERP와 재고 기능이 HYD의 업무 시스템 시뮬레이션에서 어떻게 이어지는지 확인한다.</t>
+          <t>bpmn.io에서 재고 부족→구매 에이전트→구매 담당자 승인·거절→ERP 발주→공급사 통지→입고 반영→종료를 그린다. 정비 흐름의 역할·승인 구조를 재사용해 승인·거절 경로를 나누고, ERP 발주와 재고 반영이 업무 시스템에서 어떻게 이어지는지 확인한다.</t>
         </is>
       </c>
       <c r="D64" s="142" t="n">
@@ -7998,7 +8009,7 @@
     <row r="73" ht="108" customHeight="1" s="1">
       <c r="A73" s="143" t="inlineStr">
         <is>
-          <t>실습(Notion)</t>
+          <t>실습(ProcessGPT 시연 · Notion)</t>
         </is>
       </c>
       <c r="B73" s="143" t="inlineStr">
